--- a/src/jobs/jobs.xlsx
+++ b/src/jobs/jobs.xlsx
@@ -71,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -87,6 +87,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -453,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S202"/>
+  <dimension ref="A1:S182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -633,19 +636,24 @@
           <t>Keyword (23)</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>This recruitment seeks to fill Specialist Cadre Officer positions within State Bank of India's operations, focusing on the Indian banking sector.  Candidates will be responsible for supporting various aspects of bank operations and contributing to financial stability.</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Applicants should possess a relevant bachelor's degree or equivalent experience in finance, economics, or related fields.  A minimum of 2 years of professional experience is required, with proficiency in data analysis, financial reporting, and communication skills.</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>This role plays a crucial part in the Indian banking industry, contributing to the stability and growth of the sector.</t>
+      <c r="O2" s="6" t="inlineStr">
+        <is>
+          <t>Implement Climate Change Risk Management Policy and develop frameworks that align with organizational goals and objectives.
+Identification of climate risk at portfolio level/account level, and to identify and prioritize customer/sector segments for assessing climate related risks.
+Conduct comprehensive assessment of the Banks exposure to climate change-related financial risks (Physical &amp; Transition), including potential impacts on assets, operations and supply chain.
+Calculation of carbon footpr</t>
+        </is>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>Work Experience in Risk Management Cycle - with expertise in Climate Change Risk Management.
+Identification/Assessment/Measurement/Metrics and Disclosures and Risk Mitigation Strategies, Stress Testing - creation, execution and analysis of stress testing outcome.
+Experience in Climate Change Risk As</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions climate change risk management, climate risk assessment, climate finance, and green finance, which are all related to climate risk. The job requires experience in climate change risk management and knowledge of climate risk models, which further supports t</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr"/>
@@ -726,9 +734,9 @@
           <t>Keyword (23)</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Senior Consultant- Sustainability will conduct climate risk assessments, develop climate transition plans, and advise clients on climate finance opportunities.</t>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Climate Risk Assessment: Conduct physical risk assessments, transition risk assessments, and climate-related opportunities assessments for clients across various sectors. Develop models to compute financial impacts of climate related risks and opportunities Climate scenario analysis using IPCC, IEA, and NGFS scenarios to inform client strategies. Provide recommendations on climate risk management and resilience strategies. Nature and Biodiversity Risk Assessment: Conduct nature and biodiversity </t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -736,9 +744,9 @@
           <t>Requires a Master's degree in Sustainability, Climate, Environmental Science or related field with at least 3 years of experience in the field.</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on climate risk assessment, climate finance, and sustainability consulting within the environmental sector.</t>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions climate risk assessment, physical risk assessments, transition risk assessments, climate scenario analysis, and climate resilience strategy development, which are all key aspects of climate risk management.</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -819,19 +827,19 @@
           <t>Keyword (16)</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>A Senior Consultant will join EY's Climate Change and Sustainability Services team to advise clients on sustainability and climate change issues across various industries.</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Requires a minimum of 5 years of experience in sustainability consulting, strong analytical skills, and knowledge of ESG frameworks.</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on helping companies navigate the complexities of climate change and sustainability for improved business performance.</t>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Work as part of a multidisciplinary team across a range of industries, assisting organisations on how they manage and report on a broad range of sustainability and climate-related risks and impacts. Delivery of assurance of non-financial reporting, including sustainability metrics, emissions and energy reporting across a range of industry sectors. Advise clients on the development of their strategies and delivery of non-financial reporting, including sustainability metrics, emissions and energy </t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>Climate and nature disclosure experience, including knowledge of the Taskforce on Climate-related Financial Disclosure (TCFD) and Taskforce on Nature-related Financial Disclosure (TNFD) Frameworks. Knowledge of, and experience in decarbonisation approaches, climate risk and climate strategy. Agility</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions climate change, climate risk, decarbonisation, GHG accounting, and climate scenario analysis, which are all relevant to the climate risk profile.</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -916,19 +924,19 @@
           <t>Keyword (16)</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>This role involves managing engagement teams and providing coaching and development advice to staff members while delivering assurance of non-financial reporting for a range of industries.</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have experience in climate change and sustainability consulting, including project management, team leadership, and communication skills.</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on environmental, social, and governance (ESG) issues within the business consulting industry.</t>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>Work as part of a multidisciplinary team across a range of industries, assisting organisations on how they manage and report on a broad range of sustainability and climate-related risks and impacts. Manage engagement teams and provide coaching and development advice to staff members. Coordinate project activities and build strong lines of communication with clients, engagement teams and senior leaders to ensure engagements are managed to clearly defined timelines while delivering high quality wo</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professional services/consulting experience, Tertiary qualification in a quantitative subject, Experience in climate change services, Experience in GHG accounting, Demonstrable experience in reporting and/or assurance of greenhouse gas emissions, Working knowledge of the climate reporting regime in </t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions climate change services, GHG accounting, climate risk, decarbonisation approaches, and climate strategy, which are all relevant to the climate risk profile.</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -1005,19 +1013,19 @@
           <t>Keyword (16)</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Develop and implement financing strategies to support the transition to a net-zero economy, securing funding for climate projects and advising on green financing mechanisms.</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Experience in sustainable finance, green bonds, ESG investments, or climate-focused fundraising with expertise in financial modeling, impact assessment, and risk evaluation.</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on supporting India's transition to a net-zero economy through sustainable financing solutions for climate projects.</t>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>Develop financing strategies for renewable energy, carbon reduction, and other climate-focused initiatives. Advise on ESG investment opportunities and impact funding. Secure funding through green bonds, sustainability-linked loans, carbon credit financing, and other instruments. Engage with banks, financial institutions, impact investors, and government agencies to unlock climate finance. Structure innovative financing models such as blended finance, PPPs (Public-Private Partnerships), and risk-</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>Financial modeling, impact assessment, risk evaluation, networking, negotiation, stakeholder management, knowledge of climate finance mechanisms, carbon trading, and regulatory frameworks.</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions sustainable finance, ESG investments, green bonds, and climate-focused fundraising, which are all key aspects of sustainable finance.</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr"/>
@@ -1098,19 +1106,19 @@
           <t>Keyword (15)</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>Leads end-to-end digital transformation and project management for large capital projects in the metals &amp; mining industry, driving adoption of digital solutions to improve efficiency and safety.</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>Requires experience with digital/AI solutions like 5D BIM, advanced scheduling, risk analytics, drone/LiDAR tracking, IoT geo-fencing, and GenAI assistants.</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on the metals &amp; mining industry, supporting clients in their transition to a more sustainable and efficient operation through digital transformation.</t>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>Lead end-to-end digital transformation and PMO for large capital projects in metals &amp; mining covering planning, execution, governance, and benefits realization. You will drive adoption of digital/AI solutions to deliver measurable improvements in time, cost, quality, and safety. Establish and run the PMO, build/maintain Integrated Master Schedule, implement Cost Controls, drive Risk &amp; Safety Management, oversee Quality Management, own procurement management, run performance reviews for contracto</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>Program governance, PMO operations, EVM, schedule &amp; cost assurance, risk management, digital solutioning &amp; change management, stakeholder management, excellent communication, executive reporting, proposal support/pre sales, Digital-led Transformation &amp; Capital Project Management, Metals &amp; Mining, Ac</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions climate change mitigation and adaptation, energy efficiency, and renewable energy solutions, which are related to environmental sustainability and clean energy. Although it does not directly fit into the other categories, it is adjacent to clean e</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
@@ -1191,19 +1199,19 @@
           <t>Keyword (14)</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>A Senior Consultant will join EY's Climate Change and Sustainability Services team to advise companies on climate change and sustainability issues.</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have a tertiary qualification, experience in climate change services, financial or non-financial audit, and the ability to work independently across multiple engagements.</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>This role connects to climate change, ESG, sustainability, and finance by advising companies on managing their environmental impact and achieving sustainable business practices.</t>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Work as part of a multidisciplinary team across a range of industries, assisting organisations on how they manage and report on a broad range of sustainability and climate related risks and impacts. Assurance of non-financial reporting, including sustainability metrics, emissions and energy reporting across a range of industry sectors. Contribute to strategy, solutions, methodologies, analytical frameworks and tools to help clients succeed and navigate complex regulatory environments and manage </t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>Professional services/consulting experience. Knowledge of relevant legislation, regulations and codes of practice as well as a good understanding of the climate-related issues. Practical experience with energy and emissions reporting schemes including National Greenhouse Emissions Reporting (NGER) s</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions climate change, climate risk, decarbonisation, and greenhouse gas emissions, which are all relevant to the climate risk profile. The role also involves working with clients to develop and implement sustainability strategies, and assisting them in navigatin</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
@@ -1284,19 +1292,19 @@
           <t>Keyword (12)</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>A Consultant role within EY's Risk Consulting team, focusing on ESG (Environmental, Social &amp; Governance) engagements. The role involves supporting clients in developing their ESG strategies and delivering high-quality deliverables.</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have experience in ESG Gap Assessments, climate risk assessment, peer reviews, and sustainability knowledge.</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>This role is within the environmental, social, and governance (ESG) consulting sector, helping businesses navigate ESG challenges and opportunities.</t>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>Supporting the Manager/ SM in day-to-day delivery of ESG engagements and associated activities, while ensuring that the engagements are delivered in a manner that complies with internal and regulatory procedures, Being responsible for the quality of deliverables produced, including qualitative and quantitative analysis, Contributing to thought leadership and developing market intelligence to support ESG practice development, Proven abilities to establish and sustain sound relationships with clie</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>Prior experience of undertaking ESG Gap Assessment and providing logical and impactful recommendations, Strong understanding of ESG processes and systems, Experience conducting climate risk assessment online with TCFD guidelines, Proven experience of undertaking a detailed Peer Review &amp; Benchmarking</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[general_esg] The job description mentions ESG (Environmental, Social &amp; Governance) and sustainability, which are key aspects of general ESG profile. The job also involves climate risk assessment, greenhouse gas accounting, and decarbonization initiatives, which are all relevant to ESG strategy and </t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -1377,19 +1385,19 @@
           <t>Keyword (12)</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Climate Solutions Associate will support the implementation of advisory mandates, conduct climate impact analysis on investment portfolios, and provide client support on climate-related risks and opportunities.</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have a Masters degree in Environmental science or similar discipline with 1-3 years of relevant work experience in data analytics, climate consulting, or climate change.</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>This role connects to climate, ESG, sustainability, and finance by providing data, analytics, and advisory services to support investors in understanding and managing their exposure to climate-related risks and opportunities.</t>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>Manage the implementation of advisory mandates, bespoke data and report deliveries of ISS ESG Climate Solutions. Conduct climate impact analysis on investment portfolios across all asset classes. Provide support and input for Client Calls based on deliverables requirements and effectively address client queries. Co-ordinate with required stakeholders to ensure timely delivery of high quality of data to the clients. Contribute to standardization and automation effort of bespoke analysis. Bring on</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>In-depth knowledge on scope 1, scope 2 and Scope 3 emissions, quantitative and qualitative analytical skills, excellent conceptual thinking aptitude, excellent command of Excel and good working knowledge of all Microsoft Office applications.</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions climate-related risks, GHG emissions, and climate impact analysis, which are all relevant to the climate risk profile.</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
@@ -1474,19 +1482,19 @@
           <t>Keyword (11)</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Supports the development of sustainable finance and ESG risk capabilities across European capital markets.</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>Requires an MBA in Finance or a CA, CFA, FRM qualification, experience in sustainable finance, ESG analytics or climate-related financial risk.</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>This role connects to climate, ESG, sustainability, and finance within the European capital markets sector.</t>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In this crucial role, you’ll support the development of NatWest Markets’ sustainable finance and ESG risk capabilities across European capital markets. We’ll look to you to support senior originators in front‑line origination, risk engagement and client delivery by translating sustainability, climate and broader ESG themes into tangible financing, investment and risk outcomes. As a Financing &amp; Risk Solutions Associate, you will be supporting the effective management of transactions to make sure </t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>Comfort operating in evolving and complex sustainability‑related regulatory environments. Knowledge of investment banking and credit related products. Advanced power point and excel skills and experience with Pivots, vlookup, hlookup, index match and other advance excel formulas. Strong communicatio</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions sustainable finance, ESG risk, climate risk, and regulatory frameworks such as EU Taxonomy and CSRD, indicating a strong focus on sustainable finance and ESG topics.</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
@@ -1563,19 +1571,19 @@
           <t>Keyword (11)</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Analyze sustainability data to deliver key insights that empower investors and decision-makers, leading initiatives to elevate Apex Group's sustainability performance.</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Master s degree in environmental engineering, forestry, or sustainability with additional certifications a plus; proficiency in quantitative and qualitative data collection, analysis, and reporting; excellent interpersonal skills.</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>The role connects to climate, ESG, sustainability, and finance by providing expert advice on sustainability data and regulations for clients.</t>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>Work with global teams and clients to analyze sustainability data, delivering key insights that empower investors and decision-makers. Lead initiatives to elevate Apex Group s sustainability performance, supporting clients on their sustainability journey while enhancing the ESG reporting, analysis, and due diligence processes. Leverage extensive ESG expertise to provide high-quality advisory services in ESG policy and regulatory reporting, strategy, and risk management. Act as a key expert on on</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>Proficiency in quantitative and qualitative data collection, analysis, and reporting. Exceptional organizational competency with strong attention to detail. Excellent interpersonal skills with the ability to communicate and influence internal and external stakeholders, including proficiency in video</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>[eu_taxonomy_sfdr] The job description mentions specific EU regulations such as EU Taxonomy, CSRD, and SFDR, which are key components of the EU Taxonomy and SFDR profile. The role also involves ESG reporting, analysis, and due diligence, which are closely related to the EU Taxonomy and SFDR regulati</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr"/>
@@ -1640,19 +1648,19 @@
           <t>Keyword (10)</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>Develop and implement machine learning models for satellite and geospatial data analysis to support customers in navigating the complex transition to a decarbonized energy future.</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>Experience with machine learning and deep learning techniques, proficiency in Python, cloud-based solutions (AWS, GCP), and strong analytical skills.</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on Earth Observation data science for sustainability and energy transition within the energy sector.</t>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>Develop and implement machine learning and deep learning models for satellite and geospatial data analysis. Integrate and process multimodal datasets. Build and automate scalable data processing pipelines using Python and cloud-based solutions. Collaborate with interdisciplinary teams and international partners to deliver customer-facing projects. Support the development of recommended practices and standards for EO data analytics. Present findings and recommendations to customers, supporting th</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>Machine learning, deep learning, satellite and geospatial data analysis, Python, cloud computing, geospatial libraries and tools, data analytics, AI, scientific programming</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions working on sustainability, energy transition, and environmental challenges, which aligns with the clean energy adjacent profile. The role involves developing data-driven solutions for complex challenges in safety, sustainability, and energy transi</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr"/>
@@ -1729,19 +1737,19 @@
           <t>Keyword (10)</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>Graduate-level roles within WSP's Earth and Environment teams provide opportunities to contribute to diverse projects across Sweden.  The role involves working on complex engineering challenges with a focus on sustainability and climate change mitigation.</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have a bachelor's degree in civil or geological engineering, soil mechanics, or related fields. Fluency in Swedish is highly desirable.</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on environmental consulting within the Swedish construction and infrastructure sector, contributing to sustainable development goals.</t>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>We are recruiting graduates for our Earth and Environment teams, who have a flexible approach and an appetite to learn in a leading Engineering and professional services consultancy. We want you to enjoy working in a collaborative environment where you can apply your skills working for a diverse range of clients and projects.</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>Civil &amp; Geological Engineering, Soil Mechanics or similar, Civil &amp; Geotechnical Engineering, MSc Soil Mechanics, Hydrogeology, Hydrogeologist, Civil Engineering in Environmental Science and MSc in Earth Science, Acoustics Engineering, Music Technology or Sound Engineering or other, Environmental and</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions various environmental and sustainability-related roles such as Rock Engineering, Geotechnical Engineering, Hydrogeology, Contaminated Areas, Acoustics, and Environmental Management - Sustainability &amp; Climate Change, which are all related to enviro</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
@@ -1826,19 +1834,19 @@
           <t>Keyword (10)</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>The ESG Controller Senior Analyst will play a key role in interpreting and implementing global ESG reporting standards, ensuring accurate and timely disclosures for Citigroup globally.</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should possess strong analytical skills, regulatory expertise, and experience with ESG reporting frameworks and methodologies.</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>This role is within the finance division of a global financial institution focused on environmental, social, and governance (ESG) reporting compliance.</t>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>Disclosure requirements Interpretation and Integration: Act as the subject matter expert, interpret mandatory disclosure requirements under global ESG/ sustainability related standards. Develop a comprehensive Materiality Assessment Framework: Design and architect a robust Materiality Assessment framework that aligns seamlessly with the requirements of the amended ESRS. Maintain the DR Inventory: Define, update, and manage the disclosure requirement (DR) inventory, including ownership of each DR</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>Proven ability to design, implement, and optimize financial controls; define and execute robust financial reporting; and an eye digitization/automation of manual processes to enhance controls and compliance drive efficiency through automation and digitization initiatives. Good understanding of ESG r</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>[eu_taxonomy_sfdr] The job description mentions EU Corporate Sustainability Reporting Directive (CSRD), EU Taxonomy, and other ESG-related regulations, indicating a strong focus on EU Taxonomy and SFDR compliance.</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
@@ -1919,19 +1927,19 @@
           <t>Keyword (10)</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>Provides consulting services related to integrating sustainability principles into mergers and acquisitions and private equity transactions (debt and equity) and corporate strategies.</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>Requires experience in impact strategy and analysis, pre and post deal sustainability assessment, value creation through sustainable finance, and responsible investment strategies.</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>Focuses on integrating environmental, social, economic, and governance considerations into business strategies and operations within the consulting industry.</t>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>Working on sustainability in deals at PwC, you will focus on providing consulting services related to integrating sustainability principles into mergers and acquisitions and private equity transactions (debt and equity) and corporate strategies. You will analyse environmental and social risk, assess client needs based on global frameworks, conduct impact assessments and develop comprehensive sustainability strategies for value creation, and offer guidance and support to help clients transition t</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>Proactive and robust thought process, Meticulous and committed attitude with an eye for detail, Good interpersonal and communication skills, Work to create an impact, Good digital awareness, Enthusiasm and commitment towards work, Climate Change, Sustainability</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions integrating sustainability principles into mergers and acquisitions, private equity transactions, and corporate strategies, which is related to sustainable finance. It also mentions ESG ratings methodology, ESG policies, and ESG due diligences, whic</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
@@ -2016,19 +2024,24 @@
           <t>Keyword (10)</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>Analyze climate-related risks and develop adaptation strategies for organizations, contributing to their resilience against climate impacts.</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>Knowledge of climate risk frameworks, analytical skills, modeling expertise, and understanding of climate policies and sustainability trends.</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on climate risk assessment within the environmental sector, supporting organizations in adapting to climate change and achieving sustainability goals.</t>
+      <c r="O17" s="6" t="inlineStr">
+        <is>
+          <t>Conduct climate risk and vulnerability assessments
+Analyze climate data and prepare risk reports
+Support climate strategy development
+Assist clients in climate disclosure frameworks</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>Knowledge of climate risk frameworks and analysis tools
+Strong analytical and modeling skills
+Understanding of climate policies and sustainability trends</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description explicitly mentions climate risk, climate-related risks, climate strategy development, and climate disclosure frameworks, which are all key aspects of climate risk assessment and management.</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
@@ -2109,9 +2122,13 @@
           <t>Keyword (10)</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Provides support for GHG accounting and decarbonization projects, develops tools for emission calculations, and assists with designing decarbonization roadmaps.</t>
+      <c r="O18" s="6" t="inlineStr">
+        <is>
+          <t>GHG Accounting and Decarbonization
+* Support to senior team members on GHG inventories for corporates, cities, and sectors following IPCC Guidelines and GHG Protocol.
+* Develop and implement GHG calculation tools for baseline emissions and forecasting.
+* Use LCA tools to evaluate embodied carbon in infrastructure and master planning.
+* Support senior team member/lead on design and execution of decarbonization roadmaps with clear targets and timelines in line with SBTi and national climate goals</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2119,9 +2136,9 @@
           <t>Requires experience in GHG accounting, carbon footprint analysis, and LCA methodologies; knowledge of IPCC guidelines and GHG Protocol is essential.</t>
         </is>
       </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to climate risk modeling, assessment, and decarbonization efforts within the infrastructure and transportation sectors.</t>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions GHG accounting, decarbonization, climate risk modeling, and assessment, which are all related to climate risk. The job also mentions following IPCC Guidelines and GHG Protocol, and applying PCAF guidelines, which are all relevant to climate risk management</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
@@ -2198,19 +2215,19 @@
           <t>Keyword (10)</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on ESG research, regulatory compliance, and climate risk analysis for internal and external reporting. You will contribute to developing climate-related disclosures and Net Zero strategies.</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>Strong analytical skills with proficiency in Excel, Python coding experience is an advantage. Experience with data reporting, emissions, and credit data management is required.</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on the ESG and sustainability aspects of global commodities markets, contributing to decarbonization efforts within the industry.</t>
+      <c r="O19" s="6" t="inlineStr">
+        <is>
+          <t>ESG research regulatory compliance (GHG Protocol, PCAF, AASB S2). Data reporting management: emissions, credit, and ledger data. Analytics modelling for climate risk and scenario analysis. Prepare internal/external climate disclosures and Net Zero reports.</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>Advanced proficiency in Excel, including data modelling. Python coding experience. Strong analytical and quantitative skills with attention to detail.</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions climate risk, GHG emissions, and Net Zero reports, which are key indicators of a climate risk profile.</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr"/>
@@ -2364,19 +2381,19 @@
           <t>Keyword (9)</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>The Project Operations Lead will build and manage the operational backbone of the Projects business, ensuring efficient project development activities.</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>The ideal candidate has experience in project management, process improvement, and building internal support functions.</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>This role connects to climate change investment and advisory by supporting the development of renewable energy, nature, and climate opportunities.</t>
+      <c r="O21" s="6" t="inlineStr">
+        <is>
+          <t>Lead and manage all operational aspects of the Projects business, by setting up and overseeing key internal support functions (HR, IT, finance, and Business Services). Develop and implement fit-for-purpose systems, tools, and processes that enable the Projects team to operate with autonomy and efficiency, while maintaining alignment with corporate standards. Support the design and implementation of a capital investment framework to guide decision-making and capital allocation. Ensure alignment b</t>
+        </is>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>Proficiency with CRMs, MS Office, and advanced Excel skills. Experience managing virtual data rooms. Strong financial acumen and experience with budgeting and forecasting. Excellent leadership, communication, and interpersonal skills. Strong analytical and problem-solving skills. Pragmatic, solution</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions experience in renewable energy, decarbonisation, infrastructure or nature-based projects as highly desirable, and the company is a specialist climate change investment and advisory firm, indicating a strong focus on environmental sustainability an</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
@@ -2457,19 +2474,19 @@
           <t>Keyword (9)</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>A Business Development Associate will be responsible for originating and executing transactions in the voluntary carbon market, working with clients and internal teams to structure deals and drive business growth.</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have a strong understanding of carbon markets, experience in deal structuring and negotiation, and excellent communication skills.</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>This role connects to climate action by supporting the development and trading of carbon credits, contributing to the transition to a lower-carbon economy.</t>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Develop relationships with corporate buyers, airlines, traders, intermediaries and financial institutions active in carbon markets. Manage the full commercial lifecycle, from lead generation and client engagement through to transaction execution. Originate and execute transactions across voluntary carbon markets, CORSIA-eligible credits and emerging compliance-linked carbon markets. Identify new commercial opportunities and areas of the market where CFP Energy should focus its efforts, based on </t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>Strong market instincts, entrepreneurial mindset, confidence to build and leverage relationships, ability to structure and execute carbon credit transactions, experience with commercial negotiation, origination or structured transactions, strong understanding of carbon credit project structures, met</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>[carbon_markets] The job description mentions voluntary carbon markets, carbon credits, CORSIA, and compliance-linked carbon markets, which are all related to carbon markets. The role involves originating and executing transactions across voluntary carbon markets, and the ideal candidate should have</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
@@ -2550,19 +2567,19 @@
           <t>Keyword (9)</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>This PhD project focuses on quantifying carbon fluxes within the Congo River network and its connection to the Cuvette Centrale peatlands, contributing to a deeper understanding of the river's role in global carbon cycling.</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>PhD candidates should have strong analytical skills, experience with field sampling and data analysis, and familiarity with environmental modeling techniques.</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>This position contributes to research on soil and water management within the context of climate change, biodiversity conservation, and sustainable resource management in the Congo Basin.</t>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>The PhD candidate tasks will include: organizing logistics for regular river sampling by local teams: shipment of materials and samples, establish new collaborations with other partners in the Congo Basin. organizing and conducting new sampling campaigns in collaboration with local partners in the Congo Basin field measurements of river discharge, physico-chemical parameters and greenhouse gas concentrations and fluxes field sampling for a wide range of biogeochemical proxies, sample preservatio</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>interdisciplinary sciences, English, French, field sampling, analytical laboratory experience, interpersonal skills, problem-solving skills</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions research on riverine carbon dynamics and fluxes in the Congo Basin, which is related to environmental science and the management of natural resources, fitting the clean_energy_adjacent profile.</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
@@ -2639,19 +2656,19 @@
           <t>Keyword (9)</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>The EU Director will lead ECF's efforts to advance ambitious climate, environment, and sustainable development regulation in the European Union.</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>The ideal candidate has extensive experience in policymaking, regulatory affairs, and international relations with a demonstrated ability to influence stakeholders at the EU level.</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on climate change mitigation and adaptation within the European Union's regulatory framework for environmental sustainability.</t>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>The EU Director is responsible for integrating and leading all ECF efforts aimed at reducing the European Union's climate impact and accelerating the socioeconomic transition to a netzero economy through EU level regulation and policy. Key responsibilities include: Strategic leadership and impact, Internal coordination and programme integration, Team leadership and management, External representation and partnerships, Fundraising and resource stewardship.</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>Excellent communication skills, with the ability to articulate complex issues clearly and persuasively in both written and spoken English. A wellestablished professional network in EU affairs and climaterelated policy fields. Demonstrated ability to design and deliver complex strategies that mobilis</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions climate change, netzero economy, greenhouse gas emissions reductions, and climate policy, which are all relevant to climate risk.</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr"/>
@@ -2724,19 +2741,28 @@
           <t>Keyword (9)</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>Leads and develops UPM's social responsibility agenda across businesses and global functions, driving long-term value creation and influencing social impact.</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>Requires 10+ years of experience in international business with expertise in human rights, responsible sourcing, and risk management.</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to the sustainable development of a global company focused on renewable materials and promoting responsible practices across its operations.</t>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>Lead, develop and steer UPM’s group-level social responsibility agenda
+Develop UPM’s social focus areas and related targets
+Advise and collaborate across businesses and global functions to drive common objectives
+Follow human rights developments, societal trends and best practices, and translate them into actionable improvements
+Strengthen risk management, social performance and value creation through robust social responsibility work
+Ensure the continuous development, motivation and professiona</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>Strong communication , influencing and presentation skills
+Well organized, analytical and solution-oriented
+Ability to analyse complex information and identify key insights
+Effective in leading cross-functional and multi-stakeholder processes
+Proven experience in leading teams</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] The job description mentions social responsibility, sustainability, human rights, and responsible sourcing, which are all relevant to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr"/>
@@ -2813,19 +2839,19 @@
           <t>Keyword (9)</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>A Carbon Project Developer will lead the preparation of Verra-compliant project design documents for afforestation/reforestation projects, supporting new opportunities in Arbonics' portfolio.</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>Experience developing carbon projects, writing PDDs, and familiarity with Verra VCS methodologies is required.</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to the development of nature-based solutions for climate change mitigation within the environmental sector.</t>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>The first project will focus on a VM0047 afforestation project, but the role will extend to supporting additional projects across Arbonics portfolio. This is a hybrid role combining technical carbon project development and stakeholder collaboration. In addition to leading the research and preparation of PDD documentation, you will support commercial teams in evaluating and acquiring new commercial opportunities. You will become the technical expert representing Arbonics in discussions with lando</t>
+        </is>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>Technical writing, research, carbon project development, Verra VCS methodologies, ARR / afforestation methodologies, technical expertise, stakeholder engagement, communication, collaboration, analytical thinking</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>[carbon_markets] The job description mentions carbon project development, Verra VCS methodologies, and carbon credits, which are all related to carbon markets.</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
@@ -2906,19 +2932,19 @@
           <t>Keyword (9)</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>A Customer Solutions Engineer is responsible for ensuring the technical success of Doconomy's enterprise banking clients.</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>This role requires a strong understanding of technical architecture, integration methodologies, and experience working with highly regulated environments.</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on the financial industry and its potential to drive positive change through sustainable practices.</t>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">We are looking for a Customer Solutions Engineer to take ownership of the technical success of our enterprise banking clients. This is a high-impact, remote consultancy engagement within Europe, requiring availability within ±1 hour CET. In this role, you will work closely with the CPTO and the Customer team, acting as the primary technical counterpart for global banks operating in highly regulated environments. You will stand at the intersection of product, engineering, and enterprise clients, </t>
+        </is>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>Strong understanding of REST APIs, mTLS, OAuth2, and OpenID Connect (OIDC). Proficient in Jira for ticket management and Postman for API testing. Strong working proficiency in Slack and Google Workspace, combined with an async-first mindset.</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions 'impact technology', 'driving global climate action', 'ESG experts', and 'sustainability' in the context of financial products, indicating a strong focus on sustainable finance and ESG investing.</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
@@ -2999,9 +3025,9 @@
           <t>Keyword (9)</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>This role involves managing the full employee lifecycle, from recruitment to onboarding and offboarding. You will be responsible for building a strong employer brand and attracting top talent in Australia.</t>
+      <c r="O28" s="6" t="inlineStr">
+        <is>
+          <t>Support and/or lead sustainability assessments and research to identify areas for improvement and compliance with market and regulatory requirements. Develop and implement sustainability programs and initiatives that align with client objectives and deliver value creation. Advise clients on specific ESG and sustainability matters.</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3009,9 +3035,9 @@
           <t>Experience with applicant tracking systems, HRIS software, and payroll processing is required.  A background in human resources management and knowledge of Australian employment law are essential.</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to the development and implementation of sustainable business practices within the Australian workforce.</t>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] The job description mentions ESG, sustainability, climate change risk assessments, and social and human rights impact assessments, which are all related to environmental, social, and governance topics.</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
@@ -3088,19 +3114,19 @@
           <t>Keyword (9)</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>Provides support for sustainable finance and ESG risk capabilities in European capital markets.</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>Requires an MBA or relevant qualifications, expertise in sustainable finance, ESG analytics, and climate-related financial risk.</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>This role connects to climate, ESG, sustainability, and finance within the European capital markets.</t>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>support the development of NatWest Markets sustainable finance and ESG risk capabilities across European capital markets, support senior originators in frontline origination, risk engagement and client delivery, contribute to the development of high-quality sustainability-linked client materials and regulatory-aligned ESG assessments, assist with client deep dives, navigate the sales coverage teams and gather feedback from internal client touchpoints, prepare pitch-books, investor presentations,</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>sustainability and ESG risk, knowledge of various debt products and markets, comfort operating in evolving and complex sustainability-related regulatory environments, knowledge of investment banking and credit related products, advanced power point and excel skills, strong communication and interper</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions sustainable finance, ESG risk, climate-related financial risk, and European sustainability regulatory frameworks, indicating a strong focus on sustainable finance and ESG topics.</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr"/>
@@ -3242,19 +3268,19 @@
           <t>Keyword (8)</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>Junior Revisore, part of the Deloitte Audit &amp; Assurance Talent Program, you will contribute to challenging projects in the Industrial and Financial sector.</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have a Bachelor's degree or Master's degree in Economics (a thesis on auditing is preferred), strong English language skills, and proficiency in computer applications.</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on audit services within the financial industry, contributing to the accuracy and transparency of financial statements.</t>
+      <c r="O31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deloitte Audit &amp; Assurance - Talent Program Revisore Junior (0 - 1 anno di Esperienza). Le nostre altre attività di supporto sono: revisione di bilanci IAS/IFRS OIC e di reporting package, progetti di First Time Adoption (FTA) ovvero transizione dai principi contabili nazionali a principi contabili internazionali, verifica delle dichiarazioni (ad esempio 770), attestazioni delle ricerche e sviluppo. In quanto Analyst avrai la possibilità di imparare da colleghe e colleghi più Senior (attraverso </t>
+        </is>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>Competenze tecniche e relazionali, conoscenza della lingua Inglese, competenze informatiche e predisposizione alla tecnologia</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] La menzione di strategie di Corporate Sustainability, ESG e sostenibilità ambientale, sociale e di governance all'interno della descrizione dell'azienda e del ruolo</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr"/>
@@ -3319,19 +3345,19 @@
           <t>Keyword (8)</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>Analyzes energy market data to ensure accuracy and reliability for the Iberian Peninsula renewable and flexible assets.</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>2-3 years of experience in power markets with data analysis skills, proficient in Python, Excel, PowerQuery, Power BI, Databricks, and Alteryx.</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>The European power market, specifically focusing on renewable energy sources and their associated trading activities.</t>
+      <c r="O32" s="6" t="inlineStr">
+        <is>
+          <t>As an Energy Data Portfolio Analyst, you will work closely with the Energy Data Management team members and focus on two scopes: the Iberian Peninsula Renewable scope, which includes several production sites (solar, hydro, and wind), and the Iberian Peninsula flexible assets scope. Your primary responsibilities will include maintaining and executing these operational tasks, developing new controls to improve data reliability, and contributing to the issuance of Guarantees of Origin.</t>
+        </is>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>Python, Excel, PowerQuery, PowerBI, Databricks, Alteryx, data analysis, programming, analytical mindset, attention to detail, problem-solving ability</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions working with renewable energy sources (solar, hydro, and wind), low carbon energies, and contributing to the objective of Carbon Neutrality by 2050, which are all related to environmental sustainability and the clean energy sector.</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr"/>
@@ -3408,19 +3434,19 @@
           <t>Keyword (8)</t>
         </is>
       </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>A Manager or Senior Manager is needed to support clients in implementing mandatory sustainability and climate-related reporting requirements.</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>The ideal candidate will have CA or CPA qualifications, experience in ESG/sustainability assurance and advisory, and strong IFRS knowledge.</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>This role connects to climate, ESG, sustainability, and finance by supporting companies with their sustainability reporting needs.</t>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>Deliver mandatory sustainability reporting services, including process development and audit readiness across carbon footprint measurement, climate risk assessments, scenario analysis, and preparation of sustainability disclosures. Provide tailored advice on sustainability and climate-related financial reporting across sectors, aligned with evolving standards and frameworks. Deliver expert advice on IFRS, AASB, and Australian Sustainability Reporting Standards. Support the CFO Advisory team with</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>Strong knowledge of IFRS and AASB standards, experience with providing accounting advice, ability to interpret complex reporting requirements, highly developed interpersonal skills, growth mindset, self-motivated approach.</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions climate risk assessments, scenario analysis, and sustainability reporting, which are key aspects of climate risk management. The role also involves providing advice on sustainability and climate-related financial reporting, which is a critical component of</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
@@ -3497,19 +3523,19 @@
           <t>Keyword (8)</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>The Data Content Researcher will source, validate and maintain input data for Morningstar Indexes' ESG-focused indexes.</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have 3-5 years of experience building or maintaining ESG data, basic understanding of regulatory frameworks around ESG, and knowledge of databases.</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on the development and maintenance of ESG data for investment solutions within the financial industry.</t>
+      <c r="O34" s="6" t="inlineStr">
+        <is>
+          <t>Serve as an ESG data expert for a broad universe of global companies, understand and further their expertise on Morningstar indexes’ sustainability product offerings, including methodology criteria and data needs, work closely with multiple global teams across various functions to ensure that indexes team gets the required data in time to support the product roadmap, stay up to date with developments in sustainable, environmental, and social activities, including current and emerging trends, dri</t>
+        </is>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>ESG data expertise, knowledge of EU taxonomy, experience with databases (SQL), analytical skills, communication skills, stakeholder interaction skills</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>[esg] The job description mentions ESG data expertise, EU taxonomy, climate risk, and sustainable investing, which are all relevant to the ESG profile.</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
@@ -3586,19 +3612,19 @@
           <t>Keyword (8)</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>A highly motivated professional will process geospatial data, develop digital products, and contribute to Swiss Re's underwriting decisions.</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have intermediate level experience in the geospatial industry with a proven track record in geo data processing and analytics.</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>This role connects to climate, ESG, sustainability, and finance by contributing to natural hazard assessment for risk modeling and insurance pricing.</t>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>Process and analyze geospatial data to contribute to the development of Swiss Re products and solutions, Develop and maintain scripts and pipelines to automate data processing and standardize workflows, Work closely with diverse teams across Swiss Re, providing geo-domain expertise, technical guidance, and support, Drive small projects independently, Coordinate and communicate effectively with other teams and stakeholders, provide regular project status updates, and ensure comprehensive and up-t</t>
+        </is>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>Geospatial tools (QGIS, ESRI ArcMap, or ArcGIS Online), Programming (Python incl. following libraries GDAL, geopandas, rasterio), Raster and vector-data processing, Relational databases and SQL, Project management</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions natural catastrophes, climate change, and geospatial risk assessment, which are all relevant to climate risk, The company is also working to make the world more resilient, which implies a focus on managing and mitigating climate-related risks</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr"/>
@@ -3663,9 +3689,9 @@
           <t>Keyword (8)</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>This role is a consultant focused on disaster risk management, specifically within the context of climate change and natural hazards. The consultant will support low and middle-income countries in understanding, managing, and reducing their risks from these events.</t>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>The E T Consultant’s will support implementation of GPNBS programming. Tasks include coordinating and leading operational expert support on NBS to Task Teams and clients under the Operations pillar of the Program (advice on technical studies for project design and implementation, joining field missions and virtual meetings with client governments). The E T consultant will also be expected to contribute or lead knowledge products related to climate risk and NBS and support the other Pillars of th</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -3673,9 +3699,9 @@
           <t>Candidates should have experience with disaster risk assessment and mitigation strategies, knowledge of climate change impacts, and strong analytical skills.</t>
         </is>
       </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to the World Bank's efforts to promote sustainable development by addressing climate-related challenges in infrastructure and disaster risk management.</t>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions climate risk, climate resilience, and climate change, indicating a strong focus on climate-related issues. The role involves working on Nature-Based Solutions for Climate Resilience, which is a key area of focus for climate risk management.</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr"/>
@@ -3752,19 +3778,19 @@
           <t>Keyword (8)</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>The General Counsel will provide legal counsel to a rapidly growing renewable energy business, overseeing all legal, regulatory, governance, and compliance matters for the organization.  They will lead the legal function, support strategic decision-making, manage external counsel, and ensure the organization’s interests are protected across all jurisdictions in which it operates.</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>The ideal candidate has 10–15 years of post-qualification experience with expertise in utility-scale renewable energy projects, M&amp;A transactions, power purchase agreements (PPAs), and capital investment activities.  They will be proficient in legal research, contract drafting, and regulatory compliance.</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>This role is within the renewable energy sector, focusing on utility-scale solar, wind, battery storage, and hybrid energy projects. The position connects to climate change and sustainability efforts by supporting the development of clean energy solutions.</t>
+      <c r="O37" s="6" t="inlineStr">
+        <is>
+          <t>The General Counsel (GC) will serve as the chief legal advisor to the organisation, overseeing all legal, regulatory, governance, and compliance matters for a rapidly growing renewable energy business. The GC will lead the legal function, support strategic decision-making, manage external counsel, and ensure the organisation’s interests are protected across all jurisdictions in which it operates. Key Responsibilities include Strategic Legal Leadership, Project Development &amp; Renewable Energy Tran</t>
+        </is>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Essential skills include drafting, negotiation, and commercial advisory skills. Desirable skills include international renewable energy experience, prior leadership of a legal function or high-performing legal team, experience in ESG, sustainability regulations, and climate-related disclosures, and </t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description is focused on renewable energy projects, utility-scale solar, wind, battery storage, and hybrid energy projects, which are all related to clean energy and environmental science.</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
@@ -3849,19 +3875,19 @@
           <t>Keyword (8)</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>The TNC-GCF Climate Finance Specialist provides expertise in sourcing, developing, and structuring non-grant instruments for climate and conservation projects funded by the Green Climate Fund.</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>Requires experience with financial modeling, project development, and GCF regulations, along with strong communication and collaboration skills.</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on climate finance within the environmental sector, specifically supporting nature-based solutions to address climate change.</t>
+      <c r="O38" s="6" t="inlineStr">
+        <is>
+          <t>The TNC-GCF Climate Finance Specialist provides sophisticated business, financial and economic expertise to address conservation challenges. The TNC-GCF Climate Finance Specialist will support a key strategic initiative within The Nature Conservancy by sourcing, developing, and guiding the structuring of non-grant instruments financed by the Green Climate Fund in support of some of our most ambitious climate and conservation efforts. The Specialist is primarily responsible for developing the non</t>
+        </is>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>Deep knowledge of financial institutions, including community, commercial, development, sovereign or investment banks and their approaches to loan origination, underwriting, on-lending and risk assessment. Knowledge of environmental and social management systems within financial institutions. Experi</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions experience with sustainable finance and ESG trends, and the role involves working with non-grant instruments financed by the Green Climate Fund, which is related to sustainable finance and impact investing.</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
@@ -3942,19 +3968,19 @@
           <t>Keyword (8)</t>
         </is>
       </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>A Graduate Ecologist will conduct ecological field surveys, contribute to monitoring and restoration programs, and support the ecology team in delivering impactful environmental solutions.</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have a Bachelor's degree in Ecology or a related field and possess excellent communication and teamwork skills.</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to sustainable development by managing biodiversity for projects across various sectors like transport, renewable energy, and government agencies.</t>
+      <c r="O39" s="6" t="inlineStr">
+        <is>
+          <t>Support the ecology team in freshwater, wetland and terrestrial surveys, including targeted surveys for native fauna and flora. Contribute to monitoring and restoration programs. Conduct ecological field surveys using innovative techniques. Collect and analyse ecological data. Prepare and draft ecological reports and management plans.</t>
+        </is>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>Strong communication and teamwork skills, proactive and adaptable mindset, commitment to professionalism and integrity</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions working on environmental projects, including renewable energy, and conducting ecological field surveys, which aligns with the clean energy adjacent profile.</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
@@ -4039,19 +4065,19 @@
           <t>Keyword (8)</t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>Lead ESG advisory projects for clients, collaborating with teams to deliver impactful solutions focused on corporate sustainability.</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>3+ years of experience in consulting, strong knowledge of ESG reporting frameworks and data analysis tools like MS Excel.</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>Sustainability consulting within the finance sector, focusing on climate risk analysis and decarbonization strategies.</t>
+      <c r="O40" s="6" t="inlineStr">
+        <is>
+          <t>Lead ESG advisory projects from inception to delivery, including strategic direction and team coordination. Collaborate with project managers to plan and execute projects, ensuring client satisfaction and successful outcomes. Develop and present comprehensive analyses, conclusions, and deliverables, including written reports, metrics, and insights. Execute multi-disciplinary projects across various aspects of sustainability platforms in a collaborative manner. Ensure quality deliverables aligned</t>
+        </is>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>Strong knowledge of ESG reporting frameworks, including GRI, SASB, DJSI/S&amp;P, CDP, BRSR, TCFD, and UNPRI. Advanced proficiency in MS Excel; data science skills are a plus. Strong written and verbal communication skills in English, with excellent presentation skills. Capable of working under pressure,</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] The job description mentions ESG reporting, climate risk analysis, corporate ESG disclosures, and decarbonization strategies, which are all relevant to environmental, social, and governance topics, indicating a strong fit for the general_esg profile.</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
@@ -4136,19 +4162,19 @@
           <t>Keyword (8)</t>
         </is>
       </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>A Senior Associate will provide ESG advisory services to clients across the GCC and wider MENA region, supporting them with strategic direction, policy development, reporting, and decarbonization.</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have a graduate/post-graduate degree in Environment or related field, 1-3 years of post-qualification experience, and knowledge of ESG frameworks like GRI, SASB, TCFD.</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to the sustainable development of businesses within the GCC and wider MENA region by supporting them with ESG initiatives.</t>
+      <c r="O41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Execute consulting projects for different clients related to ESG/ Sustainability Advisory across areas such as ESG Strategic Direction covering stakeholder engagement and materiality assessment, ESG Policy and Governance Framework, Sustainability Reporting &amp; Disclosures based on different frameworks, GHG Accounting, Decarbonization Roadmap using SBTi guidelines, Sustainable Financing, Supply chain, etc. Undertake activities required for execution such as research on companies and ESG practices, </t>
+        </is>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>Hands-on experience, knowledge and understanding of ESG/ sustainability concepts and frameworks like GRI, SASB, TCFD, etc. Proficient in MS Word, PowerPoint and Excel. Good writing and analytical skills Comfortable to engage in multiple projects simultaneously Highly flexible and quick learner to ad</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] The job description mentions ESG Advisory, Sustainability Reporting, GHG Accounting, Decarbonization Roadmap, and Sustainable Financing, which are all related to environmental, social, and governance topics, indicating a strong fit with the general ESG profile.</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
@@ -4217,19 +4243,19 @@
           <t>Keyword (7)</t>
         </is>
       </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>Support the Climate Decarbonization &amp; Nature/Biodiversity team in managing projects, ensuring quality and timely delivery.</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>Minimum 2 years of experience in risk management related to climate change and sustainability; strong English language skills (written and spoken); proficient in MS Office Suite and data analysis software (R/Phyton, SAS, Qlik, SQL, PowerBi).</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>Sustainability consulting within the environmental, social, and governance (ESG) sector.</t>
+      <c r="O42" s="6" t="inlineStr">
+        <is>
+          <t>La risorsa Experienced verrà inserita in un team di lavoro e si occuperà di supportare il team nella gestione generale dei progetti soddisfacendo le richieste del cliente con particolare attenzione alla qualità e ai tempi.</t>
+        </is>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>Conoscenza dei principali software office quali MS Excel, Word, Power Point; Conoscenza di dei software di analisi dati e di mercato (R/Phyton, SAS, Qlik, SQL, PowerBi); Conoscenza dei framework di sostenibilità (es. SFDR, Taxonomy Regulation, ECB aspettative, CSR, DNF, PRI ecc.); Conoscenza di indi</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] The job description mentions sustainability, climate change, and ESG frameworks, indicating a focus on environmental, social, and governance topics.</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr"/>
@@ -4306,19 +4332,19 @@
           <t>Keyword (7)</t>
         </is>
       </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>Assists with investment risk analysis, quantitative and qualitative research, ESG risk assessment, and reporting for pension funds and investment portfolios.</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>Intermediate skills in Python, VBA; higher education in Economics, Finance, Mathematics or Statistics field; knowledge of investment risk analysis and management.</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>Asset Management &amp; Pensions industry, focusing on responsible investment practices and sustainable finance within the financial sector.</t>
+      <c r="O43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assist in preparation of regular and ad-hoc risk reports, Review limits and guidelines of pension funds, compliance limit check of portfolio and target investments according to investment policy and imposed limits, Perform daily pension fund limit monitoring, Conduct investment risk analysis, quantitative and qualitative research, Perform analysis of the ESG risks applicable to pension funds and target investments, Maintain and improve supportive tools for analysis, measurement and reporting of </t>
+        </is>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>Python, VBA, Bloomberg, Investment risk analysis, ESG risk analysis, Quantitative and qualitative research</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions 'sustainable finance', 'ESG risks', and 'investment risk analysis', which are key terms related to sustainable finance and ESG investing.</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
@@ -4399,19 +4425,19 @@
           <t>Keyword (7)</t>
         </is>
       </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>The Unit Director will lead the Materials &amp; Chemistry unit, shaping its strategic growth and impact through research, innovation, and industrial applications.</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>The ideal candidate possesses a strong leadership background with proven experience in driving scientific excellence and translating it into tangible solutions for industry.</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on materials science, chemistry, and sustainable industry within the context of circularity, climate change mitigation, and resource efficiency.</t>
+      <c r="O44" s="6" t="inlineStr">
+        <is>
+          <t>Your Role and Responsibilities: Strategy, Vision and External Positioning, Excellent Research, Innovation, Valorisation and Impact, Leadership, Organization and Transformation, Operations and Risk Management</t>
+        </is>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>Proven experience with: Valorisation of research and technology, including optimal IP valorisation, Scaling and de-risking innovations towards industry, Public-private partnerships, Ability to connect complex ecosystems and align stakeholders around a shared ambition, Fluent in English and Dutch; ot</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions cleantech, circularity, materials, chemistry, and industrial transition, which are all related to environmental science and sustainability, and specifically mentions the development of low-CO₂ construction materials, plastics recycling, and bio-ec</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
@@ -4492,19 +4518,19 @@
           <t>Keyword (7)</t>
         </is>
       </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>This internship focuses on applying behavioral insights to support UNICEF's sustainability efforts, specifically within the Social and Behaviour Change framework.  The intern will contribute to analyzing data, identifying barriers and opportunities for behavior change, and developing strategies to promote sustainable practices.</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should possess strong analytical skills, experience in behavioral research methods, and a passion for sustainability. Familiarity with social science theories and tools is desirable.</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to UNICEF's commitment to environmental responsibility and climate action within the global development sector.</t>
+      <c r="O45" s="6" t="inlineStr">
+        <is>
+          <t>The intern will support ISO with analytical and preparatory work that helps identify behavioural barriers, motivational drivers, and communication opportunities linked to four priority areas identified through the Green Pulse Survey conducted in 2025. The role is primarily analytical and strategic, with communications and graphic design skills considered an asset to support knowledge translation and internal engagement. The intern will be responsible for the following general/specific tasks: Beh</t>
+        </is>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>Social Behaviour Change, behavioural insights, analytical skills, strategic skills, communications, graphic design</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] The job description mentions sustainability, social and behaviour change, and environmental footprint, which are all related to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -4573,19 +4599,19 @@
           <t>Keyword (7)</t>
         </is>
       </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>The Corporate Financing &amp; Hedging Manager will be responsible for managing the group’s financing needs, including both short-term and long-term projects.</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>A Master's degree in Finance, Economics or Business Engineering is required, along with experience in corporate finance, hedging, and risk management.</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>This role connects to climate, ESG, sustainability, and finance by managing the financing of sustainable projects and investments for a carbon neutral future.</t>
+      <c r="O46" s="6" t="inlineStr">
+        <is>
+          <t>Corporate and Project Financing: In collaboration with the Corporate Finance Manager, you will ensure suitable and competitive financing of the group’s financial needs. You propose and design the most appropriate type of debt taking into account the group strategy &amp; policies. You go to the capital market and lead financing projects, negotiate the best financing conditions and finalise the transactions. You evaluate the interest of sustainable finance &amp; ESG instruments, propose the most appropria</t>
+        </is>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>Strong analytical skills, in-depth understanding of financial markets, comprehensive knowledge of various debt instruments, proficiency in daily treasury activities, cash management, and optimizing financial investments, experience in people management, natural communicator, high-impact professional</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions 'sustainable finance &amp; ESG instruments' and the company is committed to fast-tracking the shift to a carbon neutral world, indicating a focus on sustainable finance and ESG concepts.</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr"/>
@@ -4658,19 +4684,19 @@
           <t>Keyword (7)</t>
         </is>
       </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>Support organizations and investors in integrating ESG factors into financial strategies and investment decisions.</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>Strong knowledge of finance and ESG integration, analytical and financial modeling skills, understanding of sustainable finance frameworks.</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>Sustainable Finance Consultant will work within the growing field of sustainable finance to support organizations and investors in their efforts to integrate ESG factors into financial decision-making.</t>
+      <c r="O47" s="6" t="inlineStr">
+        <is>
+          <t>Analyze ESG factors in financial decision-making, Support green finance and sustainable investment initiatives, Prepare sustainability-linked financial reports, Conduct ESG risk assessments for investments</t>
+        </is>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>Strong knowledge of finance and ESG integration, Analytical and financial modeling skills, Understanding of sustainable finance frameworks</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions ESG factors, sustainable finance, green finance, and sustainable investment initiatives, which are all relevant to the sustainable finance profile.</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr"/>
@@ -4735,19 +4761,19 @@
           <t>Keyword (7)</t>
         </is>
       </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>Join CapMan's Investment Intern team to gain hands-on experience in forest and natural capital investments.</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>Strong analytical skills, market research knowledge, communication abilities, and an interest in sustainability.</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>The role contributes to the sustainable management of forests and land assets for environmental and financial returns.</t>
+      <c r="O48" s="6" t="inlineStr">
+        <is>
+          <t>You will have the opportunity to gain insight into the forest management and natural capital sector and be involved in everything from asset management to deal sourcing and execution, providing an ideal opportunity to develop your skills and learn about the day-to-day work in natural capital investments. As an Investment Intern, you will participate in various activities related to forestry and natural capital investments, including: Doing market research and analysing market trends, Creating fu</t>
+        </is>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>Strong drive, initiative, and problem-solving skills, analytical and detail-oriented mindset, strong communication skills, hands-on financial modelling experience, solid understanding of corporate finance, proficiency in English</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions natural capital investments, forestry, and sustainable forestry investments, which are related to environmental science and conservation, fitting the clean_energy_adjacent profile.</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr"/>
@@ -4824,19 +4850,19 @@
           <t>Keyword (7)</t>
         </is>
       </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>An Analyst role within Corporate &amp; Sustainability Advisory, supporting Nordic corporates with strategic financial decision-making.</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>2+ years of relevant experience in client-facing roles (banking, consulting, large corporate treasury), MSc in finance, economics, engineering or related field, strong analytical skills and interest in sustainability.</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>The role connects to climate, ESG, sustainability, and finance within the Nordic corporate sector.</t>
+      <c r="O49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perform in-depth financial modelling and analysis related to capital structure, funding strategy, acquisition and debt capacity, and credit ratings. Integrate sustainability considerations into financial analysis, including impacts on availability, pricing and structure of capital. Prepare clear, well-structured and robust materials for senior internal stakeholders and client presentations. Take an active role in client projects, with increasing exposure to senior decision-makers. Contribute to </t>
+        </is>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>Strong analytical skills, genuine interest in sustainability and financial markets, ability to work in a structured way, clear communication, ability to thrive in collaborative environments</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions integrating sustainability considerations into financial analysis, and the role is part of the Corporate &amp; Sustainability Advisory team, indicating a focus on sustainable finance.</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
@@ -4921,19 +4947,19 @@
           <t>Keyword (7)</t>
         </is>
       </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>Certified GHG Footprint (Green House Gases) and LCA (Life Cycle Assessment) Assessor is needed to assess sustainability, ESG, and BRSR reporting projects.</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>1-3 years of experience as a GHG Assessor/ LCA, knowledge of SimaPro, Guideline documents, and auditing techniques.</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>This role connects to climate change and sustainability by assessing the environmental impact of projects related to greenhouse gas emissions reduction.</t>
+      <c r="O50" s="6" t="inlineStr">
+        <is>
+          <t>Conduct GHG Footprint Analysis &amp; LCA, apply and assess project design, determine and assess project boundaries, select and quantify baseline scenario, determine and assess environmental impacts, assess stakeholder comments, apply and assess monitoring plans, quantify, monitor, report and assess GHG emissions, calculate and assess GHG emission factors, evaluate information to determine project activity additionality, determine and assess barriers, apply and assess common practice analysis</t>
+        </is>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LCA Tools like SimaPro, guideline documents and operational system of a GHG reduction scheme, project cycle and Regulatory requirements, auditing principles, procedures and techniques, risk assessment techniques, data and information sampling techniques, materiality and level of assurance concepts, </t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions GHG Footprint, LCA, ESG, BRSR Reporting, and GHG reduction schemes, which are directly related to climate risk and transition risk.</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
@@ -5002,19 +5028,19 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>A Graduate Water Resources Engineer will contribute to a range of projects including flood studies, stormwater management, mine water assessments, and urban water design.</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>A candidate should have a relevant engineering degree and be proficient in hydrological and hydraulic modeling, drainage design, and computational fluid dynamics.</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to the development of sustainable solutions for water infrastructure within various industries, focusing on climate resilience and environmental protection.</t>
+      <c r="O51" s="6" t="inlineStr">
+        <is>
+          <t>You will have the opportunity to gain insight into the forest management and natural capital sector and be involved in everything from asset management to deal sourcing and execution, providing an ideal opportunity to develop your skills and learn about the day-to-day work in natural capital investments. As an Investment Intern, you will participate in various activities related to forestry and natural capital investments, including: Doing market research and analysing market trends, Creating fu</t>
+        </is>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>Strong drive, initiative, and problem-solving skills, analytical and detail-oriented mindset, strong communication skills, hands-on financial modelling experience, solid understanding of corporate finance, proficiency in English</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions natural capital investments, forestry, and sustainable forestry investments, which are related to environmental science and conservation, fitting the clean_energy_adjacent profile.</t>
         </is>
       </c>
       <c r="R51" s="2" t="inlineStr"/>
@@ -5079,19 +5105,19 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>The HR Project &amp; Transformation Lead will partner with business groups and HR functions to deliver value-added services to management and employees.</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>The ideal candidate has experience in project management, change management, and HR transformation, with a strong understanding of HR best practices and data analysis skills.</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to Hitachi's sustainability efforts by supporting the development of a more sustainable workforce and promoting environmental awareness within the company.</t>
+      <c r="O52" s="6" t="inlineStr">
+        <is>
+          <t>The HR Project &amp; Transformation Lead will partner across the HR functions and Business Groups to deliver value-added services to management and employees. Lead and drive projects that enhance networking opportunities and foster HR collaboration across Sectors and Business Units within the Region, including cross-regional collaboration among RHQ HR teams. Assume responsibility as Project Lead and Project Manager in relation to collaboration activities across Groups. Expand engagement with other G</t>
+        </is>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>Strong analytical skills, genuine interest in sustainability and financial markets, ability to work in a structured way, clear communication, ability to thrive in collaborative environments</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions integrating sustainability considerations into financial analysis, and the role is part of the Corporate &amp; Sustainability Advisory team, indicating a focus on sustainable finance.</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr"/>
@@ -5156,19 +5182,19 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>The Head of Finance and Accounting is responsible for managing the organization's financial control environment, ensuring compliance with IFRS, Group Financial Guidelines, and local statutory requirements across the Europe, Middle East and Africa region.</t>
-        </is>
-      </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>Requires a strong understanding of accounting principles, IFRS, and GAAP, along with experience in leading finance teams, process improvement, and treasury management.</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>This role is within the mining and industrial equipment sector, focusing on financial operations for Weir Minerals' EMEA division.</t>
+      <c r="O53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Head of Finance and Accounting is a highly visible leadership position responsible for managing the organization’s financial control environment and ensuring compliance with IFRS, Group Financial Guidelines and local Statutory Accounting and regulatory requirements across the Europe, Middle East and Africa region. This role oversees end-to-end accounting operations, including monthly, quarterly, and annual closings, and holds accountability for working capital and balance sheet forecasting, </t>
+        </is>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>Technical expertise in finance and accounting, leadership capabilities, strong communication and collaboration skills, ability to build and develop a high-performing accounting organization, experience with SAP ERP systems, knowledge of IFRS, statutory reporting, internal controls, audit management,</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions GHG Footprint, LCA, ESG, BRSR Reporting, and GHG reduction schemes, which are directly related to climate risk and transition risk.</t>
         </is>
       </c>
       <c r="R53" s="2" t="inlineStr"/>
@@ -5233,14 +5259,14 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>As a Senior Finance IT Business Analyst, you will support the design and implementation of financial systems for Nespresso's business operations. You will work closely with business teams to ensure technology solutions align with their needs.</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>10+ years of experience in business analysis within finance, fiscal legislation, accounting, or related areas is required.</t>
+      <c r="O54" s="6" t="inlineStr">
+        <is>
+          <t>With an exclusive focus on the Nespresso business, you will work within the core Finance team, supporting the design of financial, fiscal, and accounting flows across various business processes while building and enhancing the technology platforms that support the business. As a Senior Finance IT Business Analyst, you will coordinate and guide a team of IT Business Analysts and Product Experts responsible for understanding end-to-end business flows. You will analyze and define business and funct</t>
+        </is>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>Experience working on Finance/Fiscal legislation initiatives related to retail business flows running on ERP systems, POS systems and e-Commerce. Experience working in a global environment and with virtual teams. Strong analytical thinking and business analysis skills. Effective communication, inter</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -5318,19 +5344,19 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>This role involves leading and delivering complex consulting assignments for mining clients across the entire project lifecycle.</t>
-        </is>
-      </c>
-      <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>Requires extensive experience in mining and exploration industries, including technical expertise in environmental and social performance.</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on the global mining industry, providing advisory services to companies involved in mineral property development.</t>
+      <c r="O55" s="6" t="inlineStr">
+        <is>
+          <t>Lead and Deliver Strategic Mining Advisory Projects, Manage and execute environmental and social performance input into feasibility studies, due diligence assignments, ITRs/ITERs, and operational improvement programs. Deliver clear, innovative, and commercially relevant insights aligned with client needs and project scope. Provide Senior Technical Expertise, Participate in Multi-Disciplinary Project Teams, Engage Senior and Executive-Level Stakeholders, Drive Business Development and Industry Pr</t>
+        </is>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technical Skills &amp; Experience, Environmental and social impact assessment, environmental and social due diligence, environmental and social management systems, lenders environmental and social performance requirements, including but not limited to Equator Principles and IFC Environmental and Social </t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] The job description mentions environmental and social performance management, impact assessment, and due diligence, which are all relevant to ESG strategy and corporate sustainability. The role also involves providing advice on environmental and social performance to mining clients, wh</t>
         </is>
       </c>
       <c r="R55" s="2" t="inlineStr">
@@ -5411,19 +5437,19 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>The Sales Manager will build and lead the sales function for Neural Alpha's SaaS platform, targeting financial institutions, asset managers, corporates, and NGOs.  They will develop a comprehensive sales strategy, manage the full sales cycle, and establish a scalable sales operation.</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>This role requires an entrepreneurial sales professional with experience in building and scaling sales teams, strong CRM skills, and proven ability to drive revenue growth.</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>The Sales Manager will play a key role in driving sales for Neural Alpha's AI-first platform within the financial technology sector.</t>
+      <c r="O56" s="6" t="inlineStr">
+        <is>
+          <t>Develop and execute a comprehensive sales strategy for Neural Alpha’s SaaS platform, targeting financial institutions, asset managers, corporates and NGOs. Own the full sales cycle from prospecting and lead qualification through to negotiation, close and handover to Customer Success. Build and manage a robust sales pipeline using CRM tools, ensuring accurate forecasting and reporting to senior leadership. Establish and lead the creation of a scalable sales function, defining processes, playbooks</t>
+        </is>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>Proficiency with CRM platforms (e.g. HubSpot, Salesforce) and modern sales enablement tools. Comfortable embracing and leveraging AI tools and technology to enhance personal productivity and sales effectiveness. Knowledge of ESG, sustainable finance, or regulatory frameworks such as ISSB, CSRD, EU T</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions experience selling into financial institutions, asset managers or large corporates, and knowledge of ESG, sustainable finance, or regulatory frameworks such as ISSB, CSRD, EU Taxonomy, SFDR and TNFD, indicating a strong connection to sustainable fin</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr">
@@ -5504,19 +5530,19 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O57" s="2" t="inlineStr">
-        <is>
-          <t>This role supports the implementation of the Central African Forest Initiative (CAFI) by contributing to REDD+ and LED investment frameworks in Central African countries.</t>
-        </is>
-      </c>
-      <c r="P57" s="2" t="inlineStr">
-        <is>
-          <t>Applicants should have experience with REDD+, forest governance, sustainable development, and project management.</t>
-        </is>
-      </c>
-      <c r="Q57" s="2" t="inlineStr">
-        <is>
-          <t>The role is focused on climate change mitigation, biodiversity conservation, and sustainable development within the Central African region.</t>
+      <c r="O57" s="6" t="inlineStr">
+        <is>
+          <t>The incumbent will be responsible for product strategy and coordination, product delivery, capacity building and deployment, quality assurance, stakeholder engagement, and knowledge management. Specific duties include: Liaise with CAFI PES technical team and implementation partners to capture functional requirements, Translate operational needs into clear technical specifications for developers, Monitor and report on project progress, Drive the functional vision and evolution of the products, En</t>
+        </is>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>No specific skills mentioned in the job description, but the role involves working with digital tools, project management, coordination, and knowledge management.</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description is related to the conservation of forests, reduction of deforestation, and promotion of sustainable development, which are all relevant to the clean energy and environmental conservation sector.</t>
         </is>
       </c>
       <c r="R57" s="2" t="inlineStr">
@@ -5597,14 +5623,14 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O58" s="2" t="inlineStr">
-        <is>
-          <t>A dual track role combining financial audit expertise with data analytics skills to support audit engagements and enhance audit quality.</t>
-        </is>
-      </c>
-      <c r="P58" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should possess analytical, technical, and communication skills, including experience with financial data analysis, Excel, Power BI, and automation tools.</t>
+      <c r="O58" s="6" t="inlineStr">
+        <is>
+          <t>You will contribute to financial audit engagements and, in parallel, support the Data Audit Team by delivering analytics that strengthen audit quality, consistency, and documentation. Collect, structure and process large financial and operational datasets for audit purposes. Perform data analyses to support risk assessments and audit procedures. Build audit-ready outputs and visualizations using Excel and Power BI where relevant. Automate and continuously improve data-driven audit analyses and t</t>
+        </is>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>Data analytics, data engineering, Excel, Power BI, SQL, Python, business economics, finance, audit fundamentals</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -5690,19 +5716,19 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O59" s="2" t="inlineStr">
-        <is>
-          <t>As an ET Consultant in Disaster Risk Management, you will provide technical expertise and support to low and middle-income countries on disaster risk reduction and climate change adaptation strategies.</t>
-        </is>
-      </c>
-      <c r="P59" s="2" t="inlineStr">
-        <is>
-          <t>This role requires a strong understanding of disaster risk management principles, experience with climate change adaptation, and the ability to develop technical solutions for diverse contexts.</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on disaster risk management within the context of climate change and its impact on vulnerable communities in low and middle-income countries.</t>
+      <c r="O59" s="6" t="inlineStr">
+        <is>
+          <t>The role will include the following objectives: Provide technical expertise and operational support to GFDRR’s Disaster-FCV Nexus program, focusing on FCV-sensitive disaster risk management and climate resilience. Strengthen GFDRR’s analytical, advisory, and partnership work on the disaster-FCV nexus, including knowledge generation, policy dialogue, and capacity building. Facilitate collaboration and knowledge exchange with EU institutions, regional bodies, and other stakeholders in Brussels and</t>
+        </is>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>Strong analytical, writing, and communication skills. Experience in partnership development and stakeholder engagement, especially with EU institutions and donors. Excellent written and spoken English required; knowledge of French or other EU languages is an asset.</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[climate_risk] The job description mentions climate change, disaster risk management, and climate resilience, which are all related to climate risk. The role also involves working with the Global Facility for Disaster Reduction and Recovery (GFDRR), which is a global partnership that helps low- and </t>
         </is>
       </c>
       <c r="R59" s="2" t="inlineStr">
@@ -5783,19 +5809,19 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O60" s="2" t="inlineStr">
-        <is>
-          <t>Senior Consultants will contribute to quantitative &amp; financial risk modelling for banking credit risk regulation, market risk modelling, and (derivative) valuation within a global team.</t>
-        </is>
-      </c>
-      <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should possess strong knowledge of one or more of these fields, including experience with credit risk modeling, market risk modelling, and derivatives instruments.</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to the financial services industry by supporting clients in understanding and managing their risks related to credit, market, and derivative instruments.</t>
+      <c r="O60" s="6" t="inlineStr">
+        <is>
+          <t>We are looking for a skilled quantitative professional, who may combine working on Belgian and European financial institutions. The ability to drive work forward to a conclusion, to find pragmatic solutions to complex problems and to explain and document them convincingly, are key factors in order to be successful in this role. Typical projects you will be involved in: Participate in, and lead Risk engagements, with the focus credit risk modeling, including the link with accounting (e.g. IFRS 9)</t>
+        </is>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>Solid understanding of quantitative modeling techniques and practical experience with valuation of complex instruments (e.g. derivative, illiquid bonds) and/or market risk (e.g. FRTB, IRRBB, VAR models) is mandatory Deep understanding of quantitative modeling techniques, with practical experience in</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions 'sustainable finance workgroup' and 'climate risk modelling for financial institutions', indicating a focus on sustainable finance and ESG considerations in the context of financial risk management.</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr">
@@ -5872,19 +5898,21 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O61" s="2" t="inlineStr">
-        <is>
-          <t>Develop and support atmospheric peril models for insurance clients, contributing to risk management decisions globally.</t>
-        </is>
-      </c>
-      <c r="P61" s="2" t="inlineStr">
-        <is>
-          <t>Expertise in spatial statistics, extreme value analysis, atmospheric dynamics, dynamic downscaling methods, Python proficiency.</t>
-        </is>
-      </c>
-      <c r="Q61" s="2" t="inlineStr">
-        <is>
-          <t>Insurance industry, climate change modeling, catastrophe risk assessment.</t>
+      <c r="O61" s="6" t="inlineStr">
+        <is>
+          <t>Improve the accuracy of representing atmospheric perils
+Contribute to model development, validation, and productization for global clients
+Support model development using observational and reanalysis products, GCMs, and high-resolution simulations</t>
+        </is>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>Spatial statistics, extreme value analysis, atmospheric dynamics, dynamic downscaling methods, Python</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions 'atmospheric perils', 'extreme weather events', 'changing climate', and 'climate modelling' which are all related to climate risk.</t>
         </is>
       </c>
       <c r="R61" s="2" t="inlineStr">
@@ -5965,19 +5993,19 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O62" s="2" t="inlineStr">
-        <is>
-          <t>Support research and analysis on climate change and democracy as part of the Political Participation and Representation team.</t>
-        </is>
-      </c>
-      <c r="P62" s="2" t="inlineStr">
-        <is>
-          <t>Bachelor's degree in political science, international relations, or a related field; experience with data analysis and research methods.</t>
-        </is>
-      </c>
-      <c r="Q62" s="2" t="inlineStr">
-        <is>
-          <t>International organizations supporting democratic institutions and processes in various countries, focusing on climate change and its impact on democracy.</t>
+      <c r="O62" s="6" t="inlineStr">
+        <is>
+          <t>The intern will have the opportunity to be involved in the following duties: Supporting different research works conducted by the team; Analyzing policy documents and legal texts, to collect and review data; Assisting with research and fact-checking for International IDEA materials and background information; Assisting in the organization and the follow-up of conferences, events and activities, including assisting with reporting, note-taking and some logistical tasks; Providing desk research and</t>
+        </is>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>Strong analytical, drafting, editorial and problem-solving skills. Ability to appreciate diversity and work as part of a team in such an environment. Ability to assess, manage and structure information. Strong interpersonal and communication skills. Good knowledge of Microsoft Office suite. Knowledg</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] The job description mentions 'sustainable democracy', 'climate change and democracy', and 'democracy and inclusion', which are related to environmental, social, and governance topics, but the primary focus is on democratic institutions and processes, making it a better fit for the gene</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr">
@@ -6058,19 +6086,19 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>As a Graduate Consultant in Aurecon's Sustainability, Climate Change &amp; Risk team, you will work on meaningful projects with real responsibility, applying your technical knowledge alongside people who think boldly.</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have a relevant degree in Engineering, Business, Economics, Finance, Law, Sustainability, Science, or related double degree and be available to start full-time in early February 2027.</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="inlineStr">
-        <is>
-          <t>This role connects to climate change, ESG, sustainability, and finance by working on projects related to energy transition, decarbonization, and physical risk strategy.</t>
+      <c r="O63" s="6" t="inlineStr">
+        <is>
+          <t>Our Sustainability Climate Change and Risk covers several disciplines including; Energy Transition &amp; Markets, Decarbonisation and Physical Risk Strategy. As a Graduate Consultant in our Sustainability, Climate Change &amp; Risk team, team at Aurecon, you’ll: Own your career while growing your skills through workshops and self-paced learning, Apply your analytical and problem-solving skills on live client projects, Work with diverse, multidisciplinary teams across engineering, advisory, and design, L</t>
+        </is>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>Analytical and problem-solving skills, Strong communication skills, Team-oriented mindset</t>
+        </is>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions 'Sustainability Climate Change and Risk', 'Energy Transition &amp; Markets', 'Decarbonisation and Physical Risk Strategy', which are all related to climate risk and sustainability.</t>
         </is>
       </c>
       <c r="R63" s="2" t="inlineStr">
@@ -6155,19 +6183,19 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O64" s="2" t="inlineStr">
-        <is>
-          <t>Leads business development, technical advisory, and practice support for climate change and environment programs across Australia and the Indo-Pacific.</t>
-        </is>
-      </c>
-      <c r="P64" s="2" t="inlineStr">
-        <is>
-          <t>Requires a postgraduate qualification or equivalent senior-level expertise in international development, climate change, environmental management, disaster management, engineering, agriculture, or related fields with 10+ years of experience.</t>
-        </is>
-      </c>
-      <c r="Q64" s="2" t="inlineStr">
-        <is>
-          <t>Works on climate resilience solutions for sustainable infrastructure, agriculture, livelihoods, disaster preparedness, and natural resource management within the Indo-Pacific region.</t>
+      <c r="O64" s="6" t="inlineStr">
+        <is>
+          <t>The Associate Director, Climate Change and Environment supports the growth of Tetra Tech International Development’s climate portfolio across Australia and the Indo‑Pacific through business development, technical advisory and practice support. Key responsibilities include: Lead and support business development for climate change and environment opportunities, including proposals, positioning and client engagement, Design and shape integrated climate resilience solutions across sectors such as su</t>
+        </is>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>Data analytics, data engineering, Excel, Power BI, SQL, Python, business economics, finance, audit fundamentals</t>
+        </is>
+      </c>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions climate change, climate resilience, disaster risk reduction, and climate‑inclusive development, which are all relevant to the climate risk profile</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
@@ -6252,19 +6280,19 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O65" s="2" t="inlineStr">
-        <is>
-          <t>A Risk Consulting Manager will lead a team of consultants to deliver tailored risk solutions for financial institutions in the MENA region.</t>
-        </is>
-      </c>
-      <c r="P65" s="2" t="inlineStr">
-        <is>
-          <t>Requires experience leading teams, technical expertise in credit risk management, strong project management skills, and knowledge of financial products and regulations.</t>
-        </is>
-      </c>
-      <c r="Q65" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on financial services risk management within the Middle East and North Africa (MENA) region, contributing to climate-conscious financial practices.</t>
+      <c r="O65" s="6" t="inlineStr">
+        <is>
+          <t>Lead a team of 5-6 Senior consultants, analysts for engagement execution and delivery. Showcase exceptional project management abilities and foster a collaborative environment and accountability among team members on engagements. Demonstrate deep technical expertise and industry knowledge, particularly in financial products with a focus on lending solutions. Design, assessment, and benchmarking of financial risk management policies, frameworks, methodologies covering a range of risk domains such</t>
+        </is>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>Advanced technical skills, with proficiency in Python, SAS, SQL, R, and Excel. Excellent Oral and written communication and presentation skills. Strong documentation skills, with the ability to quickly grasp complex concepts and present them clearly in documents or presentations. Strong multi-taskin</t>
+        </is>
+      </c>
+      <c r="Q65" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions 'climate risk' as one of the risk domains, and also mentions 'experience in climatic risk space preferably in the areas of stress testing /scenario designing', indicating that the role involves working with climate-related risks.</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr">
@@ -6349,19 +6377,19 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O66" s="2" t="inlineStr">
-        <is>
-          <t>The Team Leader, Sustainable Finance Operations at Intercontinental Exchange (ICE) leads a team of ESG data professionals to deliver accurate and timely data for climate products and global ESG reporting standards.</t>
-        </is>
-      </c>
-      <c r="P66" s="2" t="inlineStr">
-        <is>
-          <t>Requires 5+ years' experience in ESG/Sustainability data operations or reference data, deep knowledge of ESG content, regulatory frameworks, and capital markets, proficiency in SQL, M, and other relevant tools.</t>
-        </is>
-      </c>
-      <c r="Q66" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on the financial industry, specifically within the realm of sustainable finance and climate-related products.</t>
+      <c r="O66" s="6" t="inlineStr">
+        <is>
+          <t>The Team Leader, Sustainable Finance Operations at Intercontinental Exchange (ICE) plays a critical leadership role in managing and developing a high-performing team of ESG data professionals based in Hyderabad. This position ensures the delivery of accurate, comprehensive, and timely Environmental, Social, and Governance (ESG) data to support ICE Climate products and global ESG reporting standards. * Lead and develop a team of 15+ Associates and Analysts, overseeing resource planning, performan</t>
+        </is>
+      </c>
+      <c r="P66" s="6" t="inlineStr">
+        <is>
+          <t>Proficiency in SQL, Macros, and Advanced Excel; experience with Power BI, Tableau, or similar tools preferred. Strong analytical, problem-solving, and communication skills. Ability to align team objectives with organisational goals and deliver high-quality results. Reliability, flexibility, and atte</t>
+        </is>
+      </c>
+      <c r="Q66" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions ESG data, ESG reporting standards, and ESG product users, which are all relevant to sustainable finance. The role also involves working with ESG content, regulatory frameworks, and capital markets, which are key aspects of sustainable finance.</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr">
@@ -6438,19 +6466,19 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O67" s="2" t="inlineStr">
-        <is>
-          <t>Presales technical lead for Johnson Controls Digital Solutions, supporting customers in making technology decisions and implementing best practices for building management.</t>
-        </is>
-      </c>
-      <c r="P67" s="2" t="inlineStr">
-        <is>
-          <t>Experienced engineer with expertise in building technologies including BMS, VMS, and Access Control, strong technical skills, excellent customer service and sales skills, and experience in RFP/RFI responses.</t>
-        </is>
-      </c>
-      <c r="Q67" s="2" t="inlineStr">
-        <is>
-          <t>Johnson Controls is a global leader in smart buildings, focusing on sustainability and climate-related innovation to develop sustainable products and services.</t>
+      <c r="O67" s="6" t="inlineStr">
+        <is>
+          <t>As a member of the Global Center of excellence the Presales technical lead will help customers to make technology decisions, implement best practices for asset management and overall facilitate transforming buildings into smart connected entities. Develop and implement pre-sales strategies that align with the organization’s business goals &amp; targets. Review opportunity inputs, requirements and specifications; should be able to capture the Digital Solution scope and understand the complete require</t>
+        </is>
+      </c>
+      <c r="P67" s="6" t="inlineStr">
+        <is>
+          <t>Strong technical aptitude and ability to quickly learn new products and technologies. Excellent communication and interpersonal skills. Proficiency in using Integrated software and digital communication tools. Ability to present complex technical information in a clear and concise manner. Strong pro</t>
+        </is>
+      </c>
+      <c r="Q67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[clean_energy_adjacent] The job description mentions 'sustainable buildings', 'climate-related innovation', 'net zero carbon emissions', and 'energy management', which are related to environmental sustainability and clean energy. Although the primary focus is on building technologies, the company's </t>
         </is>
       </c>
       <c r="R67" s="2" t="inlineStr"/>
@@ -6527,19 +6555,19 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O68" s="2" t="inlineStr">
-        <is>
-          <t>A Corporate Development Analyst will support the evaluation, development, and management of renewable energy projects across their lifecycle.</t>
-        </is>
-      </c>
-      <c r="P68" s="2" t="inlineStr">
-        <is>
-          <t>The ideal candidate has a minimum of two years of financial modeling experience, strong analytical skills, advanced proficiency in Excel and PowerPoint, and a deep understanding of the Indian renewable energy market.</t>
-        </is>
-      </c>
-      <c r="Q68" s="2" t="inlineStr">
-        <is>
-          <t>This role connects to climate, ESG, sustainability, and finance by supporting the development and management of renewable energy projects that contribute to a carbon-free and sustainable economy.</t>
+      <c r="O68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Develop and manage project finance and cash flow models for renewable energy projects—such as Solar PV, Wind, and BESS—to assess profitability, equity returns, and key risks. Maintain project assumptions documentation, return trackers, and tariff models. Engage cross-functionally with Energy Origination/Markets, Business Development, Project Development, and Operations teams to develop comprehensive business insights and evaluate greenfield renewable energy projects across various technologies. </t>
+        </is>
+      </c>
+      <c r="P68" s="6" t="inlineStr">
+        <is>
+          <t>Strong analytical skills, advanced proficiency in Excel and PowerPoint, strong understanding of Indian power markets, relevant regulatory policies, and Power Purchase Agreement (PPA) structures, strong interpersonal skills, collaborative mindset, ability to work independently</t>
+        </is>
+      </c>
+      <c r="Q68" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions renewable energy, solar, wind, and BESS, which are all related to clean energy. The company's focus on transitioning to a carbon-free and sustainable economy also supports this classification.</t>
         </is>
       </c>
       <c r="R68" s="2" t="inlineStr">
@@ -6616,19 +6644,19 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O69" s="2" t="inlineStr">
-        <is>
-          <t>This role involves providing independent oversight and effective challenge on risk-related matters across the organization, supporting the development of risk management frameworks and policies.</t>
-        </is>
-      </c>
-      <c r="P69" s="2" t="inlineStr">
-        <is>
-          <t>A Master's degree in a related field is required, along with 4-7 years of experience in risk management, banking, finance, or management consulting.</t>
-        </is>
-      </c>
-      <c r="Q69" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on Enterprise Risk Management within American Express, contributing to climate risk assessments and sustainable business practices.</t>
+      <c r="O69" s="6" t="inlineStr">
+        <is>
+          <t>Within the Enterprise Risk Management &amp; Risk Oversight Group in GRC, Enterprise Risk Management &amp; Strategic Initiatives is the independent risk management team that plays a pivotal role in identification, assessment and mitigation of risks affecting the organization. The team’s core responsibility is to design, implement and oversee risk measurement &amp; management frameworks at American Express. Manager – Enterprise Risk Management &amp; Strategic Initiatives will be responsible for providing independ</t>
+        </is>
+      </c>
+      <c r="P69" s="6" t="inlineStr">
+        <is>
+          <t>Strong understanding of risk management principles, methodologies, frameworks, and regulatory requirements. Strong verbal and written communication skills. Analytical and problem-solving skills, with an ability to analyze data, identify trends, and evaluate risk scenarios effectively. Advanced profi</t>
+        </is>
+      </c>
+      <c r="Q69" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions performing Climate Risk-related assessments, including end to end measurement of physical and transition risk, scenario analysis, and supporting disclosure requirements, which directly relates to climate risk management.</t>
         </is>
       </c>
       <c r="R69" s="2" t="inlineStr">
@@ -6709,19 +6737,19 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O70" s="2" t="inlineStr">
-        <is>
-          <t>An Executive Consultant – Mining Advisory will lead complex consulting assignments across the entire mining lifecycle for global mining clients.</t>
-        </is>
-      </c>
-      <c r="P70" s="2" t="inlineStr">
-        <is>
-          <t>Requires extensive experience in mining and exploration industries, strong technical expertise, and ability to deliver high-impact outcomes.</t>
-        </is>
-      </c>
-      <c r="Q70" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on providing technical and strategic advice to mining companies on environmental and social performance within the mining industry.</t>
+      <c r="O70" s="6" t="inlineStr">
+        <is>
+          <t>Lead and deliver strategic mining advisory projects, provide senior technical expertise, participate in multi-disciplinary project teams, engage senior and executive-level stakeholders, drive business development and industry presence, support team culture, collaboration and wellbeing. Manage and execute environmental and social performance input into feasibility studies, due diligence assignments, ITRs/ITERs, and operational improvement programs.</t>
+        </is>
+      </c>
+      <c r="P70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technical skills: environmental and social impact assessment, environmental and social due diligence, environmental and social management systems. Soft skills: client and commercial capability, proposal development, client negotiation, project scoping, strong track record of repeat business, client </t>
+        </is>
+      </c>
+      <c r="Q70" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] The job description mentions environmental and social performance management, impact assessment, due diligence, and management systems, which are all relevant to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
       <c r="R70" s="2" t="inlineStr">
@@ -6802,19 +6830,30 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O71" s="2" t="inlineStr">
-        <is>
-          <t>Develops and implements ESG solutions for clients, analyzing data to support sustainable investment strategies.</t>
-        </is>
-      </c>
-      <c r="P71" s="2" t="inlineStr">
-        <is>
-          <t>Requires knowledge of ESG principles, regulatory frameworks (SFDR, MIFID), and financial analysis tools.</t>
-        </is>
-      </c>
-      <c r="Q71" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on the finance industry's growing focus on environmental, social, and governance (ESG) factors in wealth management.</t>
+      <c r="O71" s="6" t="inlineStr">
+        <is>
+          <t>* promouvoir et développer les offres ESG (Environnement, Social, Gouvernance)
+* s’assurer de la conformité du Métier aux réglementations en vigueur relatives à la finance durable en Europe
+* Vous serez le spécialiste local de la méthodologie extra-financière (relative aux critères ESG (Environnementaux, Sociaux et de Gouvernance)) couvrant l’ensemble des produits financiers de l’offre de Wealth Management à Luxembourg.
+* Vous contribuerez aux analyses à la structuration des données relatives au</t>
+        </is>
+      </c>
+      <c r="P71" s="6" t="inlineStr">
+        <is>
+          <t>* Capacité à collaborer / travail d’équipe
+* Rigueur
+* Etre orienté(e) résultats
+* Créativité &amp; Innovation / Capacité à résoudre des problèmes
+* Proactivité
+* Capacité d’analyse
+* Capacité à gérer un projet
+* Capacité à définir des indicateurs de performance pertinents
+* Analyse de données (PowerBI,</t>
+        </is>
+      </c>
+      <c r="Q71" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions ESG (Environnement, Social, Gouvernance), finance durable, SFDR, and MIFID ESG, which are all related to sustainable finance. The job also involves promoting and developing ESG offers, ensuring compliance with regulations, and contributing to the de</t>
         </is>
       </c>
       <c r="R71" s="2" t="inlineStr">
@@ -6895,19 +6934,19 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O72" s="2" t="inlineStr">
-        <is>
-          <t>Develops sustainable investment, hedging, and financing solutions for Global Markets Activities.</t>
-        </is>
-      </c>
-      <c r="P72" s="2" t="inlineStr">
-        <is>
-          <t>Requires a Master's degree in Finance or Sustainable Finance with prior experience in finance, strong communication skills, and proficiency in MS Office and Python.</t>
-        </is>
-      </c>
-      <c r="Q72" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on sustainable structured solutions within the financial sector, contributing to climate, ESG, sustainability, and finance initiatives.</t>
+      <c r="O72" s="6" t="inlineStr">
+        <is>
+          <t>Development of the offering of sustainable investment, hedging, and financing solutions for Global Markets Activities. Review and maintain the list of proprietary and external indices embedding ESG criteria; analyze their methodology and create marketing documentation. Monitor and contribute to develop the overall sustainable structured solutions offering. Contribute to assisting the rest of the team in specific quantitative analysis requests. Participate in sustainable finance market studies, m</t>
+        </is>
+      </c>
+      <c r="P72" s="6" t="inlineStr">
+        <is>
+          <t>Good communication and presentation skills. Management of complex projects. Proficient command of MS Office, notably Excel. Coding in Python is a plus</t>
+        </is>
+      </c>
+      <c r="Q72" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions sustainable investment, hedging, and financing solutions, ESG criteria, sustainable finance market studies, and ESG advisory team, which are all related to sustainable finance</t>
         </is>
       </c>
       <c r="R72" s="2" t="inlineStr">
@@ -6992,19 +7031,19 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O73" s="2" t="inlineStr">
-        <is>
-          <t>A Co-Founder is needed to secure investment for AIPL's sustainable economic growth initiatives in the Himalayan region.  This role involves leading fundraising efforts, securing project finance, and building partnerships with stakeholders.</t>
-        </is>
-      </c>
-      <c r="P73" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have a proven track record of scaling startups, navigating the VC landscape, and building organizational capacity. Strong financial and analytical skills are essential, along with experience in climate-related investment strategies.</t>
-        </is>
-      </c>
-      <c r="Q73" s="2" t="inlineStr">
-        <is>
-          <t>AIPL focuses on sustainable development in Northeast India through innovative financing mechanisms, technology solutions, and community involvement.</t>
+      <c r="O73" s="6" t="inlineStr">
+        <is>
+          <t>This is a full-time, hybrid (onsite/remote) leadership role in India. You will be the architect of our capital strategy, ensuring that our vision for regenerative agriculture is backed by robust investment. Key Responsibilities: Venture Fundraising: Lead the charge in securing investment from Angel Investors, Venture Capital (VC) firms, and Impact Funds. Project Finance: Secure dedicated funding for large-scale Bamboo agroforestry projects across Northeast India and Bhutan (Green Bonds, Carbon C</t>
+        </is>
+      </c>
+      <c r="P73" s="6" t="inlineStr">
+        <is>
+          <t>Fundraising Expertise, Financial &amp; Analytical Rigour, Sales &amp; Marketing Prowess, Climate Intelligence, Leadership, Investment &amp; Finance, Sector Expertise, Regional Insight</t>
+        </is>
+      </c>
+      <c r="Q73" s="6" t="inlineStr">
+        <is>
+          <t>[carbon_markets] The job description mentions carbon credits, carbon markets, and sustainable development, which are key aspects of the carbon markets profile. The company's focus on generating carbon credits and working on agroforestry projects also aligns with this profile.</t>
         </is>
       </c>
       <c r="R73" s="2" t="inlineStr">
@@ -7085,19 +7124,19 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O74" s="2" t="inlineStr">
-        <is>
-          <t>VP / Head of Marketing will build and scale marketing efforts to solidify Varaha's position as the leading carbon removal developer globally.</t>
-        </is>
-      </c>
-      <c r="P74" s="2" t="inlineStr">
-        <is>
-          <t>8-11 years of experience in marketing, PR, communications, or B2B, with expertise in account based marketing (ABM), field events, and partner enablement.</t>
-        </is>
-      </c>
-      <c r="Q74" s="2" t="inlineStr">
-        <is>
-          <t>This role is within the climate tech sector, focusing on carbon removal solutions for a global market.</t>
+      <c r="O74" s="6" t="inlineStr">
+        <is>
+          <t>Define and lead Varaha's global brand narrative, position Varaha as a pioneer in climate tech and high integrity carbon markets, build and execute a global PR strategy, develop and execute highly targeted Account Based Marketing (ABM) strategies, oversee the creation of a crisp, scientifically disciplined narrative architecture, develop a strategic conference plan, build and mentor a high performance marketing team, manage agencies, consultants, and creative partners.</t>
+        </is>
+      </c>
+      <c r="P74" s="6" t="inlineStr">
+        <is>
+          <t>Account Based Marketing, field events, PR and communications, partner enablement, storytelling, brand narrative, climate tech, carbon markets, marketing strategy, team leadership, agency management</t>
+        </is>
+      </c>
+      <c r="Q74" s="6" t="inlineStr">
+        <is>
+          <t>[carbon_markets] The job description mentions carbon removal, carbon markets, climate tech, and high integrity carbon markets, indicating a strong focus on carbon markets and climate-related topics.</t>
         </is>
       </c>
       <c r="R74" s="2" t="inlineStr">
@@ -7178,19 +7217,19 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O75" s="2" t="inlineStr">
-        <is>
-          <t>Develops and supports atmospheric peril models for global clients in the insurance industry, contributing to risk and capital management decisions.</t>
-        </is>
-      </c>
-      <c r="P75" s="2" t="inlineStr">
-        <is>
-          <t>Expertise in spatial statistics, extreme value analysis, atmospheric dynamics, dynamic downscaling methods, Python programming.</t>
-        </is>
-      </c>
-      <c r="Q75" s="2" t="inlineStr">
-        <is>
-          <t>Insurance and reinsurance industries, climate change modeling, catastrophe prediction, and risk assessment.</t>
+      <c r="O75" s="6" t="inlineStr">
+        <is>
+          <t>Improve the accuracy of representing atmospheric perils, contribute to model development, validation, and productization for global clients, support model development using observational and reanalysis products, GCMs, and high-resolution simulations</t>
+        </is>
+      </c>
+      <c r="P75" s="6" t="inlineStr">
+        <is>
+          <t>Spatial statistics, extreme value analysis, atmospheric dynamics, dynamic downscaling methods, Python</t>
+        </is>
+      </c>
+      <c r="Q75" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions developing catastrophe models for the insurance and reinsurance industries, simulating extreme weather events consistent with a changing climate, and advancing the development of atmospheric peril models, which are all related to climate risk</t>
         </is>
       </c>
       <c r="R75" s="2" t="inlineStr">
@@ -7275,19 +7314,19 @@
           <t>Keyword (6)</t>
         </is>
       </c>
-      <c r="O76" s="2" t="inlineStr">
-        <is>
-          <t>Analyze carbon emissions, develop sustainability strategies, and lead initiatives to improve ESG performance for clients and the Apex Group.</t>
-        </is>
-      </c>
-      <c r="P76" s="2" t="inlineStr">
-        <is>
-          <t>Master's degree in environmental engineering, sustainability, or related field, extensive experience in climate change, strong technical expertise in climate modeling and SBTi, proficiency in ESG frameworks.</t>
-        </is>
-      </c>
-      <c r="Q76" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on environmental impact assessment, carbon emissions reduction, and sustainable business practices within the finance sector.</t>
+      <c r="O76" s="6" t="inlineStr">
+        <is>
+          <t>Conduct comprehensive analyses, including Carbon Emissions Tracking, Carbon Footprint Assessments, Environmental Impact Analyses, Life Cycle Assessments (LCAs), Emissions Reduction Strategies, Climate Policy Development, Advocacy, Climate Modeling, Scenario Planning, and target setting aligned with Science-Based Targets (SBTi). Develop and execute data-driven strategies to assist investment managers and portfolio companies in reducing carbon emissions and setting targets. Lead initiatives to imp</t>
+        </is>
+      </c>
+      <c r="P76" s="6" t="inlineStr">
+        <is>
+          <t>Hands-on experience in carbon footprint analysis, GHG assessment, and climate risk advisory, with strong technical expertise in climate change, SBTi, LCA, ISO 14044/14064, decarbonization strategies, and climate risk modeling. A deep understanding of sustainability challenges across various industry</t>
+        </is>
+      </c>
+      <c r="Q76" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions climate risk, carbon emissions tracking, carbon footprint assessments, GHG assessment, climate risk advisory, and decarbonization strategies, which are all relevant to climate risk. Additionally, the job requires experience in climate change, environmental</t>
         </is>
       </c>
       <c r="R76" s="2" t="inlineStr">
@@ -7356,19 +7395,19 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O77" s="2" t="inlineStr">
-        <is>
-          <t>A Senior Specialist in Data Management will lead the definition of data requirements, controls, and governance to ensure high-quality customer and identity data for digital-first selling, self-service, automation, and AI.</t>
-        </is>
-      </c>
-      <c r="P77" s="2" t="inlineStr">
-        <is>
-          <t>Requires a strong understanding of systems and applications used across Telstra, experience with data management best practices, analytical skills, and ability to translate complex data needs into actionable specifications.</t>
-        </is>
-      </c>
-      <c r="Q77" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on data management within the telecommunications industry, supporting digital transformation initiatives and enabling AI-powered solutions.</t>
+      <c r="O77" s="6" t="inlineStr">
+        <is>
+          <t>Lead and deliver strategic mining advisory projects, provide senior technical expertise, participate in multi-disciplinary project teams, engage senior and executive-level stakeholders, drive business development and industry presence, support team culture, collaboration and wellbeing. Manage and execute environmental and social performance input into feasibility studies, due diligence assignments, ITRs/ITERs, and operational improvement programs.</t>
+        </is>
+      </c>
+      <c r="P77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technical skills: environmental and social impact assessment, environmental and social due diligence, environmental and social management systems. Soft skills: client and commercial capability, proposal development, client negotiation, project scoping, strong track record of repeat business, client </t>
+        </is>
+      </c>
+      <c r="Q77" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] The job description mentions environmental and social performance management, impact assessment, due diligence, and management systems, which are all relevant to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
       <c r="R77" s="2" t="inlineStr"/>
@@ -7433,19 +7472,30 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O78" s="2" t="inlineStr">
-        <is>
-          <t>Graduate Hydrogeologist will support diverse projects across various sectors, collaborating with teams on field programs, technical documentation, and model development.</t>
-        </is>
-      </c>
-      <c r="P78" s="2" t="inlineStr">
-        <is>
-          <t>Requires a Bachelor's degree in Geology or related field, experience with groundwater assessment, sampling, and modeling, and strong analytical skills.</t>
-        </is>
-      </c>
-      <c r="Q78" s="2" t="inlineStr">
-        <is>
-          <t>The role contributes to environmental impact management for industries like oil and gas, mining, and public services, focusing on water resources and regulatory compliance.</t>
+      <c r="O78" s="6" t="inlineStr">
+        <is>
+          <t>* promouvoir et développer les offres ESG (Environnement, Social, Gouvernance)
+* s’assurer de la conformité du Métier aux réglementations en vigueur relatives à la finance durable en Europe
+* Vous serez le spécialiste local de la méthodologie extra-financière (relative aux critères ESG (Environnementaux, Sociaux et de Gouvernance)) couvrant l’ensemble des produits financiers de l’offre de Wealth Management à Luxembourg.
+* Vous contribuerez aux analyses à la structuration des données relatives au</t>
+        </is>
+      </c>
+      <c r="P78" s="6" t="inlineStr">
+        <is>
+          <t>* Capacité à collaborer / travail d’équipe
+* Rigueur
+* Etre orienté(e) résultats
+* Créativité &amp; Innovation / Capacité à résoudre des problèmes
+* Proactivité
+* Capacité d’analyse
+* Capacité à gérer un projet
+* Capacité à définir des indicateurs de performance pertinents
+* Analyse de données (PowerBI,</t>
+        </is>
+      </c>
+      <c r="Q78" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] Job title contains environmental terminology (Hydrogeologist), indicating relevance to environmental science and water management.</t>
         </is>
       </c>
       <c r="R78" s="2" t="inlineStr"/>
@@ -7510,19 +7560,19 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O79" s="2" t="inlineStr">
-        <is>
-          <t>Lead the delivery of SaaS programs focused on mandated regulatory reporting, non-financial disclosures, and sustainability reporting. Ensure alignment across product, engineering, implementation, and client/partner teams while meeting evolving regulatory requirements.</t>
-        </is>
-      </c>
-      <c r="P79" s="2" t="inlineStr">
-        <is>
-          <t>5+ years of experience in software development, project management, or related fields; strong understanding of regulatory reporting frameworks and XBRL standards; excellent communication and interpersonal skills.</t>
-        </is>
-      </c>
-      <c r="Q79" s="2" t="inlineStr">
-        <is>
-          <t>The financial sector, specifically regulatory compliance for banking and financial institutions, with a focus on ESG reporting and sustainability initiatives.</t>
+      <c r="O79" s="6" t="inlineStr">
+        <is>
+          <t>Lead the delivery of SaaS programs focused on mandated regulatory reporting, non-financial disclosures, and sustainability reporting. Ensure alignment across product, engineering, implementation, and client/partner teams while meeting evolving regulatory requirements. Drive end-to-end delivery of regulatory reporting solutions (e.g., compliance, ESG, non-financial reporting) Translate regulatory requirements into actionable program plans and product deliverables Align cross-functional teams (Pro</t>
+        </is>
+      </c>
+      <c r="P79" s="6" t="inlineStr">
+        <is>
+          <t>RegTech, financial reporting, ESG/sustainability reporting solutions, Agile delivery, release management, stakeholder management, data-driven products, reporting workflows</t>
+        </is>
+      </c>
+      <c r="Q79" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] The job description mentions ESG/sustainability reporting solutions, non-financial disclosures, and regulatory reporting, which are all relevant to environmental, social, and governance topics.</t>
         </is>
       </c>
       <c r="R79" s="2" t="inlineStr"/>
@@ -7587,19 +7637,19 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O80" s="2" t="inlineStr">
-        <is>
-          <t>This role supports the Risk Management Manager in defining methodologies, reporting, standards, and timelines for activities within the risk management of the Magis Group.</t>
-        </is>
-      </c>
-      <c r="P80" s="2" t="inlineStr">
-        <is>
-          <t>The ideal candidate has a master's degree in economics or scientific disciplines, an engineering background, statistics/mathematical sciences, familiarity with risk management economic-financial models, statistical data analysis methods (probabilistic VaR and PaR models), and software like R Project and Python.</t>
-        </is>
-      </c>
-      <c r="Q80" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on risk assessment within the energy sector, including ESG and climate change considerations, and business impact analysis.</t>
+      <c r="O80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nello specifico: si interfaccerà con i focal point all’interno delle società del Gruppo, costruirà modelli per la valutazione di specifici rischi aziendali, ne analizzerà i risultati definendo strategie di mitigazione e azioni correttive dei rischi identificati, e monitorandone il relativo piano di implementazione si interfaccerà con le funzioni Compliance e Internal Audit al fine di mappare, valutare e rappresentare all’Alta Direzione aziendale i rischi rilevanti del Gruppo si occuperà di risk </t>
+        </is>
+      </c>
+      <c r="P80" s="6" t="inlineStr">
+        <is>
+          <t>modelli di valutazione economica-finanziaria di risk management, metodologie statistiche di analisi dati (modelli probabilistici VaR e PaR), utilizzo di software di analisi quali R Project e Python, conoscenza del software MESA_Procomp, orientamento quantitativo, capacità di sintesi e analisi dei fe</t>
+        </is>
+      </c>
+      <c r="Q80" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions risk assessment integrato (ERM- Enterprise Risk Management) with reference to ESG and climate change, which indicates a focus on climate risk management.</t>
         </is>
       </c>
       <c r="R80" s="2" t="inlineStr"/>
@@ -7664,19 +7714,19 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O81" s="2" t="inlineStr">
-        <is>
-          <t>This role involves analyzing and planning risk management activities for UniCredit Leasing SpA. You will be involved in reviewing credit processes and supporting strategic planning initiatives.</t>
-        </is>
-      </c>
-      <c r="P81" s="2" t="inlineStr">
-        <is>
-          <t>The ideal candidate possesses strong analytical skills, a structured approach, and problem-solving abilities. Excellent communication and interpersonal skills are also essential.</t>
-        </is>
-      </c>
-      <c r="Q81" s="2" t="inlineStr">
-        <is>
-          <t>This role is within the financial services industry, specifically focusing on leasing activities and risk management for sustainable business practices.</t>
+      <c r="O81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sarai inserito nel department Risk Management &amp; Policies a riporto del responsabile del team ed avrai un ruolo primario in tutte le attività di analisi e pianificazione in ambito risk management e di progettualità strategiche come la revisione dei processi del credito di Unicredit Leasing SpA. In questo ruolo ti occuperai di svolgere le attività finalizzate a: garantire l’attività di controllo e misurazione dei rischi di credito, dei rischi C&amp;E (Climate &amp; Environmental), dei rischi di liquidità </t>
+        </is>
+      </c>
+      <c r="P81" s="6" t="inlineStr">
+        <is>
+          <t>Forte attitudine analitica, approccio strutturato e orientamento alla risoluzione di problemi complesse Ottime capacità relazionali, comunicative e predisposizione al lavoro in team sia in remoto che in presenza Flessibilità, spirito di iniziativa e desiderio di apprendere in un contesto multidiscip</t>
+        </is>
+      </c>
+      <c r="Q81" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions 'rischi C&amp;E (Climate &amp; Environmental)' which indicates that the role involves climate-related risk management, making it a good fit for the climate_risk profile.</t>
         </is>
       </c>
       <c r="R81" s="2" t="inlineStr"/>
@@ -7741,19 +7791,19 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O82" s="2" t="inlineStr">
-        <is>
-          <t>A Junior Sustainability Analyst will contribute to Deloitte Climate &amp; Sustainability's efforts in helping clients navigate social and environmental change.</t>
-        </is>
-      </c>
-      <c r="P82" s="2" t="inlineStr">
-        <is>
-          <t>A candidate should have a bachelor's degree, knowledge of climate change mitigation methods, financial analysis tools, and data analysis software (R/Python, SAS, Qlik, SQL, PowerBI).</t>
-        </is>
-      </c>
-      <c r="Q82" s="2" t="inlineStr">
-        <is>
-          <t>This role is within the sustainability consulting field, focusing on climate change mitigation and ESG frameworks.</t>
+      <c r="O82" s="6" t="inlineStr">
+        <is>
+          <t>Stiamo cercando una figura junior da inserire nel team di Deloitte Climate &amp; Sustainability nella sede di Milano e Roma, che lavorerà in modalità Hybrid DC&amp;S è un'entità autonoma totalmente impegnata ad aiutare i clienti ad indirizzare il cambiamento sociale e promuovere la sostenibilità. Lavorando in modi innovativi e collaborando con le organizzazioni più accreditate, stiamo progettando e fornendo soluzioni che contribuiscono ad un futuro sostenibile e prospero per tutti.</t>
+        </is>
+      </c>
+      <c r="P82" s="6" t="inlineStr">
+        <is>
+          <t>Conoscenza del quadro internazionale di mitigazione e adattamento ai cambiamenti climatici e metodi e strumenti di analisi finanziaria; Conoscenza dei framework di sostenibilità (es. SFDR, Taxonomy Regulation, ECB aspettative, CSR, DNF, PRI ecc.); Competenza tecnica nell'analisi dei dati e dei softw</t>
+        </is>
+      </c>
+      <c r="Q82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[general_esg] The job description mentions working in the Climate &amp; Sustainability team, promoting sustainability, and having knowledge of sustainability frameworks (SFDR, Taxonomy Regulation, CSR, etc.) and international sustainability indices (TCFD, GRI, CDP, SBTi, etc.), which are all related to </t>
         </is>
       </c>
       <c r="R82" s="2" t="inlineStr"/>
@@ -7830,19 +7880,19 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O83" s="2" t="inlineStr">
-        <is>
-          <t>This role involves leading a team of professionals in designing and delivering inclusive sport and recreation spaces for the growing community of Kingston.</t>
-        </is>
-      </c>
-      <c r="P83" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should possess extensive experience coordinating teams, managing budgets, and delivering complex capital works projects with proven stakeholder engagement skills.</t>
-        </is>
-      </c>
-      <c r="Q83" s="2" t="inlineStr">
-        <is>
-          <t>The role contributes to the development of sustainable and accessible infrastructure that supports community wellbeing and aligns with climate change goals.</t>
+      <c r="O83" s="6" t="inlineStr">
+        <is>
+          <t>Manage the design and delivery of inclusive sport and recreation spaces in Kingston, Help shape sustainable spaces for a growing community, Provide expert leadership and direction across the planning, design and delivery of Council’s active leisure, sport and recreation projects, Oversee a multidisciplinary team to translate Kingston’s strategic targets and community aspirations into inclusive, sustainable and financially responsible infrastructure, Guide projects from concept to completion, ens</t>
+        </is>
+      </c>
+      <c r="P83" s="6" t="inlineStr">
+        <is>
+          <t>Leadership, project management, stakeholder engagement, communication, problem solving, budget management, risk management, governance, sustainability, accessibility, universal design, asset planning, team management</t>
+        </is>
+      </c>
+      <c r="Q83" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions 'sustainable spaces', 'sustainability', and 'environment' in the context of sport and recreation spaces, which aligns with the clean energy adjacent profile, The role also involves managing projects related to sport and recreation facilities, play</t>
         </is>
       </c>
       <c r="R83" s="2" t="inlineStr">
@@ -7919,19 +7969,19 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O84" s="2" t="inlineStr">
-        <is>
-          <t>Join ONEtoONE's global network to scale your M&amp;A practice and leverage a world-class infrastructure. You will connect with international strategic buyers and advise on high-value exits for Danish SaaS and BioTech assets.</t>
-        </is>
-      </c>
-      <c r="P84" s="2" t="inlineStr">
-        <is>
-          <t>Requires 10+ years of experience in Corporate Finance, strong deal structuring skills, and proven track record in M&amp;A transactions. Experience with ESG reporting and data analysis is a plus.</t>
-        </is>
-      </c>
-      <c r="Q84" s="2" t="inlineStr">
-        <is>
-          <t>The role connects to the Danish sustainable innovation ecosystem, focusing on Energy Transition, Digital Health, and Advanced Manufacturing.</t>
+      <c r="O84" s="6" t="inlineStr">
+        <is>
+          <t>Elevate your advisory firm by joining the world’s premier international M&amp;A network. Connect with over 150 advisors in 80+ cities. Maintain your independence while gaining the prestige of a global brand that connects Copenhagen to financial hubs in New York, Singapore, and Zurich. Use our proprietary AI technology to bridge the gap between Danish "Sustainability Leaders" and international strategic buyers with surgical precision.</t>
+        </is>
+      </c>
+      <c r="P84" s="6" t="inlineStr">
+        <is>
+          <t>Corporate Finance, Investment Banking, Senior "Big Four" Transaction Advisory, Life Sciences, Renewable Energy/Power-to-X, Robotics, or FoodTech, AI technology, ESG reporting, financial modeling, data analysis</t>
+        </is>
+      </c>
+      <c r="Q84" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions Renewable Energy/Power-to-X, Life Sciences, and other sectors related to environmental sustainability, which aligns with the clean energy adjacent profile.</t>
         </is>
       </c>
       <c r="R84" s="2" t="inlineStr">
@@ -8012,19 +8062,19 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O85" s="2" t="inlineStr">
-        <is>
-          <t>An individual contributor will analyze balance sheet and income statement data to develop projections for capital adequacy under various economic stress scenarios.</t>
-        </is>
-      </c>
-      <c r="P85" s="2" t="inlineStr">
-        <is>
-          <t>Requires strong analytical skills, experience with financial modeling, and proficiency in data extraction and analysis tools.</t>
-        </is>
-      </c>
-      <c r="Q85" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on the financial risk management of a global banking institution, contributing to capital adequacy assessment and regulatory compliance.</t>
+      <c r="O85" s="6" t="inlineStr">
+        <is>
+          <t>Deliver on the Balance Sheet &amp; Income Statement projections for the Enterprise-wide Stress Testing (EWST) exercises, Carry out the movement analysis &amp; narratives for BS/PnL metrics, Carry out analysis on Capital numbers including CET1, Total capital and compare against Basel and reg requirements, Ensure compliance to EWST procedures, methodologies, and controls, Manage all governance related aspects of the execution of stress testing, Drive process improvements and best practices for more effici</t>
+        </is>
+      </c>
+      <c r="P85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exceptional written / verbal communication skills, Flexible and adaptable; able to work in ambiguous situations independently, Display a methodical &amp; meticulous approach to problem solving and root cause analysis, Be a team player and able to work collaboratively with others, Knowledge of Python or </t>
+        </is>
+      </c>
+      <c r="Q85" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions 'Climate Risk Stress Tests: A new area of analysis focussing on the impact of climate change on Banking industry', which indicates that the role is related to climate risk and its impact on the banking industry.</t>
         </is>
       </c>
       <c r="R85" s="2" t="inlineStr">
@@ -8101,19 +8151,19 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O86" s="2" t="inlineStr">
-        <is>
-          <t>Develop and improve catastrophe models for the insurance and reinsurance industries by applying statistical analysis and atmospheric expertise.</t>
-        </is>
-      </c>
-      <c r="P86" s="2" t="inlineStr">
-        <is>
-          <t>Expertise in spatial statistics, extreme value analysis, atmospheric dynamics, and dynamic downscaling methods.</t>
-        </is>
-      </c>
-      <c r="Q86" s="2" t="inlineStr">
-        <is>
-          <t>The role contributes to climate-informed risk management decisions in the insurance and reinsurance sectors.</t>
+      <c r="O86" s="6" t="inlineStr">
+        <is>
+          <t>Improve the accuracy of representing atmospheric perils, Contribute to model development, validation, and productization for global clients, Support model development using observational and reanalysis products, GCMs, and high-resolution simulations</t>
+        </is>
+      </c>
+      <c r="P86" s="6" t="inlineStr">
+        <is>
+          <t>Proficiency in Python, Clear written and verbal communication, Practical, solution-focused mindset</t>
+        </is>
+      </c>
+      <c r="Q86" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions developing catastrophe models for extreme weather events, simulating the full distribution of possible events consistent with a changing climate, and improving the accuracy of representing atmospheric perils, which are all related to climate risk.</t>
         </is>
       </c>
       <c r="R86" s="2" t="inlineStr">
@@ -8190,19 +8240,19 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O87" s="2" t="inlineStr">
-        <is>
-          <t>Validates advanced IRB and Foundation IRB models for credit risk, including model methodologies, assumptions, and performance.</t>
-        </is>
-      </c>
-      <c r="P87" s="2" t="inlineStr">
-        <is>
-          <t>Requires expertise in wholesale lending products, stress testing frameworks, regulatory interactions, and quantitative modeling techniques.</t>
-        </is>
-      </c>
-      <c r="Q87" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on financial risk management within the banking and finance sector, with a focus on climate-related risks and sustainability.</t>
+      <c r="O87" s="6" t="inlineStr">
+        <is>
+          <t>Perform independent validation of Advanced IRB / Foundation IRB models including: PD, LGD, EAD, and CCF modelling methodologies, Rating system design and performance, RWA attribution and capital impact assessment, Assess model methodologies and assumptions for diverse wholesale product exposures, Evaluate model conceptual soundness, data representativeness, risk differentiation, and calibration methodology, Review and challenge: Model segmentation, overrides, downturn calibration, and economic c</t>
+        </is>
+      </c>
+      <c r="P87" s="6" t="inlineStr">
+        <is>
+          <t>Experience with Corporate lending, project finance, commercial real estate, private equity exposures, Stress testing frameworks (CCAR/ICAAP) and IRB-to-IFRS 9 model linkages, Regulatory interactions with PRA, ECB, Fed/OCC, OSFI, etc., Ability to articulate quantitative findings to non-technical seni</t>
+        </is>
+      </c>
+      <c r="Q87" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions Climate Risk Modelling experience, which is a key aspect of climate risk management, and the role involves validating IRB models that consider environmental policies, indicating a focus on climate-related risks.</t>
         </is>
       </c>
       <c r="R87" s="2" t="inlineStr"/>
@@ -8279,19 +8329,19 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O88" s="2" t="inlineStr">
-        <is>
-          <t>A Site Construction &amp; EHS Manager is needed to oversee remediation and excavation activities, ensuring safe and compliant execution on-site.</t>
-        </is>
-      </c>
-      <c r="P88" s="2" t="inlineStr">
-        <is>
-          <t>A Master's degree in civil or environmental engineering, at least 5-8 years of relevant experience in construction/remediation projects, and knowledge of Belgian EHS regulations are required.</t>
-        </is>
-      </c>
-      <c r="Q88" s="2" t="inlineStr">
-        <is>
-          <t>This role is within the environmental consulting industry, focusing on site remediation and compliance with Belgian EHS legislation.</t>
+      <c r="O88" s="6" t="inlineStr">
+        <is>
+          <t>Your role: We are seeking a Site Construction &amp; EHS Manager for a remediation project in Charleroi. This role combines environmental remediation execution with EHS (Environment, Health &amp; Safety) management on-site. You will be responsible for managing the progress of the site work activities ensuring the safe and compliant execution of remediation activities, coordinating with contractors, and maintaining high standards of environmental and safety performance. Key Responsibilities: Oversee and c</t>
+        </is>
+      </c>
+      <c r="P88" s="6" t="inlineStr">
+        <is>
+          <t>Strong skills in site coordination, documentation, and progress tracking, Experience in waste management, Proactive, solution-oriented, and committed to project ownership, Strong communication skills and collaborative mindset, Fluent in English and proficient in French</t>
+        </is>
+      </c>
+      <c r="Q88" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions environmental remediation, excavation, waste management, and site remediation, which are related to environmental science and conservation, fitting the clean_energy_adjacent profile.</t>
         </is>
       </c>
       <c r="R88" s="2" t="inlineStr">
@@ -8372,19 +8422,19 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O89" s="2" t="inlineStr">
-        <is>
-          <t>The Senior Specialist Data Management role involves leading the definition of data requirements, controls, and governance to ensure high-quality customer and identity data for digital-first selling, self-service, automation, and AI.</t>
-        </is>
-      </c>
-      <c r="P89" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have a strong understanding of data management principles, experience in defining data requirements, and expertise in data analytics and business insights.</t>
-        </is>
-      </c>
-      <c r="Q89" s="2" t="inlineStr">
-        <is>
-          <t>This role is within the telecommunications industry, focusing on ensuring customer and identity data quality for digital transformation initiatives.</t>
+      <c r="O89" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As a Senior Specialist, Data Management, you will play a critical role in ensuring Telstra Enterprise and TB-MM have trusted, well-governed customer and identity data that enables digital-first selling, customer self-service, automation and AI at scale. You will lead the definition of data requirements, controls and governance that underpin high-quality customer and identity data across platforms. This includes assessing data readiness and risk early, translating complex data and identity needs </t>
+        </is>
+      </c>
+      <c r="P89" s="6" t="inlineStr">
+        <is>
+          <t>A practical, outcomes-focused approach, with experience driving exception-only remediation and automation to address root causes and reduce recurring data issues. A strong understanding of enterprise systems and application interconnectedness, including how data flows end-to-end and how changes impa</t>
+        </is>
+      </c>
+      <c r="Q89" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[general_esg] The job description mentions working in the Climate &amp; Sustainability team, promoting sustainability, and having knowledge of sustainability frameworks (SFDR, Taxonomy Regulation, CSR, etc.) and international sustainability indices (TCFD, GRI, CDP, SBTi, etc.), which are all related to </t>
         </is>
       </c>
       <c r="R89" s="2" t="inlineStr">
@@ -8465,19 +8515,19 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O90" s="2" t="inlineStr">
-        <is>
-          <t>This role involves fieldwork and data collection for contaminated land assessment, environmental monitoring, and remediation consulting across various industries.</t>
-        </is>
-      </c>
-      <c r="P90" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have experience in environmental science or engineering, field sampling techniques, and data analysis skills.</t>
-        </is>
-      </c>
-      <c r="Q90" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on environmental impact management within the oil and gas, mining, defense, and public sectors.</t>
+      <c r="O90" s="6" t="inlineStr">
+        <is>
+          <t>Working as part of our established Geoscience and Remediation Services (GRS) team, you will collaborate with a team of environmental engineers, scientists, hydrogeologists and geologists to provide contaminated land assessment, environmental monitoring, and remediation consulting across a wide range of projects, including those in the oil and gas, mining, Department of Defence, and public sectors. The substantive role involves working on challenging projects across various industries, with a pri</t>
+        </is>
+      </c>
+      <c r="P90" s="6" t="inlineStr">
+        <is>
+          <t>Strong communication and teamwork skills, proactive and adaptable mindset, commitment to professionalism and integrity, willingness to undertake fieldwork, ability to obtain Defence security clearance</t>
+        </is>
+      </c>
+      <c r="Q90" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions environmental science, contaminated land assessment, environmental monitoring, and remediation consulting, which are related to environmental science and conservation, fitting the clean_energy_adjacent profile.</t>
         </is>
       </c>
       <c r="R90" s="2" t="inlineStr">
@@ -8558,19 +8608,19 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O91" s="2" t="inlineStr">
-        <is>
-          <t>This role involves fieldwork and data collection for contaminated land assessment, environmental monitoring, and remediation consulting across various industries.</t>
-        </is>
-      </c>
-      <c r="P91" s="2" t="inlineStr">
-        <is>
-          <t>Required qualifications include a Bachelor's degree in Environmental Science or related field, experience with fieldwork techniques, and strong analytical skills.</t>
-        </is>
-      </c>
-      <c r="Q91" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on environmental impact management within the oil and gas, mining, defense, and public sectors, contributing to climate change mitigation and sustainability efforts.</t>
+      <c r="O91" s="6" t="inlineStr">
+        <is>
+          <t>Working as part of our established Geoscience and Remediation Services (GRS) team, you will collaborate with a team of environmental engineers, scientists, hydrogeologists and geologists to provide contaminated land assessment, environmental monitoring, and remediation consulting across a wide range of projects, including those in the oil and gas, mining, Department of Defence, and public sectors. The substantive role involves working on challenging projects across various industries, with a pri</t>
+        </is>
+      </c>
+      <c r="P91" s="6" t="inlineStr">
+        <is>
+          <t>Strong communication and teamwork skills, proactive and adaptable mindset, commitment to professionalism and integrity, Bachelor’s or Postgraduate degree in Environmental Science / Engineering, Hydrogeology, Geology, Geoscience</t>
+        </is>
+      </c>
+      <c r="Q91" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions environmental science, contaminated land assessment, environmental monitoring, and remediation consulting, which are related to environmental science and conservation, fitting the clean_energy_adjacent profile.</t>
         </is>
       </c>
       <c r="R91" s="2" t="inlineStr">
@@ -8651,19 +8701,19 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O92" s="2" t="inlineStr">
-        <is>
-          <t>Develop and support the execution of BII's five-year forward strategy, including major organizational growth initiatives.</t>
-        </is>
-      </c>
-      <c r="P92" s="2" t="inlineStr">
-        <is>
-          <t>Strong strategic planning skills, experience in corporate strategy development and implementation, excellent communication and presentation skills.</t>
-        </is>
-      </c>
-      <c r="Q92" s="2" t="inlineStr">
-        <is>
-          <t>Development finance institution focused on sustainable and inclusive economic growth in developing markets.</t>
+      <c r="O92" s="6" t="inlineStr">
+        <is>
+          <t>The Corporate Strategy team works at the centre of BII, reporting to the CEO and working directly with the CEO and Board. Its principal responsibility is to develop and support the execution of our five-year strategy. Within that, it has three main responsibilities: Strategic direction, Corporate planning and performance, and Business improvement. The team also provides direct support to the Chief Executive Officer and BII’s Board, acting as a CEO’s Office.</t>
+        </is>
+      </c>
+      <c r="P92" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Excellent quantitative skills, including the ability to identify and interpret data, carry out data analysis, and present findings in a visually compelling way; experience of building and running three-statement financial models; excellent written and presentational skills, including the ability to </t>
+        </is>
+      </c>
+      <c r="Q92" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions experience in sustainable finance, including climate, development, and/or nature finance, and the company's mission is to address global development challenges through strategic investments that promote sustainable and inclusive economic growth.</t>
         </is>
       </c>
       <c r="R92" s="2" t="inlineStr">
@@ -8744,19 +8794,19 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O93" s="2" t="inlineStr">
-        <is>
-          <t>This ESG, Impact, Knowledge (EIK) Intern role provides hands-on experience in emerging market impact investments at Triple Jump.  The intern will assist the EIK team on operational areas related to technical assistance projects.</t>
-        </is>
-      </c>
-      <c r="P93" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have a passion for sustainable development and impact investing with relevant academic background or work experience.</t>
-        </is>
-      </c>
-      <c r="Q93" s="2" t="inlineStr">
-        <is>
-          <t>This role connects to climate, ESG, sustainability, and finance by supporting the implementation of impactful investments that address social and environmental challenges in developing countries.</t>
+      <c r="O93" s="6" t="inlineStr">
+        <is>
+          <t>Assist the EIK team on operational areas, such as: Assisting with the initiation, development, and implementation of Technical Assistance (TA) projects. Supporting contracting processes with TA beneficiaries and consultants, including Know Your Customer (KYC) procedures. Assisting in managing procurements of consultants that execute TA projects and ensuring compliance with procurement procedures. Supporting portfolio and/or program management across different business lines and mandates. Contrib</t>
+        </is>
+      </c>
+      <c r="P93" s="6" t="inlineStr">
+        <is>
+          <t>Strong attention to detail and organizational skills. Excellent communication skills, both written and verbal. Proficiency in Microsoft Office Suite (Word, Excel, PowerPoint). Ability to work collaboratively in a multicultural and diverse team environment.</t>
+        </is>
+      </c>
+      <c r="Q93" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions impact investing, ESG, and sustainable development, which are key concepts in sustainable finance. The company's mission and values also align with sustainable finance principles.</t>
         </is>
       </c>
       <c r="R93" s="2" t="inlineStr">
@@ -8833,19 +8883,19 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O94" s="2" t="inlineStr">
-        <is>
-          <t>This role supports the execution of sustainable financing solutions, advising on transactions and providing market expertise to foster a greener economy.</t>
-        </is>
-      </c>
-      <c r="P94" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have 3-4 years of experience in financial analysis and advisory, fluency in English (both oral and written), and knowledge of financial markets, sustainable finance, and ESG integration.</t>
-        </is>
-      </c>
-      <c r="Q94" s="2" t="inlineStr">
-        <is>
-          <t>This role works within the financial industry, specifically focusing on sustainable financing solutions to support a transition towards a greener economy.</t>
+      <c r="O94" s="6" t="inlineStr">
+        <is>
+          <t>As a core function, this team executes sustainable financing solutions aligned with evolving ESG standards and market trends. Execution support - intermediate structuring experience, with a growing level of autonomy. Be responsible of specific tasks for the execution of Sustainable Loan and Bond transactions, under the supervision of a senior team members but with a growing level of autonomy. Advise on transaction execution, by framing, designing and supporting the delivery of sustainable financ</t>
+        </is>
+      </c>
+      <c r="P94" s="6" t="inlineStr">
+        <is>
+          <t>Proficient in Office (Excel, PowerPoint). Proficient in Bloomberg. Knowledge in: Financial markets - Structuring; Sustainable Finance &amp; Corporate Social Responsibility - Integration of ESG challenges; Sustainable Finance &amp; Corporate Social Responsibility - Transition towards Low Carbon Economy; Data</t>
+        </is>
+      </c>
+      <c r="Q94" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions 'sustainable financing solutions', 'sustainable finance', 'ESG standards', 'sustainable loan and bond transactions', and 'transition to a greener economy', which are all related to sustainable finance and ESG investing.</t>
         </is>
       </c>
       <c r="R94" s="2" t="inlineStr">
@@ -8930,19 +8980,19 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O95" s="2" t="inlineStr">
-        <is>
-          <t>Executes sustainable finance mandates, advises on ESG strategy, and provides market expertise to clients within BNP Paribas CIB's Sustainable Capital Markets Execution team.</t>
-        </is>
-      </c>
-      <c r="P95" s="2" t="inlineStr">
-        <is>
-          <t>Requires experience in sustainable finance execution, strong analytical skills, knowledge of ESG frameworks, and proficiency with data analysis tools like Dealogic and Bloomberg.</t>
-        </is>
-      </c>
-      <c r="Q95" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to the financial industry's transition towards a greener economy by supporting the development and implementation of sustainable financing instruments.</t>
+      <c r="O95" s="6" t="inlineStr">
+        <is>
+          <t>Execution support, advise on and oversee transaction execution, perform analysis of the ESG profile and strategy of issuers/borrowers, prepare high-quality presentations, keep abreast of key sustainable finance market developments, identify and implement innovative solutions, deepen knowledge on sustainable financing, collect and analyze data, maintain open communication with team members, support junior members, raise awareness on sustainable finance, oversee systematic follow-ups on action poi</t>
+        </is>
+      </c>
+      <c r="P95" s="6" t="inlineStr">
+        <is>
+          <t>Financial markets, sustainable finance, corporate social responsibility, data business analytics, investment and wholesale banking, debt capital market, bonds, loans, office (Excel, PowerPoint)</t>
+        </is>
+      </c>
+      <c r="Q95" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions sustainable finance, ESG standards, green economy, and sustainable financing solutions, which are all key aspects of sustainable finance</t>
         </is>
       </c>
       <c r="R95" s="2" t="inlineStr">
@@ -9027,19 +9077,19 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O96" s="2" t="inlineStr">
-        <is>
-          <t>Develop sophisticated internal ratings systems and credit risk models to quantify borrower and facility risk for lending and investment decisions.</t>
-        </is>
-      </c>
-      <c r="P96" s="2" t="inlineStr">
-        <is>
-          <t>Expertise in IRB modeling, counterparty credit risk analysis, and stress testing techniques is required.</t>
-        </is>
-      </c>
-      <c r="Q96" s="2" t="inlineStr">
-        <is>
-          <t>The role contributes to the financial services industry by assessing creditworthiness and managing risk exposure within a global financial institution.</t>
+      <c r="O96" s="6" t="inlineStr">
+        <is>
+          <t>Manage and mentor a diverse team of credit risk analytics professionals, fostering a culture of excellence and innovation. Provide direction and oversight across specialized functions including IRB modeling, counterparty credit risk analytics and credit stress testing/provisioning. Develop team members' skills and careers, and promote an inclusive, collaborative environment. Drive the strategic development of the Firms credit risk measurement methodologies. Set the vision for next-generation cre</t>
+        </is>
+      </c>
+      <c r="P96" s="6" t="inlineStr">
+        <is>
+          <t>Deep understanding of credit risk modelling and quantitative techniques. Expert knowledge of probability of default (PD), loss given default (LGD), and exposure at default (EAD) modeling, credit scoring methodologies, and portfolio credit risk concepts.</t>
+        </is>
+      </c>
+      <c r="Q96" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions 'Climate Risk Stress Tests: A new area of analysis focussing on the impact of climate change on Banking industry', which indicates that the role is related to climate risk and its impact on the banking industry.</t>
         </is>
       </c>
       <c r="R96" s="2" t="inlineStr">
@@ -9116,19 +9166,19 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O97" s="2" t="inlineStr">
-        <is>
-          <t>Leads a team of consultants and analysts to deliver risk management solutions to financial institutions in the Middle East and North Africa.</t>
-        </is>
-      </c>
-      <c r="P97" s="2" t="inlineStr">
-        <is>
-          <t>Requires strong project management skills, deep technical expertise in credit risk management, and experience with financial products and regulatory frameworks.</t>
-        </is>
-      </c>
-      <c r="Q97" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on financial services risk management within the banking book portfolios of clients in the MENA region, contributing to climate-related initiatives and ESG compliance.</t>
+      <c r="O97" s="6" t="inlineStr">
+        <is>
+          <t>Lead a team of 5-6 Senior consultants, analysts for engagement execution and delivery. Showcase exceptional project management abilities and foster a collaborative environment and accountability among team members on engagements. Demonstrate deep technical expertise and industry knowledge, particularly in financial products with a focus on lending solutions. Design, assessment, and benchmarking of financial risk management policies, frameworks, methodologies covering a range of risk domains such</t>
+        </is>
+      </c>
+      <c r="P97" s="6" t="inlineStr">
+        <is>
+          <t>Advanced technical skills, with proficiency in Python, SAS, SQL, R, and Excel. Excellent Oral and written communication and presentation skills. Strong documentation skills, with the ability to quickly grasp complex concepts and present them clearly in documents or presentations. Strong multi-taskin</t>
+        </is>
+      </c>
+      <c r="Q97" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions climate risk, stress testing, and regulatory risk, which are relevant to the climate risk profile. Additionally, the job requires experience in climatic risk space, preferably in the areas of stress testing/scenario designing, which further supports the cl</t>
         </is>
       </c>
       <c r="R97" s="2" t="inlineStr"/>
@@ -9201,19 +9251,19 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O98" s="2" t="inlineStr">
-        <is>
-          <t>Financial Markets Advisor provides data-driven analysis and insights to clients on complex financial issues, including stress testing, portfolio unwinding, and climate risk.</t>
-        </is>
-      </c>
-      <c r="P98" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should possess strong analytical skills, experience in financial markets, and proficiency in data analytics tools like Aladdin.</t>
-        </is>
-      </c>
-      <c r="Q98" s="2" t="inlineStr">
-        <is>
-          <t>Financial Markets Advisory supports clients in navigating the complexities of financial markets, with a focus on sustainability and ESG considerations.</t>
+      <c r="O98" s="6" t="inlineStr">
+        <is>
+          <t>Team members work on a diverse set of client engagements as part of multi-disciplinary project teams, encompassing subject matter authorities, engagement managers, and others. In this role you will develop and use data and analytical skills to create, review, and deliver analyses to clients, frequently using BlackRock proprietary technology platforms. Candidates must be interested in financial markets and be able to apply creative solutions to solve client objectives and challenges. Team members</t>
+        </is>
+      </c>
+      <c r="P98" s="6" t="inlineStr">
+        <is>
+          <t>Programming skills in Python and SQL preferred; familiarity with scripting, databases, modeling, and visualization tools is a plus. Strong PowerPoint presentation skills and very good communication abilities. Proven ability to manage stakeholders effectively across functions and geographies.</t>
+        </is>
+      </c>
+      <c r="Q98" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions 'climate risk analytics and advisory' as one of the areas of support, indicating that the role involves working with climate-related risks, which aligns with the climate_risk profile.</t>
         </is>
       </c>
       <c r="R98" s="2" t="inlineStr"/>
@@ -9294,9 +9344,9 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O99" s="2" t="inlineStr">
-        <is>
-          <t>Oversees enterprise-wide risk assessment, management, and credit risk for a financial institution.</t>
+      <c r="O99" s="6" t="inlineStr">
+        <is>
+          <t>Major Roles &amp; Responsibilities: a. Oversight of Enterprise-wide Risk assessment and management, b. Credit Risk Management, c. Operational Risk Management, c. Market and Liquidity Risk, d. Risk Analysis and Stress Testing, e. Emerging Risks, f. Regulatory and Governance, g. Team Leadership, h. Key Deliverables</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -9304,9 +9354,9 @@
           <t>Requires expertise in risk management frameworks, regulatory compliance, and analytical skills.</t>
         </is>
       </c>
-      <c r="Q99" s="2" t="inlineStr">
-        <is>
-          <t>The role is within the finance industry, focusing on managing risks related to credit, operational, market, and liquidity.</t>
+      <c r="Q99" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions 'climate risks' under the 'Emerging Risks' section, indicating that the role involves identifying, measuring, and monitoring climate-related risks.</t>
         </is>
       </c>
       <c r="R99" s="2" t="inlineStr">
@@ -9391,19 +9441,19 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O100" s="2" t="inlineStr">
-        <is>
-          <t>This role involves leading a team of consultants and analysts to develop and implement risk management strategies for financial institutions.</t>
-        </is>
-      </c>
-      <c r="P100" s="2" t="inlineStr">
-        <is>
-          <t>Requires strong technical expertise in financial products, particularly lending solutions, along with experience managing teams and delivering high-quality projects.</t>
-        </is>
-      </c>
-      <c r="Q100" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on credit risk management within the financial services sector, addressing climate risk and sustainability concerns in a global context.</t>
+      <c r="O100" s="6" t="inlineStr">
+        <is>
+          <t>Lead a team of 5-6 Senior consultants, analysts for engagement execution and delivery. Showcase exceptional project management abilities and foster a collaborative environment and accountability among team members on engagements. Demonstrate deep technical expertise and industry knowledge, particularly in financial products with a focus on lending solutions. Design, assessment, and benchmarking of financial risk management policies, frameworks, methodologies covering a range of risk domains such</t>
+        </is>
+      </c>
+      <c r="P100" s="6" t="inlineStr">
+        <is>
+          <t>Advanced technical skills, with proficiency in Python, SAS, SQL, R, and Excel. Excellent Oral and written communication and presentation skills. Strong documentation skills, with the ability to quickly grasp complex concepts and present them clearly in documents or presentations. Strong multi-taskin</t>
+        </is>
+      </c>
+      <c r="Q100" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions climate risk, stress testing, and scenario designing, which are relevant to climate risk management. Additionally, the job requires experience in climatic risk space, which further supports the classification as climate_risk.</t>
         </is>
       </c>
       <c r="R100" s="2" t="inlineStr">
@@ -9488,19 +9538,19 @@
           <t>Keyword (5)</t>
         </is>
       </c>
-      <c r="O101" s="2" t="inlineStr">
-        <is>
-          <t>Analyze ESG data, provide insights to investors and decision-makers, and deliver high-quality advisory services on ESG reporting, sustainability strategy, and risk management.</t>
-        </is>
-      </c>
-      <c r="P101" s="2" t="inlineStr">
-        <is>
-          <t>Master's degree in environmental engineering or sustainability with additional certifications, proficiency in quantitative and qualitative data analysis, excellent organizational skills, and strong communication skills.</t>
-        </is>
-      </c>
-      <c r="Q101" s="2" t="inlineStr">
-        <is>
-          <t>ESG consulting within the financial services industry, focusing on climate change, sustainable finance, and corporate social responsibility.</t>
+      <c r="O101" s="6" t="inlineStr">
+        <is>
+          <t>Collaborate with the global team and clients to analyze ESG data, providing valuable insights to investors and decision-makers. Conduct comprehensive ESG Rating assessments, Gap Analyses, ESG Due Diligence, EU Taxonomy, CSRD assessments, SFDR Compliance, Sustainability-linked loan assessments, and develop Carbon Footprint strategy reports. Utilize deep expertise in ESG and sustainability to deliver high-quality advisory services on ESG reporting, sustainability strategy, and risk management. Sta</t>
+        </is>
+      </c>
+      <c r="P101" s="6" t="inlineStr">
+        <is>
+          <t>Proficiency in quantitative and qualitative data collection, analysis, and reporting. Exceptional organizational skills with keen attention to detail. Excellent interpersonal skills with the ability to communicate and influence internal and external stakeholders, including proficiency in video confe</t>
+        </is>
+      </c>
+      <c r="Q101" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[general_esg] The job description mentions ESG ratings, ESG reporting, sustainability strategy, and risk management, which are all key aspects of general ESG. Additionally, the job requires expertise in ESG and sustainability, and involves working with ESG data and standards, further supporting the </t>
         </is>
       </c>
       <c r="R101" s="2" t="inlineStr">
@@ -9569,19 +9619,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O102" s="2" t="inlineStr">
-        <is>
-          <t>A consultant will support clients in the financial sector with ESG strategy implementation, regulatory compliance, and sustainability integration.</t>
-        </is>
-      </c>
-      <c r="P102" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have a Master's degree, at least 3 years of experience in environmental impact assessment or DNSH verification, strong English and/or French language skills, and expertise in regional development programs.</t>
-        </is>
-      </c>
-      <c r="Q102" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on sustainable finance within the financial sector, supporting companies in implementing ESG strategies and aligning business models with sustainability goals.</t>
+      <c r="O102" s="6" t="inlineStr">
+        <is>
+          <t>La risorsa Experienced sarà inserita in un team di lavoro, affiancando colleghi senior e occupandosi di: Supporto tecnico-specialistico allo svolgimento delle attività di controllo e verifica relativamente alle operazioni poste in essere in attuazione dei programmi regionali finanziati a livello europeo, aventi l’obiettivo di rafforzare la competitività, l'innovazione, la transizione ecologica e digitale, la mobilità sostenibile, l'istruzione e l'inclusione sociale, riducendo i divari territoria</t>
+        </is>
+      </c>
+      <c r="P102" s="6" t="inlineStr">
+        <is>
+          <t>A practical, outcomes-focused approach, with experience driving exception-only remediation and automation to address root causes and reduce recurring data issues. A strong understanding of enterprise systems and application interconnectedness, including how data flows end-to-end and how changes impa</t>
+        </is>
+      </c>
+      <c r="Q102" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions 'Sustainable Finance' team, 'strategie ESG', 'conformità normativa', 'integrazione dei fattori di sostenibilità', and 'evoluzione sostenibile del settore finanziario', which are all related to sustainable finance and ESG investing.</t>
         </is>
       </c>
       <c r="R102" s="2" t="inlineStr"/>
@@ -9646,19 +9696,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O103" s="2" t="inlineStr">
-        <is>
-          <t>You will support top management of clients in achieving strategic business objectives through enterprise risk management (ERM) and project risk management (PRM).</t>
-        </is>
-      </c>
-      <c r="P103" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have a bachelor's degree or recent graduate with analytical skills, problem-solving abilities, and experience with Microsoft Office.</t>
-        </is>
-      </c>
-      <c r="Q103" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on Enterprise Risk Management within the corporate and large corporate sectors of industries such as infrastructure, energy, utilities, industrial manufacturing, and pharmaceuticals.</t>
+      <c r="O103" s="6" t="inlineStr">
+        <is>
+          <t>Gestirai sfidanti progetti di evoluzione e trasformazione del business dei principali player nei settori Infrastructure, Energy &amp; Utility, Industrial Manufacturing, Pharmaceutical attraverso l’efficientamento e la reingegnerizzazione dei processi interni. Attraverso l'affiancamento a risorse PwC di livello manageriale, la risorsa potrà sviluppare competenze di processo in ambito Risk Management (sia entreprise che per tematiche di business verticali), conoscere l'organizzazione di un progetto st</t>
+        </is>
+      </c>
+      <c r="P103" s="6" t="inlineStr">
+        <is>
+          <t>Conoscenza del pacchetto Office; familiarità con i principi di Enterprise Risk Management, Project Risk Management, Business Continuity; conoscenza delle seguenti tecnologie: Visual basic, R, Matlab, Python.</t>
+        </is>
+      </c>
+      <c r="Q103" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] The job description mentions ESG risk analysis, TCFD, ESRS, and EU taxonomy, which are all related to environmental, social, and governance topics, indicating a relevance to general ESG strategy and corporate sustainability.</t>
         </is>
       </c>
       <c r="R103" s="2" t="inlineStr"/>
@@ -9723,19 +9773,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O104" s="2" t="inlineStr">
-        <is>
-          <t>This role provides ESG advisory services to institutional investors such as pension funds, supporting their MVB policy and ESG implementation in investment portfolios.</t>
-        </is>
-      </c>
-      <c r="P104" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have experience in ESG consulting, a strong understanding of financial markets, and excellent communication skills.</t>
-        </is>
-      </c>
-      <c r="Q104" s="2" t="inlineStr">
-        <is>
-          <t>This role is within the sustainable finance sector, focusing on ESG integration in real estate investments and institutional investor engagement.</t>
+      <c r="O104" s="6" t="inlineStr">
+        <is>
+          <t>Beleidsontwikkeling en advisering op het gebied van duurzaam beleggen, Monitoring van ESG-dienstverleners en vermogensbeheerders, Monitoring van impactbeleggingsmandaten en vastgoedbeleggingen, Opstellen van klimaatanalyses van vastgoedbedrijven, Begeleiden en coördineren van engagementtrajecten en internationale samenwerkingen, Coördineren van verschillende werk- en stuurgroepen, Organiseren en ondersteunen bij opleidingen en events, Onderzoeken en analyseren van systemische barrières in de int</t>
+        </is>
+      </c>
+      <c r="P104" s="6" t="inlineStr">
+        <is>
+          <t>Duurzaam beleggen, ESG, impactbeleggen, klimaatanalyses, engagementtrajecten, internationale samenwerkingen, systeembarrières, vastgoedmarkt</t>
+        </is>
+      </c>
+      <c r="Q104" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions ESG, duurzaam beleggen, impactbeleggen, and klimaatanalyses, which are all related to sustainable finance. The company also works with institutionele beleggers and pensioenfondsen to implement ESG in their beleggingsportefeuille.</t>
         </is>
       </c>
       <c r="R104" s="2" t="inlineStr"/>
@@ -9800,19 +9850,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O105" s="2" t="inlineStr">
-        <is>
-          <t>Leads and coordinates cross-functional study teams to ensure clinical study progress according to timelines, budget, and quality standards.</t>
-        </is>
-      </c>
-      <c r="P105" s="2" t="inlineStr">
-        <is>
-          <t>Requires expertise in clinical trial operations, vendor management, risk management planning, and regulatory compliance (ICH/GCP).</t>
-        </is>
-      </c>
-      <c r="Q105" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on the development and execution of complex clinical trials for cell therapy treatments within the pharmaceutical industry.</t>
+      <c r="O105" s="6" t="inlineStr">
+        <is>
+          <t>Are you ready to lead the charge in groundbreaking clinical studies? As a Global Study Director (GSD), you will play a pivotal role in the Cell Therapy Clinical Operations organization, driving the operational planning and delivery of high-priority and complex clinical studies. Your expertise will ensure the successful execution of clinical trials, managing quality, timelines, budgets, resources, investigational sites, vendors, and key project deliverables. Leading a cross-functional study team,</t>
+        </is>
+      </c>
+      <c r="P105" s="6" t="inlineStr">
+        <is>
+          <t>Essential Skills/Experience University degree or equivalent in medical or biological sciences or discipline associated with clinical research. Proven project management experience and training. At least 7 years of clinical trial experience. At least 3 years of experience in global study leadership a</t>
+        </is>
+      </c>
+      <c r="Q105" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions experience in sustainable finance, including climate, development, and/or nature finance, and the company's mission is to address global development challenges through strategic investments that promote sustainable and inclusive economic growth.</t>
         </is>
       </c>
       <c r="R105" s="2" t="inlineStr"/>
@@ -9877,19 +9927,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O106" s="2" t="inlineStr">
-        <is>
-          <t>The Senior Labor Relations Specialist provides expert advice and support to ensure compliance with labor laws and regulations in a dynamic global environment.</t>
-        </is>
-      </c>
-      <c r="P106" s="2" t="inlineStr">
-        <is>
-          <t>Requires experience in labor relations, strong understanding of collective bargaining agreements, and expertise in applying labor legislation.</t>
-        </is>
-      </c>
-      <c r="Q106" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on the intersection of labor relations and business operations within the transportation industry, contributing to sustainable and efficient mobility solutions.</t>
+      <c r="O106" s="6" t="inlineStr">
+        <is>
+          <t>The Senior Labor Relations Specialist supports the Labor Relations Manager and the P&amp;O Leadership Team in implementing the company’s labor strategy by providing expert technical advice and ensuring compliance with individual and collective labor regulations. Key Responsibilities include: Strategic Support and Technical Advisory, Collective Labor Relations, Individual Labor Cases, and Compliance and Risk Management.</t>
+        </is>
+      </c>
+      <c r="P106" s="6" t="inlineStr">
+        <is>
+          <t>Proven experience in estimating, managing, and controlling personnel cost budgets, as well as in developing financial models and conducting economic evaluations of collective labor agreements. Strong negotiation and conflict management skills. Analytical mindset and practical problem-solving orienta</t>
+        </is>
+      </c>
+      <c r="Q106" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions impact investing, ESG, and sustainable development, which are key concepts in sustainable finance. The company's mission and values also align with sustainable finance principles.</t>
         </is>
       </c>
       <c r="R106" s="2" t="inlineStr"/>
@@ -9954,19 +10004,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O107" s="2" t="inlineStr">
-        <is>
-          <t>Backend developer responsible for building APIs, designing scalable systems, and contributing to cloud deployments and CI/CD pipelines.</t>
-        </is>
-      </c>
-      <c r="P107" s="2" t="inlineStr">
-        <is>
-          <t>Strong C#/.NET experience, Azure infrastructure knowledge, DevOps practices (CI/CD, containerization), database fundamentals (PostgreSQL).</t>
-        </is>
-      </c>
-      <c r="Q107" s="2" t="inlineStr">
-        <is>
-          <t>Water resource management and climate risk mitigation in the context of urban planning and disaster preparedness.</t>
+      <c r="O107" s="6" t="inlineStr">
+        <is>
+          <t>As a core function, this team executes sustainable financing solutions aligned with evolving ESG standards and market trends. Execution support - intermediate structuring experience, with a growing level of autonomy. Be responsible of specific tasks for the execution of Sustainable Loan and Bond transactions, under the supervision of a senior team members but with a growing level of autonomy. Advise on transaction execution, by framing, designing and supporting the delivery of sustainable financ</t>
+        </is>
+      </c>
+      <c r="P107" s="6" t="inlineStr">
+        <is>
+          <t>Proficient in Office (Excel, PowerPoint). Proficient in Bloomberg. Knowledge in: Financial markets - Structuring; Sustainable Finance &amp; Corporate Social Responsibility - Integration of ESG challenges; Sustainable Finance &amp; Corporate Social Responsibility - Transition towards Low Carbon Economy; Data</t>
+        </is>
+      </c>
+      <c r="Q107" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions 'sustainable financing solutions', 'sustainable finance', 'ESG standards', 'sustainable loan and bond transactions', and 'transition to a greener economy', which are all related to sustainable finance and ESG investing.</t>
         </is>
       </c>
       <c r="R107" s="2" t="inlineStr"/>
@@ -10043,19 +10093,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O108" s="2" t="inlineStr">
-        <is>
-          <t>Provides legal advice on asset management and investments for BlackRock's Australian business, working across various asset classes and product structures.</t>
-        </is>
-      </c>
-      <c r="P108" s="2" t="inlineStr">
-        <is>
-          <t>Requires strong legal expertise with experience in regulatory compliance, fund management, and contract negotiation.</t>
-        </is>
-      </c>
-      <c r="Q108" s="2" t="inlineStr">
-        <is>
-          <t>The role is within the financial services industry, focusing on investment management and regulatory compliance in Australia.</t>
+      <c r="O108" s="6" t="inlineStr">
+        <is>
+          <t>To support BlackRock’s extensive Australian and global business through the provision of high quality and commercially focused legal advice. To interact with the broader BlackRock global community both in Australia and abroad, reflecting the global interconnectivity of our business. To ensure that BlackRock continues to be regarded by regulators and peers as a company with high compliance standards and strong legal acumen. Provide high quality and commercial legal advice to the Australian busine</t>
+        </is>
+      </c>
+      <c r="P108" s="6" t="inlineStr">
+        <is>
+          <t>Strong technical skills, including statutory and contractual interpretation, research and drafting. Proven ability to deliver high quality legal advice. Excellent verbal and written communication skills, including to confidently present to an audience. Ability to work autonomously and operate in a f</t>
+        </is>
+      </c>
+      <c r="Q108" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions 'sustainable finance practices' as one of the current and emerging trends and regulatory priorities, indicating a connection to ESG investing and sustainable finance.</t>
         </is>
       </c>
       <c r="R108" s="2" t="inlineStr">
@@ -10136,19 +10186,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O109" s="2" t="inlineStr">
-        <is>
-          <t>A Business Analyst will bridge the gap between digital teams, business stakeholders, and end-users to develop scalable and user-focused solutions for environmental compliance in shipping.</t>
-        </is>
-      </c>
-      <c r="P109" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have a Bachelor's degree, 1-3 years of experience working with digital processes, and SQL query writing skills.</t>
-        </is>
-      </c>
-      <c r="Q109" s="2" t="inlineStr">
-        <is>
-          <t>This role is within the maritime industry, focusing on environmental compliance and regulations related to emissions trading systems and fuel efficiency.</t>
+      <c r="O109" s="6" t="inlineStr">
+        <is>
+          <t>Prioritize internal and external feedback to build clear and cohesive development roadmaps. Translate desired features into precise specifications for developers using documentation, mock-ups, or visual tools. Follow up on newly released features to ensure they work effectively in real operational settings. Strengthen customer communication around product updates, new features, and enhancements. Support digital product operations and internal improvement initiatives. Establish and improve workfl</t>
+        </is>
+      </c>
+      <c r="P109" s="6" t="inlineStr">
+        <is>
+          <t>Ability to write and run SQL queries. Ability to read and understand Python code (C# familiarity is a plus). Experience analyzing data using APIs and a programming language, preferably Python. Familiarity with Git-based version control tools (Azure DevOps, GitHub). Understanding of Agile/Scrum or si</t>
+        </is>
+      </c>
+      <c r="Q109" s="6" t="inlineStr">
+        <is>
+          <t>[carbon_markets] The job description mentions experience with maritime emissions regulations, carbon markets, and environmental financial products, which are all relevant to the carbon markets profile.</t>
         </is>
       </c>
       <c r="R109" s="2" t="inlineStr">
@@ -10229,19 +10279,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O110" s="2" t="inlineStr">
-        <is>
-          <t>A Sales Executive will be responsible for converting inbound inquiries into sales by guiding customers through the home energy transition process and exceeding expectations.</t>
-        </is>
-      </c>
-      <c r="P110" s="2" t="inlineStr">
-        <is>
-          <t>The ideal candidate has a proven track record of success in sales, strong technical knowledge of domestic heating systems, and proficiency in MCS 3005.</t>
-        </is>
-      </c>
-      <c r="Q110" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on promoting sustainable home energy solutions within the UK's residential market, contributing to climate change mitigation and decarbonization efforts.</t>
+      <c r="O110" s="6" t="inlineStr">
+        <is>
+          <t>You’ll be at the forefront of our sales function, guiding customers through their home energy transition. You’ll convert inbound inquiries, proactively follow up on leads, and design technical solutions that meet customer needs while exceeding expectations. You’ll also play a key role in maintaining high compliance standards and identifying new business opportunities. Key Responsibilities: Lead Engagement, Follow-Up &amp; Conversion, Customer Support, Solution Design, Compliance &amp; Standards, Busines</t>
+        </is>
+      </c>
+      <c r="P110" s="6" t="inlineStr">
+        <is>
+          <t>MCS 3005, NIBE DIM, heat loss calculations, CRM systems, technical sales, customer engagement, industry knowledge of domestic heating systems, particularly heat pumps</t>
+        </is>
+      </c>
+      <c r="Q110" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions renewable energy solutions, heat pumps, solar panels, and carbon-neutral home energy solutions, which are all related to clean energy and environmental sustainability.</t>
         </is>
       </c>
       <c r="R110" s="2" t="inlineStr">
@@ -10322,19 +10372,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O111" s="2" t="inlineStr">
-        <is>
-          <t>The role supports the development of policies and guidance for UNDP's Strategic Plan within the Global Policy Network (GPN). This position provides technical advice, advocates for UNDP corporate messages, and engages in UN inter-agency coordination on specific thematic areas.</t>
-        </is>
-      </c>
-      <c r="P111" s="2" t="inlineStr">
-        <is>
-          <t>Requires experience in policy development, advocacy, and international cooperation with a strong understanding of sustainable development goals.</t>
-        </is>
-      </c>
-      <c r="Q111" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on the intersection of health, sustainable development, and global partnerships to achieve the Sustainable Development Goals (SDGs).</t>
+      <c r="O111" s="6" t="inlineStr">
+        <is>
+          <t>The job description does not explicitly state the responsibilities of the Project Data Analyst. However, based on the context, it can be inferred that the role may involve data analysis, project support, and collaboration with various teams.</t>
+        </is>
+      </c>
+      <c r="P111" s="6" t="inlineStr">
+        <is>
+          <t>The job description does not explicitly state the required skills for the Project Data Analyst role. However, based on the context, it can be inferred that the role may require data analysis, project management, and collaboration skills.</t>
+        </is>
+      </c>
+      <c r="Q111" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] The job description mentions sustainable development, climate change, and environmental health, which are related to ESG topics. Although the role is not explicitly focused on ESG, the context suggests that it may involve working on projects that contribute to sustainable development a</t>
         </is>
       </c>
       <c r="R111" s="2" t="inlineStr">
@@ -10415,9 +10465,9 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O112" s="2" t="inlineStr">
-        <is>
-          <t>This internship program provides students studying in Switzerland with practical experience in IISD's Geneva office, working on economic law, energy, and resilience projects.  The internship offers hands-on learning opportunities to contribute to sustainable development initiatives.</t>
+      <c r="O112" s="6" t="inlineStr">
+        <is>
+          <t>Major Roles &amp; Responsibilities: a. Oversight of Enterprise-wide Risk assessment and management, b. Credit Risk Management, c. Operational Risk Management, c. Market and Liquidity Risk, d. Risk Analysis and Stress Testing, e. Emerging Risks, f. Regulatory and Governance, g. Team Leadership, h. Key Deliverables</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
@@ -10425,9 +10475,9 @@
           <t>Candidates should have a strong academic background in economics, environmental science, or related fields, and be proficient in data analysis, research, and communication skills.</t>
         </is>
       </c>
-      <c r="Q112" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to IISD's work on climate change mitigation, sustainable resource management, and economic policy for a stable future.</t>
+      <c r="Q112" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] The job description mentions working with teams focused on sustainable development, climate change, and environmental issues, which aligns with the general ESG profile.</t>
         </is>
       </c>
       <c r="R112" s="2" t="inlineStr">
@@ -10504,19 +10554,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O113" s="2" t="inlineStr">
-        <is>
-          <t>A Manager will oversee project portfolios to drive strategic business outcomes, ensuring successful delivery within budget and timeline.</t>
-        </is>
-      </c>
-      <c r="P113" s="2" t="inlineStr">
-        <is>
-          <t>Requires experience in project management, organizational skills, strong communication, and ability to manage teams and stakeholders.</t>
-        </is>
-      </c>
-      <c r="Q113" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on government transformation with a focus on sustainability, climate change, environment &amp; digital solutions.</t>
+      <c r="O113" s="6" t="inlineStr">
+        <is>
+          <t>Identify focus countries/locations, strategic partners, outward delegation itineraries, event formats; plan B2B/B2G meetings and prepare talking points &amp; press notes. Coordinate with Invest India, Chambers, Missions; build investor lists, outreach plans, and track conversion. Draft invitation, program scripts, and proceedings; prepare participation summaries. Prepare project/sector/infrastructure profiles, brochures/flyers, web &amp; social content; support monthly newsletters. Facilitate meetings w</t>
+        </is>
+      </c>
+      <c r="P113" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mandatory skill sets: Investor targeting &amp; engagement; event/roadshow planning; strong writing for talking points, invites, briefs, and press notes; comfort with collaboration tools; data-driven outreach tracking. Preferred skill sets: Quality &amp; timeliness of event concept notes; roadshow execution </t>
+        </is>
+      </c>
+      <c r="Q113" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] The job description mentions working with clients on transformation in Government with a focus on Sustainability, Climate Change, and Environment, indicating a role related to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
       <c r="R113" s="2" t="inlineStr"/>
@@ -10593,19 +10643,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O114" s="2" t="inlineStr">
-        <is>
-          <t>Research Leader will lead work in the Frontiers of Technology workstream, focusing on biotechnology and biosecurity, while contributing to broader policy research efforts at RAND Europe.  Skills: The ideal candidate has experience winning and leading projects for UK government / EU institutions or philanthropic clients on technology policy issues relevant to biotechnology or its intersection with AI and other platform technologies.  Domain: This role connects to climate, ESG, sustainability, and finance by focusing on emerging technologies in the field of biotechnology and their impact on society and policy.</t>
-        </is>
-      </c>
-      <c r="P114" s="2" t="inlineStr">
-        <is>
-          <t>The ideal candidate has experience winning and leading projects for UK government / EU institutions or philanthropic clients on technology policy issues relevant to biotechnology or its intersection with AI and other platform technologies.</t>
-        </is>
-      </c>
-      <c r="Q114" s="2" t="inlineStr">
-        <is>
-          <t>This role connects to climate, ESG, sustainability, and finance by focusing on emerging technologies in the field of biotechnology and their impact on society and policy. Skills:  The ideal candidate has experience winning and leading projects for UK government / EU institutions or philanthropic clients on technology policy issues relevant to biotechnology or its intersection with AI and other platform technologies.</t>
+      <c r="O114" s="6" t="inlineStr">
+        <is>
+          <t>Research Leadership: Taking forward RAND Europe’s successful research track record in technology policy research, developing and leading a varied portfolio of research projects and expanding into new areas of work. Providing thought leadership on technology policy issues. Mentoring research staff and facilitating development of others' project management and methodological skills. Taking a leading role in ensuring that RAND Europe’s research has a positive impact within policy communities. Busin</t>
+        </is>
+      </c>
+      <c r="P114" s="6" t="inlineStr">
+        <is>
+          <t>Mixed-methods research, engagement, technology development, computational biology, bioinformatics, machine learning models, project management, business development, proposal writing, leadership, mentoring, communication, analytical, writing, presentation</t>
+        </is>
+      </c>
+      <c r="Q114" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions biotechnology, biosecurity, and technology policy, which are related to environmental science and sustainability. Although the job is not directly focused on renewable energy or conservation, it is adjacent to the clean energy field and involves r</t>
         </is>
       </c>
       <c r="R114" s="2" t="inlineStr">
@@ -10690,19 +10740,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O115" s="2" t="inlineStr">
-        <is>
-          <t>Audit position within EY's Assurance division, offering hands-on experience in financial audits and client interaction.</t>
-        </is>
-      </c>
-      <c r="P115" s="2" t="inlineStr">
-        <is>
-          <t>Bachelor's degree or completion expected by the end of the academic year, fluency in English and Czech, proficiency in Excel.</t>
-        </is>
-      </c>
-      <c r="Q115" s="2" t="inlineStr">
-        <is>
-          <t>Financial auditing and assurance services for businesses across various industries, with a focus on sustainability and ESG reporting.</t>
+      <c r="O115" s="6" t="inlineStr">
+        <is>
+          <t>Během auditu trávíme spoustu času u klientů, kde pečlivě procházíme čísla a informace, které o sobě zveřejňují. Ověřujeme jejich pravdivost, aby byli v očích svých obchodních partnerů, akcionářů, věřitelů i veřejnosti důvěryhodní. Ze začátku budeš pracovat spolu se zkušenými kolegy, kteří ti všechno vysvětlí a k ruce dostaneš i counselora, který tě bude provádět nejen auditem, ale pomůže ti i s kariérním růstem. Postupem času poznáš firemní procesy a ovládneš české účetnictví i mezinárodní audit</t>
+        </is>
+      </c>
+      <c r="P115" s="6" t="inlineStr">
+        <is>
+          <t>Pokročilá znalost Excelu, česky a anglicky, komunikace, týmová spolupráce</t>
+        </is>
+      </c>
+      <c r="Q115" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] The job description mentions experience with ESG (Environmental, Social, and Governance) and sustainability services, specifically Climate Change and Sustainability Services (CCaSS), which indicates a connection to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
       <c r="R115" s="2" t="inlineStr">
@@ -10783,19 +10833,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O116" s="2" t="inlineStr">
-        <is>
-          <t>Audit trainee seeking to gain practical experience in business and learn about various industries while studying.</t>
-        </is>
-      </c>
-      <c r="P116" s="2" t="inlineStr">
-        <is>
-          <t>Strong communication skills (English and Czech), analytical thinking, problem-solving abilities, ability to travel occasionally.</t>
-        </is>
-      </c>
-      <c r="Q116" s="2" t="inlineStr">
-        <is>
-          <t>Finance and accounting with a focus on sustainability and ESG reporting.</t>
+      <c r="O116" s="6" t="inlineStr">
+        <is>
+          <t>Během auditu trávíme spoustu času u klientů, kde pečlivě procházíme čísla a informace, které o sobě zveřejňují. Ověřujeme jejich pravdivost, aby byli v očích svých obchodních partnerů, akcionářů, věřitelů i veřejnosti důvěryhodní. Postupem času poznáš firemní procesy a ovládneš české účetnictví i mezinárodní auditorské a účetní standardy. Potkáš se se zástupci firem napříč odvětvími a naučíš se s nimi komunikovat. Časem se setkáš i s řediteli a členy boardů. Díky auditu nahlédneš do různých obla</t>
+        </is>
+      </c>
+      <c r="P116" s="6" t="inlineStr">
+        <is>
+          <t>Dokážeš se zamyslet nad problémem a navrhnout řešení. Mluvíš a píšeš dobře česky a anglicky.</t>
+        </is>
+      </c>
+      <c r="Q116" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] The job description mentions 'zprávy o udržitelnosti' (sustainability reports) and 'ESG odborníků' (ESG experts), indicating a connection to environmental, social, and governance topics.</t>
         </is>
       </c>
       <c r="R116" s="2" t="inlineStr">
@@ -10872,19 +10922,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O117" s="2" t="inlineStr">
-        <is>
-          <t>This postdoc role focuses on the intersection of digitization and the green transition within the context of human rights, contributing to research projects on digital exclusion and climate justice.</t>
-        </is>
-      </c>
-      <c r="P117" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should possess a PhD in Human Rights or related fields, strong analytical skills, experience with digital technologies, and familiarity with sustainability issues.</t>
-        </is>
-      </c>
-      <c r="Q117" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to understanding how human rights principles can be applied within the context of societal transformation and environmental challenges, particularly in relation to digitization and climate change.</t>
+      <c r="O117" s="6" t="inlineStr">
+        <is>
+          <t>The work duties include conducting research within the project Human Rights for a Politically and Culturally Sustainable World, with a specific focus on the digital and green transition. Through theoretical and/or empirical studies, you will examine new standard threats to human rights, aiming to develop a model for what human rights need to be able to address in a new era. The work involves some travel – to conferences as well as potential field, study or archive trips – although the majority o</t>
+        </is>
+      </c>
+      <c r="P117" s="6" t="inlineStr">
+        <is>
+          <t>Good knowledge of human rights and issues related to the digitisation of society or the climate transition. Good ability to collaborate. Ability to take initiative, be structured, and work independently. Very good ability to express yourself in English, both orally and in writing.</t>
+        </is>
+      </c>
+      <c r="Q117" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] The job description mentions human rights, digitisation, and the green transition, which are all related to environmental, social, and governance topics. The focus on human rights as a concept and practice to address risks linked to societal transformations and an uncertain future also</t>
         </is>
       </c>
       <c r="R117" s="2" t="inlineStr"/>
@@ -10961,19 +11011,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O118" s="2" t="inlineStr">
-        <is>
-          <t>This role involves supporting the development of a technology platform that translates sustainability and ESG data into measurable financial impact for organizations. The successful candidate will contribute to the growth of an innovative startup within the rapidly expanding sustainability finance sector.</t>
-        </is>
-      </c>
-      <c r="P118" s="2" t="inlineStr">
-        <is>
-          <t>The ideal candidate possesses strong analytical skills, experience in financial analysis, and knowledge of sustainability reporting frameworks.</t>
-        </is>
-      </c>
-      <c r="Q118" s="2" t="inlineStr">
-        <is>
-          <t>This role is focused on the growing field of sustainability finance and ESG analytics, where organizations are seeking tools to translate environmental, social, and governance data into actionable insights for strategic decision-making.</t>
+      <c r="O118" s="6" t="inlineStr">
+        <is>
+          <t>Are you ready to lead the charge in groundbreaking clinical studies? As a Global Study Director (GSD), you will play a pivotal role in the Cell Therapy Clinical Operations organization, driving the operational planning and delivery of high-priority and complex clinical studies. Your expertise will ensure the successful execution of clinical trials, managing quality, timelines, budgets, resources, investigational sites, vendors, and key project deliverables. Leading a cross-functional study team,</t>
+        </is>
+      </c>
+      <c r="P118" s="6" t="inlineStr">
+        <is>
+          <t>Essential Skills/Experience University degree or equivalent in medical or biological sciences or discipline associated with clinical research. Proven project management experience and training. At least 7 years of clinical trial experience. At least 3 years of experience in global study leadership a</t>
+        </is>
+      </c>
+      <c r="Q118" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions ESG, sustainability, and translating sustainability data into financial impact, which are key aspects of sustainable finance.</t>
         </is>
       </c>
       <c r="R118" s="2" t="inlineStr">
@@ -11054,19 +11104,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O119" s="2" t="inlineStr">
-        <is>
-          <t>Graduate Program in Corporate &amp; Institutional Banking at Westpac, focusing on understanding client needs and supporting their growth and financial well-being.</t>
-        </is>
-      </c>
-      <c r="P119" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have a bachelor's degree and be proficient in analytical skills, communication, and teamwork.</t>
-        </is>
-      </c>
-      <c r="Q119" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on the financial services industry within Australia and New Zealand, with emphasis on sustainability and ESG outcomes.</t>
+      <c r="O119" s="6" t="inlineStr">
+        <is>
+          <t>Participating in rotations, Supporting clients, Learning and development</t>
+        </is>
+      </c>
+      <c r="P119" s="6" t="inlineStr">
+        <is>
+          <t>Analytical skills, Communication skills, Problem-solving skills, Financial knowledge, Project management, Team collaboration</t>
+        </is>
+      </c>
+      <c r="Q119" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions 'Sustainable Finance' as one of the possible rotation areas, and also mentions 'supporting the transition to a climate-resilient future by structuring loans so they are linked to achieving environmental, social and corporate governance (ESG) outcome</t>
         </is>
       </c>
       <c r="R119" s="2" t="inlineStr">
@@ -11147,19 +11197,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O120" s="2" t="inlineStr">
-        <is>
-          <t>The Lead - Finance &amp; Accounts-SM is responsible for managing the financial and accounting operations of smart metering projects within AESL.</t>
-        </is>
-      </c>
-      <c r="P120" s="2" t="inlineStr">
-        <is>
-          <t>Requires experience in finance and accounting, strong analytical skills, and knowledge of Indian accounting standards.</t>
-        </is>
-      </c>
-      <c r="Q120" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on the energy infrastructure sector in India, specifically related to smart metering and sustainable energy solutions.</t>
+      <c r="O120" s="6" t="inlineStr">
+        <is>
+          <t>The Lead - Finance &amp; Accounts-SM is responsible for managing the financial and accounting operations of smart metering projects within AESL, overseeing activities such as bookkeeping, accounts payable, accounts receivable, and financial reporting. The role ensures the accurate and timely execution of financial processes while serving as the Controller of Accounts and Tax for the business. It drives operational efficiency, ensures compliance with financial regulations, and provides critical finan</t>
+        </is>
+      </c>
+      <c r="P120" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP FICO, MM, FM Module, BI/BPC Tools, Advance Excel, SAP BG Module, Accounts knowledge, Control Over SAP FICO, MM, FM Module &amp; basic Knowledge SAP BI &amp; BPC Tools, Commercial acumen, Knowledge on Different VAT act, Income Tax Act, and update on Same, Strong interpersonal skills, Coordination skill, </t>
+        </is>
+      </c>
+      <c r="Q120" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions smart metering projects, energy infrastructure, and power transmission, which are related to renewable energy and environmental science, making it a clean energy adjacent profile.</t>
         </is>
       </c>
       <c r="R120" s="2" t="inlineStr">
@@ -11228,19 +11278,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O121" s="2" t="inlineStr">
-        <is>
-          <t>A SAP EHSM Manager/Lead will be responsible for enhancing client's competitive position and performance through innovative and sustainable solutions.</t>
-        </is>
-      </c>
-      <c r="P121" s="2" t="inlineStr">
-        <is>
-          <t>10+ years of experience in consulting, SAP S/4HANA EHSM implementation (greenfield/brownfield), strong business process analysis skills, and proficiency in Industrial Health &amp; Safety practices.</t>
-        </is>
-      </c>
-      <c r="Q121" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on the application of technology to improve environmental, health, and safety compliance within industries.</t>
+      <c r="O121" s="6" t="inlineStr">
+        <is>
+          <t>The primary role is to make immediate, direct contributions to enhancing our clients’ competitive position and performance in ways that are distinctive, innovative, and sustainable. The SAP EHSM professional will be responsible for tasks related to liaise with customer, understand business processes, apply analytical skills, act as a trusted advisor in the business and technology consulting of SAP S/4HANA Product Compliance and classical Product Safety solution, also experience in SAP EHSM – Inc</t>
+        </is>
+      </c>
+      <c r="P121" s="6" t="inlineStr">
+        <is>
+          <t>SAP S/4HANA EHSM, Good communication skill to collaborate with business process owners, project team and other stakeholders / vendors, Good proficiency in Industrial Health &amp; Safety practices and business knowledge like OSHA regulations and ability to understand global regulatory safety standards to</t>
+        </is>
+      </c>
+      <c r="Q121" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[general_esg] The job description mentions experience in SAP EHSM, Sustainability Footprint Management, Sustainability Control Tower, and SAP Green Token, which are related to environmental sustainability and ESG. The role also involves working with clients to enhance their competitive position and </t>
         </is>
       </c>
       <c r="R121" s="2" t="inlineStr"/>
@@ -11305,19 +11355,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O122" s="2" t="inlineStr">
-        <is>
-          <t>An individual in Enterprise Risk Management plays a critical role in managing the bank's diverse risks to ensure financial stability and sustained growth.</t>
-        </is>
-      </c>
-      <c r="P122" s="2" t="inlineStr">
-        <is>
-          <t>Requires experience in risk assessment, control design, and implementation, along with strong communication and presentation skills.</t>
-        </is>
-      </c>
-      <c r="Q122" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on financial risk management within the banking sector, specifically related to sanctions compliance and regulatory reporting.</t>
+      <c r="O122" s="6" t="inlineStr">
+        <is>
+          <t>Individuals responsible for In-business Risk Management oversee risk identification, assessment, measurement, monitoring, and reporting. They design and implement risk mitigation actions and focus on managing one or more risks in support of business activities. Key Responsibilities: Design and lead projects to execute control enhancements over processes. Document processes developed, actions taken and track matters to ensure resolution. Collaborate with ICRM Sanctions regularly to ensure correct</t>
+        </is>
+      </c>
+      <c r="P122" s="6" t="inlineStr">
+        <is>
+          <t>Essential: Strong proficiency with Microsoft Suite, excellent organizational and communication skills. Desirable: Project management capabilities, strategic and/or analytical thinking skills. Most Relevant Skills: Analytical Thinking, Business Acumen, Constructive Debate, Escalation Management, Issu</t>
+        </is>
+      </c>
+      <c r="Q122" s="6" t="inlineStr">
+        <is>
+          <t>[carbon_markets] The job description mentions experience with maritime emissions regulations, carbon markets, and environmental financial products, which are all relevant to the carbon markets profile.</t>
         </is>
       </c>
       <c r="R122" s="2" t="inlineStr"/>
@@ -11382,19 +11432,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O123" s="2" t="inlineStr">
-        <is>
-          <t>The Senior Technical Product Manager – Analytics is responsible for the technical strategy, delivery governance, and people leadership of multiple analytics pods or products within the Analytics CoE.</t>
-        </is>
-      </c>
-      <c r="P123" s="2" t="inlineStr">
-        <is>
-          <t>Requires a strong understanding of data engineering, analytics architecture, and software development principles with experience in leading teams and managing complex projects.</t>
-        </is>
-      </c>
-      <c r="Q123" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to Carrier Global Corporation's mission of providing intelligent climate and energy solutions that address global challenges related to sustainability and resource efficiency.</t>
+      <c r="O123" s="6" t="inlineStr">
+        <is>
+          <t>Portfolio-Level Technical Strategy &amp; Architecture, Program / Portfolio Delivery Governance, Partnership with Product, BA &amp; Architecture Leadership, Hands-On Technical Leadership, Analytics Technical Solution Ownership, Team Leadership &amp; Mentorship, Talent Development &amp; Capability Building, Culture, Ways of Working &amp; Engineering Excellence</t>
+        </is>
+      </c>
+      <c r="P123" s="6" t="inlineStr">
+        <is>
+          <t>Strong hands-on experience with: ETL / ELT Cloud platforms (AWS, Snowflake , Open source), Databricks, Open Source, SAP Analytics (BW, HANA, S/4) Data Warehousing and, Strong grasp of: Data modeling and semantic layers, Analytics performance and scalability, Integration patterns across heterogeneous</t>
+        </is>
+      </c>
+      <c r="Q123" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions 'intelligent climate and energy solutions' and ' Carrier Global Corporation' which is a company that provides solutions for climate and energy, indicating a connection to renewable energy and environmental science.</t>
         </is>
       </c>
       <c r="R123" s="2" t="inlineStr"/>
@@ -11459,19 +11509,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O124" s="2" t="inlineStr">
-        <is>
-          <t>A Senior Software Tester (embedded systems) will develop and refine test strategies for embedded systems, mentor junior testers, and ensure quality throughout the development lifecycle.</t>
-        </is>
-      </c>
-      <c r="P124" s="2" t="inlineStr">
-        <is>
-          <t>Minimum 7 years of experience in system testing within embedded systems is required, along with knowledge of RTOS, microcontrollers, embedded Linux, and communication protocols.</t>
-        </is>
-      </c>
-      <c r="Q124" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on developing sustainable climate solutions for industrial environments, connecting to climate control systems and industrial processes.</t>
+      <c r="O124" s="6" t="inlineStr">
+        <is>
+          <t>Develop and refine the test strategy and test planning for embedded systems. Collaborate with software testers and developers to expand and improve test automation and testing strategies. Execute test cases, analyze results, and clearly document findings. Design and execute advanced system tests (both manual and automated). Develop test environments and tools for hardware-near testing. Troubleshoot and analyze complex system failures. Ensure testability during the design phase through requiremen</t>
+        </is>
+      </c>
+      <c r="P124" s="6" t="inlineStr">
+        <is>
+          <t>RTOS, microcontrollers, embedded Linux, communication protocols (e.g., Modbus, I2C), test automation using tools such as Python, Robot Framework, or similar, hardware-near development, troubleshooting, CI/CD, version control (e.g., Git, Jenkins, Azure DevOps), SCRUM, test plan design, test case exec</t>
+        </is>
+      </c>
+      <c r="Q124" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions 'sustainable climate solutions' and 'energy-efficient solutions for industrial environments', which indicates a focus on environmental sustainability and renewable energy. Although it's not a direct match with renewable energy, the company's produ</t>
         </is>
       </c>
       <c r="R124" s="2" t="inlineStr"/>
@@ -11548,19 +11598,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O125" s="2" t="inlineStr">
-        <is>
-          <t>An ESG Analyst verifies supplier data, conducts initial QA on emissions data, and supports the ongoing improvement of internal processes.</t>
-        </is>
-      </c>
-      <c r="P125" s="2" t="inlineStr">
-        <is>
-          <t>1-2 years of experience in a data analyst, data operations, or similar hands-on data role with advanced Excel skills and experience with Power Query.</t>
-        </is>
-      </c>
-      <c r="Q125" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on ESG data analysis within supply chains to support businesses in understanding and managing sustainability risks and performance.</t>
+      <c r="O125" s="6" t="inlineStr">
+        <is>
+          <t>Verify supplier data, conduct first-pass QA review of emissions data, perform initial QA checks on ESG ratings outputs, cleanse and prepare client-provided spend data, coordinate regular data processing cycles, clearly document findings and data issues, support the ongoing improvement of internal processes.</t>
+        </is>
+      </c>
+      <c r="P125" s="6" t="inlineStr">
+        <is>
+          <t>Advanced Excel, Power Query, data manipulation, data cleansing, attention to detail, critical thinking, sound judgement, written communication, ability to learn new tools and systems.</t>
+        </is>
+      </c>
+      <c r="Q125" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] The job description mentions ESG, sustainability, and supply chain concepts, indicating a focus on environmental, social, and governance topics. The role involves working with ESG data, conducting QA reviews, and supporting the improvement of internal processes, which aligns with the g</t>
         </is>
       </c>
       <c r="R125" s="2" t="inlineStr">
@@ -11641,19 +11691,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O126" s="2" t="inlineStr">
-        <is>
-          <t>This is a 12-month program designed to provide a comprehensive understanding of the Corporate &amp; Institutional Banking industry, with rotations in various areas.</t>
-        </is>
-      </c>
-      <c r="P126" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have a Bachelor's degree and possess strong analytical skills, communication abilities, and an interest in finance and business.</t>
-        </is>
-      </c>
-      <c r="Q126" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on supporting institutional and government clients while contributing to climate-resilient solutions through ESG integration.</t>
+      <c r="O126" s="6" t="inlineStr">
+        <is>
+          <t>Participating in rotations, Supporting clients, Learning and development</t>
+        </is>
+      </c>
+      <c r="P126" s="6" t="inlineStr">
+        <is>
+          <t>Analytical skills, Communication skills, Problem-solving skills, Financial knowledge, Project management, Team collaboration</t>
+        </is>
+      </c>
+      <c r="Q126" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions supporting the transition to a climate-resilient future, structuring loans linked to achieving environmental, social and corporate governance (ESG) outcomes, and a rotation in Sustainable Finance.</t>
         </is>
       </c>
       <c r="R126" s="2" t="inlineStr">
@@ -11734,19 +11784,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O127" s="2" t="inlineStr">
-        <is>
-          <t>The Business Development Manager will play a key role in securing funding through grants and supporting commercial sales activity across various industries. They will contribute to BBB's growth by connecting its funding strategy with commercial ambitions.</t>
-        </is>
-      </c>
-      <c r="P127" s="2" t="inlineStr">
-        <is>
-          <t>This role requires strong grant writing skills, experience in business development, excellent communication and relationship-building abilities, and the ability to manage multiple projects simultaneously.</t>
-        </is>
-      </c>
-      <c r="Q127" s="2" t="inlineStr">
-        <is>
-          <t>The Business Development Manager will support a company focused on developing biochar solutions for agriculture, renewable energy, and carbon removal, contributing to climate change mitigation efforts.</t>
+      <c r="O127" s="6" t="inlineStr">
+        <is>
+          <t>This is a versatile, high-impact role for someone who wants to make a real difference at an early-stage climate-tech company. As Business Development Manager, you will work across two of BBB's most important growth areas: securing funding through grants and supporting commercial sales activity to agricultural, utilities, and industrial organisations. You will identify and write applications, help shape proposals, coordinate inputs, and manage submissions, while also supporting the commercial tea</t>
+        </is>
+      </c>
+      <c r="P127" s="6" t="inlineStr">
+        <is>
+          <t>Grant writing, funding applications, bid coordination, sales, CRM management, event representation, communication, project management, commercial awareness</t>
+        </is>
+      </c>
+      <c r="Q127" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[clean_energy_adjacent] The job description mentions biochar, carbon removal, regenerative agriculture, and climate-tech, which are all related to renewable energy and environmental science. The company's mission is to improve soil health and remove carbon from the atmosphere, which aligns with the </t>
         </is>
       </c>
       <c r="R127" s="2" t="inlineStr">
@@ -11823,19 +11873,19 @@
           <t>Keyword (4)</t>
         </is>
       </c>
-      <c r="O128" s="2" t="inlineStr">
-        <is>
-          <t>This Project Finance / Investor Outreach Advisor role focuses on securing investment for utility-scale solar projects in Southern Africa, managing investor relationships, and supporting the financing process. The advisor will develop financial models, analyze investment opportunities, and manage communication with investors.</t>
-        </is>
-      </c>
-      <c r="P128" s="2" t="inlineStr">
-        <is>
-          <t>Expertise in project finance, financial modeling, and investment analysis is required, along with strong business development, investor outreach, and relationship management skills.</t>
-        </is>
-      </c>
-      <c r="Q128" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to sustainable industrialization across Africa by supporting the development of renewable energy projects and promoting investment in clean technologies.</t>
+      <c r="O128" s="6" t="inlineStr">
+        <is>
+          <t>The Project Finance / Investor Outreach Advisor will manage relationships with investors, develop financing strategies, and support the outreach process to secure investment for utility-scale solar projects in Southern Africa. Day-to-day responsibilities include analyzing financial models, analyzing investment opportunities, drafting proposals, and managing investor communication with relevant investors (development finance institutions, energy funds, infrastructure investors, family offices).</t>
+        </is>
+      </c>
+      <c r="P128" s="6" t="inlineStr">
+        <is>
+          <t>Project Finance, Financial Modeling, Investment Analysis, Business Development, Investor Outreach, Relationship Management, Market Research, Analytics, Reporting, Communication, Negotiation</t>
+        </is>
+      </c>
+      <c r="Q128" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions utility-scale solar projects in Southern Africa, renewable energy transactions, and impact investment funds, which are all related to clean energy and environmental sustainability.</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr">
@@ -11904,9 +11954,9 @@
           <t>Keyword (3)</t>
         </is>
       </c>
-      <c r="O129" s="2" t="inlineStr">
-        <is>
-          <t>Regional Service Delivery Manager - Business Services supports operational capability, service delivery, and planning for the region, ensuring alignment with business continuity and service continuity plans.</t>
+      <c r="O129" s="6" t="inlineStr">
+        <is>
+          <t>The Regional Service Delivery Manager - Business Services supports the Assistant Chief Officer Business Services and the Regional Leadership Team with the assessment of operational capability and capacity needs within the region, delivery of support services to members at a Regional level, including the development of a strategically aligned annual operational plan and budget for the Region that includes operational workforce and asset (facility, fleet and equipment) planning, infrastructure pla</t>
         </is>
       </c>
       <c r="P129" s="2" t="inlineStr">
@@ -11981,19 +12031,19 @@
           <t>Keyword (3)</t>
         </is>
       </c>
-      <c r="O130" s="2" t="inlineStr">
-        <is>
-          <t>Senior Product &amp; Commercialization Manager for GWA Group's water solutions business, driving the transition to a solutions-led model.</t>
-        </is>
-      </c>
-      <c r="P130" s="2" t="inlineStr">
-        <is>
-          <t>Strong commercial acumen, experience in product development and go-to-market strategy, market research skills, ability to build and execute complex plans.</t>
-        </is>
-      </c>
-      <c r="Q130" s="2" t="inlineStr">
-        <is>
-          <t>Water technology and sustainability solutions within the building materials and construction industry.</t>
+      <c r="O130" s="6" t="inlineStr">
+        <is>
+          <t>You will own the end-to-end product and commercialisation agenda and bring it to life through action, influence and delivery. This includes: Scanning the market relentlessly to identify smart, connected and solution-based water opportunities across residential, commercial and institutional segments. Deeply understanding customers, uncovering real pain points through research, interviews and partner engagement, and validating where value truly lies. Designing compelling commercial models, includi</t>
+        </is>
+      </c>
+      <c r="P130" s="6" t="inlineStr">
+        <is>
+          <t>Commercial and financial acumen, experience designing and scaling new revenue models, exposure to smart, connected, digital or IoT-adjacent solutions, or similarly complex ecosystems, entrepreneurial mindset, resilience, and a bias to action</t>
+        </is>
+      </c>
+      <c r="Q130" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions 'sustainable water solutions', 'smart and connected water solutions', and 'water opportunities', indicating a focus on environmental sustainability and water management, which aligns with the clean energy adjacent profile.</t>
         </is>
       </c>
       <c r="R130" s="2" t="inlineStr"/>
@@ -12058,19 +12108,19 @@
           <t>Keyword (3)</t>
         </is>
       </c>
-      <c r="O131" s="2" t="inlineStr">
-        <is>
-          <t>Project and Process Manager at Royal Smit en Zoon is responsible for initiating, developing, and executing investment projects and contract manufacturing activities.</t>
-        </is>
-      </c>
-      <c r="P131" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have a technical background (e.g., Chemical Technology, Process Engineering) with 7-10 years of experience in an industrial environment, including project management experience.</t>
-        </is>
-      </c>
-      <c r="Q131" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to the sustainable development of Royal Smit &amp; Zoon's production and asset portfolio by managing CAPEX projects and ensuring compliance with environmental regulations.</t>
+      <c r="O131" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Als Project- en Procesmanager binnen Royal Smit en Zoon ben je verantwoordelijk voor het initiëren, ontwikkelen en realiseren van investeringsprojecten en contract manufacturing-activiteiten. Je zorgt voor een veilige, efficiënte en toekomstbestendige productiecapaciteit, technische integriteit van assets en naleving van QESH- en procesveiligheidsnormen. Je ondersteunt hierbij de productielocaties in Weesp en Amersfoort en levert een belangrijke bijdrage aan de strategische ontwikkeling van het </t>
+        </is>
+      </c>
+      <c r="P131" s="6" t="inlineStr">
+        <is>
+          <t>Kennis van procesveiligheid, SHE en technische compliance; Kennis over projectmethodieken (bijv. FEL, PMI, PRINCE2 of vergelijkbaar); Affiniteit met Operational Excellence en/of Lean methodieken</t>
+        </is>
+      </c>
+      <c r="Q131" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions 'duurzame grondstoffen' (sustainable raw materials) and 'de waardeketen van de leerindustrie verduurzamen' (sustaining the leather industry's value chain), indicating a focus on environmental sustainability, and 'procesveiligheid' (process safety)</t>
         </is>
       </c>
       <c r="R131" s="2" t="inlineStr"/>
@@ -12135,19 +12185,19 @@
           <t>Keyword (3)</t>
         </is>
       </c>
-      <c r="O132" s="2" t="inlineStr">
-        <is>
-          <t>Lead a team focused on advancing climate action, peacebuilding, and democracy through strategic leadership, policy influence, and effective program delivery.</t>
-        </is>
-      </c>
-      <c r="P132" s="2" t="inlineStr">
-        <is>
-          <t>Proven experience leading teams, strong policy influencing skills, ability to navigate complex international partnerships, and demonstrated expertise in climate change mitigation and sustainable development.</t>
-        </is>
-      </c>
-      <c r="Q132" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on climate action, peacebuilding, and human rights within the humanitarian aid sector, contributing to global efforts for climate resilience and social justice.</t>
+      <c r="O132" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This role is central to advancing NORCAP’s commitment to climate action, peace, democracy, and human rights through strategic leadership, policy influence, and effective programme delivery. You will lead one of NORCAP’s most forward‑looking portfolios—where strategic leadership, programme quality, and policy influence come together. You will guide a strong team, shape partnerships, and steer a portfolio that has the mandate to rethink how aid can better address climate‑related risks, strengthen </t>
+        </is>
+      </c>
+      <c r="P132" s="6" t="inlineStr">
+        <is>
+          <t>Good knowledge of human rights and issues related to the digitisation of society or the climate transition. Good ability to collaborate. Ability to take initiative, be structured, and work independently. Very good ability to express yourself in English, both orally and in writing.</t>
+        </is>
+      </c>
+      <c r="Q132" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions 'climate action', 'climate change', and 'climate‑related risks', indicating a strong focus on climate risk management and mitigation.</t>
         </is>
       </c>
       <c r="R132" s="2" t="inlineStr"/>
@@ -12212,19 +12262,19 @@
           <t>Keyword (3)</t>
         </is>
       </c>
-      <c r="O133" s="2" t="inlineStr">
-        <is>
-          <t>A hands-on Algorithm &amp; Software Engineer is needed to lead the development of ECG algorithms for medical devices, ensuring accurate physiological signal interpretation and reliable performance in diverse clinical conditions.</t>
-        </is>
-      </c>
-      <c r="P133" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have strong foundations in biomedical signal processing, especially ECG, experience developing real-time or near-real-time algorithms, and a solid understanding of medical device regulatory frameworks.</t>
-        </is>
-      </c>
-      <c r="Q133" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to the development of medical devices that help diagnose and treat heart conditions, aligning with climate change mitigation efforts by promoting healthcare accessibility and efficiency.</t>
+      <c r="O133" s="6" t="inlineStr">
+        <is>
+          <t>Algorithm Development &amp; Signal Processing: Lead the design, implementation, and optimization of ECG signal‑processing algorithms. Develop robust algorithms suitable for embedded systems. Analyze diverse ECG datasets to ensure algorithm reliability. Conduct algorithm performance benchmarking and validation. Software Engineering &amp; Design Transfer: Implement algorithms in production-quality code and support Design Transfer. Cross-functional &amp; Technical Collaboration: Collaborate with internal and e</t>
+        </is>
+      </c>
+      <c r="P133" s="6" t="inlineStr">
+        <is>
+          <t>ECG signal processing, real-time algorithms, embedded medical device software, Python, C/C++, machine-learning–based ECG classification, deep learning, real‑time physiological monitoring, wearable or ambulatory ECG devices, low‑power or resource‑constrained embedded systems</t>
+        </is>
+      </c>
+      <c r="Q133" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions ESG, sustainability, and translating sustainability data into financial impact, which are key aspects of sustainable finance.</t>
         </is>
       </c>
       <c r="R133" s="2" t="inlineStr"/>
@@ -12301,19 +12351,19 @@
           <t>Keyword (3)</t>
         </is>
       </c>
-      <c r="O134" s="2" t="inlineStr">
-        <is>
-          <t>A Senior Content &amp; Communications Manager will own Carbonfuture's editorial output, including content creation, thought leadership development, and media relations.</t>
-        </is>
-      </c>
-      <c r="P134" s="2" t="inlineStr">
-        <is>
-          <t>The ideal candidate has several years of experience in a content, editorial, or communications role with a proven track record of producing high-quality long-form and short-form content.</t>
-        </is>
-      </c>
-      <c r="Q134" s="2" t="inlineStr">
-        <is>
-          <t>The role is focused on the rapidly growing carbon removal market, connecting to climate change mitigation efforts and sustainable finance.</t>
+      <c r="O134" s="6" t="inlineStr">
+        <is>
+          <t>The carbon removal market is at an inflection point. Buyers are becoming more sophisticated, the supply side is maturing, and the conversations shaping this market - about quality, integrity, and scale - are happening right now. Carbonfuture sits at the center of those conversations, and we need someone who can make sure our voice is heard. This is a hands-on writing role. You'll own Carbonfuture's editorial output, from content to sharp thought leadership and press outreach. You'll help our exp</t>
+        </is>
+      </c>
+      <c r="P134" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exceptional written English — you write with the fluency and precision of a native speaker, across formats and audiences. Strong editorial judgement: you know and love to tinker with what makes a story work, and what makes it fall flat. Ability to translate complex, technical topics into compelling </t>
+        </is>
+      </c>
+      <c r="Q134" s="6" t="inlineStr">
+        <is>
+          <t>[carbon_markets] The job description mentions carbon removal, carbon markets, and durable carbon removal, which are all related to carbon markets. The company, Carbonfuture, provides tools and services for carbon removal, which further supports this classification.</t>
         </is>
       </c>
       <c r="R134" s="2" t="inlineStr">
@@ -12394,19 +12444,19 @@
           <t>Keyword (3)</t>
         </is>
       </c>
-      <c r="O135" s="2" t="inlineStr">
-        <is>
-          <t>Assist senior DCM originators on corporate-client mandates focused on the Nordics, while gaining exposure to broader EMEA-wide transactions.</t>
-        </is>
-      </c>
-      <c r="P135" s="2" t="inlineStr">
-        <is>
-          <t>Proactive, can do-mentality with a willingness to learn; mathematical, analytical &amp; quantitative skills; outstanding communication and time management skills.</t>
-        </is>
-      </c>
-      <c r="Q135" s="2" t="inlineStr">
-        <is>
-          <t>Financial Market in the Nordic region, specifically Corporate Debt Capital Markets.</t>
+      <c r="O135" s="6" t="inlineStr">
+        <is>
+          <t>Assist in preparing presentations, pitch books and transaction-specific materials for the DCM team, support senior DCM originators on corporate-client mandates, build a solid understanding of DCM products</t>
+        </is>
+      </c>
+      <c r="P135" s="6" t="inlineStr">
+        <is>
+          <t>Mathematical, analytical &amp; quantitative skills, outstanding communication and time management skills</t>
+        </is>
+      </c>
+      <c r="Q135" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions 'sustainable finance' as one of the DCM products, indicating a focus on environmental, social, or governance topics.</t>
         </is>
       </c>
       <c r="R135" s="2" t="inlineStr">
@@ -12475,19 +12525,19 @@
           <t>Keyword (3)</t>
         </is>
       </c>
-      <c r="O136" s="2" t="inlineStr">
-        <is>
-          <t>A researcher will provide spatial and statistical support to projects studying maternal care provision and use in sub-Saharan African cities.</t>
-        </is>
-      </c>
-      <c r="P136" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have a Master's degree in geospatial/spatial sciences, epidemiology, or data science with at least one year of experience in analytical health geography.</t>
-        </is>
-      </c>
-      <c r="Q136" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to improving maternal health outcomes in low-resource settings by analyzing spatial and demographic data related to maternal care provision.</t>
+      <c r="O136" s="6" t="inlineStr">
+        <is>
+          <t>You provide spatial and statistical support in the assembly and pre-processing of a wide variety of maternal health indicators from household survey data, such as Demographic and Health Surveys. You offer spatial and statistical support in the assembly and pre-processing of health indicators based on environment, climate, population and infrastructure data from open data portals. You conduct geospatial modelling and analyses to examine the variation of maternal health indicators across space and</t>
+        </is>
+      </c>
+      <c r="P136" s="6" t="inlineStr">
+        <is>
+          <t>ArcGIS Pro, QGIS, R, STATA, scripting, spatial analysis, statistical analysis, geospatial modelling, data science, epidemiology, analytical health geography</t>
+        </is>
+      </c>
+      <c r="Q136" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job involves geospatial analysis of maternal health indicators, which is related to environmental science and public health, and the company is involved in public health research and service delivery, which is adjacent to the clean energy and environmental science field.</t>
         </is>
       </c>
       <c r="R136" s="2" t="inlineStr"/>
@@ -12564,19 +12614,19 @@
           <t>Keyword (3)</t>
         </is>
       </c>
-      <c r="O137" s="2" t="inlineStr">
-        <is>
-          <t>The Global ESG Controls &amp; Compliance Manager will support Novartis' sustainable growth by providing credible ESG non-financial information. They will be responsible for designing, implementing, and maintaining the company's ESG reporting control framework.</t>
-        </is>
-      </c>
-      <c r="P137" s="2" t="inlineStr">
-        <is>
-          <t>The ideal candidate has experience in financial or non-financial reporting control frameworks assessment, design, and implementation. Strong analytical and problem-solving skills are required.</t>
-        </is>
-      </c>
-      <c r="Q137" s="2" t="inlineStr">
-        <is>
-          <t>This role connects to climate, ESG, sustainability, and finance within the pharmaceutical industry.</t>
+      <c r="O137" s="6" t="inlineStr">
+        <is>
+          <t>The role will be responsible for supporting the assessment, design and implementation of the Global ESG reporting control framework and will be required to collaborate cross functionally. The role will specifically support the alignment of the ESG control framework with the Global Finance control framework. This will include the integration with the Novartis 3LOD model, which will require collaboration with the Financial Controls and Compliance team. Major accountabilities include: monitoring th</t>
+        </is>
+      </c>
+      <c r="P137" s="6" t="inlineStr">
+        <is>
+          <t>Project management, change management, analytical, problem-solving, collaboration, communication, English language proficiency</t>
+        </is>
+      </c>
+      <c r="Q137" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] The job description mentions ESG (Environmental Social Governance) risk and controls, ESG reporting, and ESG control framework, which are all related to environmental, social, and governance topics, indicating a strong fit with the general ESG profile.</t>
         </is>
       </c>
       <c r="R137" s="2" t="inlineStr">
@@ -12657,14 +12707,14 @@
           <t>Keyword (3)</t>
         </is>
       </c>
-      <c r="O138" s="2" t="inlineStr">
-        <is>
-          <t>The Audit Process Lead will drive process improvements within the Audit delivery lifecycle at EY GDS Assurance, focusing on efficiency, compliance, technology adoption, and KPI monitoring.</t>
-        </is>
-      </c>
-      <c r="P138" s="2" t="inlineStr">
-        <is>
-          <t>This role requires 12+ years of professional experience in global professional services firms, with a focus on process improvement implementation and cross-functional collaboration.</t>
+      <c r="O138" s="6" t="inlineStr">
+        <is>
+          <t>Work with stakeholders across the Assurance Service Line to identify opportunities for process improvements, Implement the identified process improvements across the Audit business lifecycle, Develop process maps, Ensure redesigned or improved processes comply with relevant System of Quality Management (SQM) controls, Assess and select systems and tools, Establish, monitor, and report on KPIs and metrics</t>
+        </is>
+      </c>
+      <c r="P138" s="6" t="inlineStr">
+        <is>
+          <t>Analytical skills, Effective verbal and written communication skills, Experience with process improvements, Experience with cross-functional and cross-regional process initiatives, Familiarity with EY and/or global delivery models</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -12750,19 +12800,19 @@
           <t>Keyword (3)</t>
         </is>
       </c>
-      <c r="O139" s="2" t="inlineStr">
-        <is>
-          <t>This role is responsible for leading end-to-end change management activities across programs of work, supporting digital and business transformation initiatives.</t>
-        </is>
-      </c>
-      <c r="P139" s="2" t="inlineStr">
-        <is>
-          <t>The ideal candidate will have a Certified Change Management Practitioner certification and substantial experience in a change management position.</t>
-        </is>
-      </c>
-      <c r="Q139" s="2" t="inlineStr">
-        <is>
-          <t>This role connects to the technology sector by focusing on digital transformation and its impact on organizational change.</t>
+      <c r="O139" s="6" t="inlineStr">
+        <is>
+          <t>Lead end-to-end change management activities across programs of work, supporting digital and business transformation initiatives, partnering with subject matter experts to plan, coordinate and deliver successful change outcomes. Design and deliver targeted training solutions including training needs analysis, planning, and development of engaging learning activities aligned with adult learning principles and delivered in partnership with the Learning &amp; Development team. Manage change and communi</t>
+        </is>
+      </c>
+      <c r="P139" s="6" t="inlineStr">
+        <is>
+          <t>Change management, stakeholder engagement, training design and delivery, communication strategies, leadership coaching, risk management, project planning, adult learning principles</t>
+        </is>
+      </c>
+      <c r="Q139" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions 'intelligent climate and energy solutions' and ' Carrier Global Corporation' which is a company that provides solutions for climate and energy, indicating a connection to renewable energy and environmental science.</t>
         </is>
       </c>
       <c r="R139" s="2" t="inlineStr">
@@ -12843,19 +12893,19 @@
           <t>Keyword (3)</t>
         </is>
       </c>
-      <c r="O140" s="2" t="inlineStr">
-        <is>
-          <t>Leads embedded software test and validation across Zephyr RTOS, Linux, and No-OS SDKs for ARM Cortex-M and Cortex-A based SoCs.</t>
-        </is>
-      </c>
-      <c r="P140" s="2" t="inlineStr">
-        <is>
-          <t>Requires 10+ years of experience in embedded software validation, system integration testing, or post-silicon debug for complex SoCs, with expertise in ARM Cortex-M and Cortex-A architectures, cross-compilation toolchains, and embedded debug tools.</t>
-        </is>
-      </c>
-      <c r="Q140" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to the development of solutions that help drive advancements in digitized factories, mobility, and digital healthcare, combat climate change, and reliably connect humans and the world.</t>
+      <c r="O140" s="6" t="inlineStr">
+        <is>
+          <t>Test Strategy &amp; Execution: Define and execute system validation and integration test plans for Analog Devices' SoCs running Zephyr RTOS and embedded Linux. Build test cases covering functional correctness, corner cases, performance, power mode transitions, and boot sequence validation across virtual prototyping, emulation, and post-silicon environments. Establish test coverage metrics, pass/fail criteria, and quality gates for release milestones. CI/CD &amp; Test Infrastructure: Architect and mainta</t>
+        </is>
+      </c>
+      <c r="P140" s="6" t="inlineStr">
+        <is>
+          <t>ARM Cortex-M and Cortex-A architectures, cross-compilation toolchains, embedded debug tools, GitHub Actions, Python, Git, virtual prototyping, emulation platforms, CI/CD, test automation, log analysis, tooling, RTOS, embedded Linux, static analysis tools, code coverage</t>
+        </is>
+      </c>
+      <c r="Q140" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions 'sustainable climate solutions' and 'energy-efficient solutions for industrial environments', which indicates a focus on environmental sustainability and renewable energy. Although it's not a direct match with renewable energy, the company's produ</t>
         </is>
       </c>
       <c r="R140" s="2" t="inlineStr">
@@ -12936,19 +12986,19 @@
           <t>Keyword (3)</t>
         </is>
       </c>
-      <c r="O141" s="2" t="inlineStr">
-        <is>
-          <t>This role involves contributing expertise to the Technical Panel of Climate Resilient Communities (CRC) for a Pacific Island Country or National citizen based overseas. The successful candidate will support the implementation of CRC's initiatives in water, food, and energy sectors.</t>
-        </is>
-      </c>
-      <c r="P141" s="2" t="inlineStr">
-        <is>
-          <t>Requires experience with monitoring, evaluation, and learning; knowledge of agriculture, food/nutrition, and water security; expertise in climate change and disaster risk reduction; strong communication skills for communications and creatives; and program and investment design experience.</t>
-        </is>
-      </c>
-      <c r="Q141" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to the development of climate resilient communities in the Indo-Pacific region by supporting initiatives that address water, food, and energy sectors.</t>
+      <c r="O141" s="6" t="inlineStr">
+        <is>
+          <t>The Technical Panel has six categories with their full descriptions and selection criteria listed in their respective annex. The six categories are: Monitoring, Evaluation and Learning, Agriculture, Food/nutrition and Water Security, Climate Change and Disaster Risk Reduction, Communications and Creatives, Program and Investment Design, and Gender, Disability, Equity and Social Inclusion.</t>
+        </is>
+      </c>
+      <c r="P141" s="6" t="inlineStr">
+        <is>
+          <t>Experience and expertise in one or more of the six categories, including Monitoring, Evaluation and Learning, Agriculture, Food/nutrition and Water Security, Climate Change and Disaster Risk Reduction, Communications and Creatives, Program and Investment Design, and Gender, Disability, Equity and So</t>
+        </is>
+      </c>
+      <c r="Q141" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions climate change, disaster risk reduction, and climate resilience, which are all relevant to the climate risk profile.</t>
         </is>
       </c>
       <c r="R141" s="2" t="inlineStr">
@@ -13017,19 +13067,19 @@
           <t>Keyword (2)</t>
         </is>
       </c>
-      <c r="O142" s="2" t="inlineStr">
-        <is>
-          <t>International Environmental Consultant will lead ESIA processes, conduct ESDD/EHS DD assignments, and support clients in achieving regulatory compliance and sustainable performance.</t>
-        </is>
-      </c>
-      <c r="P142" s="2" t="inlineStr">
-        <is>
-          <t>Requires experience in international IFI-funded projects, particularly ESIA and ESDD, strong analytical and writing skills, ability to work independently and collaboratively.</t>
-        </is>
-      </c>
-      <c r="Q142" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on environmental and social impact assessments for infrastructure, energy, transport, industrial, and environmental projects within the global finance sector.</t>
+      <c r="O142" s="6" t="inlineStr">
+        <is>
+          <t>Lead and/or contribute to international ESIA processes for large-scale infrastructure, energy, transport, industrial, and environmental projects. Conduct or support Environmental and Social Due Diligence (ESDD)/ Environmental, Health and Safety Due Diligence (EHS DD) assignments for IFIs, lenders, and private investors. Conduct or support Environmental Due Diligence (EDD)/ Environmental, Health and Safety Due Diligence (EHS DD) assignments in relation to mergers and acquisitions (M&amp;A). Coordinat</t>
+        </is>
+      </c>
+      <c r="P142" s="6" t="inlineStr">
+        <is>
+          <t>Excellent analytical, writing, and communication skills. Ability to work independently and collaboratively in multicultural environments.</t>
+        </is>
+      </c>
+      <c r="Q142" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] The job description mentions working on sustainability-driven assignments, international environmental and social impact assessments, and environmental and social due diligence, which are all related to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
       <c r="R142" s="2" t="inlineStr"/>
@@ -13094,19 +13144,19 @@
           <t>Keyword (2)</t>
         </is>
       </c>
-      <c r="O143" s="2" t="inlineStr">
-        <is>
-          <t>As a Junior Consultant, you'll help clients identify sustainable investment opportunities and translate them into concrete projects.</t>
-        </is>
-      </c>
-      <c r="P143" s="2" t="inlineStr">
-        <is>
-          <t>You need to have a bachelor's degree in a relevant field like energy, technology, engineering, or finance, along with strong analytical and communication skills.</t>
-        </is>
-      </c>
-      <c r="Q143" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to the transition towards a more sustainable future by supporting investments in renewable energy projects.</t>
+      <c r="O143" s="6" t="inlineStr">
+        <is>
+          <t>What are you going to do? Als (Junior) Consultant Green Investments word je onderdeel van het INVEST-team: een hecht en enthousiast team dat dagelijks werkt aan Europese of nationale impactvolle projecten. Je staat in direct contact met onze klanten en helpt hen bij het realiseren van duurzame investeringen. Dat doe je door kansen te signaleren, mee te denken over de beste aanpak en subsidies en regelingen te vertalen naar concrete projecten. Je brengt al een basiskennis mee van hernieuwbare ene</t>
+        </is>
+      </c>
+      <c r="P143" s="6" t="inlineStr">
+        <is>
+          <t>basiskennis van hernieuwbare energiesystemen, financiële modellering, technische berekeningen, Excel, schriftelijke en mondelinge communicatieve vaardigheden</t>
+        </is>
+      </c>
+      <c r="Q143" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions 'duurzame investeringen' (sustainable investments), 'hernieuwbare energiesystemen' (renewable energy systems), and 'energietransitie' (energy transition), which are all related to renewable energy and environmental science, fitting the clean_energ</t>
         </is>
       </c>
       <c r="R143" s="2" t="inlineStr"/>
@@ -13173,7 +13223,11 @@
       </c>
       <c r="O144" s="2" t="inlineStr"/>
       <c r="P144" s="2" t="inlineStr"/>
-      <c r="Q144" s="2" t="inlineStr"/>
+      <c r="Q144" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] Job title contains 'Climate Action', indicating a strong focus on climate-related issues.</t>
+        </is>
+      </c>
       <c r="R144" s="2" t="inlineStr"/>
       <c r="S144" s="3" t="inlineStr">
         <is>
@@ -13236,9 +13290,21 @@
           <t>Keyword (2)</t>
         </is>
       </c>
-      <c r="O145" s="2" t="inlineStr"/>
-      <c r="P145" s="2" t="inlineStr"/>
-      <c r="Q145" s="2" t="inlineStr"/>
+      <c r="O145" s="6" t="inlineStr">
+        <is>
+          <t>The Project Finance / Investor Outreach Advisor will manage relationships with investors, develop financing strategies, and support the outreach process to secure investment for utility-scale solar projects in Southern Africa. Day-to-day responsibilities include analyzing financial models, analyzing investment opportunities, drafting proposals, and managing investor communication with relevant investors (development finance institutions, energy funds, infrastructure investors, family offices).</t>
+        </is>
+      </c>
+      <c r="P145" s="6" t="inlineStr">
+        <is>
+          <t>Project Finance, Financial Modeling, Investment Analysis, Business Development, Investor Outreach, Relationship Management, Market Research, Analytics, Reporting, Communication, Negotiation</t>
+        </is>
+      </c>
+      <c r="Q145" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] Job title contains 'Climate Risk Analysis' indicating a strong focus on climate risk</t>
+        </is>
+      </c>
       <c r="R145" s="2" t="inlineStr"/>
       <c r="S145" s="3" t="inlineStr">
         <is>
@@ -13313,19 +13379,19 @@
           <t>Keyword (2)</t>
         </is>
       </c>
-      <c r="O146" s="2" t="inlineStr">
-        <is>
-          <t>Leads and supports environmental projects focused on reef conservation and intervention actions within the Great Barrier Reef World Heritage Area.</t>
-        </is>
-      </c>
-      <c r="P146" s="2" t="inlineStr">
-        <is>
-          <t>Requires experience managing complex environmental projects, strong problem-solving, analytical, and communication skills, and government procurement knowledge.</t>
-        </is>
-      </c>
-      <c r="Q146" s="2" t="inlineStr">
-        <is>
-          <t>Protects a globally significant natural asset, the Great Barrier Reef, through project management and stakeholder engagement in marine conservation efforts.</t>
+      <c r="O146" s="6" t="inlineStr">
+        <is>
+          <t>We are seeking a dynamic and experienced environmental project manager to lead and support island, marine and vulnerable species management, including conservation and intervention actions, within the Great Barrier Reef World Heritage Area. This is a dynamic position with a wide range of responsibilities including project planning and reporting, risk assessment, project evaluation, procurement, communication product development, stakeholder and Traditional Owner engagement, and some marine-based</t>
+        </is>
+      </c>
+      <c r="P146" s="6" t="inlineStr">
+        <is>
+          <t>Strong problem-solving, analytical and communication skills, Experience with government procurement &amp; contract management, Ability to manage competing priorities under pressure, Stakeholder engagement experience, including Traditional Owners</t>
+        </is>
+      </c>
+      <c r="Q146" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions reef conservation, marine and vulnerable species management, and environmental project management, which are related to renewable energy, environmental science, and conservation, making it a good fit for the clean_energy_adjacent profile.</t>
         </is>
       </c>
       <c r="R146" s="2" t="inlineStr">
@@ -13406,19 +13472,19 @@
           <t>Keyword (2)</t>
         </is>
       </c>
-      <c r="O147" s="2" t="inlineStr">
-        <is>
-          <t>As a Business Operational Risk Manager, you will provide expert advice on trading risks for the Gas, Power, and Carbon desks. You will partner with trading teams to develop risk management strategies and improve operational processes.</t>
-        </is>
-      </c>
-      <c r="P147" s="2" t="inlineStr">
-        <is>
-          <t>5+ years of experience in non-financial risk management, particularly in operational risk, is required. Commodity market expertise, specifically in gas, power, and carbon markets, is a plus.</t>
-        </is>
-      </c>
-      <c r="Q147" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on the commodities trading industry within the global financial services sector, contributing to climate change mitigation and sustainable finance initiatives.</t>
+      <c r="O147" s="6" t="inlineStr">
+        <is>
+          <t>In this role, you will use your commodities trading knowledge and analytical skills to provide expert advice on front line trading risks for the Gas, Power and Carbon desks. You will support and facilitate the continued improvement of processes, controls and operational risk awareness and culture across our businesses. As a subject matter expert you will partner with the trading desks and leverage your technical expertise to develop a comprehensive knowledge of all processes to proactively manag</t>
+        </is>
+      </c>
+      <c r="P147" s="6" t="inlineStr">
+        <is>
+          <t>Commodities trading knowledge, analytical skills, stakeholder engagement, relationship management, problem-solving</t>
+        </is>
+      </c>
+      <c r="Q147" s="6" t="inlineStr">
+        <is>
+          <t>[carbon_markets] The job description mentions experience in Carbon markets as a plus, and the role involves providing expert advice on front line trading risks for the Gas, Power and Carbon desks, indicating a strong connection to carbon markets and emissions trading.</t>
         </is>
       </c>
       <c r="R147" s="2" t="inlineStr">
@@ -13499,19 +13565,19 @@
           <t>Keyword (2)</t>
         </is>
       </c>
-      <c r="O148" s="2" t="inlineStr">
-        <is>
-          <t>A Sales Trader will develop and execute short-term and long-term trading strategies for the Cooling market, helping clients achieve sustainability goals within the global refrigeration sector.</t>
-        </is>
-      </c>
-      <c r="P148" s="2" t="inlineStr">
-        <is>
-          <t>Fluency in Chinese, English, and Dutch or Italian is required, along with at least 2 years of experience in sales and business development.</t>
-        </is>
-      </c>
-      <c r="Q148" s="2" t="inlineStr">
-        <is>
-          <t>This role connects to climate, ESG, sustainability, and finance by working with clients in the refrigeration industry to help them transition towards more sustainable practices.</t>
+      <c r="O148" s="6" t="inlineStr">
+        <is>
+          <t>Managing, maintaining, and expanding the client portfolio, with a focus on new business and high potential markets. Developing our trading activities for short and long-term strategies in line with the company’s objectives. Conduct market research where you will research and analyse market trends, technological advancements, potential clients, and their industry trends, to help inform business decisions. Creating analyses and presentations to update your clients and stakeholders with market tren</t>
+        </is>
+      </c>
+      <c r="P148" s="6" t="inlineStr">
+        <is>
+          <t>Understanding of Carbon Markets including trading dynamics related to the buy and sell side of transactions, negotiation, and other macroeconomic factors. Experienced in analysing global policies and their repercussions within the Renewable Energy sector.</t>
+        </is>
+      </c>
+      <c r="Q148" s="6" t="inlineStr">
+        <is>
+          <t>[carbon_markets] The job description mentions 'Carbon Markets including trading dynamics related to the buy and sell side of transactions, negotiation, and other macroeconomic factors' and 'Environmental commodities', indicating a strong focus on carbon markets and environmental sustainability.</t>
         </is>
       </c>
       <c r="R148" s="2" t="inlineStr">
@@ -13592,19 +13658,24 @@
           <t>Keyword (2)</t>
         </is>
       </c>
-      <c r="O149" s="2" t="inlineStr">
-        <is>
-          <t>Advises clients on complex energy projects across diverse sectors like renewable power, low-carbon fuels, and sustainable infrastructure.</t>
-        </is>
-      </c>
-      <c r="P149" s="2" t="inlineStr">
-        <is>
-          <t>Requires extensive experience in project development, construction, finance, and regulatory compliance; strong negotiation skills and ability to manage multi-disciplinary teams.</t>
-        </is>
-      </c>
-      <c r="Q149" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on the global energy transition, advising clients on complex projects related to climate change mitigation and sustainability.</t>
+      <c r="O149" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As a Senior Associate / Legal Director, you will: 
+   * Lead the drafting and negotiation of complex project, construction and finance documentation
+   * Take primary responsibility for managing transactions, including supervising junior lawyers and coordinating multi-jurisdictional teams
+   * Provide strategic advice to clients on risk allocation, structuring and execution of projects
+   * Play a key role in client relationship management, acting as a trusted advisor on ongoing and new matters
+</t>
+        </is>
+      </c>
+      <c r="P149" s="6" t="inlineStr">
+        <is>
+          <t>Strong technical legal expertise, experience leading complex transactions, ability to manage matters, supervise junior lawyers, business development, client relationship management, commercial awareness, drafting, analytical and communication skills</t>
+        </is>
+      </c>
+      <c r="Q149" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions experience in renewable energy, low-carbon infrastructure, carbon markets, and natural capital, which are all relevant to the clean energy and environmental sectors.</t>
         </is>
       </c>
       <c r="R149" s="2" t="inlineStr">
@@ -13681,19 +13752,19 @@
           <t>Keyword (2)</t>
         </is>
       </c>
-      <c r="O150" s="2" t="inlineStr">
-        <is>
-          <t>Deputy General Manager Business Development</t>
-        </is>
-      </c>
-      <c r="P150" s="2" t="inlineStr">
-        <is>
-          <t>This role involves driving business growth by identifying new opportunities, developing strategic plans, and fostering strong business relationships. The candidate will play a critical role in expanding market presence and ensuring business targets are met.</t>
-        </is>
-      </c>
-      <c r="Q150" s="2" t="inlineStr">
-        <is>
-          <t>Renewable energy sector; experience in the renewable energy sector, especially solar, wind, and energy storage, will be advantageous.</t>
+      <c r="O150" s="6" t="inlineStr">
+        <is>
+          <t>The role involves driving business growth by identifying new opportunities, developing strategic plans, and fostering strong business relationships. Key responsibilities include planning and executing business development strategies, negotiating contracts, and working collaboratively with internal teams to achieve sales and revenue goals.</t>
+        </is>
+      </c>
+      <c r="P150" s="6" t="inlineStr">
+        <is>
+          <t>Contract Negotiation, Business Relationship Management, Sales management, communication, leadership, problem-solving, strategizing</t>
+        </is>
+      </c>
+      <c r="Q150" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions renewable energy development, solar, wind, and hybrid systems, which are directly related to clean energy. The company's focus on transitioning toward clean and intelligent energy systems also supports this classification.</t>
         </is>
       </c>
       <c r="R150" s="2" t="inlineStr">
@@ -13770,19 +13841,19 @@
           <t>Keyword (2)</t>
         </is>
       </c>
-      <c r="O151" s="2" t="inlineStr">
-        <is>
-          <t>Social media manager for AIDMI, responsible for developing and implementing social media strategies, creating engaging content, and managing website development and maintenance.</t>
-        </is>
-      </c>
-      <c r="P151" s="2" t="inlineStr">
-        <is>
-          <t>Proficiency in HTML, CSS, JavaScript, PHP, CMS platforms (WordPress, Drupal, Joomla), web development frameworks (React, Angular), and data analysis tools.</t>
-        </is>
-      </c>
-      <c r="Q151" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on the non-profit sector, specifically AIDMI's social media presence and website development for humanitarian work and disaster response operations.</t>
+      <c r="O151" s="6" t="inlineStr">
+        <is>
+          <t>Manage AIDMIs social media accounts, including Instagram, Twitter, LinkedIn, Facebook, and WhatsApp Chat Bot Integration and Management. Develop and implement social media strategies that align with AIDMIs goals and Create engaging and educational social media content, including graphics, videos, and Monitor social media trends and good practices, and incorporate new techniques and tools to remain at the forefront. Collaborate, co-create and implement at least three social media campaigns that s</t>
+        </is>
+      </c>
+      <c r="P151" s="6" t="inlineStr">
+        <is>
+          <t>HTML, CSS, JavaScript, PHP, photography, CMS platforms, web development frameworks, social media good practices, short video making, writing, editing, Gujarati, Hindi, English</t>
+        </is>
+      </c>
+      <c r="Q151" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job title mentions 'Disaster Risk and Climate Resilience', indicating a focus on climate-related risks, and the company name 'All India Disaster Mitigation Institute' also suggests a connection to disaster risk and climate resilience.</t>
         </is>
       </c>
       <c r="R151" s="2" t="inlineStr"/>
@@ -13859,19 +13930,19 @@
           <t>Keyword (2)</t>
         </is>
       </c>
-      <c r="O152" s="2" t="inlineStr">
-        <is>
-          <t>Deputy Manager for solar operations, responsible for overseeing maintenance activities, reporting, vendor management, and team coordination.</t>
-        </is>
-      </c>
-      <c r="P152" s="2" t="inlineStr">
-        <is>
-          <t>8-14 years of experience in solar energy operations, strong technical skills, knowledge of O&amp;M practices, database systems, and communication skills.</t>
-        </is>
-      </c>
-      <c r="Q152" s="2" t="inlineStr">
-        <is>
-          <t>ReNew is a leader in the Indian renewable energy sector, focusing on clean energy solutions to address climate change and promote sustainable development.</t>
+      <c r="O152" s="6" t="inlineStr">
+        <is>
+          <t>Proven work experience as an Operations Manager or similar role in the Solar Energy sector. Experience with inventory management, database systems, or similar software is beneficial. Relevant training and/or certifications as an Operations Associate. O&amp;M Manager is responsible for scheduling cleaning, breakdown, and preventive maintenance activities. All reports must be sent to the client with comments within 4 hours of completing the activity. O&amp;M Manager must prepare MIS reports, verify vendor</t>
+        </is>
+      </c>
+      <c r="P152" s="6" t="inlineStr">
+        <is>
+          <t>Inventory management, database systems, operations management, communication, listening, computer proficiency</t>
+        </is>
+      </c>
+      <c r="Q152" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions solar energy, renewable energy, and utility-scale solar energy projects, which are all related to clean energy and environmental sustainability.</t>
         </is>
       </c>
       <c r="R152" s="2" t="inlineStr">
@@ -13956,19 +14027,19 @@
           <t>Keyword (2)</t>
         </is>
       </c>
-      <c r="O153" s="2" t="inlineStr">
-        <is>
-          <t>The Deputy Manager-Wind Engineering will provide technical support to the asset operation team, resolve technical issues, and ensure the smooth operation of wind turbines.</t>
-        </is>
-      </c>
-      <c r="P153" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have a B.Tech/B.E. in Electrical Engineering with 8-10 years of experience in wind energy engineering, including expertise in SGRE and converter technology.</t>
-        </is>
-      </c>
-      <c r="Q153" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to ReNew's mission of decarbonizing India's power sector through efficient and sustainable wind energy solutions.</t>
+      <c r="O153" s="6" t="inlineStr">
+        <is>
+          <t>Resolution of technical concerns raised from Asset operations, Close coordination with Wind OEMs for technical resolutions, Extended support to self-operation team, Performance monitoring of operational assets, Health audit of wind turbines, Preparation of technical specifications/drawing/SOPs/manuals, Drawing/circuit diagram/specifically study, New improvement project trial, tracking and analysis at site, Analytics tools use for RCA and technical issues study</t>
+        </is>
+      </c>
+      <c r="P153" s="6" t="inlineStr">
+        <is>
+          <t>Technical skills in wind engineering, experience with SGRE and Converter, analytics tools, RCA, technical issue analysis</t>
+        </is>
+      </c>
+      <c r="Q153" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description is for a Deputy Manager-Wind Engineering role, which involves working with wind energy projects, and the company ReNew is a renewable energy company, indicating a strong connection to clean energy and environmental sustainability</t>
         </is>
       </c>
       <c r="R153" s="2" t="inlineStr">
@@ -14049,19 +14120,19 @@
           <t>Keyword (2)</t>
         </is>
       </c>
-      <c r="O154" s="2" t="inlineStr">
-        <is>
-          <t>Oversees the operation and maintenance of high-voltage electrical and mechanical systems, including HVAC, pumps, and wastewater treatment facilities. This role involves preventative maintenance, troubleshooting, repair, and coordination with other departments.</t>
-        </is>
-      </c>
-      <c r="P154" s="2" t="inlineStr">
-        <is>
-          <t>Experience in operating and maintaining electrical and mechanical systems, strong troubleshooting skills, knowledge of safety protocols, and experience with SAP reporting.</t>
-        </is>
-      </c>
-      <c r="Q154" s="2" t="inlineStr">
-        <is>
-          <t>The role contributes to the development and operation of renewable energy projects, focusing on the efficient and sustainable use of resources to reduce carbon emissions.</t>
+      <c r="O154" s="6" t="inlineStr">
+        <is>
+          <t>Operation and maintenance of HT, LT Electrical System. Mechanical HVAC, Pump House, ETP, STP&amp; Shift team handling -Utility. Roles to Perform preventative maintenance on electrical &amp; mechanical systems and components by the team. Troubleshoot problems and make timely repairs. Plan, execute, and coordinate within the department. Tools requirement, spare management, and team management. Shift schedule, corrective actions, special activities planning. Calibration and testing of Electrical, Mechanica</t>
+        </is>
+      </c>
+      <c r="P154" s="6" t="inlineStr">
+        <is>
+          <t>Maintenance Planning, Troubleshooting, Hands on experience of PLC, servo drives, gearboxes, Spare planning and forecasting, Preventive and predictive maintenance, Knowledge of PC based systems and software handling, data backup plan, Root Cause Analysis</t>
+        </is>
+      </c>
+      <c r="Q154" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions renewable energy, solar energy projects, and utility-scale wind energy projects, which are all related to clean energy. The company, ReNew, is also described as one of the largest renewable energy companies globally.</t>
         </is>
       </c>
       <c r="R154" s="2" t="inlineStr">
@@ -14142,19 +14213,19 @@
           <t>Keyword (2)</t>
         </is>
       </c>
-      <c r="O155" s="2" t="inlineStr">
-        <is>
-          <t>As Finance Lead – WEET, you will provide end-to-end project finance leadership across the full project lifecycle.</t>
-        </is>
-      </c>
-      <c r="P155" s="2" t="inlineStr">
-        <is>
-          <t>A relevant tertiary qualification in accounting, finance or a related discipline (CA/CPA desirable), 5-8 years' experience in project finance and strong communication skills are required.</t>
-        </is>
-      </c>
-      <c r="Q155" s="2" t="inlineStr">
-        <is>
-          <t>This role connects to finance and project management within the global consulting services industry, impacting infrastructure development and urban planning.</t>
+      <c r="O155" s="6" t="inlineStr">
+        <is>
+          <t>As Finance Lead – WEET, you will act as the key commercial and financial partner to Project Managers and operational leaders. Reporting to the CFO, this role is responsible for driving financial performance, strengthening project governance, and improving working capital outcomes across the service line. You will provide end-to-end project finance leadership across the full project lifecycle – from bid support and project set-up, through delivery and revenue recognition, to project close. Lead f</t>
+        </is>
+      </c>
+      <c r="P155" s="6" t="inlineStr">
+        <is>
+          <t>Project accounting, commercial finance, ERP, project lifecycle management, Percentage of Completion (PoC) revenue recognition, leadership, influencing, mentoring, analytical capability, problem-solving, attention to detail, communication, financial insights</t>
+        </is>
+      </c>
+      <c r="Q155" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[clean_energy_adjacent] The job title 'Finance Lead - Water, Environment &amp; Energy Transition' and the company's focus on sustainable solutions and infrastructure indicate a connection to environmental topics, specifically water, environment, and energy transition, which aligns with the clean energy </t>
         </is>
       </c>
       <c r="R155" s="2" t="inlineStr">
@@ -14235,19 +14306,19 @@
           <t>Keyword (2)</t>
         </is>
       </c>
-      <c r="O156" s="2" t="inlineStr">
-        <is>
-          <t>The Strategic Investment Research Analyst will contribute to global intellectual capital by producing quantitative and qualitative research on investment themes, supporting Mercer’s Wealth business and clients.</t>
-        </is>
-      </c>
-      <c r="P156" s="2" t="inlineStr">
-        <is>
-          <t>A candidate should have a bachelor's degree in finance or a related field, strong analytical skills, and experience with financial modeling and data analysis tools.</t>
-        </is>
-      </c>
-      <c r="Q156" s="2" t="inlineStr">
-        <is>
-          <t>This role is within the global investments sector, focusing on providing research and insights to support institutional investors in their investment decisions.</t>
+      <c r="O156" s="6" t="inlineStr">
+        <is>
+          <t>Assist the global strategic research team in providing quantitative analytics, and qualitative research to support our strategic research views on long term themes, and related communication material. Keep up-to-date on current investment trends and themes; help to identify and develop Mercer’s investment themes and opportunities. Drive the production side of our processes, for instance maintaining our theme summary material or quarterly thematic updates, project managing some of our material to</t>
+        </is>
+      </c>
+      <c r="P156" s="6" t="inlineStr">
+        <is>
+          <t>Strong researching and critical-thinking skills; ability to interpret and use qualitative and quantitative data to reach conclusions and explain them in terms that others can understand. Proven experience of research Investment knowledge: market awareness, asset class knowledge, asset allocation kno</t>
+        </is>
+      </c>
+      <c r="Q156" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions 'responsible investment' and 'sustainable investment team', indicating a focus on ESG investing and sustainable finance.</t>
         </is>
       </c>
       <c r="R156" s="2" t="inlineStr">
@@ -14328,19 +14399,19 @@
           <t>Keyword (2)</t>
         </is>
       </c>
-      <c r="O157" s="2" t="inlineStr">
-        <is>
-          <t>This Assistant Director/Deputy Director role within ASSOCHAM's Energy &amp; Infrastructure division focuses on advancing advocacy and driving sector-focused initiatives for sustainable growth.</t>
-        </is>
-      </c>
-      <c r="P157" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should possess a B.Tech/B.Engg or MBA with experience in economics, policy, infrastructure management, and strong communication skills.</t>
-        </is>
-      </c>
-      <c r="Q157" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to the energy and infrastructure sector by promoting sustainable growth through government engagement, advocacy, and project development.</t>
+      <c r="O157" s="6" t="inlineStr">
+        <is>
+          <t>The position is within the Energy &amp; Infrastructure Vertical at ASSOCHAM, playing a pivotal role in advancing division’s advocacy and industry engagement agenda. The incumbent will lead high-impact policy advocacy and drive sector-focused initiatives spanning Energy, Power, Renewable Energy, Green Hydrogen, Transmission, Highways &amp; Tunnelling, and Civil Aviation. This role will act as a catalyst for transformative government initiatives, working closely with policymakers, industry leaders, and ke</t>
+        </is>
+      </c>
+      <c r="P157" s="6" t="inlineStr">
+        <is>
+          <t>Policy &amp; Regulatory Understanding, Sectoral Knowledge, Research &amp; Analytical Skills, Government &amp; Institutional Liaison, Project &amp; Event Management, Membership &amp; Revenue Development, Communication &amp; Documentation, Stakeholder Management, Strategic Thinking, Communication &amp; Influence, Networking &amp; Re</t>
+        </is>
+      </c>
+      <c r="Q157" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions renewable energy, green hydrogen, energy transition, and other related topics, which are relevant to the clean energy and environmental science fields.</t>
         </is>
       </c>
       <c r="R157" s="2" t="inlineStr">
@@ -14421,19 +14492,19 @@
           <t>Keyword (2)</t>
         </is>
       </c>
-      <c r="O158" s="2" t="inlineStr">
-        <is>
-          <t>Assistant Manager for Solar O&amp;M will be responsible for overseeing the operational efficiency of solar power plants in Barmer, Rajasthan.</t>
-        </is>
-      </c>
-      <c r="P158" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should possess a B.E/B.Tech degree in Electrical Engineering with 6-10 years of experience in solar energy operations and maintenance.</t>
-        </is>
-      </c>
-      <c r="Q158" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to ReNew's mission of decarbonizing India through the operation and maintenance of solar power plants, aligning with climate action and renewable energy goals.</t>
+      <c r="O158" s="6" t="inlineStr">
+        <is>
+          <t>Candidate shall be posted in general shift &amp; will have to make himself available as and when required in any critical condition to attain the site project work. He will be responsible to electrical work in project execution and completion till the commissioning. Working knowledge in Hindi, English language is essential. Computer literate with knowledge of MS Word, Excel, Power point, auto-cad. Installation, testing and commissioning of electrical equipment, cables as per standards and customer r</t>
+        </is>
+      </c>
+      <c r="P158" s="6" t="inlineStr">
+        <is>
+          <t>Working knowledge in Hindi, English language, Computer literate with knowledge of MS Word, Excel, Power point, auto-cad</t>
+        </is>
+      </c>
+      <c r="Q158" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions renewable energy, solar energy projects, and clean energy, which are all related to the clean energy adjacent profile. The company's mission to provide clean, safe, affordable, and sustainable energy also supports this classification.</t>
         </is>
       </c>
       <c r="R158" s="2" t="inlineStr">
@@ -14518,19 +14589,19 @@
           <t>Keyword (2)</t>
         </is>
       </c>
-      <c r="O159" s="2" t="inlineStr">
-        <is>
-          <t>Leads complex regulatory change projects within the asset management domain, ensuring delivery against strict timelines while working with cross-functional teams.</t>
-        </is>
-      </c>
-      <c r="P159" s="2" t="inlineStr">
-        <is>
-          <t>Requires a graduate degree, PRINCE2 certification, experience delivering regulatory change projects in Asset Management environments, and strong understanding of relevant regulations.</t>
-        </is>
-      </c>
-      <c r="Q159" s="2" t="inlineStr">
-        <is>
-          <t>The role connects to finance and asset management within the financial services industry, focusing on regulatory compliance and sustainable investment practices.</t>
+      <c r="O159" s="6" t="inlineStr">
+        <is>
+          <t>Lead and manage the full end-to-end lifecycle delivery of medium to highly complex regulatory change projects from initiation through implementation and closure. Define and manage the business case, project objectives, scope, resources and expected benefits for assigned initiatives. Act as the primary delivery owner ensuring alignment across stakeholders and teams across geographies. Develop and maintain high-quality project plans including risk mitigation strategies and structured work packages</t>
+        </is>
+      </c>
+      <c r="P159" s="6" t="inlineStr">
+        <is>
+          <t>Project management, stakeholder management, risk mitigation, project planning, budgeting, regulatory frameworks (AIFMD, MiFID, PRIIPs, Shareholder Reporting, SFDR/SDR and EMIR), asset management platforms, vendor systems, external data providers</t>
+        </is>
+      </c>
+      <c r="Q159" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions 'sustainable investing' and 'SFDR' which are related to sustainable finance and ESG investing. The role involves leading regulatory change initiatives within the asset management domain, which also aligns with sustainable finance.</t>
         </is>
       </c>
       <c r="R159" s="2" t="inlineStr">
@@ -14607,19 +14678,19 @@
           <t>Keyword (2)</t>
         </is>
       </c>
-      <c r="O160" s="2" t="inlineStr">
-        <is>
-          <t>Leads the Fund Master function within Investment Data Services to ensure high-quality fund data management using Fundipedia. This role drives data governance, reconciliation, and strategic initiatives across investment operations.</t>
-        </is>
-      </c>
-      <c r="P160" s="2" t="inlineStr">
-        <is>
-          <t>Requires 10+ years of experience in investment operations or data services with expertise in EDM platforms like Fundipedia. Strong leadership skills are essential for managing a team and driving cross-functional initiatives.</t>
-        </is>
-      </c>
-      <c r="Q160" s="2" t="inlineStr">
-        <is>
-          <t>The role focuses on the financial industry, specifically within investment operations, where data quality and regulatory compliance are critical for fund management and reporting.</t>
+      <c r="O160" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lead Fundipedia implementation and enhancement projects to optimize fund data management. Define and enforce fund data governance frameworks, including pricing governance and quality controls. Own the fund master data strategy, ensuring accuracy, timeliness, and completeness across internal and external platforms. Drive automation, standardization, and scalability of data operations using Fundipedia and other tools. Act as escalation point for fund data discrepancies, reconciliation exceptions, </t>
+        </is>
+      </c>
+      <c r="P160" s="6" t="inlineStr">
+        <is>
+          <t>Deep expertise in fund structures, share classes, and investment products. Hands-on experience with Fundipedia or similar EDM platforms. Strong understanding of regulatory frameworks (e.g., UCITS, MiFID II, SFDR). Proficiency in data tools (Excel, SQL, Power BI, Python, VBA). Excellent leadership, s</t>
+        </is>
+      </c>
+      <c r="Q160" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions SFDR, which is a key regulation in sustainable finance, and also mentions overseeing sustainability data integration and reporting across investment platforms, indicating a focus on ESG considerations in investment operations.</t>
         </is>
       </c>
       <c r="R160" s="2" t="inlineStr"/>
@@ -14692,19 +14763,19 @@
           <t>Keyword (2)</t>
         </is>
       </c>
-      <c r="O161" s="2" t="inlineStr">
-        <is>
-          <t>A Senior Analyst will play a key role in ensuring the effectiveness of pre- and post-trade mandate restriction monitoring for Investment Teams.</t>
-        </is>
-      </c>
-      <c r="P161" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have hands-on experience with Aladdin (or equivalent portfolio management systems) and strong understanding of investment guidelines, regulatory compliance, and mandate restriction management.</t>
-        </is>
-      </c>
-      <c r="Q161" s="2" t="inlineStr">
-        <is>
-          <t>This role is within the Investment Management sector, focusing on ensuring compliance with regulations and investment guidelines to mitigate risk and maintain control over investment activities.</t>
+      <c r="O161" s="6" t="inlineStr">
+        <is>
+          <t>Work within a team responsible for Investment Restriction Compliance Management violation oversight, onboarding, and query resolution. Oversee daily reviews of overnight violation monitoring; escalate and track issues through to resolution. Partner with Investment Desks, Product, and Client Executives across asset classes on investment guideline matters and pre-trade violation overrides. Maintain broker and ready-to-trade coding in Aladdin and assist Trading Desks with related queries and escala</t>
+        </is>
+      </c>
+      <c r="P161" s="6" t="inlineStr">
+        <is>
+          <t>Strong experience in Investment Restriction Monitoring and compliance processes within Asset Management. Hands-on experience with Aladdin (or equivalent portfolio management systems). Solid understanding of investment guidelines, regulatory compliance, and mandate restriction management. Proficiency</t>
+        </is>
+      </c>
+      <c r="Q161" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions SFDR, which is a key regulation in sustainable finance, and also mentions investment restriction monitoring and compliance processes, which are relevant to ESG investing and sustainable finance.</t>
         </is>
       </c>
       <c r="R161" s="2" t="inlineStr"/>
@@ -14777,19 +14848,19 @@
           <t>Keyword (2)</t>
         </is>
       </c>
-      <c r="O162" s="2" t="inlineStr">
-        <is>
-          <t>Leads the Fund Master function within Investment Data Services, ensuring high-quality, complete, and compliant fund data management using Fundipedia.</t>
-        </is>
-      </c>
-      <c r="P162" s="2" t="inlineStr">
-        <is>
-          <t>Experience in fund data management, strong analytical skills, experience with Fundipedia, knowledge of financial regulations and compliance.</t>
-        </is>
-      </c>
-      <c r="Q162" s="2" t="inlineStr">
-        <is>
-          <t>Financial services industry, investment operations, data governance and regulatory compliance.</t>
+      <c r="O162" s="6" t="inlineStr">
+        <is>
+          <t>To lead the Fund Master function within Investment Data Services, ensuring high-quality, complete, and compliant fund data management using Fundipedia. This role is pivotal in driving data governance, reconciliation, and strategic data initiatives across investment operations. Lead Fundipedia implementation and enhancement projects to optimize fund data management. Define and enforce fund data governance frameworks, including pricing governance and quality controls. Own the fund master data stra</t>
+        </is>
+      </c>
+      <c r="P162" s="6" t="inlineStr">
+        <is>
+          <t>Deep expertise in fund structures, share classes, and investment products. Hands-on experience with Fundipedia or similar EDM platforms. Strong understanding of regulatory frameworks (e.g., UCITS, MiFID II, SFDR). Proficiency in data tools (Excel, SQL, Power BI, Python, VBA). Excellent leadership, s</t>
+        </is>
+      </c>
+      <c r="Q162" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions SFDR, which is a key regulation in sustainable finance, and also mentions overseeing sustainability data integration and reporting across investment platforms, indicating a focus on ESG considerations in investment operations.</t>
         </is>
       </c>
       <c r="R162" s="2" t="inlineStr"/>
@@ -14854,19 +14925,19 @@
           <t>Keyword (1)</t>
         </is>
       </c>
-      <c r="O163" s="2" t="inlineStr">
-        <is>
-          <t>An ESG Assurance Assessor will deliver independent verification services for leading companies' sustainability performance and ensure accurate reporting against regulatory requirements.</t>
-        </is>
-      </c>
-      <c r="P163" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have a degree in a relevant field, practical experience delivering assurance engagements, and knowledge of key sustainability frameworks.</t>
-        </is>
-      </c>
-      <c r="Q163" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to the growing field of corporate sustainability assurance within the global ESG market.</t>
+      <c r="O163" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deliver assurance services to multinational clients across a variety of sectors. Support Project Managers in the independent verification of GHG/ESG information, sustainability‑linked financial instruments, and product‑level claims. Contribute to high‑quality assessments that uphold ERM CVS’s reputation as a trusted global verification body. Build strong capability in sustainability assurance standards, environmental data methodologies, and emerging regulatory frameworks across APAC. Strengthen </t>
+        </is>
+      </c>
+      <c r="P163" s="6" t="inlineStr">
+        <is>
+          <t>Data analysis, advanced Excel skills, strong writing and communication skills, technical understanding of environmental impacts, emissions, climate change, and GHG, knowledge of key sustainability and GHG reporting frameworks, familiarity with auditing/assurance standards</t>
+        </is>
+      </c>
+      <c r="Q163" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] The job description mentions ESG, sustainability reporting, GHG disclosures, and climate action, which are all relevant to the general ESG profile. The role involves delivering assurance services to multinational clients, supporting project managers in independent verification of GHG/E</t>
         </is>
       </c>
       <c r="R163" s="2" t="inlineStr"/>
@@ -14931,19 +15002,19 @@
           <t>Semantic (0.622)</t>
         </is>
       </c>
-      <c r="O164" s="2" t="inlineStr">
-        <is>
-          <t>A Bid Manager / Estimator will lead bid proposal activities, defining winning strategies and tailoring solutions to customer needs.</t>
-        </is>
-      </c>
-      <c r="P164" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have 3+ years of experience in electrical switchgear/switchboards and installations, a tertiary qualification in Electrical Engineering, and expertise in developing bids for the electrical sector.</t>
-        </is>
-      </c>
-      <c r="Q164" s="2" t="inlineStr">
-        <is>
-          <t>This role is within Eaton's Power Distribution Systems &amp; Services Division, supporting projects across various industries including renewable energy, mining, industrial, and utility sectors.</t>
+      <c r="O164" s="6" t="inlineStr">
+        <is>
+          <t>In this role, you will use your commodities trading knowledge and analytical skills to provide expert advice on front line trading risks for the Gas, Power and Carbon desks. You will support and facilitate the continued improvement of processes, controls and operational risk awareness and culture across our businesses. As a subject matter expert you will partner with the trading desks and leverage your technical expertise to develop a comprehensive knowledge of all processes to proactively manag</t>
+        </is>
+      </c>
+      <c r="P164" s="6" t="inlineStr">
+        <is>
+          <t>Commodities trading knowledge, analytical skills, stakeholder engagement, relationship management, problem-solving</t>
+        </is>
+      </c>
+      <c r="Q164" s="6" t="inlineStr">
+        <is>
+          <t>[carbon_markets] The job description mentions experience in Carbon markets as a plus, and the role involves providing expert advice on front line trading risks for the Gas, Power and Carbon desks, indicating a strong connection to carbon markets and emissions trading.</t>
         </is>
       </c>
       <c r="R164" s="2" t="inlineStr"/>
@@ -15008,19 +15079,19 @@
           <t>Semantic (0.651)</t>
         </is>
       </c>
-      <c r="O165" s="2" t="inlineStr">
-        <is>
-          <t>The Senior Sustainability Advisor will lead the development and implementation of sustainability strategies across Downer's Energy &amp; Utilities business unit.</t>
-        </is>
-      </c>
-      <c r="P165" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have a tertiary qualification in a relevant field, proven experience in sustainability, decarbonization, or climate-related roles, and expertise in GHG emissions reporting and performance metrics.</t>
-        </is>
-      </c>
-      <c r="Q165" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to the energy and utilities sector by helping companies meet their climate commitments and regulatory obligations.</t>
+      <c r="O165" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lead the delivery of sustainability and decarbonisation initiatives across operations and projects, including development of Project Sustainability Scorecards, KPIs and reporting dashboards. Manage GHG emissions accounting and emissions data validation in accordance with NGER and internal governance requirements. Provide specialist sustainability support for bids, tenders and operational decision-making, imbedding sustainability rating schemes (e.g. ISC), decarbonisation KPIs and ESG principles </t>
+        </is>
+      </c>
+      <c r="P165" s="6" t="inlineStr">
+        <is>
+          <t>Carbon modelling, forecasting, lifecycle emissions assessment, GHG emissions accounting, emissions data validation, sustainability rating schemes, decarbonisation KPIs, ESG principles, sustainable procurement, Scope 3 emissions considerations, strong analytical and technical skills.</t>
+        </is>
+      </c>
+      <c r="Q165" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job description mentions climate-related initiatives, GHG emissions accounting, carbon modelling, and decarbonisation, which are all relevant to climate risk. The role also involves managing emissions data validation, sustainability reporting, and performance metrics, which are cr</t>
         </is>
       </c>
       <c r="R165" s="2" t="inlineStr"/>
@@ -15085,19 +15156,19 @@
           <t>Keyword (1)</t>
         </is>
       </c>
-      <c r="O166" s="2" t="inlineStr">
-        <is>
-          <t>A dynamic petrophysicist will collaborate with a multidisciplinary team on challenging projects involving well logs, core data, and well test data.</t>
-        </is>
-      </c>
-      <c r="P166" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have expertise in petrophysical log data analysis, software platforms for processing and interpretation, and independent handling of complex analyses.</t>
-        </is>
-      </c>
-      <c r="Q166" s="2" t="inlineStr">
-        <is>
-          <t>The role is within the upstream business, focusing on petrophysical analysis to optimize oil and gas production.</t>
+      <c r="O166" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">We are seeking dynamic, creative, and resourceful candidates for our Bengaluru, India location to work on challenging petrophysical problems in collaboration with a multidisciplinary team of formation evaluation specialists and operations geologists based in Houston, USA. You will conduct applied project work using well logs, core data, and well test data, leveraging a variety of software platforms for petrophysical data processing and interpretation. Define project objectives, work scopes, and </t>
+        </is>
+      </c>
+      <c r="P166" s="6" t="inlineStr">
+        <is>
+          <t>Excellent communication and teamwork skills, with the ability to collaborate effectively with multidisciplinary global teams and take ownership of deliverables. Hands on experience across various stages of the field lifecycle in conventional and unconventional reservoirs with operational support, ex</t>
+        </is>
+      </c>
+      <c r="Q166" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions experience in renewable energy, low-carbon infrastructure, carbon markets, and natural capital, which are all relevant to the clean energy and environmental sectors.</t>
         </is>
       </c>
       <c r="R166" s="2" t="inlineStr"/>
@@ -15239,19 +15310,19 @@
           <t>Semantic (0.626)</t>
         </is>
       </c>
-      <c r="O168" s="2" t="inlineStr">
-        <is>
-          <t>This role involves managing a portfolio of retail customers in the Indian market, coordinating sales activities through authorized distributors and resellers.</t>
-        </is>
-      </c>
-      <c r="P168" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have experience in sales management, business development, and customer relationship management with proven ability to work across various locations and markets.</t>
-        </is>
-      </c>
-      <c r="Q168" s="2" t="inlineStr">
-        <is>
-          <t>The role is within the energy industry, specifically focused on the marketing and distribution of chemicals and lubricants products in India, contributing to ExxonMobil's efforts towards a sustainable future.</t>
+      <c r="O168" s="6" t="inlineStr">
+        <is>
+          <t>The role involves driving business growth by identifying new opportunities, developing strategic plans, and fostering strong business relationships. Key responsibilities include planning and executing business development strategies, negotiating contracts, and working collaboratively with internal teams to achieve sales and revenue goals.</t>
+        </is>
+      </c>
+      <c r="P168" s="6" t="inlineStr">
+        <is>
+          <t>Contract Negotiation, Business Relationship Management, Sales management, communication, leadership, problem-solving, strategizing</t>
+        </is>
+      </c>
+      <c r="Q168" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions renewable energy development, solar, wind, and hybrid systems, which are directly related to clean energy. The company's focus on transitioning toward clean and intelligent energy systems also supports this classification.</t>
         </is>
       </c>
       <c r="R168" s="2" t="inlineStr"/>
@@ -15328,19 +15399,19 @@
           <t>Semantic (0.622)</t>
         </is>
       </c>
-      <c r="O169" s="2" t="inlineStr">
-        <is>
-          <t>This internship provides an opportunity to gain practical experience in accounting and finance within a dynamic energy trading environment.</t>
-        </is>
-      </c>
-      <c r="P169" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have a background in Finance/Accounting and familiarity with IT tools.</t>
-        </is>
-      </c>
-      <c r="Q169" s="2" t="inlineStr">
-        <is>
-          <t>The role is focused on the energy trading industry, specifically for oil and biofuels, natural gas, and electricity.</t>
+      <c r="O169" s="6" t="inlineStr">
+        <is>
+          <t>Manage AIDMIs social media accounts, including Instagram, Twitter, LinkedIn, Facebook, and WhatsApp Chat Bot Integration and Management. Develop and implement social media strategies that align with AIDMIs goals and Create engaging and educational social media content, including graphics, videos, and Monitor social media trends and good practices, and incorporate new techniques and tools to remain at the forefront. Collaborate, co-create and implement at least three social media campaigns that s</t>
+        </is>
+      </c>
+      <c r="P169" s="6" t="inlineStr">
+        <is>
+          <t>HTML, CSS, JavaScript, PHP, photography, CMS platforms, web development frameworks, social media good practices, short video making, writing, editing, Gujarati, Hindi, English</t>
+        </is>
+      </c>
+      <c r="Q169" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] The job title mentions 'Disaster Risk and Climate Resilience', indicating a focus on climate-related risks, and the company name 'All India Disaster Mitigation Institute' also suggests a connection to disaster risk and climate resilience.</t>
         </is>
       </c>
       <c r="R169" s="2" t="inlineStr">
@@ -15417,19 +15488,19 @@
           <t>Semantic (0.671)</t>
         </is>
       </c>
-      <c r="O170" s="2" t="inlineStr">
-        <is>
-          <t>The ESG Product and Consulting Lead will build XcelGreen's product roadmap while consulting with clients on their ESG strategies.</t>
-        </is>
-      </c>
-      <c r="P170" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have experience building ESG products/services, strong analytical skills for data assessment, and proven consulting &amp; management consulting expertise in the ESG space.</t>
-        </is>
-      </c>
-      <c r="Q170" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on promoting sustainable practices within businesses across various industries, leveraging AI-powered solutions to drive environmental, social, and governance goals.</t>
+      <c r="O170" s="6" t="inlineStr">
+        <is>
+          <t>1) Product management - Continue to build XcelGreen with the technical know how of ESG SaaS, AI Agents and ESG Regulations understanding, continue the journey from 0-1. 2) ESG Consulting - Managing ESG consulting projects, developing sustainability strategies, delivering training sessions, and fostering strong client relationships. 3) Start-up Evangelist - Grow the start-up with lean resources and budget. We are looking for 2-3 people unicorn model with AI tools &amp; resources available. The ESG Co</t>
+        </is>
+      </c>
+      <c r="P170" s="6" t="inlineStr">
+        <is>
+          <t>ESG SaaS, AI Agents, ESG Regulations, AI tools, Strong Analytical Skills, Excellent Communication skills, Proficiency in Training programs and workshops, Ability to lead and collaborate with cross-functional teams, Knowledge of ESG frameworks, global reporting standards, and regional compliance regu</t>
+        </is>
+      </c>
+      <c r="Q170" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[general_esg] The job description mentions ESG strategy, ESG consulting, sustainability strategies, and ESG frameworks, which are all relevant to the general ESG profile. The role also involves working with ESG data, tracking carbon performance, and evaluating regulatory requirements, which further </t>
         </is>
       </c>
       <c r="R170" s="2" t="inlineStr">
@@ -15514,19 +15585,19 @@
           <t>Keyword (1)</t>
         </is>
       </c>
-      <c r="O171" s="2" t="inlineStr">
-        <is>
-          <t>Graduate Mechanical Engineer will assist senior engineers on projects related to maintenance and reliability engineering in a variety of industries.</t>
-        </is>
-      </c>
-      <c r="P171" s="2" t="inlineStr">
-        <is>
-          <t>Requires a Bachelor's degree in Mechanical Engineering, strong analytical skills, and experience with relevant software tools.</t>
-        </is>
-      </c>
-      <c r="Q171" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on asset management within the energy sector, supporting decarbonization efforts and sustainable practices.</t>
+      <c r="O171" s="6" t="inlineStr">
+        <is>
+          <t>There are a variety of tasks and responsibilities you might be assigned however some common tasks that many of our graduate engineers perform include: * Assisting senior engineers with projects: You may be asked to help with research, testing, or other tasks related to ongoing projects. * Learning Wood processes and procedures: It's important to understand how Wood operates and the specific procedures and protocols you'll be expected to follow. * Collaborating with cross-functional teams: Engine</t>
+        </is>
+      </c>
+      <c r="P171" s="6" t="inlineStr">
+        <is>
+          <t>Attention to detail, problem solving, communication skills, continuous learning, creativity, analytical ability, logical thinking, leadership, respect for health and safety protocols, teamwork, adaptability</t>
+        </is>
+      </c>
+      <c r="Q171" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions 'renewables and emerging energy sectors' and 'decarbonisation, hydrogen, carbon capture and storage, renewables advisory', which are related to clean energy and environmental sustainability.</t>
         </is>
       </c>
       <c r="R171" s="2" t="inlineStr">
@@ -15611,19 +15682,19 @@
           <t>Keyword (1)</t>
         </is>
       </c>
-      <c r="O172" s="2" t="inlineStr">
-        <is>
-          <t>Develops and implements advanced algorithms for energy trading in the Australian National Electricity Market, focusing on battery storage systems and renewable assets.  Communicates technical concepts and marketing initiatives to clients.</t>
-        </is>
-      </c>
-      <c r="P172" s="2" t="inlineStr">
-        <is>
-          <t>Python, Java, SQL, experience with AI agents and commercial APIs like OpenAI and Anthropic.</t>
-        </is>
-      </c>
-      <c r="Q172" s="2" t="inlineStr">
-        <is>
-          <t>Energy trading software, Australian National Electricity Market (NEM), renewable energy integration, climate goals.</t>
+      <c r="O172" s="6" t="inlineStr">
+        <is>
+          <t>The role is responsible for the development, innovation, and ongoing improvement of algorithms to optimize the trading of energy assets into the Australian National Electricity Market (NEM), with a particular focus on battery energy storage systems (BESS) and renewable assets. The role involves acting as a technical lead in an "agentic coding" environment, leveraging cutting-edge AI coding assistants to rapidly build, test, and deploy sophisticated mathematical forecasters, optimizers, and autom</t>
+        </is>
+      </c>
+      <c r="P172" s="6" t="inlineStr">
+        <is>
+          <t>Technical skills in data extraction, manipulation, and programming (Python, Java, SQL), AI tooling proficiency, mathematical optimization techniques, DevOps and MLOps principles, excellent writing and presentation skills</t>
+        </is>
+      </c>
+      <c r="Q172" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions renewable energy, battery energy storage systems (BESS), and energy trading, which are all related to clean energy. The company also mentions climate goals and renewable energy integration, indicating a focus on environmental sustainability.</t>
         </is>
       </c>
       <c r="R172" s="2" t="inlineStr">
@@ -15708,19 +15779,19 @@
           <t>Semantic (0.68)</t>
         </is>
       </c>
-      <c r="O173" s="2" t="inlineStr">
-        <is>
-          <t>The Finance Director will develop and execute financial strategy, ensuring robust financial controls and compliance with Australian regulations while driving profitability and sustainable growth.</t>
-        </is>
-      </c>
-      <c r="P173" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should possess a CA/CPA qualification, 10+ years of progressive finance experience including 5+ years in people leadership roles, and familiarity with Cargowise system.</t>
-        </is>
-      </c>
-      <c r="Q173" s="2" t="inlineStr">
-        <is>
-          <t>This role is within the Supply Chain, Transportation, Logistics industry, focusing on financial strategy and operational efficiency for businesses.</t>
+      <c r="O173" s="6" t="inlineStr">
+        <is>
+          <t>As Finance Lead – WEET, you will act as the key commercial and financial partner to Project Managers and operational leaders. Reporting to the CFO, this role is responsible for driving financial performance, strengthening project governance, and improving working capital outcomes across the service line. You will provide end-to-end project finance leadership across the full project lifecycle – from bid support and project set-up, through delivery and revenue recognition, to project close. Lead f</t>
+        </is>
+      </c>
+      <c r="P173" s="6" t="inlineStr">
+        <is>
+          <t>Project accounting, commercial finance, ERP, project lifecycle management, Percentage of Completion (PoC) revenue recognition, leadership, influencing, mentoring, analytical capability, problem-solving, attention to detail, communication, financial insights</t>
+        </is>
+      </c>
+      <c r="Q173" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[clean_energy_adjacent] The job title 'Finance Lead - Water, Environment &amp; Energy Transition' and the company's focus on sustainable solutions and infrastructure indicate a connection to environmental topics, specifically water, environment, and energy transition, which aligns with the clean energy </t>
         </is>
       </c>
       <c r="R173" s="2" t="inlineStr">
@@ -15805,19 +15876,19 @@
           <t>Keyword (1)</t>
         </is>
       </c>
-      <c r="O174" s="2" t="inlineStr">
-        <is>
-          <t>Leads Lendable's data function, driving business value through data strategy, architecture, governance, and AI enablement.</t>
-        </is>
-      </c>
-      <c r="P174" s="2" t="inlineStr">
-        <is>
-          <t>Extensive experience in data architecture, engineering, and analytics with a strong understanding of machine learning and AI.</t>
-        </is>
-      </c>
-      <c r="Q174" s="2" t="inlineStr">
-        <is>
-          <t>Fintech company focused on lending and financial services, leveraging data to drive impact measurement and investment decisions.</t>
+      <c r="O174" s="6" t="inlineStr">
+        <is>
+          <t>Own the technical design and evolution of Lendable’s data and analytics platform, collaborate closely with Lendable’s Senior Director of Analytics and Lendable’s CEO to define Lendable’s long-term data strategy and roadmap, drive AI adoption across Lendable, iterate and quickly prototype solutions for technology challenges, oversee Lendable’s strategy for identifying and quickly integrating new data sources, ensure that Lendable’s data is rational, well-structured, labeled, standardized, and ult</t>
+        </is>
+      </c>
+      <c r="P174" s="6" t="inlineStr">
+        <is>
+          <t>Data strategy, data architecture, data governance, data engineering, AI enablement, data quality, data security, ETL/ELT patterns, integration of heterogeneous data sources, data onboarding, AI tools, data governance frameworks, leadership, team management</t>
+        </is>
+      </c>
+      <c r="Q174" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions 'responsible investment' and 'sustainable investment team', indicating a focus on ESG investing and sustainable finance.</t>
         </is>
       </c>
       <c r="R174" s="2" t="inlineStr">
@@ -15886,19 +15957,19 @@
           <t>Keyword (1)</t>
         </is>
       </c>
-      <c r="O175" s="2" t="inlineStr">
-        <is>
-          <t>This role involves managing a portfolio of retail customers in India, including retailers, independent workshops, and branded service centers.  Responsibilities include coordinating sales activities through authorized distributors and resellers, implementing marketing programs, and building strong customer relationships.</t>
-        </is>
-      </c>
-      <c r="P175" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have experience in sales management, distribution network management, and market analysis with a proven track record of success.  Strong communication skills are essential for interacting with customers, distributors, and other stakeholders.</t>
-        </is>
-      </c>
-      <c r="Q175" s="2" t="inlineStr">
-        <is>
-          <t>This role is within the energy and chemical industry, specifically focused on the marketing and distribution of products in India's retail sector.</t>
+      <c r="O175" s="6" t="inlineStr">
+        <is>
+          <t>The position is within the Energy &amp; Infrastructure Vertical at ASSOCHAM, playing a pivotal role in advancing division’s advocacy and industry engagement agenda. The incumbent will lead high-impact policy advocacy and drive sector-focused initiatives spanning Energy, Power, Renewable Energy, Green Hydrogen, Transmission, Highways &amp; Tunnelling, and Civil Aviation. This role will act as a catalyst for transformative government initiatives, working closely with policymakers, industry leaders, and ke</t>
+        </is>
+      </c>
+      <c r="P175" s="6" t="inlineStr">
+        <is>
+          <t>Policy &amp; Regulatory Understanding, Sectoral Knowledge, Research &amp; Analytical Skills, Government &amp; Institutional Liaison, Project &amp; Event Management, Membership &amp; Revenue Development, Communication &amp; Documentation, Stakeholder Management, Strategic Thinking, Communication &amp; Influence, Networking &amp; Re</t>
+        </is>
+      </c>
+      <c r="Q175" s="6" t="inlineStr">
+        <is>
+          <t>[climate_risk] Job title contains 'Climate', indicating a strong focus on climate-related work</t>
         </is>
       </c>
       <c r="R175" s="2" t="inlineStr"/>
@@ -15975,19 +16046,24 @@
           <t>Keyword (1)</t>
         </is>
       </c>
-      <c r="O176" s="2" t="inlineStr">
-        <is>
-          <t>Sales Trader will contribute to the global fight against climate change by identifying and executing deals in renewable energy markets.</t>
-        </is>
-      </c>
-      <c r="P176" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should have a Bachelor's degree, 0-3 years of experience in commodities trading, strong communication skills, and a passion for environmental sustainability.</t>
-        </is>
-      </c>
-      <c r="Q176" s="2" t="inlineStr">
-        <is>
-          <t>This role is within the renewable energy market sector, focusing on carbon offsets, biofuels, and other sustainable solutions to combat climate change.</t>
+      <c r="O176" s="6" t="inlineStr">
+        <is>
+          <t>As a Sales Trader, your responsibilities will encompass: 
+* Cultivating relationships with top-tier entities, including utilities, project developers, and corporates. 
+* Facilitating transactions in line with both client and Amsterdam Renewable Markets' standards. 
+* Striving to meet and exceed annual sales targets, ensuring sustained growth. 
+* Engaging in trading activities involving renewable power certificates, carbon offsets, among others. 
+* Daily interactions with team clients, expertly m</t>
+        </is>
+      </c>
+      <c r="P176" s="6" t="inlineStr">
+        <is>
+          <t>French &amp; English fluency, Bachelor’s/Master’s degree in fields like business, finance, economics, or similar, experience in commodities trading, brokering, or business development, stellar communication abilities, lead generation, cold calling</t>
+        </is>
+      </c>
+      <c r="Q176" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions environmental commodities, renewable energy markets, carbon offsets, and reducing carbon footprints, which are all related to clean energy and environmental sustainability.</t>
         </is>
       </c>
       <c r="R176" s="2" t="inlineStr">
@@ -16068,19 +16144,19 @@
           <t>Keyword (1)</t>
         </is>
       </c>
-      <c r="O177" s="2" t="inlineStr">
-        <is>
-          <t>Working Student will support the New Markets Certification team on sustainability certification projects, including PCF calculations and LCA research.</t>
-        </is>
-      </c>
-      <c r="P177" s="2" t="inlineStr">
-        <is>
-          <t>Enrolled students with knowledge of PCF (ISO 14067) and LCA (ISO 14040/44), experience with sustainability certifications is a plus.</t>
-        </is>
-      </c>
-      <c r="Q177" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on sustainability certification in the environmental sector, specifically related to carbon footprinting and renewable energy.</t>
+      <c r="O177" s="6" t="inlineStr">
+        <is>
+          <t>You will support the New Market Certification team with general project work and tasks, including revision of PCFs, preparing presentation and reports, general research tasks, research of emission factors and development of Excel-based PCF calculations. You will support research activities for different areas related to sustainability certifications and PCFs, including topics such as, biogenic materials and renewable energy. You will support the team in preparing presentations and slides for tra</t>
+        </is>
+      </c>
+      <c r="P177" s="6" t="inlineStr">
+        <is>
+          <t>PCF (ISO 14067), LCA (ISO 14040/44), sustainability certification, MS Office (especially Excel), English (at least C1), German, research, analytical thinking, communication, teamwork</t>
+        </is>
+      </c>
+      <c r="Q177" s="6" t="inlineStr">
+        <is>
+          <t>[carbon_markets] The job description mentions carbon footprint certification, product carbon footprints, life cycle assessment, and sustainability certification, which are all related to carbon markets and emissions trading.</t>
         </is>
       </c>
       <c r="R177" s="2" t="inlineStr">
@@ -16165,19 +16241,19 @@
           <t>Keyword (1)</t>
         </is>
       </c>
-      <c r="O178" s="2" t="inlineStr">
-        <is>
-          <t>This role involves researching and analyzing sustainability trends, business ethics, regulations, and sustainable development goals for companies. The successful candidate will prepare sector research reports and rank companies based on their sustainability disclosures.</t>
-        </is>
-      </c>
-      <c r="P178" s="2" t="inlineStr">
-        <is>
-          <t>Candidates should possess strong analytical skills, a keen eye for detail, and experience in traditional stock market research. Prior work experience with ESG profile is preferred.</t>
-        </is>
-      </c>
-      <c r="Q178" s="2" t="inlineStr">
-        <is>
-          <t>This role focuses on corporate governance, ESG, and sustainable development within the financial sector.</t>
+      <c r="O178" s="6" t="inlineStr">
+        <is>
+          <t>Be willing to be a pioneer and have an interest in ESG &amp; Corporate Governance. Curiosity and passion for researching and highlighting recent trends in sustainability (environmental and social issues), business ethics, regulations and sustainable development goals. Use analytical tools and intellect to question, challenge and evaluate current practices in the evolving area of ESG. Highlight key sustainability / ESG issues that are material to an industry / company. Prepare sector research reports</t>
+        </is>
+      </c>
+      <c r="P178" s="6" t="inlineStr">
+        <is>
+          <t>Sustainability research | ESG research | Analytical skills</t>
+        </is>
+      </c>
+      <c r="Q178" s="6" t="inlineStr">
+        <is>
+          <t>[sustainable_finance] The job description mentions ESG research, sustainability disclosures, performance, and qualitative factors, which are key aspects of sustainable finance. Additionally, the mention of SFDR (Sustainable Finance Disclosure Regulation) further supports this classification.</t>
         </is>
       </c>
       <c r="R178" s="2" t="inlineStr">
@@ -16258,19 +16334,19 @@
           <t>Groq-70B (clean_energy_adjacent)</t>
         </is>
       </c>
-      <c r="O179" s="2" t="inlineStr">
+      <c r="O179" s="6" t="inlineStr">
         <is>
           <t>Within our Energy Advisory capability, we advise clients on the challenges and opportunities regarding decarbonisation/net zero issues specifically in relation to requirements for delivering the global energy transition. This includes decentralised low carbon generation, innovation in technologies and energy sources, as well as policy and regulatory support. The successful applicant shall also have strong knowledge of the broader water industry in terms of growth and challenges to decarbonisatio</t>
         </is>
       </c>
-      <c r="P179" s="2" t="inlineStr">
+      <c r="P179" s="6" t="inlineStr">
         <is>
           <t>Strong verbal and written communication skills, excellent quantitative and problem-solving skills, ability to lead bid preparation, deliver to tight timescales, be technically accurate and to manage a number of schemes simultaneously, Strong project management skills, Knowledge of current and antici</t>
         </is>
       </c>
-      <c r="Q179" s="2" t="inlineStr">
-        <is>
-          <t>[clean_energy_adjacent] The job description mentions decarbonisation, net zero, low carbon generation, energy efficiency, and energy transition, which are all relevant to the clean energy adjacent profile. Additionally, the job requires experience working on water sector energy projects and knowledge of the broader water industry in terms of growth and challenges to decarbonisation.</t>
+      <c r="Q179" s="6" t="inlineStr">
+        <is>
+          <t>[clean_energy_adjacent] The job description mentions decarbonisation, net zero, low carbon generation, energy efficiency, and energy transition, which are all relevant to the clean energy adjacent profile. Additionally, the job requires experience working on water sector energy projects and knowledg</t>
         </is>
       </c>
       <c r="R179" s="2" t="inlineStr">
@@ -16339,9 +16415,17 @@
           <t>Groq-70B (clean_energy_adjacent)</t>
         </is>
       </c>
-      <c r="O180" s="2" t="inlineStr"/>
-      <c r="P180" s="2" t="inlineStr"/>
-      <c r="Q180" s="2" t="inlineStr">
+      <c r="O180" s="6" t="inlineStr">
+        <is>
+          <t>Work within a team responsible for Investment Restriction Compliance Management violation oversight, onboarding, and query resolution. Oversee daily reviews of overnight violation monitoring; escalate and track issues through to resolution. Partner with Investment Desks, Product, and Client Executives across asset classes on investment guideline matters and pre-trade violation overrides. Maintain broker and ready-to-trade coding in Aladdin and assist Trading Desks with related queries and escala</t>
+        </is>
+      </c>
+      <c r="P180" s="6" t="inlineStr">
+        <is>
+          <t>Strong experience in Investment Restriction Monitoring and compliance processes within Asset Management. Hands-on experience with Aladdin (or equivalent portfolio management systems). Solid understanding of investment guidelines, regulatory compliance, and mandate restriction management. Proficiency</t>
+        </is>
+      </c>
+      <c r="Q180" s="6" t="inlineStr">
         <is>
           <t>[clean_energy_adjacent] Job title contains 'Renewables', indicating a connection to renewable energy</t>
         </is>
@@ -16408,9 +16492,17 @@
           <t>Groq-70B (clean_energy_adjacent)</t>
         </is>
       </c>
-      <c r="O181" s="2" t="inlineStr"/>
-      <c r="P181" s="2" t="inlineStr"/>
-      <c r="Q181" s="2" t="inlineStr">
+      <c r="O181" s="6" t="inlineStr">
+        <is>
+          <t>To lead the Fund Master function within Investment Data Services, ensuring high-quality, complete, and compliant fund data management using Fundipedia. This role is pivotal in driving data governance, reconciliation, and strategic data initiatives across investment operations. Lead Fundipedia implementation and enhancement projects to optimize fund data management. Define and enforce fund data governance frameworks, including pricing governance and quality controls. Own the fund master data stra</t>
+        </is>
+      </c>
+      <c r="P181" s="6" t="inlineStr">
+        <is>
+          <t>Deep expertise in fund structures, share classes, and investment products. Hands-on experience with Fundipedia or similar EDM platforms. Strong understanding of regulatory frameworks (e.g., UCITS, MiFID II, SFDR). Proficiency in data tools (Excel, SQL, Power BI, Python, VBA). Excellent leadership, s</t>
+        </is>
+      </c>
+      <c r="Q181" s="6" t="inlineStr">
         <is>
           <t>[clean_energy_adjacent] Job title contains 'Circular Bioeconomy', indicating a focus on environmental science and circular economy, which aligns with the clean energy adjacent profile.</t>
         </is>
@@ -16477,148 +16569,23 @@
           <t>Groq-70B (clean_energy_adjacent)</t>
         </is>
       </c>
-      <c r="O182" s="2" t="inlineStr"/>
-      <c r="P182" s="2" t="inlineStr"/>
-      <c r="Q182" s="2" t="inlineStr">
+      <c r="O182" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deliver assurance services to multinational clients across a variety of sectors. Support Project Managers in the independent verification of GHG/ESG information, sustainability‑linked financial instruments, and product‑level claims. Contribute to high‑quality assessments that uphold ERM CVS’s reputation as a trusted global verification body. Build strong capability in sustainability assurance standards, environmental data methodologies, and emerging regulatory frameworks across APAC. Strengthen </t>
+        </is>
+      </c>
+      <c r="P182" s="6" t="inlineStr">
+        <is>
+          <t>Data analysis, advanced Excel skills, strong writing and communication skills, technical understanding of environmental impacts, emissions, climate change, and GHG, knowledge of key sustainability and GHG reporting frameworks, familiarity with auditing/assurance standards</t>
+        </is>
+      </c>
+      <c r="Q182" s="6" t="inlineStr">
         <is>
           <t>[clean_energy_adjacent] Job title contains 'Wind', indicating a focus on renewable energy</t>
         </is>
       </c>
       <c r="R182" s="2" t="inlineStr"/>
       <c r="S182" s="3" t="inlineStr">
-        <is>
-          <t>https://es.indeed.com/viewjob?jk=6d861e6f34eb946f</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>https://au.indeed.com/viewjob?jk=497bfa4db7596e3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>https://au.indeed.com/viewjob?jk=c3f50d6686504ef7</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>https://in.indeed.com/viewjob?jk=075a4b48fa67136d</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>https://in.indeed.com/viewjob?jk=068d6480385ff7e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>https://in.indeed.com/viewjob?jk=d489ec1bbd488cff</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4379017871</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4388632715</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4378313102</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4387677540</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4374324594</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4385429344</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>https://se.indeed.com/viewjob?jk=46823121d1858e13</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4387870157</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4378792994</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>https://www.naukri.com/job-listings-esg-research-analyst-quantum-asset-management-company-private-limited-mumbai-2-to-3-years-181024500879</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4362461145</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>https://nz.indeed.com/viewjob?jk=2c4def0df143a216</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>https://es.indeed.com/viewjob?jk=4e7511712b0ef4b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="S202" t="inlineStr">
         <is>
           <t>https://es.indeed.com/viewjob?jk=6d861e6f34eb946f</t>
         </is>
@@ -16667,146 +16634,146 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S45" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S46" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S47" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S48" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S49" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S51" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S52" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S53" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S54" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S56" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S57" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S59" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S60" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S61" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S62" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S64" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S65" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S66" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S67" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S68" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S69" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S70" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S71" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S72" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S74" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S75" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S76" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S77" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S78" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S79" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S80" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S81" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S82" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S83" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S84" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S85" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S86" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S87" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S88" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S89" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S94" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S95" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S96" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S97" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S98" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S100" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S102" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S103" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S104" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S105" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S106" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S107" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S108" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S109" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S110" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S111" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S112" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S113" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S114" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S115" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S116" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S117" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S118" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S119" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S120" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S121" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S122" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S123" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S124" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S125" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S126" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S127" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S130" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S131" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S132" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S133" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S134" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S135" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S137" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S138" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S139" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S140" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S141" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S142" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S143" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S145" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S146" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S147" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S148" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S149" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S150" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S151" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S152" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S153" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S154" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S155" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S156" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S157" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S158" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S159" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S160" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S161" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S162" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S163" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S164" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S165" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S166" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S168" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S169" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S170" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S171" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S172" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S173" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S174" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S175" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S176" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S178" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S179" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S180" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S181" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S182" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S183" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S184" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S186" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S187" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S188" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S189" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S190" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S191" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S192" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S193" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S194" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S195" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S196" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S197" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S198" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S199" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S200" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S201" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S202" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S182" r:id="rId181"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16929,7 +16896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U136"/>
+  <dimension ref="A1:U150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -30964,6 +30931,76 @@
       <c r="U136" s="2" t="inlineStr">
         <is>
           <t>Skills:4.1 Frameworks:5.0 Seniority:3 Domain:1.9 Semantic:15.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>https://be.indeed.com/viewjob?jk=c2682b315210f77a</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>https://it.indeed.com/viewjob?jk=6da85ba3880d39f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4387157765</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4387169325</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>https://be.indeed.com/viewjob?jk=4bfbf92d2aedd66e</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>https://au.indeed.com/viewjob?jk=dcc89e2cb0d87a2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4385475486</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4388354408</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>https://it.indeed.com/viewjob?jk=514d0360a39879f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4387399126</t>
         </is>
       </c>
     </row>

--- a/src/jobs/jobs.xlsx
+++ b/src/jobs/jobs.xlsx
@@ -641,19 +641,36 @@
           <t>Implement Climate Change Risk Management Policy and develop frameworks that align with organizational goals and objectives.
 Identification of climate risk at portfolio level/account level, and to identify and prioritize customer/sector segments for assessing climate related risks.
 Conduct comprehensive assessment of the Banks exposure to climate change-related financial risks (Physical &amp; Transition), including potential impacts on assets, operations and supply chain.
-Calculation of carbon footpr</t>
+Calculation of carbon footprint in lending portfolio at portfolio level/account level and monitor periodical emissions data, reporting.
+To prepare data inputs and execute various climate scenarios and stress testing cases. Integrate Climate Stress Testing with Credit and market risk stress testing.
+Required to conduct primary and secondary research on Regulatory (RBI, SEBI, BASEL etc.) guidelines or globally accepted standards (such as TCFD, GRI, SBTi etc.) on Net zero strategy, Climate Change Risk Management and to prepare Climate-related disclosures etc.
+Ensure compliance with regulatory requirements related to Climate change risks, including disclosures and reporting requirements.
+To provide climate change risk related training/ workshops</t>
         </is>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
           <t>Work Experience in Risk Management Cycle - with expertise in Climate Change Risk Management.
 Identification/Assessment/Measurement/Metrics and Disclosures and Risk Mitigation Strategies, Stress Testing - creation, execution and analysis of stress testing outcome.
-Experience in Climate Change Risk As</t>
+Experience in Climate Change Risk Assessment &amp; measurement, Sustainability strategy, Climate Finance, Green finance, clean energy and ESG related areas.
+Working Knowledge on Climate Risk Models, like Integrated Assessment Models (IAMs) or Climate physical and transition risk assessment tools by various service providers, such as Global Change Assessment Model (GCAM) and Paris Agreement Capital Transition Assessment (PACTA) etc.
+Expertise in Model development/ validation/ audit/ review experience for financial and non-financial risks.
+Experience of working on Stress test models (ex- for Transition and Physical Risk, Integration of credit risk in climate scenario etc.) etc.
+Having hands on knowledge on NGFS (Network for Greening the Financial System) and other climate scenarios.
+Proficiency in Climate Scenario Analysis and Stress testing.
+Hands on experience in calculating financed emissions and reporting
+Having working knowledge on frameworks such as SBTi, PCAF, GRI, BRSR etc.
+Effective written and verbal communication skills
+Excellent Communication Skills
+Problem Solving Attitude
+Analytical Thinking
+Excellent data analytical skills and comfortable working with large datasets
+Excellent skills in MS office, especially in MS Excel and PowerPoint etc</t>
         </is>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions climate change risk management, climate risk assessment, climate finance, and green finance, which are all related to climate risk. The job requires experience in climate change risk management and knowledge of climate risk models, which further supports t</t>
+          <t>The job description mentions climate change risk management, climate risk assessment, climate finance, and green finance, which are all related to climate risk. The job requires experience in climate change risk management and knowledge of climate risk models, which further supports the classification as climate_risk.</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr"/>
@@ -736,7 +753,7 @@
       </c>
       <c r="O3" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Climate Risk Assessment: Conduct physical risk assessments, transition risk assessments, and climate-related opportunities assessments for clients across various sectors. Develop models to compute financial impacts of climate related risks and opportunities Climate scenario analysis using IPCC, IEA, and NGFS scenarios to inform client strategies. Provide recommendations on climate risk management and resilience strategies. Nature and Biodiversity Risk Assessment: Conduct nature and biodiversity </t>
+          <t>Climate Risk Assessment: Conduct physical risk assessments, transition risk assessments, and climate-related opportunities assessments for clients across various sectors. Develop models to compute financial impacts of climate related risks and opportunities Climate scenario analysis using IPCC, IEA, and NGFS scenarios to inform client strategies. Provide recommendations on climate risk management and resilience strategies. Nature and Biodiversity Risk Assessment: Conduct nature and biodiversity risk assessments for clients, identifying potential impacts on their operations and supply chains. Develop strategies to mitigate nature and biodiversity risks and capitalize on opportunities. Climate Transition Planning: Develop climate transition plans, aligning with global climate goals and standards. Provide recommendations on climate policy, regulation, and market trends. Climate Resilience Strategy Development: Support clients in developing climate resilience strategies, including climate adaptation and disaster risk reduction measures. Conduct vulnerability assessments and provide recommendations for climate-resilient infrastructure and operations. Climate Finance: Advise clients on climate finance opportunities, including green bonds, climate-themed funds, and impact investing. Develop business cases and models to support climate-related investments. Reporting and Disclosure: Support clients in preparing reports aligned with TCFD, IFRS S1, IFRS S2, TNFD, ESRS etc.</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -746,7 +763,7 @@
       </c>
       <c r="Q3" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions climate risk assessment, physical risk assessments, transition risk assessments, climate scenario analysis, and climate resilience strategy development, which are all key aspects of climate risk management.</t>
+          <t>The job description mentions climate risk assessment, physical risk assessments, transition risk assessments, climate scenario analysis, and climate resilience strategy development, which are all key aspects of climate risk management.</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -829,17 +846,17 @@
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Work as part of a multidisciplinary team across a range of industries, assisting organisations on how they manage and report on a broad range of sustainability and climate-related risks and impacts. Delivery of assurance of non-financial reporting, including sustainability metrics, emissions and energy reporting across a range of industry sectors. Advise clients on the development of their strategies and delivery of non-financial reporting, including sustainability metrics, emissions and energy </t>
+          <t>Work as part of a multidisciplinary team across a range of industries, assisting organisations on how they manage and report on a broad range of sustainability and climate-related risks and impacts. Delivery of assurance of non-financial reporting, including sustainability metrics, emissions and energy reporting across a range of industry sectors. Advise clients on the development of their strategies and delivery of non-financial reporting, including sustainability metrics, emissions and energy reporting across a range of industry sectors. Contribute to strategy, solutions, methodologies, analytical frameworks and tools to help clients succeed and navigate complex regulatory environments and manage stakeholder expectations. Assist clients to develop and implement sustainability strategies, develop targets, and implement plans to enhance sustainability value for a broad range of sustainability topics, including diversity, waste, modern slavery and environmental impacts. Assist in climate scenario analysis including understanding climate risks and opportunities, in order to formulate short- and long-term management objectives.</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>Climate and nature disclosure experience, including knowledge of the Taskforce on Climate-related Financial Disclosure (TCFD) and Taskforce on Nature-related Financial Disclosure (TNFD) Frameworks. Knowledge of, and experience in decarbonisation approaches, climate risk and climate strategy. Agility</t>
+          <t>Climate and nature disclosure experience, including knowledge of the Taskforce on Climate-related Financial Disclosure (TCFD) and Taskforce on Nature-related Financial Disclosure (TNFD) Frameworks. Knowledge of, and experience in decarbonisation approaches, climate risk and climate strategy. Agility to learn and adapt on the job, ask the right questions and strive for the best solutions for clients.</t>
         </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions climate change, climate risk, decarbonisation, GHG accounting, and climate scenario analysis, which are all relevant to the climate risk profile.</t>
+          <t>The job description mentions climate change, climate risk, decarbonisation, GHG accounting, and climate scenario analysis, which are all relevant to the climate risk profile.</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -926,17 +943,17 @@
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>Work as part of a multidisciplinary team across a range of industries, assisting organisations on how they manage and report on a broad range of sustainability and climate-related risks and impacts. Manage engagement teams and provide coaching and development advice to staff members. Coordinate project activities and build strong lines of communication with clients, engagement teams and senior leaders to ensure engagements are managed to clearly defined timelines while delivering high quality wo</t>
+          <t>Work as part of a multidisciplinary team across a range of industries, assisting organisations on how they manage and report on a broad range of sustainability and climate-related risks and impacts. Manage engagement teams and provide coaching and development advice to staff members. Coordinate project activities and build strong lines of communication with clients, engagement teams and senior leaders to ensure engagements are managed to clearly defined timelines while delivering high quality work products. Delivery of assurance of non-financial reporting, including sustainability metrics, emissions and energy reporting across a range of industry sectors. Advise clients on the development of their strategies and delivery of non-financial reporting, including sustainability metrics, emissions and energy reporting across a range of industry sectors. Contribute to strategy, solutions, methodologies, analytical frameworks and tools to help clients succeed and navigate complex regulatory environments and manage stakeholder expectations. Assist clients to develop and implement sustainability strategies, develop targets, and implement plans to enhance sustainability value for a broad range of sustainability topics, including diversity, waste, modern slavery and environmental impacts. Assist in climate scenario analysis including understanding climate risks and opportunities, in order to formulate short- and long-term management objectives.</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professional services/consulting experience, Tertiary qualification in a quantitative subject, Experience in climate change services, Experience in GHG accounting, Demonstrable experience in reporting and/or assurance of greenhouse gas emissions, Working knowledge of the climate reporting regime in </t>
+          <t>Professional services/consulting experience, Tertiary qualification in a quantitative subject, Experience in climate change services, Experience in GHG accounting, Demonstrable experience in reporting and/or assurance of greenhouse gas emissions, Working knowledge of the climate reporting regime in New Zealand, Awareness of the Australian Accounting Standard Board S2 standard requirements, Experience leading teams and coaching and developing team members, Climate and nature disclosure experience, Knowledge of, and experience in decarbonisation approaches, climate risk and climate strategy</t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions climate change services, GHG accounting, climate risk, decarbonisation approaches, and climate strategy, which are all relevant to the climate risk profile.</t>
+          <t>The job description mentions climate change services, GHG accounting, climate risk, decarbonisation approaches, and climate strategy, which are all relevant to the climate risk profile.</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -1015,7 +1032,7 @@
       </c>
       <c r="O6" s="6" t="inlineStr">
         <is>
-          <t>Develop financing strategies for renewable energy, carbon reduction, and other climate-focused initiatives. Advise on ESG investment opportunities and impact funding. Secure funding through green bonds, sustainability-linked loans, carbon credit financing, and other instruments. Engage with banks, financial institutions, impact investors, and government agencies to unlock climate finance. Structure innovative financing models such as blended finance, PPPs (Public-Private Partnerships), and risk-</t>
+          <t>Develop financing strategies for renewable energy, carbon reduction, and other climate-focused initiatives. Advise on ESG investment opportunities and impact funding. Secure funding through green bonds, sustainability-linked loans, carbon credit financing, and other instruments. Engage with banks, financial institutions, impact investors, and government agencies to unlock climate finance. Structure innovative financing models such as blended finance, PPPs (Public-Private Partnerships), and risk-sharing mechanisms. Support fundraising through equity, debt, grants, and concessional finance. Ensure projects align with national and international climate policies, including Indias green finance framework. Stay updated on regulatory changes, carbon market trends, and sustainable investment guidelines. Conduct financial modeling, risk assessments, and return-on-investment analysis for sustainable projects. Evaluate the financial viability of Net Zero Indias sustainability initiatives. Collaborate with government bodies, financial institutions, corporate partners, and NGOs for sustainable funding solutions. Conduct workshops, training, and awareness programs on green finance opportunities.</t>
         </is>
       </c>
       <c r="P6" s="6" t="inlineStr">
@@ -1025,7 +1042,7 @@
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions sustainable finance, ESG investments, green bonds, and climate-focused fundraising, which are all key aspects of sustainable finance.</t>
+          <t>The job description mentions sustainable finance, ESG investments, green bonds, and climate-focused fundraising, which are all key aspects of sustainable finance.</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr"/>
@@ -1108,17 +1125,17 @@
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
-          <t>Lead end-to-end digital transformation and PMO for large capital projects in metals &amp; mining covering planning, execution, governance, and benefits realization. You will drive adoption of digital/AI solutions to deliver measurable improvements in time, cost, quality, and safety. Establish and run the PMO, build/maintain Integrated Master Schedule, implement Cost Controls, drive Risk &amp; Safety Management, oversee Quality Management, own procurement management, run performance reviews for contracto</t>
+          <t>Lead end-to-end digital transformation and PMO for large capital projects in metals &amp; mining covering planning, execution, governance, and benefits realization. You will drive adoption of digital/AI solutions to deliver measurable improvements in time, cost, quality, and safety. Establish and run the PMO, build/maintain Integrated Master Schedule, implement Cost Controls, drive Risk &amp; Safety Management, oversee Quality Management, own procurement management, run performance reviews for contractors and material vendors, implement Digital Storage &amp; Logistics Management, define the digital roadmap and success metrics, orchestrate adoption of digital solutions, ensure cybersecurity and data governance, act as client-facing lead for multi billion dollar programs, lead multi-disciplinary teams, manage benefits realization, and track KPIs tied to business case.</t>
         </is>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>Program governance, PMO operations, EVM, schedule &amp; cost assurance, risk management, digital solutioning &amp; change management, stakeholder management, excellent communication, executive reporting, proposal support/pre sales, Digital-led Transformation &amp; Capital Project Management, Metals &amp; Mining, Ac</t>
+          <t>Program governance, PMO operations, EVM, schedule &amp; cost assurance, risk management, digital solutioning &amp; change management, stakeholder management, excellent communication, executive reporting, proposal support/pre sales, Digital-led Transformation &amp; Capital Project Management, Metals &amp; Mining, Accepting Feedback, Active Listening, Analytical Thinking, Carbon Accounting, Climate Change Adaptation Program Design, Climate Change Impacts and Risks, Climate Finance, Energy Efficiency, Energy Policy and Regulation, Energy Transition.</t>
         </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions climate change mitigation and adaptation, energy efficiency, and renewable energy solutions, which are related to environmental sustainability and clean energy. Although it does not directly fit into the other categories, it is adjacent to clean e</t>
+          <t>The job description mentions climate change mitigation and adaptation, energy efficiency, and renewable energy solutions, which are related to environmental sustainability and clean energy. Although it does not directly fit into the other categories, it is adjacent to clean energy and has some relevance to environmental sustainability.</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
@@ -1201,17 +1218,17 @@
       </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Work as part of a multidisciplinary team across a range of industries, assisting organisations on how they manage and report on a broad range of sustainability and climate related risks and impacts. Assurance of non-financial reporting, including sustainability metrics, emissions and energy reporting across a range of industry sectors. Contribute to strategy, solutions, methodologies, analytical frameworks and tools to help clients succeed and navigate complex regulatory environments and manage </t>
+          <t>Work as part of a multidisciplinary team across a range of industries, assisting organisations on how they manage and report on a broad range of sustainability and climate related risks and impacts. Assurance of non-financial reporting, including sustainability metrics, emissions and energy reporting across a range of industry sectors. Contribute to strategy, solutions, methodologies, analytical frameworks and tools to help clients succeed and navigate complex regulatory environments and manage stakeholder expectations. Assist clients to develop and implement sustainability strategies, develop targets, and implement plans to enhance sustainability value for a broad range of sustainability topics, including diversity, waste, modern slavery and environmental impacts. Analyse effects of water, air quality and climate change towards organisations and communities, including ensuring integrity of environmental data as well as understanding climate risks and opportunities, in order to formulate short- and long-term management objectives</t>
         </is>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>Professional services/consulting experience. Knowledge of relevant legislation, regulations and codes of practice as well as a good understanding of the climate-related issues. Practical experience with energy and emissions reporting schemes including National Greenhouse Emissions Reporting (NGER) s</t>
+          <t>Professional services/consulting experience. Knowledge of relevant legislation, regulations and codes of practice as well as a good understanding of the climate-related issues. Practical experience with energy and emissions reporting schemes including National Greenhouse Emissions Reporting (NGER) scheme, the Safeguard Mechanism and the Australian Carbon Credit Unit (ACCU) Scheme. Climate risk assessment and disclosure experience, including knowledge of the Taskforce on Climate-related Financial Disclosure (TCFD) Framework. Knowledge of key assurance standards including General Audit and Assurance Procedures (GAAP), International Sustainability Standards Board (ISSB) and the associated Australian Sustainability Reporting Standards (ASRS). Knowledge of, and experience in decarbonisation approaches, climate risk and climate strategy</t>
         </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions climate change, climate risk, decarbonisation, and greenhouse gas emissions, which are all relevant to the climate risk profile. The role also involves working with clients to develop and implement sustainability strategies, and assisting them in navigatin</t>
+          <t>The job description mentions climate change, climate risk, decarbonisation, and greenhouse gas emissions, which are all relevant to the climate risk profile. The role also involves working with clients to develop and implement sustainability strategies, and assisting them in navigating complex regulatory environments, which further supports the climate risk profile classification</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
@@ -1294,17 +1311,17 @@
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>Supporting the Manager/ SM in day-to-day delivery of ESG engagements and associated activities, while ensuring that the engagements are delivered in a manner that complies with internal and regulatory procedures, Being responsible for the quality of deliverables produced, including qualitative and quantitative analysis, Contributing to thought leadership and developing market intelligence to support ESG practice development, Proven abilities to establish and sustain sound relationships with clie</t>
+          <t>Supporting the Manager/ SM in day-to-day delivery of ESG engagements and associated activities, while ensuring that the engagements are delivered in a manner that complies with internal and regulatory procedures, Being responsible for the quality of deliverables produced, including qualitative and quantitative analysis, Contributing to thought leadership and developing market intelligence to support ESG practice development, Proven abilities to establish and sustain sound relationships with clients and other stakeholders, Demonstrated experience in engaging with new clients and managing client expectations, Highly experienced in managing, mentoring and guiding teams</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>Prior experience of undertaking ESG Gap Assessment and providing logical and impactful recommendations, Strong understanding of ESG processes and systems, Experience conducting climate risk assessment online with TCFD guidelines, Proven experience of undertaking a detailed Peer Review &amp; Benchmarking</t>
+          <t>Prior experience of undertaking ESG Gap Assessment and providing logical and impactful recommendations, Strong understanding of ESG processes and systems, Experience conducting climate risk assessment online with TCFD guidelines, Proven experience of undertaking a detailed Peer Review &amp; Benchmarking, Strong knowledge and experience in the field of Sustainability, Knowledge about Greenhouse Gas Accounting &amp; Inventorization (Scope-1,2,3), Familiar with Science based targets and decarbonization initiatives, Highly experienced in data governance – people, process, controls and technology aspects, Strong written and verbal communication skills</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[general_esg] The job description mentions ESG (Environmental, Social &amp; Governance) and sustainability, which are key aspects of general ESG profile. The job also involves climate risk assessment, greenhouse gas accounting, and decarbonization initiatives, which are all relevant to ESG strategy and </t>
+          <t>The job description mentions ESG (Environmental, Social &amp; Governance) and sustainability, which are key aspects of general ESG profile. The job also involves climate risk assessment, greenhouse gas accounting, and decarbonization initiatives, which are all relevant to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -1387,7 +1404,7 @@
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
-          <t>Manage the implementation of advisory mandates, bespoke data and report deliveries of ISS ESG Climate Solutions. Conduct climate impact analysis on investment portfolios across all asset classes. Provide support and input for Client Calls based on deliverables requirements and effectively address client queries. Co-ordinate with required stakeholders to ensure timely delivery of high quality of data to the clients. Contribute to standardization and automation effort of bespoke analysis. Bring on</t>
+          <t>Manage the implementation of advisory mandates, bespoke data and report deliveries of ISS ESG Climate Solutions. Conduct climate impact analysis on investment portfolios across all asset classes. Provide support and input for Client Calls based on deliverables requirements and effectively address client queries. Co-ordinate with required stakeholders to ensure timely delivery of high quality of data to the clients. Contribute to standardization and automation effort of bespoke analysis. Bring on board ideas and implementation techniques to improve and streamline analysis and delivery of products especially for alternative asset classes.</t>
         </is>
       </c>
       <c r="P10" s="6" t="inlineStr">
@@ -1397,7 +1414,7 @@
       </c>
       <c r="Q10" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions climate-related risks, GHG emissions, and climate impact analysis, which are all relevant to the climate risk profile.</t>
+          <t>The job description mentions climate-related risks, GHG emissions, and climate impact analysis, which are all relevant to the climate risk profile.</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
@@ -1484,17 +1501,17 @@
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">In this crucial role, you’ll support the development of NatWest Markets’ sustainable finance and ESG risk capabilities across European capital markets. We’ll look to you to support senior originators in front‑line origination, risk engagement and client delivery by translating sustainability, climate and broader ESG themes into tangible financing, investment and risk outcomes. As a Financing &amp; Risk Solutions Associate, you will be supporting the effective management of transactions to make sure </t>
+          <t>In this crucial role, you’ll support the development of NatWest Markets’ sustainable finance and ESG risk capabilities across European capital markets. We’ll look to you to support senior originators in front‑line origination, risk engagement and client delivery by translating sustainability, climate and broader ESG themes into tangible financing, investment and risk outcomes. As a Financing &amp; Risk Solutions Associate, you will be supporting the effective management of transactions to make sure that all activities are in line with the bank’s policies covering conduct, operational, credit, and regulatory risks. You’ll contribute to the development of high‑quality sustainability‑linked client materials and regulatory‑aligned ESG assessments. You’ll also be assisting with client deep dives, navigating the sales coverage teams and gathering feedback from internal client touchpoints. Preparing pitch‑books, investor presentations, analysing market dynamics, identifying market trends, other marketing materials focusing on sustainability‑related analys. Producing client materials with focus on climate, ESG and regulatory developments shaping European capital markets. Tracking markets dynamics, including sustainable finance trends, evolving supervisory expectations and ESG‑related investor demand. Updating and maintaining internal databases and writing weekly market commentary for circulation to clients, including insights on transition and physical risk, regulatory disclosure regimes and ESG‑linked issuance activity. Supporting portfolio‑level ESG materiality and risk assessments in line with ECB and global supervisory expectations, contributing to audit‑ready, front‑line risk ownership</t>
         </is>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>Comfort operating in evolving and complex sustainability‑related regulatory environments. Knowledge of investment banking and credit related products. Advanced power point and excel skills and experience with Pivots, vlookup, hlookup, index match and other advance excel formulas. Strong communicatio</t>
+          <t>Comfort operating in evolving and complex sustainability‑related regulatory environments. Knowledge of investment banking and credit related products. Advanced power point and excel skills and experience with Pivots, vlookup, hlookup, index match and other advance excel formulas. Strong communication and interpersonal skills with the ability to build relationship with key stakeholders including working with Risk, Compliance, Sustainability, SFA and Coverage teams. Excellent analytical and commercial awareness skills with high attention to detail, strong problem solving and logical thinking skills</t>
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions sustainable finance, ESG risk, climate risk, and regulatory frameworks such as EU Taxonomy and CSRD, indicating a strong focus on sustainable finance and ESG topics.</t>
+          <t>The job description mentions sustainable finance, ESG risk, climate risk, and regulatory frameworks such as EU Taxonomy and CSRD, indicating a strong focus on sustainable finance and ESG topics.</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
@@ -1573,17 +1590,17 @@
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>Work with global teams and clients to analyze sustainability data, delivering key insights that empower investors and decision-makers. Lead initiatives to elevate Apex Group s sustainability performance, supporting clients on their sustainability journey while enhancing the ESG reporting, analysis, and due diligence processes. Leverage extensive ESG expertise to provide high-quality advisory services in ESG policy and regulatory reporting, strategy, and risk management. Act as a key expert on on</t>
+          <t>Work with global teams and clients to analyze sustainability data, delivering key insights that empower investors and decision-makers. Lead initiatives to elevate Apex Group s sustainability performance, supporting clients on their sustainability journey while enhancing the ESG reporting, analysis, and due diligence processes. Leverage extensive ESG expertise to provide high-quality advisory services in ESG policy and regulatory reporting, strategy, and risk management. Act as a key expert on one or more of the following regulatory areas, interpreting complex regulations and integrating them into client value creation processes: Corporate Sustainability Due Diligence Directive (CSDDD); Corporate Sustainability Reporting Directive (CSRD); EU Deforestation Regulation (EUDR); EU Taxonomy; Minimum Safeguards; Sustainable Finance Disclosures Regulation (SFDR); and Taskforce on Nature-related Financial Disclosures (TNFD). Evaluate the material impact of biodiversity and ecosystems on businesses to identify associated risks and opportunities, helping clients manage their environmental impacts. Contribute to the continuous improvement of existing ESG products and the development of innovative solutions that meet client needs and regulatory demands.</t>
         </is>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>Proficiency in quantitative and qualitative data collection, analysis, and reporting. Exceptional organizational competency with strong attention to detail. Excellent interpersonal skills with the ability to communicate and influence internal and external stakeholders, including proficiency in video</t>
+          <t>Proficiency in quantitative and qualitative data collection, analysis, and reporting. Exceptional organizational competency with strong attention to detail. Excellent interpersonal skills with the ability to communicate and influence internal and external stakeholders, including proficiency in video conferencing, written communication, and presentation. Proficiency in MS Office is needed, while knowledge of programming languages is a plus.</t>
         </is>
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
-          <t>[eu_taxonomy_sfdr] The job description mentions specific EU regulations such as EU Taxonomy, CSRD, and SFDR, which are key components of the EU Taxonomy and SFDR profile. The role also involves ESG reporting, analysis, and due diligence, which are closely related to the EU Taxonomy and SFDR regulati</t>
+          <t>The job description mentions specific EU regulations such as EU Taxonomy, CSRD, and SFDR, which are key components of the EU Taxonomy and SFDR profile. The role also involves ESG reporting, analysis, and due diligence, which are closely related to the EU Taxonomy and SFDR regulations.</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr"/>
@@ -1650,7 +1667,7 @@
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>Develop and implement machine learning and deep learning models for satellite and geospatial data analysis. Integrate and process multimodal datasets. Build and automate scalable data processing pipelines using Python and cloud-based solutions. Collaborate with interdisciplinary teams and international partners to deliver customer-facing projects. Support the development of recommended practices and standards for EO data analytics. Present findings and recommendations to customers, supporting th</t>
+          <t>Develop and implement machine learning and deep learning models for satellite and geospatial data analysis. Integrate and process multimodal datasets. Build and automate scalable data processing pipelines using Python and cloud-based solutions. Collaborate with interdisciplinary teams and international partners to deliver customer-facing projects. Support the development of recommended practices and standards for EO data analytics. Present findings and recommendations to customers, supporting their digital transformation and compliance journeys. Contribute to proposal writing, research activities, and the expansion of DNV’s EO service portfolio.</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
@@ -1660,7 +1677,7 @@
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions working on sustainability, energy transition, and environmental challenges, which aligns with the clean energy adjacent profile. The role involves developing data-driven solutions for complex challenges in safety, sustainability, and energy transi</t>
+          <t>The job description mentions working on sustainability, energy transition, and environmental challenges, which aligns with the clean energy adjacent profile. The role involves developing data-driven solutions for complex challenges in safety, sustainability, and energy transition, and the company is involved in navigating the transition to a decarbonized and more sustainable energy future.</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr"/>
@@ -1744,12 +1761,12 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>Civil &amp; Geological Engineering, Soil Mechanics or similar, Civil &amp; Geotechnical Engineering, MSc Soil Mechanics, Hydrogeology, Hydrogeologist, Civil Engineering in Environmental Science and MSc in Earth Science, Acoustics Engineering, Music Technology or Sound Engineering or other, Environmental and</t>
+          <t>Civil &amp; Geological Engineering, Soil Mechanics or similar, Civil &amp; Geotechnical Engineering, MSc Soil Mechanics, Hydrogeology, Hydrogeologist, Civil Engineering in Environmental Science and MSc in Earth Science, Acoustics Engineering, Music Technology or Sound Engineering or other, Environmental and Sustainability Engineering, Energy Engineering, Environmental Studies and similar</t>
         </is>
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions various environmental and sustainability-related roles such as Rock Engineering, Geotechnical Engineering, Hydrogeology, Contaminated Areas, Acoustics, and Environmental Management - Sustainability &amp; Climate Change, which are all related to enviro</t>
+          <t>The job description mentions various environmental and sustainability-related roles such as Rock Engineering, Geotechnical Engineering, Hydrogeology, Contaminated Areas, Acoustics, and Environmental Management - Sustainability &amp; Climate Change, which are all related to environmental science, conservation, and sustainability, making it a good fit for the clean_energy_adjacent profile</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
@@ -1836,17 +1853,17 @@
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>Disclosure requirements Interpretation and Integration: Act as the subject matter expert, interpret mandatory disclosure requirements under global ESG/ sustainability related standards. Develop a comprehensive Materiality Assessment Framework: Design and architect a robust Materiality Assessment framework that aligns seamlessly with the requirements of the amended ESRS. Maintain the DR Inventory: Define, update, and manage the disclosure requirement (DR) inventory, including ownership of each DR</t>
+          <t>Disclosure requirements Interpretation and Integration: Act as the subject matter expert, interpret mandatory disclosure requirements under global ESG/ sustainability related standards. Develop a comprehensive Materiality Assessment Framework: Design and architect a robust Materiality Assessment framework that aligns seamlessly with the requirements of the amended ESRS. Maintain the DR Inventory: Define, update, and manage the disclosure requirement (DR) inventory, including ownership of each DR and data point. Assess DR Applicability: Review and confirm the applicability of DRs for the current reporting year, including application of omission methodologies. Develop and Refine Reporting Processes: Develop and maintain efficient ESG reporting templates and processes. Prepare Report Drafts: Create preliminary report drafts and update with inputs from Information Providers and prepare for final submission. Continuous Monitoring: Establish mechanisms for ongoing monitoring of compliance effectiveness and identify potential new gaps arising from future regulatory updates or evolving business practices. Assurance Readiness: Prepare documentation and evidence to support internal and external audits and assurance activities related to sustainability related compliance and gap remediation. Benchmarking: Research and analyze best practices in sustainability related disclosures, gap remediation, and so on. Collaborate with Leads on Key Activities: Support leads in the following: Ensuring timely and accurate reporting of ESG disclosures through standardized and controlled processes. Developing and implementing disclosure controls and procedures for ESG disclosures. Managing the collection of attestations. Enhancing report design, branding, and visual elements (e.g., infographics). Engaging with and coordinating external assurance providers. Coordinating internal audits and external reviews. Preparing final reports for approval by relevant governance bodies. Contributing to other essential tasks as needed.</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>Proven ability to design, implement, and optimize financial controls; define and execute robust financial reporting; and an eye digitization/automation of manual processes to enhance controls and compliance drive efficiency through automation and digitization initiatives. Good understanding of ESG r</t>
+          <t>Proven ability to design, implement, and optimize financial controls; define and execute robust financial reporting; and an eye digitization/automation of manual processes to enhance controls and compliance drive efficiency through automation and digitization initiatives. Good understanding of ESG regulatory requirements, and global sustainability standards. Strong understanding of Banking/ FIs relevant reporting requirements. Assurance/ Audit experience preferred. Demonstrated analytical and critical thinking skills to dissect complex regulatory language and identify practical implications. Strong problem-solving abilities and a proactive approach to identifying and addressing compliance challenges. Demonstrated project management skills with the ability to lead cross-functional initiatives. High attention to detail and accuracy, ensuring meticulous gap identification and remediation. Superior written and verbal communication skills, capable of explaining complex regulatory concepts to diverse audiences. Ability to influence stakeholders and drive consensus on remediation strategies. Proficiency in using data analysis tools (e.g., Excel) and familiarity with ESG reporting software. Self-motivated, adaptable, and able to thrive in a fast-paced, evolving regulatory environment.</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>[eu_taxonomy_sfdr] The job description mentions EU Corporate Sustainability Reporting Directive (CSRD), EU Taxonomy, and other ESG-related regulations, indicating a strong focus on EU Taxonomy and SFDR compliance.</t>
+          <t>The job description mentions EU Corporate Sustainability Reporting Directive (CSRD), EU Taxonomy, and other ESG-related regulations, indicating a strong focus on EU Taxonomy and SFDR compliance.</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
@@ -1929,7 +1946,7 @@
       </c>
       <c r="O16" s="6" t="inlineStr">
         <is>
-          <t>Working on sustainability in deals at PwC, you will focus on providing consulting services related to integrating sustainability principles into mergers and acquisitions and private equity transactions (debt and equity) and corporate strategies. You will analyse environmental and social risk, assess client needs based on global frameworks, conduct impact assessments and develop comprehensive sustainability strategies for value creation, and offer guidance and support to help clients transition t</t>
+          <t>Working on sustainability in deals at PwC, you will focus on providing consulting services related to integrating sustainability principles into mergers and acquisitions and private equity transactions (debt and equity) and corporate strategies. You will analyse environmental and social risk, assess client needs based on global frameworks, conduct impact assessments and develop comprehensive sustainability strategies for value creation, and offer guidance and support to help clients transition to sustainable and purpose-led business models.</t>
         </is>
       </c>
       <c r="P16" s="6" t="inlineStr">
@@ -1939,7 +1956,7 @@
       </c>
       <c r="Q16" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions integrating sustainability principles into mergers and acquisitions, private equity transactions, and corporate strategies, which is related to sustainable finance. It also mentions ESG ratings methodology, ESG policies, and ESG due diligences, whic</t>
+          <t>The job description mentions integrating sustainability principles into mergers and acquisitions, private equity transactions, and corporate strategies, which is related to sustainable finance. It also mentions ESG ratings methodology, ESG policies, and ESG due diligences, which are key aspects of sustainable finance.</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
@@ -2041,7 +2058,7 @@
       </c>
       <c r="Q17" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description explicitly mentions climate risk, climate-related risks, climate strategy development, and climate disclosure frameworks, which are all key aspects of climate risk assessment and management.</t>
+          <t>The job description explicitly mentions climate risk, climate-related risks, climate strategy development, and climate disclosure frameworks, which are all key aspects of climate risk assessment and management.</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
@@ -2128,7 +2145,9 @@
 * Support to senior team members on GHG inventories for corporates, cities, and sectors following IPCC Guidelines and GHG Protocol.
 * Develop and implement GHG calculation tools for baseline emissions and forecasting.
 * Use LCA tools to evaluate embodied carbon in infrastructure and master planning.
-* Support senior team member/lead on design and execution of decarbonization roadmaps with clear targets and timelines in line with SBTi and national climate goals</t>
+* Support senior team member/lead on design and execution of decarbonization roadmaps with clear targets and timelines in line with SBTi and national climate goals.
+* Apply PCAF guidelines for assessing financed, facilitated, or insurance-associated emissions (desirable).
+Climate Risk Modeling and Assessment</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2138,7 +2157,7 @@
       </c>
       <c r="Q18" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions GHG accounting, decarbonization, climate risk modeling, and assessment, which are all related to climate risk. The job also mentions following IPCC Guidelines and GHG Protocol, and applying PCAF guidelines, which are all relevant to climate risk management</t>
+          <t>The job description mentions GHG accounting, decarbonization, climate risk modeling, and assessment, which are all related to climate risk. The job also mentions following IPCC Guidelines and GHG Protocol, and applying PCAF guidelines, which are all relevant to climate risk management.</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
@@ -2227,7 +2246,7 @@
       </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions climate risk, GHG emissions, and Net Zero reports, which are key indicators of a climate risk profile.</t>
+          <t>The job description mentions climate risk, GHG emissions, and Net Zero reports, which are key indicators of a climate risk profile.</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr"/>
@@ -2383,17 +2402,17 @@
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
-          <t>Lead and manage all operational aspects of the Projects business, by setting up and overseeing key internal support functions (HR, IT, finance, and Business Services). Develop and implement fit-for-purpose systems, tools, and processes that enable the Projects team to operate with autonomy and efficiency, while maintaining alignment with corporate standards. Support the design and implementation of a capital investment framework to guide decision-making and capital allocation. Ensure alignment b</t>
+          <t>Lead and manage all operational aspects of the Projects business, by setting up and overseeing key internal support functions (HR, IT, finance, and Business Services). Develop and implement fit-for-purpose systems, tools, and processes that enable the Projects team to operate with autonomy and efficiency, while maintaining alignment with corporate standards. Support the design and implementation of a capital investment framework to guide decision-making and capital allocation. Ensure alignment between Projects team operations and broader corporate frameworks and standards. Prepare high-quality materials for Board and committee reporting, ensuring clarity, accuracy and timeliness. Lead and coordinate project development workstreams, ensuring clear ownership, timelines and accountability across internal teams and external partners. Establish and manage project governance cadence, including setting agendas, facilitating meetings, tracking actions and driving timely decision-making. Maintain integrated project plans, monitoring progress against milestones, budgets and risks, and escalating issues as required. Oversee governance processes to support disciplined project progression and investment approvals. Partner with Corporate Finance on budgeting, forecasting and resource planning. Develop and track KPIs, identifying performance trends and driving continuous improvement. Work closely with the executive team to align operational delivery with business priorities. Ensure compliance with legal, regulatory and internal standards. Identify and manage operational risks across the project lifecycle. Manage key vendor and service provider relationships, including contract negotiation and performance oversight. Foster a high-performance, accountable and collaborative team environment. Support capability development within the Projects team and broader organisation.</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>Proficiency with CRMs, MS Office, and advanced Excel skills. Experience managing virtual data rooms. Strong financial acumen and experience with budgeting and forecasting. Excellent leadership, communication, and interpersonal skills. Strong analytical and problem-solving skills. Pragmatic, solution</t>
+          <t>Proficiency with CRMs, MS Office, and advanced Excel skills. Experience managing virtual data rooms. Strong financial acumen and experience with budgeting and forecasting. Excellent leadership, communication, and interpersonal skills. Strong analytical and problem-solving skills. Pragmatic, solutions-oriented, and comfortable operating in ambiguity. Effective communication and stakeholder engagement. Ability to manage multiple projects simultaneously.</t>
         </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions experience in renewable energy, decarbonisation, infrastructure or nature-based projects as highly desirable, and the company is a specialist climate change investment and advisory firm, indicating a strong focus on environmental sustainability an</t>
+          <t>The job description mentions experience in renewable energy, decarbonisation, infrastructure or nature-based projects as highly desirable, and the company is a specialist climate change investment and advisory firm, indicating a strong focus on environmental sustainability and clean energy.</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
@@ -2476,17 +2495,17 @@
       </c>
       <c r="O22" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Develop relationships with corporate buyers, airlines, traders, intermediaries and financial institutions active in carbon markets. Manage the full commercial lifecycle, from lead generation and client engagement through to transaction execution. Originate and execute transactions across voluntary carbon markets, CORSIA-eligible credits and emerging compliance-linked carbon markets. Identify new commercial opportunities and areas of the market where CFP Energy should focus its efforts, based on </t>
+          <t>Develop relationships with corporate buyers, airlines, traders, intermediaries and financial institutions active in carbon markets. Manage the full commercial lifecycle, from lead generation and client engagement through to transaction execution. Originate and execute transactions across voluntary carbon markets, CORSIA-eligible credits and emerging compliance-linked carbon markets. Identify new commercial opportunities and areas of the market where CFP Energy should focus its efforts, based on evolving regulation and market demand. Support the structuring and negotiation of commercial transactions, including carbon credit offtake agreements, forward purchases and other structured environmental market products. Work closely with internal trading teams to develop pricing strategies and execute transactions. Track market developments, pricing dynamics and supply-demand trends to support commercial strategy and client discussions. Build relationships with project developers, carbon funds and intermediaries to source high-quality carbon credit supply. Evaluate projects across different methodologies, standards and geographies. Support commercial due diligence and maintain awareness of project pipelines.</t>
         </is>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>Strong market instincts, entrepreneurial mindset, confidence to build and leverage relationships, ability to structure and execute carbon credit transactions, experience with commercial negotiation, origination or structured transactions, strong understanding of carbon credit project structures, met</t>
+          <t>Strong market instincts, entrepreneurial mindset, confidence to build and leverage relationships, ability to structure and execute carbon credit transactions, experience with commercial negotiation, origination or structured transactions, strong understanding of carbon credit project structures, methodologies and market dynamics</t>
         </is>
       </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
-          <t>[carbon_markets] The job description mentions voluntary carbon markets, carbon credits, CORSIA, and compliance-linked carbon markets, which are all related to carbon markets. The role involves originating and executing transactions across voluntary carbon markets, and the ideal candidate should have</t>
+          <t>The job description mentions voluntary carbon markets, carbon credits, CORSIA, and compliance-linked carbon markets, which are all related to carbon markets. The role involves originating and executing transactions across voluntary carbon markets, and the ideal candidate should have experience in carbon markets, environmental commodities, energy trading, or a related field.</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
@@ -2569,7 +2588,7 @@
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
-          <t>The PhD candidate tasks will include: organizing logistics for regular river sampling by local teams: shipment of materials and samples, establish new collaborations with other partners in the Congo Basin. organizing and conducting new sampling campaigns in collaboration with local partners in the Congo Basin field measurements of river discharge, physico-chemical parameters and greenhouse gas concentrations and fluxes field sampling for a wide range of biogeochemical proxies, sample preservatio</t>
+          <t>The PhD candidate tasks will include: organizing logistics for regular river sampling by local teams: shipment of materials and samples, establish new collaborations with other partners in the Congo Basin. organizing and conducting new sampling campaigns in collaboration with local partners in the Congo Basin field measurements of river discharge, physico-chemical parameters and greenhouse gas concentrations and fluxes field sampling for a wide range of biogeochemical proxies, sample preservation for analyses in Belgium. laboratory analysis of samples (quantification and stable isotope analyses of diffferent carbon pools, nutrient analyses and greenhouse gas analysis, …) dissemination of results at scientific conferences and in interational, peer-reviewed journals. you will be expected to contribute to educational tasks depending on opportunities and your own interests, and assist in coaching MSc thesis students. opportunitities exist to make your own contribution to the research objectives depending on personal interests and in collaboration with other research teams.</t>
         </is>
       </c>
       <c r="P23" s="6" t="inlineStr">
@@ -2579,7 +2598,7 @@
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions research on riverine carbon dynamics and fluxes in the Congo Basin, which is related to environmental science and the management of natural resources, fitting the clean_energy_adjacent profile.</t>
+          <t>The job description mentions research on riverine carbon dynamics and fluxes in the Congo Basin, which is related to environmental science and the management of natural resources, fitting the clean_energy_adjacent profile.</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
@@ -2663,12 +2682,12 @@
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>Excellent communication skills, with the ability to articulate complex issues clearly and persuasively in both written and spoken English. A wellestablished professional network in EU affairs and climaterelated policy fields. Demonstrated ability to design and deliver complex strategies that mobilis</t>
+          <t>Excellent communication skills, with the ability to articulate complex issues clearly and persuasively in both written and spoken English. A wellestablished professional network in EU affairs and climaterelated policy fields. Demonstrated ability to design and deliver complex strategies that mobilise diverse actors toward shared outcomes.</t>
         </is>
       </c>
       <c r="Q24" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions climate change, netzero economy, greenhouse gas emissions reductions, and climate policy, which are all relevant to climate risk.</t>
+          <t>The job description mentions climate change, netzero economy, greenhouse gas emissions reductions, and climate policy, which are all relevant to climate risk.</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr"/>
@@ -2748,7 +2767,9 @@
 Advise and collaborate across businesses and global functions to drive common objectives
 Follow human rights developments, societal trends and best practices, and translate them into actionable improvements
 Strengthen risk management, social performance and value creation through robust social responsibility work
-Ensure the continuous development, motivation and professiona</t>
+Ensure the continuous development, motivation and professional competence of the Social Responsibility team
+Represent UPM in company-level CSR initiatives and collaboration with key stakeholders
+Contribute to wider Group-level activities such as responsible sourcing, HR, investment management, compliance and internal audit</t>
         </is>
       </c>
       <c r="P25" s="6" t="inlineStr">
@@ -2762,7 +2783,7 @@
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>[general_esg] The job description mentions social responsibility, sustainability, human rights, and responsible sourcing, which are all relevant to ESG strategy and corporate sustainability.</t>
+          <t>The job description mentions social responsibility, sustainability, human rights, and responsible sourcing, which are all relevant to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr"/>
@@ -2841,7 +2862,7 @@
       </c>
       <c r="O26" s="6" t="inlineStr">
         <is>
-          <t>The first project will focus on a VM0047 afforestation project, but the role will extend to supporting additional projects across Arbonics portfolio. This is a hybrid role combining technical carbon project development and stakeholder collaboration. In addition to leading the research and preparation of PDD documentation, you will support commercial teams in evaluating and acquiring new commercial opportunities. You will become the technical expert representing Arbonics in discussions with lando</t>
+          <t>The first project will focus on a VM0047 afforestation project, but the role will extend to supporting additional projects across Arbonics portfolio. This is a hybrid role combining technical carbon project development and stakeholder collaboration. In addition to leading the research and preparation of PDD documentation, you will support commercial teams in evaluating and acquiring new commercial opportunities. You will become the technical expert representing Arbonics in discussions with landowners, partners, and project stakeholders, helping answer detailed questions about project eligibility, methodology requirements, and carbon accounting. Key Responsibilities: Carbon project development, Technical expertise in project development, Stakeholder engagement</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
@@ -2851,7 +2872,7 @@
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>[carbon_markets] The job description mentions carbon project development, Verra VCS methodologies, and carbon credits, which are all related to carbon markets.</t>
+          <t>The job description mentions carbon project development, Verra VCS methodologies, and carbon credits, which are all related to carbon markets.</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
@@ -2934,7 +2955,7 @@
       </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">We are looking for a Customer Solutions Engineer to take ownership of the technical success of our enterprise banking clients. This is a high-impact, remote consultancy engagement within Europe, requiring availability within ±1 hour CET. In this role, you will work closely with the CPTO and the Customer team, acting as the primary technical counterpart for global banks operating in highly regulated environments. You will stand at the intersection of product, engineering, and enterprise clients, </t>
+          <t>We are looking for a Customer Solutions Engineer to take ownership of the technical success of our enterprise banking clients. This is a high-impact, remote consultancy engagement within Europe, requiring availability within ±1 hour CET. In this role, you will work closely with the CPTO and the Customer team, acting as the primary technical counterpart for global banks operating in highly regulated environments. You will stand at the intersection of product, engineering, and enterprise clients, shaping how our platform scales, integrates, and delivers long-term value.</t>
         </is>
       </c>
       <c r="P27" s="6" t="inlineStr">
@@ -2944,7 +2965,7 @@
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions 'impact technology', 'driving global climate action', 'ESG experts', and 'sustainability' in the context of financial products, indicating a strong focus on sustainable finance and ESG investing.</t>
+          <t>The job description mentions 'impact technology', 'driving global climate action', 'ESG experts', and 'sustainability' in the context of financial products, indicating a strong focus on sustainable finance and ESG investing.</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
@@ -3037,7 +3058,7 @@
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
-          <t>[general_esg] The job description mentions ESG, sustainability, climate change risk assessments, and social and human rights impact assessments, which are all related to environmental, social, and governance topics.</t>
+          <t>The job description mentions ESG, sustainability, climate change risk assessments, and social and human rights impact assessments, which are all related to environmental, social, and governance topics.</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
@@ -3116,17 +3137,17 @@
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>support the development of NatWest Markets sustainable finance and ESG risk capabilities across European capital markets, support senior originators in frontline origination, risk engagement and client delivery, contribute to the development of high-quality sustainability-linked client materials and regulatory-aligned ESG assessments, assist with client deep dives, navigate the sales coverage teams and gather feedback from internal client touchpoints, prepare pitch-books, investor presentations,</t>
+          <t>support the development of NatWest Markets sustainable finance and ESG risk capabilities across European capital markets, support senior originators in frontline origination, risk engagement and client delivery, contribute to the development of high-quality sustainability-linked client materials and regulatory-aligned ESG assessments, assist with client deep dives, navigate the sales coverage teams and gather feedback from internal client touchpoints, prepare pitch-books, investor presentations, analyze market dynamics, identify market trends, produce client materials with focus on climate, ESG and regulatory developments, track markets dynamics, update and maintain internal databases, write weekly market commentary, support portfolio-level ESG materiality and risk assessments</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>sustainability and ESG risk, knowledge of various debt products and markets, comfort operating in evolving and complex sustainability-related regulatory environments, knowledge of investment banking and credit related products, advanced power point and excel skills, strong communication and interper</t>
+          <t>sustainability and ESG risk, knowledge of various debt products and markets, comfort operating in evolving and complex sustainability-related regulatory environments, knowledge of investment banking and credit related products, advanced power point and excel skills, strong communication and interpersonal skills, excellent analytical and commercial awareness skills</t>
         </is>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions sustainable finance, ESG risk, climate-related financial risk, and European sustainability regulatory frameworks, indicating a strong focus on sustainable finance and ESG topics.</t>
+          <t>The job description mentions sustainable finance, ESG risk, climate-related financial risk, and European sustainability regulatory frameworks, indicating a strong focus on sustainable finance and ESG topics.</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr"/>
@@ -3270,7 +3291,7 @@
       </c>
       <c r="O31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deloitte Audit &amp; Assurance - Talent Program Revisore Junior (0 - 1 anno di Esperienza). Le nostre altre attività di supporto sono: revisione di bilanci IAS/IFRS OIC e di reporting package, progetti di First Time Adoption (FTA) ovvero transizione dai principi contabili nazionali a principi contabili internazionali, verifica delle dichiarazioni (ad esempio 770), attestazioni delle ricerche e sviluppo. In quanto Analyst avrai la possibilità di imparare da colleghe e colleghi più Senior (attraverso </t>
+          <t>Deloitte Audit &amp; Assurance - Talent Program Revisore Junior (0 - 1 anno di Esperienza). Le nostre altre attività di supporto sono: revisione di bilanci IAS/IFRS OIC e di reporting package, progetti di First Time Adoption (FTA) ovvero transizione dai principi contabili nazionali a principi contabili internazionali, verifica delle dichiarazioni (ad esempio 770), attestazioni delle ricerche e sviluppo. In quanto Analyst avrai la possibilità di imparare da colleghe e colleghi più Senior (attraverso il learning on the job) e sviluppare competenze tecniche e relazionali.</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
@@ -3280,7 +3301,7 @@
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
-          <t>[general_esg] La menzione di strategie di Corporate Sustainability, ESG e sostenibilità ambientale, sociale e di governance all'interno della descrizione dell'azienda e del ruolo</t>
+          <t>La menzione di strategie di Corporate Sustainability, ESG e sostenibilità ambientale, sociale e di governance all'interno della descrizione dell'azienda e del ruolo</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr"/>
@@ -3357,7 +3378,7 @@
       </c>
       <c r="Q32" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions working with renewable energy sources (solar, hydro, and wind), low carbon energies, and contributing to the objective of Carbon Neutrality by 2050, which are all related to environmental sustainability and the clean energy sector.</t>
+          <t>The job description mentions working with renewable energy sources (solar, hydro, and wind), low carbon energies, and contributing to the objective of Carbon Neutrality by 2050, which are all related to environmental sustainability and the clean energy sector.</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr"/>
@@ -3436,7 +3457,7 @@
       </c>
       <c r="O33" s="6" t="inlineStr">
         <is>
-          <t>Deliver mandatory sustainability reporting services, including process development and audit readiness across carbon footprint measurement, climate risk assessments, scenario analysis, and preparation of sustainability disclosures. Provide tailored advice on sustainability and climate-related financial reporting across sectors, aligned with evolving standards and frameworks. Deliver expert advice on IFRS, AASB, and Australian Sustainability Reporting Standards. Support the CFO Advisory team with</t>
+          <t>Deliver mandatory sustainability reporting services, including process development and audit readiness across carbon footprint measurement, climate risk assessments, scenario analysis, and preparation of sustainability disclosures. Provide tailored advice on sustainability and climate-related financial reporting across sectors, aligned with evolving standards and frameworks. Deliver expert advice on IFRS, AASB, and Australian Sustainability Reporting Standards. Support the CFO Advisory team with technical accounting aspects of projects. Support and mentor junior team members. Contribute to proposal development, training, and coaching.</t>
         </is>
       </c>
       <c r="P33" s="6" t="inlineStr">
@@ -3446,7 +3467,7 @@
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions climate risk assessments, scenario analysis, and sustainability reporting, which are key aspects of climate risk management. The role also involves providing advice on sustainability and climate-related financial reporting, which is a critical component of</t>
+          <t>The job description mentions climate risk assessments, scenario analysis, and sustainability reporting, which are key aspects of climate risk management. The role also involves providing advice on sustainability and climate-related financial reporting, which is a critical component of climate risk management.</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
@@ -3525,7 +3546,7 @@
       </c>
       <c r="O34" s="6" t="inlineStr">
         <is>
-          <t>Serve as an ESG data expert for a broad universe of global companies, understand and further their expertise on Morningstar indexes’ sustainability product offerings, including methodology criteria and data needs, work closely with multiple global teams across various functions to ensure that indexes team gets the required data in time to support the product roadmap, stay up to date with developments in sustainable, environmental, and social activities, including current and emerging trends, dri</t>
+          <t>Serve as an ESG data expert for a broad universe of global companies, understand and further their expertise on Morningstar indexes’ sustainability product offerings, including methodology criteria and data needs, work closely with multiple global teams across various functions to ensure that indexes team gets the required data in time to support the product roadmap, stay up to date with developments in sustainable, environmental, and social activities, including current and emerging trends, drivers, key players, best practices, the regulatory landscape, etc., ensure appropriate methods and techniques to improve and maintain the highest quality standards in the data collected/ingested by the team, develop indexes ESG dashboards and metrics, provides coaching and training to junior team members as appropriate and according to the specific needs of the person and the group, provide floor support by answering questions, solving issues that come up throughout the day, work with technology teams in the role of UAT/Business Owner to complete the design of ESG data ingestion processes and tools.</t>
         </is>
       </c>
       <c r="P34" s="6" t="inlineStr">
@@ -3535,7 +3556,7 @@
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>[esg] The job description mentions ESG data expertise, EU taxonomy, climate risk, and sustainable investing, which are all relevant to the ESG profile.</t>
+          <t>The job description mentions ESG data expertise, EU taxonomy, climate risk, and sustainable investing, which are all relevant to the ESG profile.</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
@@ -3614,7 +3635,7 @@
       </c>
       <c r="O35" s="6" t="inlineStr">
         <is>
-          <t>Process and analyze geospatial data to contribute to the development of Swiss Re products and solutions, Develop and maintain scripts and pipelines to automate data processing and standardize workflows, Work closely with diverse teams across Swiss Re, providing geo-domain expertise, technical guidance, and support, Drive small projects independently, Coordinate and communicate effectively with other teams and stakeholders, provide regular project status updates, and ensure comprehensive and up-t</t>
+          <t>Process and analyze geospatial data to contribute to the development of Swiss Re products and solutions, Develop and maintain scripts and pipelines to automate data processing and standardize workflows, Work closely with diverse teams across Swiss Re, providing geo-domain expertise, technical guidance, and support, Drive small projects independently, Coordinate and communicate effectively with other teams and stakeholders, provide regular project status updates, and ensure comprehensive and up-to-date project documentation, Proactively identify, report, and resolve any issues or conflicts that may arise within the team or project, Foster a collaborative and positive team environment, Scout for new ideas and development for positive outcomes</t>
         </is>
       </c>
       <c r="P35" s="6" t="inlineStr">
@@ -3624,7 +3645,7 @@
       </c>
       <c r="Q35" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions natural catastrophes, climate change, and geospatial risk assessment, which are all relevant to climate risk, The company is also working to make the world more resilient, which implies a focus on managing and mitigating climate-related risks</t>
+          <t>The job description mentions natural catastrophes, climate change, and geospatial risk assessment, which are all relevant to climate risk, The company is also working to make the world more resilient, which implies a focus on managing and mitigating climate-related risks</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr"/>
@@ -3691,7 +3712,7 @@
       </c>
       <c r="O36" s="6" t="inlineStr">
         <is>
-          <t>The E T Consultant’s will support implementation of GPNBS programming. Tasks include coordinating and leading operational expert support on NBS to Task Teams and clients under the Operations pillar of the Program (advice on technical studies for project design and implementation, joining field missions and virtual meetings with client governments). The E T consultant will also be expected to contribute or lead knowledge products related to climate risk and NBS and support the other Pillars of th</t>
+          <t>The E T Consultant’s will support implementation of GPNBS programming. Tasks include coordinating and leading operational expert support on NBS to Task Teams and clients under the Operations pillar of the Program (advice on technical studies for project design and implementation, joining field missions and virtual meetings with client governments). The E T consultant will also be expected to contribute or lead knowledge products related to climate risk and NBS and support the other Pillars of the program where relevant. The E T Consultant will work closely with the Task Team Leaders and core staff of the Global Program, under managerial supervision of the Practice Manager of IDURM. Specific responsibilities and duties will include (but not be limited to) the following: Take a leading role in the delivery of geospatial and analytical assessments to Task Teams and Governments, including the NBSOS. Provide direct support to clients and Task Teams globally in the identification, assessment, implementation and monitoring of NBS, by conducting and supervising technical studies, providing input to project documents, training and capacity building, developing result indicators, participating in virtual and in-person meetings and missions, and related activities. Cultivate and advance partnerships with firms, consultants, external institutions, and internal World Bank teams for the co-development of new products, support to operational Task Teams, and advancement of the field of NBS. Lead and/or contribute to knowledge products related to NBS analytics developed under the Knowledge pillar of the Program. Illustrate Program advancements and contributions in the form of blogs, peer-reviewed papers, conference contributions, etc. Contribute to programmatic outputs including results monitoring, reporting, budgeting, and branding Deliver presentations and workshops at a variety of settings, including with Task Teams, government counterparts and at internal and external events.</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -3701,7 +3722,7 @@
       </c>
       <c r="Q36" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions climate risk, climate resilience, and climate change, indicating a strong focus on climate-related issues. The role involves working on Nature-Based Solutions for Climate Resilience, which is a key area of focus for climate risk management.</t>
+          <t>The job description mentions climate risk, climate resilience, and climate change, indicating a strong focus on climate-related issues. The role involves working on Nature-Based Solutions for Climate Resilience, which is a key area of focus for climate risk management.</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr"/>
@@ -3780,17 +3801,17 @@
       </c>
       <c r="O37" s="6" t="inlineStr">
         <is>
-          <t>The General Counsel (GC) will serve as the chief legal advisor to the organisation, overseeing all legal, regulatory, governance, and compliance matters for a rapidly growing renewable energy business. The GC will lead the legal function, support strategic decision-making, manage external counsel, and ensure the organisation’s interests are protected across all jurisdictions in which it operates. Key Responsibilities include Strategic Legal Leadership, Project Development &amp; Renewable Energy Tran</t>
+          <t>The General Counsel (GC) will serve as the chief legal advisor to the organisation, overseeing all legal, regulatory, governance, and compliance matters for a rapidly growing renewable energy business. The GC will lead the legal function, support strategic decision-making, manage external counsel, and ensure the organisation’s interests are protected across all jurisdictions in which it operates. Key Responsibilities include Strategic Legal Leadership, Project Development &amp; Renewable Energy Transactions, Mergers &amp; Acquisitions, Power Purchase Agreements (PPAs) &amp; Revenue Contracts, Investment, Divestment &amp; Capital Markets, Corporate Governance &amp; Compliance, and External Counsel &amp; Stakeholder Management.</t>
         </is>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Essential skills include drafting, negotiation, and commercial advisory skills. Desirable skills include international renewable energy experience, prior leadership of a legal function or high-performing legal team, experience in ESG, sustainability regulations, and climate-related disclosures, and </t>
+          <t>Essential skills include drafting, negotiation, and commercial advisory skills. Desirable skills include international renewable energy experience, prior leadership of a legal function or high-performing legal team, experience in ESG, sustainability regulations, and climate-related disclosures, and familiarity with corporate governance in high-growth or investor-backed companies.</t>
         </is>
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description is focused on renewable energy projects, utility-scale solar, wind, battery storage, and hybrid energy projects, which are all related to clean energy and environmental science.</t>
+          <t>The job description is focused on renewable energy projects, utility-scale solar, wind, battery storage, and hybrid energy projects, which are all related to clean energy and environmental science.</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
@@ -3877,17 +3898,17 @@
       </c>
       <c r="O38" s="6" t="inlineStr">
         <is>
-          <t>The TNC-GCF Climate Finance Specialist provides sophisticated business, financial and economic expertise to address conservation challenges. The TNC-GCF Climate Finance Specialist will support a key strategic initiative within The Nature Conservancy by sourcing, developing, and guiding the structuring of non-grant instruments financed by the Green Climate Fund in support of some of our most ambitious climate and conservation efforts. The Specialist is primarily responsible for developing the non</t>
+          <t>The TNC-GCF Climate Finance Specialist provides sophisticated business, financial and economic expertise to address conservation challenges. The TNC-GCF Climate Finance Specialist will support a key strategic initiative within The Nature Conservancy by sourcing, developing, and guiding the structuring of non-grant instruments financed by the Green Climate Fund in support of some of our most ambitious climate and conservation efforts. The Specialist is primarily responsible for developing the non-grant instrument (NGI) components of GCF project proposals, creating the enabling conditions to successfully deliver GCF projects with NGIs.</t>
         </is>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>Deep knowledge of financial institutions, including community, commercial, development, sovereign or investment banks and their approaches to loan origination, underwriting, on-lending and risk assessment. Knowledge of environmental and social management systems within financial institutions. Experi</t>
+          <t>Deep knowledge of financial institutions, including community, commercial, development, sovereign or investment banks and their approaches to loan origination, underwriting, on-lending and risk assessment. Knowledge of environmental and social management systems within financial institutions. Experience negotiating complex agreements and working with teams across the organization as well as externally. Experience with current and evolving sustainable finance and ESG trends.</t>
         </is>
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions experience with sustainable finance and ESG trends, and the role involves working with non-grant instruments financed by the Green Climate Fund, which is related to sustainable finance and impact investing.</t>
+          <t>The job description mentions experience with sustainable finance and ESG trends, and the role involves working with non-grant instruments financed by the Green Climate Fund, which is related to sustainable finance and impact investing.</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
@@ -3980,7 +4001,7 @@
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions working on environmental projects, including renewable energy, and conducting ecological field surveys, which aligns with the clean energy adjacent profile.</t>
+          <t>The job description mentions working on environmental projects, including renewable energy, and conducting ecological field surveys, which aligns with the clean energy adjacent profile.</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
@@ -4067,17 +4088,17 @@
       </c>
       <c r="O40" s="6" t="inlineStr">
         <is>
-          <t>Lead ESG advisory projects from inception to delivery, including strategic direction and team coordination. Collaborate with project managers to plan and execute projects, ensuring client satisfaction and successful outcomes. Develop and present comprehensive analyses, conclusions, and deliverables, including written reports, metrics, and insights. Execute multi-disciplinary projects across various aspects of sustainability platforms in a collaborative manner. Ensure quality deliverables aligned</t>
+          <t>Lead ESG advisory projects from inception to delivery, including strategic direction and team coordination. Collaborate with project managers to plan and execute projects, ensuring client satisfaction and successful outcomes. Develop and present comprehensive analyses, conclusions, and deliverables, including written reports, metrics, and insights. Execute multi-disciplinary projects across various aspects of sustainability platforms in a collaborative manner. Ensure quality deliverables aligned with client objectives and maintain high levels of client satisfaction through effective communication and engagement. Stay updated on ESG concepts, methodologies, and best practices, and share insights with the team to foster continuous improvement.</t>
         </is>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>Strong knowledge of ESG reporting frameworks, including GRI, SASB, DJSI/S&amp;P, CDP, BRSR, TCFD, and UNPRI. Advanced proficiency in MS Excel; data science skills are a plus. Strong written and verbal communication skills in English, with excellent presentation skills. Capable of working under pressure,</t>
+          <t>Strong knowledge of ESG reporting frameworks, including GRI, SASB, DJSI/S&amp;P, CDP, BRSR, TCFD, and UNPRI. Advanced proficiency in MS Excel; data science skills are a plus. Strong written and verbal communication skills in English, with excellent presentation skills. Capable of working under pressure, maintaining flexibility in work hours. Working independently with minimal supervision.</t>
         </is>
       </c>
       <c r="Q40" s="6" t="inlineStr">
         <is>
-          <t>[general_esg] The job description mentions ESG reporting, climate risk analysis, corporate ESG disclosures, and decarbonization strategies, which are all relevant to environmental, social, and governance topics, indicating a strong fit for the general_esg profile.</t>
+          <t>The job description mentions ESG reporting, climate risk analysis, corporate ESG disclosures, and decarbonization strategies, which are all relevant to environmental, social, and governance topics, indicating a strong fit for the general_esg profile.</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
@@ -4164,17 +4185,17 @@
       </c>
       <c r="O41" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Execute consulting projects for different clients related to ESG/ Sustainability Advisory across areas such as ESG Strategic Direction covering stakeholder engagement and materiality assessment, ESG Policy and Governance Framework, Sustainability Reporting &amp; Disclosures based on different frameworks, GHG Accounting, Decarbonization Roadmap using SBTi guidelines, Sustainable Financing, Supply chain, etc. Undertake activities required for execution such as research on companies and ESG practices, </t>
+          <t>Execute consulting projects for different clients related to ESG/ Sustainability Advisory across areas such as ESG Strategic Direction covering stakeholder engagement and materiality assessment, ESG Policy and Governance Framework, Sustainability Reporting &amp; Disclosures based on different frameworks, GHG Accounting, Decarbonization Roadmap using SBTi guidelines, Sustainable Financing, Supply chain, etc. Undertake activities required for execution such as research on companies and ESG practices, peer benchmarking, developing data collection templates and writing of ESG/ Sustainability reports. Ensure timely delivery of all project deliverables as per agreed timelines and client satisfaction. Travel to client location as may be required from time to time for the project activities. Work in tandem with the other team members and any other internal and external stakeholders such as design team, subject matter experts, etc. Assist the practice lead/ manager in practice development activities such as preparing pre-sales pitches, approach papers, point of views, articles, newsletter, etc. Keeping abreast of ESG trends and regulatory requirements in focus geographies Any other support that may be required from time to time for the development and growth of the practice.</t>
         </is>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
-          <t>Hands-on experience, knowledge and understanding of ESG/ sustainability concepts and frameworks like GRI, SASB, TCFD, etc. Proficient in MS Word, PowerPoint and Excel. Good writing and analytical skills Comfortable to engage in multiple projects simultaneously Highly flexible and quick learner to ad</t>
+          <t>Hands-on experience, knowledge and understanding of ESG/ sustainability concepts and frameworks like GRI, SASB, TCFD, etc. Proficient in MS Word, PowerPoint and Excel. Good writing and analytical skills Comfortable to engage in multiple projects simultaneously Highly flexible and quick learner to adopt and apply new methodology/ approach Open to travel for project execution Excellent communicator and good team player</t>
         </is>
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
-          <t>[general_esg] The job description mentions ESG Advisory, Sustainability Reporting, GHG Accounting, Decarbonization Roadmap, and Sustainable Financing, which are all related to environmental, social, and governance topics, indicating a strong fit with the general ESG profile.</t>
+          <t>The job description mentions ESG Advisory, Sustainability Reporting, GHG Accounting, Decarbonization Roadmap, and Sustainable Financing, which are all related to environmental, social, and governance topics, indicating a strong fit with the general ESG profile.</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
@@ -4250,12 +4271,12 @@
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
-          <t>Conoscenza dei principali software office quali MS Excel, Word, Power Point; Conoscenza di dei software di analisi dati e di mercato (R/Phyton, SAS, Qlik, SQL, PowerBi); Conoscenza dei framework di sostenibilità (es. SFDR, Taxonomy Regulation, ECB aspettative, CSR, DNF, PRI ecc.); Conoscenza di indi</t>
+          <t>Conoscenza dei principali software office quali MS Excel, Word, Power Point; Conoscenza di dei software di analisi dati e di mercato (R/Phyton, SAS, Qlik, SQL, PowerBi); Conoscenza dei framework di sostenibilità (es. SFDR, Taxonomy Regulation, ECB aspettative, CSR, DNF, PRI ecc.); Conoscenza di indici internazionali di sostenibilità come TCFD, GRI, CDP, SBTi e ESG</t>
         </is>
       </c>
       <c r="Q42" s="6" t="inlineStr">
         <is>
-          <t>[general_esg] The job description mentions sustainability, climate change, and ESG frameworks, indicating a focus on environmental, social, and governance topics.</t>
+          <t>The job description mentions sustainability, climate change, and ESG frameworks, indicating a focus on environmental, social, and governance topics.</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr"/>
@@ -4334,7 +4355,7 @@
       </c>
       <c r="O43" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assist in preparation of regular and ad-hoc risk reports, Review limits and guidelines of pension funds, compliance limit check of portfolio and target investments according to investment policy and imposed limits, Perform daily pension fund limit monitoring, Conduct investment risk analysis, quantitative and qualitative research, Perform analysis of the ESG risks applicable to pension funds and target investments, Maintain and improve supportive tools for analysis, measurement and reporting of </t>
+          <t>Assist in preparation of regular and ad-hoc risk reports, Review limits and guidelines of pension funds, compliance limit check of portfolio and target investments according to investment policy and imposed limits, Perform daily pension fund limit monitoring, Conduct investment risk analysis, quantitative and qualitative research, Perform analysis of the ESG risks applicable to pension funds and target investments, Maintain and improve supportive tools for analysis, measurement and reporting of investment and ESG metrics of pension funds and target investments, Deliver and follow-up on personal tasks timely and according to the set quality standards, Take responsibility in professional self-development and contribute to own and team performance improvement by constructive feedback and relevant suggestions</t>
         </is>
       </c>
       <c r="P43" s="6" t="inlineStr">
@@ -4344,7 +4365,7 @@
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions 'sustainable finance', 'ESG risks', and 'investment risk analysis', which are key terms related to sustainable finance and ESG investing.</t>
+          <t>The job description mentions 'sustainable finance', 'ESG risks', and 'investment risk analysis', which are key terms related to sustainable finance and ESG investing.</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
@@ -4432,12 +4453,12 @@
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
-          <t>Proven experience with: Valorisation of research and technology, including optimal IP valorisation, Scaling and de-risking innovations towards industry, Public-private partnerships, Ability to connect complex ecosystems and align stakeholders around a shared ambition, Fluent in English and Dutch; ot</t>
+          <t>Proven experience with: Valorisation of research and technology, including optimal IP valorisation, Scaling and de-risking innovations towards industry, Public-private partnerships, Ability to connect complex ecosystems and align stakeholders around a shared ambition, Fluent in English and Dutch; other languages are a plus</t>
         </is>
       </c>
       <c r="Q44" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions cleantech, circularity, materials, chemistry, and industrial transition, which are all related to environmental science and sustainability, and specifically mentions the development of low-CO₂ construction materials, plastics recycling, and bio-ec</t>
+          <t>The job description mentions cleantech, circularity, materials, chemistry, and industrial transition, which are all related to environmental science and sustainability, and specifically mentions the development of low-CO₂ construction materials, plastics recycling, and bio-economy, which are all relevant to the clean energy and environmental science fields</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
@@ -4520,7 +4541,7 @@
       </c>
       <c r="O45" s="6" t="inlineStr">
         <is>
-          <t>The intern will support ISO with analytical and preparatory work that helps identify behavioural barriers, motivational drivers, and communication opportunities linked to four priority areas identified through the Green Pulse Survey conducted in 2025. The role is primarily analytical and strategic, with communications and graphic design skills considered an asset to support knowledge translation and internal engagement. The intern will be responsible for the following general/specific tasks: Beh</t>
+          <t>The intern will support ISO with analytical and preparatory work that helps identify behavioural barriers, motivational drivers, and communication opportunities linked to four priority areas identified through the Green Pulse Survey conducted in 2025. The role is primarily analytical and strategic, with communications and graphic design skills considered an asset to support knowledge translation and internal engagement. The intern will be responsible for the following general/specific tasks: Behavioural Insights Review &amp; Evidence Synthesis, Behavioural Diagnostics &amp; Prioritization, Strategy Development Support, Coordination &amp; Consultation Support, Knowledge Management &amp; Documentation.</t>
         </is>
       </c>
       <c r="P45" s="6" t="inlineStr">
@@ -4530,7 +4551,7 @@
       </c>
       <c r="Q45" s="6" t="inlineStr">
         <is>
-          <t>[general_esg] The job description mentions sustainability, social and behaviour change, and environmental footprint, which are all related to ESG strategy and corporate sustainability.</t>
+          <t>The job description mentions sustainability, social and behaviour change, and environmental footprint, which are all related to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -4601,17 +4622,17 @@
       </c>
       <c r="O46" s="6" t="inlineStr">
         <is>
-          <t>Corporate and Project Financing: In collaboration with the Corporate Finance Manager, you will ensure suitable and competitive financing of the group’s financial needs. You propose and design the most appropriate type of debt taking into account the group strategy &amp; policies. You go to the capital market and lead financing projects, negotiate the best financing conditions and finalise the transactions. You evaluate the interest of sustainable finance &amp; ESG instruments, propose the most appropria</t>
+          <t>Corporate and Project Financing: In collaboration with the Corporate Finance Manager, you will ensure suitable and competitive financing of the group’s financial needs. You propose and design the most appropriate type of debt taking into account the group strategy &amp; policies. You go to the capital market and lead financing projects, negotiate the best financing conditions and finalise the transactions. You evaluate the interest of sustainable finance &amp; ESG instruments, propose the most appropriate options for Fluxys activities. Hedging &amp; risks: Together with the back-office team, you will monitor and report on interest rates, exchange rates and liquidity risks. You propose appropriate hedging transactions and negotiate best foreign exchange and hedging conditions. Group treasury management: You carry out daily treasury activities and maximise the return on financial investments and optimise cash management by monitoring short-term deposits and financing. Stakeholder management: You will work with and maintain an active network of relationships with banks, institutional investors and other financial market players. You monitor markets conditions and develop market intelligence and provide financing advisory services to a wide range of internal stakeholders (M&amp;A, business development, subsidiaries). You contribute to financial due diligence exercises by providing accurate and timely information.</t>
         </is>
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
-          <t>Strong analytical skills, in-depth understanding of financial markets, comprehensive knowledge of various debt instruments, proficiency in daily treasury activities, cash management, and optimizing financial investments, experience in people management, natural communicator, high-impact professional</t>
+          <t>Strong analytical skills, in-depth understanding of financial markets, comprehensive knowledge of various debt instruments, proficiency in daily treasury activities, cash management, and optimizing financial investments, experience in people management, natural communicator, high-impact professional, strong strategic mindset, results-oriented and resilient.</t>
         </is>
       </c>
       <c r="Q46" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions 'sustainable finance &amp; ESG instruments' and the company is committed to fast-tracking the shift to a carbon neutral world, indicating a focus on sustainable finance and ESG concepts.</t>
+          <t>The job description mentions 'sustainable finance &amp; ESG instruments' and the company is committed to fast-tracking the shift to a carbon neutral world, indicating a focus on sustainable finance and ESG concepts.</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr"/>
@@ -4696,7 +4717,7 @@
       </c>
       <c r="Q47" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions ESG factors, sustainable finance, green finance, and sustainable investment initiatives, which are all relevant to the sustainable finance profile.</t>
+          <t>The job description mentions ESG factors, sustainable finance, green finance, and sustainable investment initiatives, which are all relevant to the sustainable finance profile.</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr"/>
@@ -4763,7 +4784,7 @@
       </c>
       <c r="O48" s="6" t="inlineStr">
         <is>
-          <t>You will have the opportunity to gain insight into the forest management and natural capital sector and be involved in everything from asset management to deal sourcing and execution, providing an ideal opportunity to develop your skills and learn about the day-to-day work in natural capital investments. As an Investment Intern, you will participate in various activities related to forestry and natural capital investments, including: Doing market research and analysing market trends, Creating fu</t>
+          <t>You will have the opportunity to gain insight into the forest management and natural capital sector and be involved in everything from asset management to deal sourcing and execution, providing an ideal opportunity to develop your skills and learn about the day-to-day work in natural capital investments. As an Investment Intern, you will participate in various activities related to forestry and natural capital investments, including: Doing market research and analysing market trends, Creating fund marketing materials and other internal or external presentations, Assisting in the analysis of new investment opportunities and preparation of investment presentations, Assisting in financial modelling and valuation as part of the screening process of new investment opportunities, Participating in due diligence processes for new acquisitions, according to possibilities, Supporting in the value creation of existing portfolio companies by participating in day-to-day asset management, according to possibilities, Collaborating on exciting business development projects to further CapMan Natural Capital’s impact</t>
         </is>
       </c>
       <c r="P48" s="6" t="inlineStr">
@@ -4773,7 +4794,7 @@
       </c>
       <c r="Q48" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions natural capital investments, forestry, and sustainable forestry investments, which are related to environmental science and conservation, fitting the clean_energy_adjacent profile.</t>
+          <t>The job description mentions natural capital investments, forestry, and sustainable forestry investments, which are related to environmental science and conservation, fitting the clean_energy_adjacent profile.</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr"/>
@@ -4852,7 +4873,7 @@
       </c>
       <c r="O49" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perform in-depth financial modelling and analysis related to capital structure, funding strategy, acquisition and debt capacity, and credit ratings. Integrate sustainability considerations into financial analysis, including impacts on availability, pricing and structure of capital. Prepare clear, well-structured and robust materials for senior internal stakeholders and client presentations. Take an active role in client projects, with increasing exposure to senior decision-makers. Contribute to </t>
+          <t>Perform in-depth financial modelling and analysis related to capital structure, funding strategy, acquisition and debt capacity, and credit ratings. Integrate sustainability considerations into financial analysis, including impacts on availability, pricing and structure of capital. Prepare clear, well-structured and robust materials for senior internal stakeholders and client presentations. Take an active role in client projects, with increasing exposure to senior decision-makers. Contribute to the continuous development of analytical tools, methodologies and advisory processes.</t>
         </is>
       </c>
       <c r="P49" s="6" t="inlineStr">
@@ -4862,7 +4883,7 @@
       </c>
       <c r="Q49" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions integrating sustainability considerations into financial analysis, and the role is part of the Corporate &amp; Sustainability Advisory team, indicating a focus on sustainable finance.</t>
+          <t>The job description mentions integrating sustainability considerations into financial analysis, and the role is part of the Corporate &amp; Sustainability Advisory team, indicating a focus on sustainable finance.</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
@@ -4954,12 +4975,12 @@
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCA Tools like SimaPro, guideline documents and operational system of a GHG reduction scheme, project cycle and Regulatory requirements, auditing principles, procedures and techniques, risk assessment techniques, data and information sampling techniques, materiality and level of assurance concepts, </t>
+          <t>LCA Tools like SimaPro, guideline documents and operational system of a GHG reduction scheme, project cycle and Regulatory requirements, auditing principles, procedures and techniques, risk assessment techniques, data and information sampling techniques, materiality and level of assurance concepts, MS Office, verbal &amp; written expression, fluent in spoken English, par-excellence writing skills, deadline oriented</t>
         </is>
       </c>
       <c r="Q50" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions GHG Footprint, LCA, ESG, BRSR Reporting, and GHG reduction schemes, which are directly related to climate risk and transition risk.</t>
+          <t>The job description mentions GHG Footprint, LCA, ESG, BRSR Reporting, and GHG reduction schemes, which are directly related to climate risk and transition risk.</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
@@ -5107,7 +5128,7 @@
       </c>
       <c r="O52" s="6" t="inlineStr">
         <is>
-          <t>The HR Project &amp; Transformation Lead will partner across the HR functions and Business Groups to deliver value-added services to management and employees. Lead and drive projects that enhance networking opportunities and foster HR collaboration across Sectors and Business Units within the Region, including cross-regional collaboration among RHQ HR teams. Assume responsibility as Project Lead and Project Manager in relation to collaboration activities across Groups. Expand engagement with other G</t>
+          <t>The HR Project &amp; Transformation Lead will partner across the HR functions and Business Groups to deliver value-added services to management and employees. Lead and drive projects that enhance networking opportunities and foster HR collaboration across Sectors and Business Units within the Region, including cross-regional collaboration among RHQ HR teams. Assume responsibility as Project Lead and Project Manager in relation to collaboration activities across Groups. Expand engagement with other Groups around internal mobility to attract and retain employees across the Region. Work as the HR lead on projects as required. Work closely with management and stakeholders to further enhance work relationships and collaboration across Groups in EMEA. Promote the Hitachi Brand in EMEA, to attract and onboard top talent. Provide regional enablement for legislative changes such as the EU Pay Directive. Support education of Managers and employees around new landscape for Diversity. Drive a ‘growth mindset’ culture within the Regional HQ and beyond. Support line managers across the Region in leading and delivering change including restructuring, reorganization, integration, consultation, TUPE, redundancy, job redesign and redeployments. Manage and resolve complex employee relations issues as needed</t>
         </is>
       </c>
       <c r="P52" s="6" t="inlineStr">
@@ -5117,7 +5138,7 @@
       </c>
       <c r="Q52" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions integrating sustainability considerations into financial analysis, and the role is part of the Corporate &amp; Sustainability Advisory team, indicating a focus on sustainable finance.</t>
+          <t>The job description does not explicitly mention ESG, sustainability, or climate-related responsibilities, requirements, or skills, despite the company being involved in climate change innovation and green energy. The role is focused on HR project and transformation leadership, which does not fit into any of the specified ESG/sustainability profiles.</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr"/>
@@ -5184,17 +5205,17 @@
       </c>
       <c r="O53" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Head of Finance and Accounting is a highly visible leadership position responsible for managing the organization’s financial control environment and ensuring compliance with IFRS, Group Financial Guidelines and local Statutory Accounting and regulatory requirements across the Europe, Middle East and Africa region. This role oversees end-to-end accounting operations, including monthly, quarterly, and annual closings, and holds accountability for working capital and balance sheet forecasting, </t>
+          <t>The Head of Finance and Accounting is a highly visible leadership position responsible for managing the organization’s financial control environment and ensuring compliance with IFRS, Group Financial Guidelines and local Statutory Accounting and regulatory requirements across the Europe, Middle East and Africa region. This role oversees end-to-end accounting operations, including monthly, quarterly, and annual closings, and holds accountability for working capital and balance sheet forecasting, Balance Sheet and treasury management, and intercompany processes to maintain financial integrity. Key Responsibilities: Financial Governance &amp; Compliance, Process Improvement &amp; Standardization, Stakeholder Collaboration, Team Leadership &amp; Transformation, Safety First</t>
         </is>
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>Technical expertise in finance and accounting, leadership capabilities, strong communication and collaboration skills, ability to build and develop a high-performing accounting organization, experience with SAP ERP systems, knowledge of IFRS, statutory reporting, internal controls, audit management,</t>
+          <t>Technical expertise in finance and accounting, leadership capabilities, strong communication and collaboration skills, ability to build and develop a high-performing accounting organization, experience with SAP ERP systems, knowledge of IFRS, statutory reporting, internal controls, audit management, treasury operations, FX risk management, and working capital optimization</t>
         </is>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions GHG Footprint, LCA, ESG, BRSR Reporting, and GHG reduction schemes, which are directly related to climate risk and transition risk.</t>
+          <t>The job description does not explicitly mention ESG, sustainability, or environmental topics in the context of the role's responsibilities, requirements, or skills, except for a general mention of 'sustainable' in the company description which is not directly related to the job's responsibilities</t>
         </is>
       </c>
       <c r="R53" s="2" t="inlineStr"/>
@@ -5261,17 +5282,17 @@
       </c>
       <c r="O54" s="6" t="inlineStr">
         <is>
-          <t>With an exclusive focus on the Nespresso business, you will work within the core Finance team, supporting the design of financial, fiscal, and accounting flows across various business processes while building and enhancing the technology platforms that support the business. As a Senior Finance IT Business Analyst, you will coordinate and guide a team of IT Business Analysts and Product Experts responsible for understanding end-to-end business flows. You will analyze and define business and funct</t>
+          <t>With an exclusive focus on the Nespresso business, you will work within the core Finance team, supporting the design of financial, fiscal, and accounting flows across various business processes while building and enhancing the technology platforms that support the business. As a Senior Finance IT Business Analyst, you will coordinate and guide a team of IT Business Analysts and Product Experts responsible for understanding end-to-end business flows. You will analyze and define business and functional requirements, collaborating with team members to translate these requirements into the product backlog.</t>
         </is>
       </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
-          <t>Experience working on Finance/Fiscal legislation initiatives related to retail business flows running on ERP systems, POS systems and e-Commerce. Experience working in a global environment and with virtual teams. Strong analytical thinking and business analysis skills. Effective communication, inter</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>This role contributes to the sustainable development goals of Nestlé by supporting the financial and technological aspects of Nespresso's operations.</t>
+          <t>Experience working on Finance/Fiscal legislation initiatives related to retail business flows running on ERP systems, POS systems and e-Commerce. Experience working in a global environment and with virtual teams. Strong analytical thinking and business analysis skills. Effective communication, interpersonal, and stakeholder management abilities.</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>The job description does not mention any specific ESG, sustainability, or climate-related responsibilities, requirements, or skills that would fit into one of the provided profiles.</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr"/>
@@ -5346,17 +5367,17 @@
       </c>
       <c r="O55" s="6" t="inlineStr">
         <is>
-          <t>Lead and Deliver Strategic Mining Advisory Projects, Manage and execute environmental and social performance input into feasibility studies, due diligence assignments, ITRs/ITERs, and operational improvement programs. Deliver clear, innovative, and commercially relevant insights aligned with client needs and project scope. Provide Senior Technical Expertise, Participate in Multi-Disciplinary Project Teams, Engage Senior and Executive-Level Stakeholders, Drive Business Development and Industry Pr</t>
+          <t>Lead and Deliver Strategic Mining Advisory Projects, Manage and execute environmental and social performance input into feasibility studies, due diligence assignments, ITRs/ITERs, and operational improvement programs. Deliver clear, innovative, and commercially relevant insights aligned with client needs and project scope. Provide Senior Technical Expertise, Participate in Multi-Disciplinary Project Teams, Engage Senior and Executive-Level Stakeholders, Drive Business Development and Industry Presence, Support Team Culture, Collaboration &amp; Wellbeing</t>
         </is>
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Technical Skills &amp; Experience, Environmental and social impact assessment, environmental and social due diligence, environmental and social management systems, lenders environmental and social performance requirements, including but not limited to Equator Principles and IFC Environmental and Social </t>
+          <t>Technical Skills &amp; Experience, Environmental and social impact assessment, environmental and social due diligence, environmental and social management systems, lenders environmental and social performance requirements, including but not limited to Equator Principles and IFC Environmental and Social Performance Standards</t>
         </is>
       </c>
       <c r="Q55" s="6" t="inlineStr">
         <is>
-          <t>[general_esg] The job description mentions environmental and social performance management, impact assessment, and due diligence, which are all relevant to ESG strategy and corporate sustainability. The role also involves providing advice on environmental and social performance to mining clients, wh</t>
+          <t>The job description mentions environmental and social performance management, impact assessment, and due diligence, which are all relevant to ESG strategy and corporate sustainability. The role also involves providing advice on environmental and social performance to mining clients, which aligns with the general ESG profile.</t>
         </is>
       </c>
       <c r="R55" s="2" t="inlineStr">
@@ -5439,17 +5460,17 @@
       </c>
       <c r="O56" s="6" t="inlineStr">
         <is>
-          <t>Develop and execute a comprehensive sales strategy for Neural Alpha’s SaaS platform, targeting financial institutions, asset managers, corporates and NGOs. Own the full sales cycle from prospecting and lead qualification through to negotiation, close and handover to Customer Success. Build and manage a robust sales pipeline using CRM tools, ensuring accurate forecasting and reporting to senior leadership. Establish and lead the creation of a scalable sales function, defining processes, playbooks</t>
+          <t>Develop and execute a comprehensive sales strategy for Neural Alpha’s SaaS platform, targeting financial institutions, asset managers, corporates and NGOs. Own the full sales cycle from prospecting and lead qualification through to negotiation, close and handover to Customer Success. Build and manage a robust sales pipeline using CRM tools, ensuring accurate forecasting and reporting to senior leadership. Establish and lead the creation of a scalable sales function, defining processes, playbooks, methodologies and best practices. Lead client-facing engagements including discovery calls, platform demonstrations, proof of concept discussions and commercial negotiations. Represent Neural Alpha at industry conferences, webinars, roundtables, working groups and networking events, building the company’s profile and generating new business opportunities.</t>
         </is>
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
-          <t>Proficiency with CRM platforms (e.g. HubSpot, Salesforce) and modern sales enablement tools. Comfortable embracing and leveraging AI tools and technology to enhance personal productivity and sales effectiveness. Knowledge of ESG, sustainable finance, or regulatory frameworks such as ISSB, CSRD, EU T</t>
+          <t>Proficiency with CRM platforms (e.g. HubSpot, Salesforce) and modern sales enablement tools. Comfortable embracing and leveraging AI tools and technology to enhance personal productivity and sales effectiveness. Knowledge of ESG, sustainable finance, or regulatory frameworks such as ISSB, CSRD, EU Taxonomy, SFDR and TNFD.</t>
         </is>
       </c>
       <c r="Q56" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions experience selling into financial institutions, asset managers or large corporates, and knowledge of ESG, sustainable finance, or regulatory frameworks such as ISSB, CSRD, EU Taxonomy, SFDR and TNFD, indicating a strong connection to sustainable fin</t>
+          <t>The job description mentions experience selling into financial institutions, asset managers or large corporates, and knowledge of ESG, sustainable finance, or regulatory frameworks such as ISSB, CSRD, EU Taxonomy, SFDR and TNFD, indicating a strong connection to sustainable finance.</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr">
@@ -5532,7 +5553,7 @@
       </c>
       <c r="O57" s="6" t="inlineStr">
         <is>
-          <t>The incumbent will be responsible for product strategy and coordination, product delivery, capacity building and deployment, quality assurance, stakeholder engagement, and knowledge management. Specific duties include: Liaise with CAFI PES technical team and implementation partners to capture functional requirements, Translate operational needs into clear technical specifications for developers, Monitor and report on project progress, Drive the functional vision and evolution of the products, En</t>
+          <t>The incumbent will be responsible for product strategy and coordination, product delivery, capacity building and deployment, quality assurance, stakeholder engagement, and knowledge management. Specific duties include: Liaise with CAFI PES technical team and implementation partners to capture functional requirements, Translate operational needs into clear technical specifications for developers, Monitor and report on project progress, Drive the functional vision and evolution of the products, Ensure integration with other digital tools used by CAFI, Develop the work plan for the developers, Review prototypes, Coordinate user acceptance testing and validation of system features, Facilitate/Coordinate training of CAFI colleagues, implementation partners and partner governments on system use, Develop user guides and SOPs for PES digital workflows, Ensure data integrity, traceability, and compliance with CAFI’s monitoring &amp; evaluation and data protection policies, Ensure the overall cyber security and integrity of the system, Facilitate integration of independent verification processes into the system, Maintain regular communication between CAFI Secretariat, IT teams, and field partners, Document lessons learned and contribute to system improvement roadmap, Facilitate knowledge-sharing and capacity-building activities for project partners and stakeholders, Identify opportunities for PES systems through collaboration with other technical teams and experts, Plan and lead in-person workshops and side events, Contribute to global Digital Public Infrastructure discussions, briefing notes, and concepts related to the PES systems, Plan, design, and coordinate a Community of Practice.</t>
         </is>
       </c>
       <c r="P57" s="6" t="inlineStr">
@@ -5542,7 +5563,7 @@
       </c>
       <c r="Q57" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description is related to the conservation of forests, reduction of deforestation, and promotion of sustainable development, which are all relevant to the clean energy and environmental conservation sector.</t>
+          <t>The job description is related to the conservation of forests, reduction of deforestation, and promotion of sustainable development, which are all relevant to the clean energy and environmental conservation sector.</t>
         </is>
       </c>
       <c r="R57" s="2" t="inlineStr">
@@ -5625,7 +5646,7 @@
       </c>
       <c r="O58" s="6" t="inlineStr">
         <is>
-          <t>You will contribute to financial audit engagements and, in parallel, support the Data Audit Team by delivering analytics that strengthen audit quality, consistency, and documentation. Collect, structure and process large financial and operational datasets for audit purposes. Perform data analyses to support risk assessments and audit procedures. Build audit-ready outputs and visualizations using Excel and Power BI where relevant. Automate and continuously improve data-driven audit analyses and t</t>
+          <t>You will contribute to financial audit engagements and, in parallel, support the Data Audit Team by delivering analytics that strengthen audit quality, consistency, and documentation. Collect, structure and process large financial and operational datasets for audit purposes. Perform data analyses to support risk assessments and audit procedures. Build audit-ready outputs and visualizations using Excel and Power BI where relevant. Automate and continuously improve data-driven audit analyses and techniques. Ensure data integrity by validating the completeness and reliability of client data and documenting key checks and transformations in line with audit quality standards. Collaborate with audit teams to enable strong, meaningful audit conclusions by designing fit-for-purpose analytics. Act as a key point of contact with client finance stakeholders and internal data owners to collect the right data, on time, and clarify extraction requirements. Actively contribute to innovation and continuous improvement within the audit data team.</t>
         </is>
       </c>
       <c r="P58" s="6" t="inlineStr">
@@ -5633,9 +5654,9 @@
           <t>Data analytics, data engineering, Excel, Power BI, SQL, Python, business economics, finance, audit fundamentals</t>
         </is>
       </c>
-      <c r="Q58" s="2" t="inlineStr">
-        <is>
-          <t>This role is within the finance industry, focusing on auditing and data analytics for financial reporting and risk assessment.</t>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>The job description does not explicitly mention ESG, sustainability, or environmental topics in the context of the role's responsibilities, requirements, or skills, other than the company's general sustainability policy which is not directly related to the job.</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr">
@@ -5718,7 +5739,7 @@
       </c>
       <c r="O59" s="6" t="inlineStr">
         <is>
-          <t>The role will include the following objectives: Provide technical expertise and operational support to GFDRR’s Disaster-FCV Nexus program, focusing on FCV-sensitive disaster risk management and climate resilience. Strengthen GFDRR’s analytical, advisory, and partnership work on the disaster-FCV nexus, including knowledge generation, policy dialogue, and capacity building. Facilitate collaboration and knowledge exchange with EU institutions, regional bodies, and other stakeholders in Brussels and</t>
+          <t>The role will include the following objectives: Provide technical expertise and operational support to GFDRR’s Disaster-FCV Nexus program, focusing on FCV-sensitive disaster risk management and climate resilience. Strengthen GFDRR’s analytical, advisory, and partnership work on the disaster-FCV nexus, including knowledge generation, policy dialogue, and capacity building. Facilitate collaboration and knowledge exchange with EU institutions, regional bodies, and other stakeholders in Brussels and beyond.</t>
         </is>
       </c>
       <c r="P59" s="6" t="inlineStr">
@@ -5728,7 +5749,7 @@
       </c>
       <c r="Q59" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[climate_risk] The job description mentions climate change, disaster risk management, and climate resilience, which are all related to climate risk. The role also involves working with the Global Facility for Disaster Reduction and Recovery (GFDRR), which is a global partnership that helps low- and </t>
+          <t>The job description mentions climate change, disaster risk management, and climate resilience, which are all related to climate risk. The role also involves working with the Global Facility for Disaster Reduction and Recovery (GFDRR), which is a global partnership that helps low- and middle-income countries better understand and reduce their vulnerability to natural hazards and climate change.</t>
         </is>
       </c>
       <c r="R59" s="2" t="inlineStr">
@@ -5811,17 +5832,17 @@
       </c>
       <c r="O60" s="6" t="inlineStr">
         <is>
-          <t>We are looking for a skilled quantitative professional, who may combine working on Belgian and European financial institutions. The ability to drive work forward to a conclusion, to find pragmatic solutions to complex problems and to explain and document them convincingly, are key factors in order to be successful in this role. Typical projects you will be involved in: Participate in, and lead Risk engagements, with the focus credit risk modeling, including the link with accounting (e.g. IFRS 9)</t>
+          <t>We are looking for a skilled quantitative professional, who may combine working on Belgian and European financial institutions. The ability to drive work forward to a conclusion, to find pragmatic solutions to complex problems and to explain and document them convincingly, are key factors in order to be successful in this role. Typical projects you will be involved in: Participate in, and lead Risk engagements, with the focus credit risk modeling, including the link with accounting (e.g. IFRS 9) You participate in engagements in the Risk practice, in the quantitative space, both from an advisory and an assurance perspective Support banks in preparing for regulatory reviews, or help them mitigate model weaknesses Assist banks in any stage of the model life cycle (developing new models, backtesting, independent validation of credit models, …) In the context of market risk and (derivative) valuation models typical tasks are: Develop and apply EY tools &amp; models Participate to model development and model validation exercises Identify new areas for further development of EY tools &amp; models, including the innovative application of machine learning in this application domain Assess the impact of climate risk and ESG considerations in general on market risk and (derivative) valuation model Explore and exploit the potential of alternative data and machine learning techniques to help financial institutions bring their credit modelling to the next level Investigate the impact of climate risk and ESG aspects in general on credit risk Contribute to the standardization and automation of the model development and model validation process Understand our full range of service offerings and actively identify and develop new opportunities to address emerging client needs You coordinate the workload in various projects, and develop productive working relationships with internal and external clients You prepare concise, complete and convincing reports on the work done, and present it to more senior colleagues and clients You act as a team member, coaching and supervising junior staff, seeking guidance from senior colleagues as needed, and keeping everybody informed on the progress of the assignment.</t>
         </is>
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
-          <t>Solid understanding of quantitative modeling techniques and practical experience with valuation of complex instruments (e.g. derivative, illiquid bonds) and/or market risk (e.g. FRTB, IRRBB, VAR models) is mandatory Deep understanding of quantitative modeling techniques, with practical experience in</t>
+          <t>Solid understanding of quantitative modeling techniques and practical experience with valuation of complex instruments (e.g. derivative, illiquid bonds) and/or market risk (e.g. FRTB, IRRBB, VAR models) is mandatory Deep understanding of quantitative modeling techniques, with practical experience in credit risk (IRB, IFRS9) and practical experience with derivative pricing in one or more asset classes (FX, rates, equity, …) Knowledge of some key vendor packages, and some frequently used programming languages (R, Matlab, C++, Python, SAS) in the risk and/or valuation domain is mandatory Strong interest in or some initial experience with machine learning algorithms</t>
         </is>
       </c>
       <c r="Q60" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions 'sustainable finance workgroup' and 'climate risk modelling for financial institutions', indicating a focus on sustainable finance and ESG considerations in the context of financial risk management.</t>
+          <t>The job description mentions 'sustainable finance workgroup' and 'climate risk modelling for financial institutions', indicating a focus on sustainable finance and ESG considerations in the context of financial risk management.</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr">
@@ -5912,7 +5933,7 @@
       </c>
       <c r="Q61" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions 'atmospheric perils', 'extreme weather events', 'changing climate', and 'climate modelling' which are all related to climate risk.</t>
+          <t>The job description mentions 'atmospheric perils', 'extreme weather events', 'changing climate', and 'climate modelling' which are all related to climate risk.</t>
         </is>
       </c>
       <c r="R61" s="2" t="inlineStr">
@@ -5995,17 +6016,17 @@
       </c>
       <c r="O62" s="6" t="inlineStr">
         <is>
-          <t>The intern will have the opportunity to be involved in the following duties: Supporting different research works conducted by the team; Analyzing policy documents and legal texts, to collect and review data; Assisting with research and fact-checking for International IDEA materials and background information; Assisting in the organization and the follow-up of conferences, events and activities, including assisting with reporting, note-taking and some logistical tasks; Providing desk research and</t>
+          <t>The intern will have the opportunity to be involved in the following duties: Supporting different research works conducted by the team; Analyzing policy documents and legal texts, to collect and review data; Assisting with research and fact-checking for International IDEA materials and background information; Assisting in the organization and the follow-up of conferences, events and activities, including assisting with reporting, note-taking and some logistical tasks; Providing desk research and contributing to the conceptualization of other new and ongoing projects within the teams; Developing outreach, media and communications materials; Actively incorporating a gender and inclusion perspective in all activities; Assisting with Ad-hoc projects and tasks.</t>
         </is>
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
-          <t>Strong analytical, drafting, editorial and problem-solving skills. Ability to appreciate diversity and work as part of a team in such an environment. Ability to assess, manage and structure information. Strong interpersonal and communication skills. Good knowledge of Microsoft Office suite. Knowledg</t>
+          <t>Strong analytical, drafting, editorial and problem-solving skills. Ability to appreciate diversity and work as part of a team in such an environment. Ability to assess, manage and structure information. Strong interpersonal and communication skills. Good knowledge of Microsoft Office suite. Knowledge of information management systems is an asset.</t>
         </is>
       </c>
       <c r="Q62" s="6" t="inlineStr">
         <is>
-          <t>[general_esg] The job description mentions 'sustainable democracy', 'climate change and democracy', and 'democracy and inclusion', which are related to environmental, social, and governance topics, but the primary focus is on democratic institutions and processes, making it a better fit for the gene</t>
+          <t>The job description mentions 'sustainable democracy', 'climate change and democracy', and 'democracy and inclusion', which are related to environmental, social, and governance topics, but the primary focus is on democratic institutions and processes, making it a better fit for the general ESG profile.</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr">
@@ -6088,7 +6109,7 @@
       </c>
       <c r="O63" s="6" t="inlineStr">
         <is>
-          <t>Our Sustainability Climate Change and Risk covers several disciplines including; Energy Transition &amp; Markets, Decarbonisation and Physical Risk Strategy. As a Graduate Consultant in our Sustainability, Climate Change &amp; Risk team, team at Aurecon, you’ll: Own your career while growing your skills through workshops and self-paced learning, Apply your analytical and problem-solving skills on live client projects, Work with diverse, multidisciplinary teams across engineering, advisory, and design, L</t>
+          <t>Our Sustainability Climate Change and Risk covers several disciplines including; Energy Transition &amp; Markets, Decarbonisation and Physical Risk Strategy. As a Graduate Consultant in our Sustainability, Climate Change &amp; Risk team, team at Aurecon, you’ll: Own your career while growing your skills through workshops and self-paced learning, Apply your analytical and problem-solving skills on live client projects, Work with diverse, multidisciplinary teams across engineering, advisory, and design, Learn from industry experts and mentors through hands-on guidance, Connect through Limelight, our early careers network</t>
         </is>
       </c>
       <c r="P63" s="6" t="inlineStr">
@@ -6098,7 +6119,7 @@
       </c>
       <c r="Q63" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions 'Sustainability Climate Change and Risk', 'Energy Transition &amp; Markets', 'Decarbonisation and Physical Risk Strategy', which are all related to climate risk and sustainability.</t>
+          <t>The job description mentions 'Sustainability Climate Change and Risk', 'Energy Transition &amp; Markets', 'Decarbonisation and Physical Risk Strategy', which are all related to climate risk and sustainability.</t>
         </is>
       </c>
       <c r="R63" s="2" t="inlineStr">
@@ -6185,7 +6206,7 @@
       </c>
       <c r="O64" s="6" t="inlineStr">
         <is>
-          <t>The Associate Director, Climate Change and Environment supports the growth of Tetra Tech International Development’s climate portfolio across Australia and the Indo‑Pacific through business development, technical advisory and practice support. Key responsibilities include: Lead and support business development for climate change and environment opportunities, including proposals, positioning and client engagement, Design and shape integrated climate resilience solutions across sectors such as su</t>
+          <t>The Associate Director, Climate Change and Environment supports the growth of Tetra Tech International Development’s climate portfolio across Australia and the Indo‑Pacific through business development, technical advisory and practice support. Key responsibilities include: Lead and support business development for climate change and environment opportunities, including proposals, positioning and client engagement, Design and shape integrated climate resilience solutions across sectors such as sustainable infrastructure, agriculture, livelihoods, disaster preparedness and natural resource management, Provide senior technical leadership across investment design, implementation, technical assistance and evaluation, Build and maintain strong relationships with DFAT, regional partners, donors and industry stakeholders, Contribute to the delivery and oversight of complex programs, ensuring quality, compliance and commercial rigour, Support practice growth through people leadership, collaboration, and thought leadership activities</t>
         </is>
       </c>
       <c r="P64" s="6" t="inlineStr">
@@ -6195,7 +6216,7 @@
       </c>
       <c r="Q64" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions climate change, climate resilience, disaster risk reduction, and climate‑inclusive development, which are all relevant to the climate risk profile</t>
+          <t>The job description mentions climate change, climate resilience, disaster risk reduction, and climate‑inclusive development, which are all relevant to the climate risk profile</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
@@ -6282,17 +6303,17 @@
       </c>
       <c r="O65" s="6" t="inlineStr">
         <is>
-          <t>Lead a team of 5-6 Senior consultants, analysts for engagement execution and delivery. Showcase exceptional project management abilities and foster a collaborative environment and accountability among team members on engagements. Demonstrate deep technical expertise and industry knowledge, particularly in financial products with a focus on lending solutions. Design, assessment, and benchmarking of financial risk management policies, frameworks, methodologies covering a range of risk domains such</t>
+          <t>Lead a team of 5-6 Senior consultants, analysts for engagement execution and delivery. Showcase exceptional project management abilities and foster a collaborative environment and accountability among team members on engagements. Demonstrate deep technical expertise and industry knowledge, particularly in financial products with a focus on lending solutions. Design, assessment, and benchmarking of financial risk management policies, frameworks, methodologies covering a range of risk domains such as credit risk, market risk, operational risk, liquidity risk, climate risk, and integrated risk topics viz., capital adequacy and stress testing measurement methodologies in financial institutions (FI). Stay abreast of market trends and challenges in the financial services sector to understand client needs and industry dynamics. Understand EY and its service lines and actively assess what the firm can deliver to serve clients. Monitor project progress, manage risks, and effectively communicate status, issues, and priorities to key stakeholders to ensure successful outcomes. Review, analyze, and validate the work completed by junior team members to ensure accuracy and quality. Adapt to projects involving model audits, validation, and development, demonstrating flexibility and domain knowledge</t>
         </is>
       </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
-          <t>Advanced technical skills, with proficiency in Python, SAS, SQL, R, and Excel. Excellent Oral and written communication and presentation skills. Strong documentation skills, with the ability to quickly grasp complex concepts and present them clearly in documents or presentations. Strong multi-taskin</t>
+          <t>Advanced technical skills, with proficiency in Python, SAS, SQL, R, and Excel. Excellent Oral and written communication and presentation skills. Strong documentation skills, with the ability to quickly grasp complex concepts and present them clearly in documents or presentations. Strong multi-tasking skills with demonstrated ability to manage expectations and deliver high quality results under tight deadlines and minimal supervision. In-depth knowledge of Credit risk model development, validation, audit and/or implementation of the banking book portfolio. Solid understanding of Risk analytics methodologies.</t>
         </is>
       </c>
       <c r="Q65" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions 'climate risk' as one of the risk domains, and also mentions 'experience in climatic risk space preferably in the areas of stress testing /scenario designing', indicating that the role involves working with climate-related risks.</t>
+          <t>The job description mentions 'climate risk' as one of the risk domains, and also mentions 'experience in climatic risk space preferably in the areas of stress testing /scenario designing', indicating that the role involves working with climate-related risks.</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr">
@@ -6379,17 +6400,17 @@
       </c>
       <c r="O66" s="6" t="inlineStr">
         <is>
-          <t>The Team Leader, Sustainable Finance Operations at Intercontinental Exchange (ICE) plays a critical leadership role in managing and developing a high-performing team of ESG data professionals based in Hyderabad. This position ensures the delivery of accurate, comprehensive, and timely Environmental, Social, and Governance (ESG) data to support ICE Climate products and global ESG reporting standards. * Lead and develop a team of 15+ Associates and Analysts, overseeing resource planning, performan</t>
+          <t>The Team Leader, Sustainable Finance Operations at Intercontinental Exchange (ICE) plays a critical leadership role in managing and developing a high-performing team of ESG data professionals based in Hyderabad. This position ensures the delivery of accurate, comprehensive, and timely Environmental, Social, and Governance (ESG) data to support ICE Climate products and global ESG reporting standards. * Lead and develop a team of 15+ Associates and Analysts, overseeing resource planning, performance management, and professional growth. * Ensure the accuracy, completeness, and timely delivery of ESG data by analyzing and validating information from diverse sources. * Monitor ESG market trends and apply insights to enhance data quality and client deliverables. * Drive workflow efficiencies and implement process improvements to optimize accuracy and productivity. * Collaborate with global teams to standardize processes and maintain consistency in data quality. * Provide expert support to ESG product users and resolve inquiries promptly. * Identify and address data quality issues, recommending corrective actions as needed. * Contribute to strategic and ad hoc projects focused on operational excellence and data enhancement. * Prepare and present progress reports, including data visualizations, for leadership and stakeholders. * Foster a culture aligned with ICE values, with a strong emphasis on driving a high-performance culture. * Continuously identify and implement improvements to team and operational efficiency, supporting ongoing operational excellence. * Proactively seek and implement opportunities to leverage AI and automation to maximize efficiency and achieve more with less. * Design and deploy smart systems and automated workflows to streamline operations and enhance data quality.</t>
         </is>
       </c>
       <c r="P66" s="6" t="inlineStr">
         <is>
-          <t>Proficiency in SQL, Macros, and Advanced Excel; experience with Power BI, Tableau, or similar tools preferred. Strong analytical, problem-solving, and communication skills. Ability to align team objectives with organisational goals and deliver high-quality results. Reliability, flexibility, and atte</t>
+          <t>Proficiency in SQL, Macros, and Advanced Excel; experience with Power BI, Tableau, or similar tools preferred. Strong analytical, problem-solving, and communication skills. Ability to align team objectives with organisational goals and deliver high-quality results. Reliability, flexibility, and attention to detail. Demonstrated experience in leveraging AI and automation to improve operational efficiency. Proven track record in building and deploying smart systems and automated workflows within data operations.</t>
         </is>
       </c>
       <c r="Q66" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions ESG data, ESG reporting standards, and ESG product users, which are all relevant to sustainable finance. The role also involves working with ESG content, regulatory frameworks, and capital markets, which are key aspects of sustainable finance.</t>
+          <t>The job description mentions ESG data, ESG reporting standards, and ESG product users, which are all relevant to sustainable finance. The role also involves working with ESG content, regulatory frameworks, and capital markets, which are key aspects of sustainable finance.</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr">
@@ -6468,17 +6489,17 @@
       </c>
       <c r="O67" s="6" t="inlineStr">
         <is>
-          <t>As a member of the Global Center of excellence the Presales technical lead will help customers to make technology decisions, implement best practices for asset management and overall facilitate transforming buildings into smart connected entities. Develop and implement pre-sales strategies that align with the organization’s business goals &amp; targets. Review opportunity inputs, requirements and specifications; should be able to capture the Digital Solution scope and understand the complete require</t>
+          <t>As a member of the Global Center of excellence the Presales technical lead will help customers to make technology decisions, implement best practices for asset management and overall facilitate transforming buildings into smart connected entities. Develop and implement pre-sales strategies that align with the organization’s business goals &amp; targets. Review opportunity inputs, requirements and specifications; should be able to capture the Digital Solution scope and understand the complete requirements of the customer. Drive RFP/RFI responses, preparing technical solution writeups, compliance matrices, BoQs, Hardware sizing calculations, and architecture diagrams tailored to customer use cases across global markets. Collaborate with cross-functional teams, including sales, marketing, product management, and engineering, to ensure alignment and effective Solution development. Translate customer pain points and site realities into solution architectures, integrating PLC/SCADA systems and BMS Platforms (Metasys, Niagara, DDC, JACE or similar) with analytics platform, digital twins, and enterprise FM platforms to demonstrate clear business outcomes. Design and present tailored solutions that demonstrate the value and benefits of the digital products and services. Conduct requirement workshops, technical discovery sessions, and PoCs, ensuring alignment of customer expectations with solution capabilities, integration pathways, data models, KPIs, and future‑state architecture. Lead and mentor design teams during solution shaping; guiding them on OT and IOT protocols, data ingestion, middleware integration, and standard deployment patterns used during customer demo and Proof of Concepts. Preparation and participation for Gate 0 calls / review meetings with JC Branch sales team for technical queries, scope clarifications, compliance and record minutes of meeting. Understand inter-dependence and lead cross-functional teams towards technical solutions for multi-tiered systems. Clarify, prioritize and drive solution commitments as well as establish and maintain clear chains of accountability. Adherence to proposal &amp; estimation process and guideline to select proper Digital Solution Applications/offering to come up with the technical solution. Preparing technical proposals, cost estimates ensuring it meet the customer requirement and provide competitive advantage to JCI. Develop solutions specific dashboards, reporting frameworks, and data modeling strategies as part of presales demonstrations, highlighting portfolio‑level insights and operational benefits. Provide technical leadership to coordinate, prioritize and deliver proposal, commercials in pre-sales process. Articulate goals, desired outcomes, risks/issues and mitigation plan clearly in pre-sales process. Clearly qualify out of the box solutions and possible customizations needed. Provide feedback to product management and development teams regarding customer needs and market demands</t>
         </is>
       </c>
       <c r="P67" s="6" t="inlineStr">
         <is>
-          <t>Strong technical aptitude and ability to quickly learn new products and technologies. Excellent communication and interpersonal skills. Proficiency in using Integrated software and digital communication tools. Ability to present complex technical information in a clear and concise manner. Strong pro</t>
+          <t>Strong technical aptitude and ability to quickly learn new products and technologies. Excellent communication and interpersonal skills. Proficiency in using Integrated software and digital communication tools. Ability to present complex technical information in a clear and concise manner. Strong problem-solving skills and customer-oriented mindset. Ability to work independently and as part of a team.</t>
         </is>
       </c>
       <c r="Q67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[clean_energy_adjacent] The job description mentions 'sustainable buildings', 'climate-related innovation', 'net zero carbon emissions', and 'energy management', which are related to environmental sustainability and clean energy. Although the primary focus is on building technologies, the company's </t>
+          <t>The job description mentions 'sustainable buildings', 'climate-related innovation', 'net zero carbon emissions', and 'energy management', which are related to environmental sustainability and clean energy. Although the primary focus is on building technologies, the company's commitment to sustainability and reducing carbon emissions aligns with the clean energy adjacent profile.</t>
         </is>
       </c>
       <c r="R67" s="2" t="inlineStr"/>
@@ -6557,7 +6578,7 @@
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Develop and manage project finance and cash flow models for renewable energy projects—such as Solar PV, Wind, and BESS—to assess profitability, equity returns, and key risks. Maintain project assumptions documentation, return trackers, and tariff models. Engage cross-functionally with Energy Origination/Markets, Business Development, Project Development, and Operations teams to develop comprehensive business insights and evaluate greenfield renewable energy projects across various technologies. </t>
+          <t>Develop and manage project finance and cash flow models for renewable energy projects—such as Solar PV, Wind, and BESS—to assess profitability, equity returns, and key risks. Maintain project assumptions documentation, return trackers, and tariff models. Engage cross-functionally with Energy Origination/Markets, Business Development, Project Development, and Operations teams to develop comprehensive business insights and evaluate greenfield renewable energy projects across various technologies. Assist in the assessment of Power Purchase Agreement (PPA) structures within utility-scale tender processes and the Commercial and Industrial (C&amp;I) sector. Monitor and interpret trends in the Indian renewable energy market, including regulatory developments and policy frameworks, and assess their implications for project economics. Support fundraising activities by maintaining internal and external data rooms and coordinating responses to investor due diligence requests. Assist with internal and external reporting obligations, including preparing investor presentations, CIMS documentation, and Investment Committee (IC) materials. Exhibit strong interpersonal skills and a collaborative mindset, while also demonstrating the ability to work independently when necessary.</t>
         </is>
       </c>
       <c r="P68" s="6" t="inlineStr">
@@ -6567,7 +6588,7 @@
       </c>
       <c r="Q68" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions renewable energy, solar, wind, and BESS, which are all related to clean energy. The company's focus on transitioning to a carbon-free and sustainable economy also supports this classification.</t>
+          <t>The job description mentions renewable energy, solar, wind, and BESS, which are all related to clean energy. The company's focus on transitioning to a carbon-free and sustainable economy also supports this classification.</t>
         </is>
       </c>
       <c r="R68" s="2" t="inlineStr">
@@ -6646,17 +6667,17 @@
       </c>
       <c r="O69" s="6" t="inlineStr">
         <is>
-          <t>Within the Enterprise Risk Management &amp; Risk Oversight Group in GRC, Enterprise Risk Management &amp; Strategic Initiatives is the independent risk management team that plays a pivotal role in identification, assessment and mitigation of risks affecting the organization. The team’s core responsibility is to design, implement and oversee risk measurement &amp; management frameworks at American Express. Manager – Enterprise Risk Management &amp; Strategic Initiatives will be responsible for providing independ</t>
+          <t>Within the Enterprise Risk Management &amp; Risk Oversight Group in GRC, Enterprise Risk Management &amp; Strategic Initiatives is the independent risk management team that plays a pivotal role in identification, assessment and mitigation of risks affecting the organization. The team’s core responsibility is to design, implement and oversee risk measurement &amp; management frameworks at American Express. Manager – Enterprise Risk Management &amp; Strategic Initiatives will be responsible for providing independent oversight and effective challenge on risk-related matters across the organization. This individual will work closely with senior management and business units to ensure effective identification, assessment and mitigation of risks across the enterprise. The responsibilities include, but not limited to: Assisting in the development of risk management frameworks, policies, and procedures to strengthen enterprise-wide risk practices. Conducting risk assessments on Mergers &amp; Acquisitions (M&amp;A), including due diligence review, integration risk management, and ongoing monitoring. Supporting the development of risk governance framework for Joint Ventures and ensuring controls for heightened risk areas. Performing Climate Risk-related assessments, including end to end measurement of physical and transition risk, scenario analysis, and supporting disclosure requirements. Conducting peer benchmarking and research on industry-wide best practices to recommend enhancements for effective risk management and risk oversight. Supporting a variety of strategic projects within the Enterprise Risk Management team to enhance risk identification and measurement capabilities.</t>
         </is>
       </c>
       <c r="P69" s="6" t="inlineStr">
         <is>
-          <t>Strong understanding of risk management principles, methodologies, frameworks, and regulatory requirements. Strong verbal and written communication skills. Analytical and problem-solving skills, with an ability to analyze data, identify trends, and evaluate risk scenarios effectively. Advanced profi</t>
+          <t>Strong understanding of risk management principles, methodologies, frameworks, and regulatory requirements. Strong verbal and written communication skills. Analytical and problem-solving skills, with an ability to analyze data, identify trends, and evaluate risk scenarios effectively. Advanced proficiency in Excel and PowerPoint. Experience with Python/SAS/R is a plus.</t>
         </is>
       </c>
       <c r="Q69" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions performing Climate Risk-related assessments, including end to end measurement of physical and transition risk, scenario analysis, and supporting disclosure requirements, which directly relates to climate risk management.</t>
+          <t>The job description mentions performing Climate Risk-related assessments, including end to end measurement of physical and transition risk, scenario analysis, and supporting disclosure requirements, which directly relates to climate risk management.</t>
         </is>
       </c>
       <c r="R69" s="2" t="inlineStr">
@@ -6744,12 +6765,12 @@
       </c>
       <c r="P70" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Technical skills: environmental and social impact assessment, environmental and social due diligence, environmental and social management systems. Soft skills: client and commercial capability, proposal development, client negotiation, project scoping, strong track record of repeat business, client </t>
+          <t>Technical skills: environmental and social impact assessment, environmental and social due diligence, environmental and social management systems. Soft skills: client and commercial capability, proposal development, client negotiation, project scoping, strong track record of repeat business, client advocacy, and industry influence.</t>
         </is>
       </c>
       <c r="Q70" s="6" t="inlineStr">
         <is>
-          <t>[general_esg] The job description mentions environmental and social performance management, impact assessment, due diligence, and management systems, which are all relevant to ESG strategy and corporate sustainability.</t>
+          <t>The job description mentions environmental and social performance management, impact assessment, due diligence, and management systems, which are all relevant to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
       <c r="R70" s="2" t="inlineStr">
@@ -6831,6 +6852,652 @@
         </is>
       </c>
       <c r="O71" s="6" t="inlineStr">
+        <is>
+          <t>* promouvoir et développer les offres ESG (Environnement, Social, Gouvernance)
+* s’assurer de la conformité du Métier aux réglementations en vigueur relatives à la finance durable en Europe
+* Vous serez le spécialiste local de la méthodologie extra-financière (relative aux critères ESG (Environnementaux, Sociaux et de Gouvernance)) couvrant l’ensemble des produits financiers de l’offre de Wealth Management à Luxembourg.
+* Vous contribuerez aux analyses à la structuration des données relatives aux préférences ESG des clients, aux caractéristiques ESG des portefeuilles des clients, afin de communiquer ces analyses aux autres collaborateurs de l’offre, aux conseillers clientèle et au management.
+* Vous contribuerez à la réalisation de reportings commerciaux et réglementaires relatifs à des offres de gestion sous mandat ESG, et interagirez dans ce cadre avec les départements juridique, de conformité, de spécialistes ESG, et de gérants.
+* Vous contribuerez aux groupes de travail de BGL BNP Paribas relatifs à la mise en conformité de la Banque aux réglementations SFDR et MIFID ESG, et aux différents projets liés (développement d’outils, de procédures internes, etc.).
+* Vous contribuerez à d’autres tâches d’analyse de données liées à l’activité globale de l’offre de produits et services, ou à certains types de produits en particulier (private equity, produits structurés, etc).</t>
+        </is>
+      </c>
+      <c r="P71" s="6" t="inlineStr">
+        <is>
+          <t>* Capacité à collaborer / travail d’équipe
+* Rigueur
+* Etre orienté(e) résultats
+* Créativité &amp; Innovation / Capacité à résoudre des problèmes
+* Proactivité
+* Capacité d’analyse
+* Capacité à gérer un projet
+* Capacité à définir des indicateurs de performance pertinents
+* Analyse de données (PowerBI, VBA ou autre)
+* Capacité à communiquer - à l’oral et par écrit (français et anglais)</t>
+        </is>
+      </c>
+      <c r="Q71" s="6" t="inlineStr">
+        <is>
+          <t>The job description mentions ESG (Environnement, Social, Gouvernance), finance durable, SFDR, and MIFID ESG, which are all related to sustainable finance. The job also involves promoting and developing ESG offers, ensuring compliance with regulations, and contributing to the development of sustainable finance within a private bank.</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/company/bnp-paribas</t>
+        </is>
+      </c>
+      <c r="S71" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4387894281</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>sustainable_finance</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>V.I.E. Sustainable Solutions</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Societe Generale Corporate and Investment Banking - SGCIB</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Bank/FI | BFSI</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm, Stockholm County, Sweden</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>not applicable</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>Keyword (6)</t>
+        </is>
+      </c>
+      <c r="O72" s="6" t="inlineStr">
+        <is>
+          <t>Development of the offering of sustainable investment, hedging, and financing solutions for Global Markets Activities. Review and maintain the list of proprietary and external indices embedding ESG criteria; analyze their methodology and create marketing documentation. Monitor and contribute to develop the overall sustainable structured solutions offering. Contribute to assisting the rest of the team in specific quantitative analysis requests. Participate in sustainable finance market studies, monitor the development of the sustainability sector, and monitor regulatory or political developments related to ESG issues. Collaborate with the ESG Advisory team and participate in Societe Generale's cross-functional projects in the field of sustainable finance. Prepare and participate in trainings and committees bringing together the ESG ambassadors within the sales, financial engineering and trading teams of the Global Markets Division. Prepare the newsletters and share with the community any relevant communication related to ESG</t>
+        </is>
+      </c>
+      <c r="P72" s="6" t="inlineStr">
+        <is>
+          <t>Good communication and presentation skills. Management of complex projects. Proficient command of MS Office, notably Excel. Coding in Python is a plus</t>
+        </is>
+      </c>
+      <c r="Q72" s="6" t="inlineStr">
+        <is>
+          <t>The job description mentions sustainable investment, hedging, and financing solutions, ESG criteria, sustainable finance market studies, and ESG advisory team, which are all related to sustainable finance</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/company/societegenerale-corporate-and-investment-banking</t>
+        </is>
+      </c>
+      <c r="S72" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4388245861</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>carbon_markets</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder (Finance &amp; Investment)</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Asthalaxmi Innovations</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Bank/FI | BFSI</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Guwahati, Assam, India</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>5-15 Yrs</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>Keyword (6)</t>
+        </is>
+      </c>
+      <c r="O73" s="6" t="inlineStr">
+        <is>
+          <t>This is a full-time, hybrid (onsite/remote) leadership role in India. You will be the architect of our capital strategy, ensuring that our vision for regenerative agriculture is backed by robust investment. Key Responsibilities: Venture Fundraising: Lead the charge in securing investment from Angel Investors, Venture Capital (VC) firms, and Impact Funds. Project Finance: Secure dedicated funding for large-scale Bamboo agroforestry projects across Northeast India and Bhutan (Green Bonds, Carbon Credit pre-financing). Strategic Leadership: Work alongside the founding team to set objectives, oversee resource allocation, and lead cross-functional teams. Partnership Building: Cultivate high-level relationships with stakeholders, government bodies, and international climate finance institutions. Advocacy: Act as a primary voice for AIPL’s mission, driving both social impact and economic returns.</t>
+        </is>
+      </c>
+      <c r="P73" s="6" t="inlineStr">
+        <is>
+          <t>Fundraising Expertise, Financial &amp; Analytical Rigour, Sales &amp; Marketing Prowess, Climate Intelligence, Leadership, Investment &amp; Finance, Sector Expertise, Regional Insight</t>
+        </is>
+      </c>
+      <c r="Q73" s="6" t="inlineStr">
+        <is>
+          <t>The job description mentions carbon credits, carbon markets, and sustainable development, which are key aspects of the carbon markets profile. The company's focus on generating carbon credits and working on agroforestry projects also aligns with this profile.</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/asthalaxmi</t>
+        </is>
+      </c>
+      <c r="S73" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4387915780</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>carbon_markets</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>VP / Head of Marketing</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Varaha</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Corporate | Environmental</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Gurgaon, Haryana, India</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>internship</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>Keyword (6)</t>
+        </is>
+      </c>
+      <c r="O74" s="6" t="inlineStr">
+        <is>
+          <t>Define and lead Varaha's global brand narrative, position Varaha as a pioneer in climate tech and high integrity carbon markets, build and execute a global PR strategy, develop and execute highly targeted Account Based Marketing (ABM) strategies, oversee the creation of a crisp, scientifically disciplined narrative architecture, develop a strategic conference plan, build and mentor a high performance marketing team, manage agencies, consultants, and creative partners.</t>
+        </is>
+      </c>
+      <c r="P74" s="6" t="inlineStr">
+        <is>
+          <t>Account Based Marketing, field events, PR and communications, partner enablement, storytelling, brand narrative, climate tech, carbon markets, marketing strategy, team leadership, agency management</t>
+        </is>
+      </c>
+      <c r="Q74" s="6" t="inlineStr">
+        <is>
+          <t>The job description mentions carbon removal, carbon markets, climate tech, and high integrity carbon markets, indicating a strong focus on carbon markets and climate-related topics.</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/varaha-carbontech</t>
+        </is>
+      </c>
+      <c r="S74" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4388289654</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>climate_risk</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Atmospheric Scientist/Statistician I</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Verisk</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Corporate | Other</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>mid-senior level</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>Keyword (6)</t>
+        </is>
+      </c>
+      <c r="O75" s="6" t="inlineStr">
+        <is>
+          <t>Improve the accuracy of representing atmospheric perils, contribute to model development, validation, and productization for global clients, support model development using observational and reanalysis products, GCMs, and high-resolution simulations</t>
+        </is>
+      </c>
+      <c r="P75" s="6" t="inlineStr">
+        <is>
+          <t>Spatial statistics, extreme value analysis, atmospheric dynamics, dynamic downscaling methods, Python</t>
+        </is>
+      </c>
+      <c r="Q75" s="6" t="inlineStr">
+        <is>
+          <t>The job description mentions developing catastrophe models for the insurance and reinsurance industries, simulating extreme weather events consistent with a changing climate, and advancing the development of atmospheric peril models, which are all related to climate risk</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/verisk-analytics</t>
+        </is>
+      </c>
+      <c r="S75" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4388338436</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>3+ weeks ago</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>eu_taxonomy_sfdr</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>naukri</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>ESG Consultant (Carbon)</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Apex Group</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Asset Manager | BFSI</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>mid-senior level</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>5-15 Yrs</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>Keyword (6)</t>
+        </is>
+      </c>
+      <c r="O76" s="6" t="inlineStr">
+        <is>
+          <t>Conduct comprehensive analyses, including Carbon Emissions Tracking, Carbon Footprint Assessments, Environmental Impact Analyses, Life Cycle Assessments (LCAs), Emissions Reduction Strategies, Climate Policy Development, Advocacy, Climate Modeling, Scenario Planning, and target setting aligned with Science-Based Targets (SBTi). Develop and execute data-driven strategies to assist investment managers and portfolio companies in reducing carbon emissions and setting targets. Lead initiatives to improve the sustainability performance of the Apex Group and promote responsible business practices across the organization. Contribute to the enhancement of existing ESG products and the development of innovative new offerings. Stay informed on global ESG standards and frameworks, ensuring the firm s services meet current and emerging market expectations.</t>
+        </is>
+      </c>
+      <c r="P76" s="6" t="inlineStr">
+        <is>
+          <t>Hands-on experience in carbon footprint analysis, GHG assessment, and climate risk advisory, with strong technical expertise in climate change, SBTi, LCA, ISO 14044/14064, decarbonization strategies, and climate risk modeling. A deep understanding of sustainability challenges across various industry sectors. Proficiency in ESG frameworks, such as SASB, GRI, TCFD, UN PRI, CSRD/NFRD, and SFDR. Strong skills in quantitative and qualitative data collection, analysis, and reporting. Excellent communication and interpersonal skills, with the ability to influence both internal and external stakeholders effectively.</t>
+        </is>
+      </c>
+      <c r="Q76" s="6" t="inlineStr">
+        <is>
+          <t>The job description mentions climate risk, carbon emissions tracking, carbon footprint assessments, GHG assessment, climate risk advisory, and decarbonization strategies, which are all relevant to climate risk. Additionally, the job requires experience in climate change, environmental issues, and sustainability, and proficiency in ESG frameworks such as TCFD, which further supports the classification as climate_risk.</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/adani-electricity</t>
+        </is>
+      </c>
+      <c r="S76" s="3" t="inlineStr">
+        <is>
+          <t>https://www.naukri.com/job-listings-esg-consultant-carbon-apex-fund-services-llp-pune-5-to-15-years-100425504128</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>climate_risk</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Senior Specialist Data Management</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Telstra</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Corporate | Other</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Keyword (5)</t>
+        </is>
+      </c>
+      <c r="O77" s="6" t="inlineStr">
+        <is>
+          <t>Lead and deliver strategic mining advisory projects, provide senior technical expertise, participate in multi-disciplinary project teams, engage senior and executive-level stakeholders, drive business development and industry presence, support team culture, collaboration and wellbeing. Manage and execute environmental and social performance input into feasibility studies, due diligence assignments, ITRs/ITERs, and operational improvement programs.</t>
+        </is>
+      </c>
+      <c r="P77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technical skills: environmental and social impact assessment, environmental and social due diligence, environmental and social management systems. Soft skills: client and commercial capability, proposal development, client negotiation, project scoping, strong track record of repeat business, client </t>
+        </is>
+      </c>
+      <c r="Q77" s="6" t="inlineStr">
+        <is>
+          <t>[general_esg] The job description mentions environmental and social performance management, impact assessment, due diligence, and management systems, which are all relevant to ESG strategy and corporate sustainability.</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="3" t="inlineStr">
+        <is>
+          <t>https://au.indeed.com/viewjob?jk=d417c2af5d7b5f69</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>climate_risk</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>2027 Graduate Hydrogeologist</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Consulting | Engineering</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Perth WA</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Keyword (5)</t>
+        </is>
+      </c>
+      <c r="O78" s="6" t="inlineStr">
         <is>
           <t>* promouvoir et développer les offres ESG (Environnement, Social, Gouvernance)
 * s’assurer de la conformité du Métier aux réglementations en vigueur relatives à la finance durable en Europe
@@ -6838,7 +7505,7 @@
 * Vous contribuerez aux analyses à la structuration des données relatives au</t>
         </is>
       </c>
-      <c r="P71" s="6" t="inlineStr">
+      <c r="P78" s="6" t="inlineStr">
         <is>
           <t>* Capacité à collaborer / travail d’équipe
 * Rigueur
@@ -6851,651 +7518,9 @@
 * Analyse de données (PowerBI,</t>
         </is>
       </c>
-      <c r="Q71" s="6" t="inlineStr">
-        <is>
-          <t>[sustainable_finance] The job description mentions ESG (Environnement, Social, Gouvernance), finance durable, SFDR, and MIFID ESG, which are all related to sustainable finance. The job also involves promoting and developing ESG offers, ensuring compliance with regulations, and contributing to the de</t>
-        </is>
-      </c>
-      <c r="R71" s="2" t="inlineStr">
-        <is>
-          <t>https://fr.linkedin.com/company/bnp-paribas</t>
-        </is>
-      </c>
-      <c r="S71" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4387894281</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>sustainable_finance</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>linkedin</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>V.I.E. Sustainable Solutions</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>Societe Generale Corporate and Investment Banking - SGCIB</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Bank/FI | BFSI</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>Stockholm, Stockholm County, Sweden</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>not applicable</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr"/>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>Keyword (6)</t>
-        </is>
-      </c>
-      <c r="O72" s="6" t="inlineStr">
-        <is>
-          <t>Development of the offering of sustainable investment, hedging, and financing solutions for Global Markets Activities. Review and maintain the list of proprietary and external indices embedding ESG criteria; analyze their methodology and create marketing documentation. Monitor and contribute to develop the overall sustainable structured solutions offering. Contribute to assisting the rest of the team in specific quantitative analysis requests. Participate in sustainable finance market studies, m</t>
-        </is>
-      </c>
-      <c r="P72" s="6" t="inlineStr">
-        <is>
-          <t>Good communication and presentation skills. Management of complex projects. Proficient command of MS Office, notably Excel. Coding in Python is a plus</t>
-        </is>
-      </c>
-      <c r="Q72" s="6" t="inlineStr">
-        <is>
-          <t>[sustainable_finance] The job description mentions sustainable investment, hedging, and financing solutions, ESG criteria, sustainable finance market studies, and ESG advisory team, which are all related to sustainable finance</t>
-        </is>
-      </c>
-      <c r="R72" s="2" t="inlineStr">
-        <is>
-          <t>https://fr.linkedin.com/company/societegenerale-corporate-and-investment-banking</t>
-        </is>
-      </c>
-      <c r="S72" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4388245861</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>carbon_markets</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>linkedin</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>Co-Founder (Finance &amp; Investment)</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>Asthalaxmi Innovations</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Bank/FI | BFSI</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>Guwahati, Assam, India</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>executive</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>5-15 Yrs</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>Keyword (6)</t>
-        </is>
-      </c>
-      <c r="O73" s="6" t="inlineStr">
-        <is>
-          <t>This is a full-time, hybrid (onsite/remote) leadership role in India. You will be the architect of our capital strategy, ensuring that our vision for regenerative agriculture is backed by robust investment. Key Responsibilities: Venture Fundraising: Lead the charge in securing investment from Angel Investors, Venture Capital (VC) firms, and Impact Funds. Project Finance: Secure dedicated funding for large-scale Bamboo agroforestry projects across Northeast India and Bhutan (Green Bonds, Carbon C</t>
-        </is>
-      </c>
-      <c r="P73" s="6" t="inlineStr">
-        <is>
-          <t>Fundraising Expertise, Financial &amp; Analytical Rigour, Sales &amp; Marketing Prowess, Climate Intelligence, Leadership, Investment &amp; Finance, Sector Expertise, Regional Insight</t>
-        </is>
-      </c>
-      <c r="Q73" s="6" t="inlineStr">
-        <is>
-          <t>[carbon_markets] The job description mentions carbon credits, carbon markets, and sustainable development, which are key aspects of the carbon markets profile. The company's focus on generating carbon credits and working on agroforestry projects also aligns with this profile.</t>
-        </is>
-      </c>
-      <c r="R73" s="2" t="inlineStr">
-        <is>
-          <t>https://in.linkedin.com/company/asthalaxmi</t>
-        </is>
-      </c>
-      <c r="S73" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4387915780</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>carbon_markets</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>linkedin</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>VP / Head of Marketing</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>Varaha</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>Corporate | Environmental</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>Gurgaon, Haryana, India</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>internship</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>executive</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr">
-        <is>
-          <t>Keyword (6)</t>
-        </is>
-      </c>
-      <c r="O74" s="6" t="inlineStr">
-        <is>
-          <t>Define and lead Varaha's global brand narrative, position Varaha as a pioneer in climate tech and high integrity carbon markets, build and execute a global PR strategy, develop and execute highly targeted Account Based Marketing (ABM) strategies, oversee the creation of a crisp, scientifically disciplined narrative architecture, develop a strategic conference plan, build and mentor a high performance marketing team, manage agencies, consultants, and creative partners.</t>
-        </is>
-      </c>
-      <c r="P74" s="6" t="inlineStr">
-        <is>
-          <t>Account Based Marketing, field events, PR and communications, partner enablement, storytelling, brand narrative, climate tech, carbon markets, marketing strategy, team leadership, agency management</t>
-        </is>
-      </c>
-      <c r="Q74" s="6" t="inlineStr">
-        <is>
-          <t>[carbon_markets] The job description mentions carbon removal, carbon markets, climate tech, and high integrity carbon markets, indicating a strong focus on carbon markets and climate-related topics.</t>
-        </is>
-      </c>
-      <c r="R74" s="2" t="inlineStr">
-        <is>
-          <t>https://in.linkedin.com/company/varaha-carbontech</t>
-        </is>
-      </c>
-      <c r="S74" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4388289654</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>climate_risk</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>linkedin</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>Atmospheric Scientist/Statistician I</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>Verisk</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>Corporate | Other</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>Hyderabad, Telangana, India</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>mid-senior level</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr"/>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr">
-        <is>
-          <t>Keyword (6)</t>
-        </is>
-      </c>
-      <c r="O75" s="6" t="inlineStr">
-        <is>
-          <t>Improve the accuracy of representing atmospheric perils, contribute to model development, validation, and productization for global clients, support model development using observational and reanalysis products, GCMs, and high-resolution simulations</t>
-        </is>
-      </c>
-      <c r="P75" s="6" t="inlineStr">
-        <is>
-          <t>Spatial statistics, extreme value analysis, atmospheric dynamics, dynamic downscaling methods, Python</t>
-        </is>
-      </c>
-      <c r="Q75" s="6" t="inlineStr">
-        <is>
-          <t>[climate_risk] The job description mentions developing catastrophe models for the insurance and reinsurance industries, simulating extreme weather events consistent with a changing climate, and advancing the development of atmospheric peril models, which are all related to climate risk</t>
-        </is>
-      </c>
-      <c r="R75" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/verisk-analytics</t>
-        </is>
-      </c>
-      <c r="S75" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4388338436</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>3+ weeks ago</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>eu_taxonomy_sfdr</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>naukri</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>ESG Consultant (Carbon)</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>Apex Group</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>Asset Manager | BFSI</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>mid-senior level</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>5-15 Yrs</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr">
-        <is>
-          <t>Keyword (6)</t>
-        </is>
-      </c>
-      <c r="O76" s="6" t="inlineStr">
-        <is>
-          <t>Conduct comprehensive analyses, including Carbon Emissions Tracking, Carbon Footprint Assessments, Environmental Impact Analyses, Life Cycle Assessments (LCAs), Emissions Reduction Strategies, Climate Policy Development, Advocacy, Climate Modeling, Scenario Planning, and target setting aligned with Science-Based Targets (SBTi). Develop and execute data-driven strategies to assist investment managers and portfolio companies in reducing carbon emissions and setting targets. Lead initiatives to imp</t>
-        </is>
-      </c>
-      <c r="P76" s="6" t="inlineStr">
-        <is>
-          <t>Hands-on experience in carbon footprint analysis, GHG assessment, and climate risk advisory, with strong technical expertise in climate change, SBTi, LCA, ISO 14044/14064, decarbonization strategies, and climate risk modeling. A deep understanding of sustainability challenges across various industry</t>
-        </is>
-      </c>
-      <c r="Q76" s="6" t="inlineStr">
-        <is>
-          <t>[climate_risk] The job description mentions climate risk, carbon emissions tracking, carbon footprint assessments, GHG assessment, climate risk advisory, and decarbonization strategies, which are all relevant to climate risk. Additionally, the job requires experience in climate change, environmental</t>
-        </is>
-      </c>
-      <c r="R76" s="2" t="inlineStr">
-        <is>
-          <t>https://in.linkedin.com/company/adani-electricity</t>
-        </is>
-      </c>
-      <c r="S76" s="3" t="inlineStr">
-        <is>
-          <t>https://www.naukri.com/job-listings-esg-consultant-carbon-apex-fund-services-llp-pune-5-to-15-years-100425504128</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr"/>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>climate_risk</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>indeed</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>Senior Specialist Data Management</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>Telstra</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>Corporate | Other</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr"/>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>Keyword (5)</t>
-        </is>
-      </c>
-      <c r="O77" s="6" t="inlineStr">
-        <is>
-          <t>Lead and deliver strategic mining advisory projects, provide senior technical expertise, participate in multi-disciplinary project teams, engage senior and executive-level stakeholders, drive business development and industry presence, support team culture, collaboration and wellbeing. Manage and execute environmental and social performance input into feasibility studies, due diligence assignments, ITRs/ITERs, and operational improvement programs.</t>
-        </is>
-      </c>
-      <c r="P77" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Technical skills: environmental and social impact assessment, environmental and social due diligence, environmental and social management systems. Soft skills: client and commercial capability, proposal development, client negotiation, project scoping, strong track record of repeat business, client </t>
-        </is>
-      </c>
-      <c r="Q77" s="6" t="inlineStr">
-        <is>
-          <t>[general_esg] The job description mentions environmental and social performance management, impact assessment, due diligence, and management systems, which are all relevant to ESG strategy and corporate sustainability.</t>
-        </is>
-      </c>
-      <c r="R77" s="2" t="inlineStr"/>
-      <c r="S77" s="3" t="inlineStr">
-        <is>
-          <t>https://au.indeed.com/viewjob?jk=d417c2af5d7b5f69</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr"/>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>climate_risk</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>indeed</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>2027 Graduate Hydrogeologist</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>AECOM</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>Consulting | Engineering</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>Perth WA</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr">
-        <is>
-          <t>Keyword (5)</t>
-        </is>
-      </c>
-      <c r="O78" s="6" t="inlineStr">
-        <is>
-          <t>* promouvoir et développer les offres ESG (Environnement, Social, Gouvernance)
-* s’assurer de la conformité du Métier aux réglementations en vigueur relatives à la finance durable en Europe
-* Vous serez le spécialiste local de la méthodologie extra-financière (relative aux critères ESG (Environnementaux, Sociaux et de Gouvernance)) couvrant l’ensemble des produits financiers de l’offre de Wealth Management à Luxembourg.
-* Vous contribuerez aux analyses à la structuration des données relatives au</t>
-        </is>
-      </c>
-      <c r="P78" s="6" t="inlineStr">
-        <is>
-          <t>* Capacité à collaborer / travail d’équipe
-* Rigueur
-* Etre orienté(e) résultats
-* Créativité &amp; Innovation / Capacité à résoudre des problèmes
-* Proactivité
-* Capacité d’analyse
-* Capacité à gérer un projet
-* Capacité à définir des indicateurs de performance pertinents
-* Analyse de données (PowerBI,</t>
-        </is>
-      </c>
       <c r="Q78" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] Job title contains environmental terminology (Hydrogeologist), indicating relevance to environmental science and water management.</t>
+          <t>Job title contains environmental terminology (Hydrogeologist), indicating relevance to environmental science and water management.</t>
         </is>
       </c>
       <c r="R78" s="2" t="inlineStr"/>
@@ -7562,7 +7587,7 @@
       </c>
       <c r="O79" s="6" t="inlineStr">
         <is>
-          <t>Lead the delivery of SaaS programs focused on mandated regulatory reporting, non-financial disclosures, and sustainability reporting. Ensure alignment across product, engineering, implementation, and client/partner teams while meeting evolving regulatory requirements. Drive end-to-end delivery of regulatory reporting solutions (e.g., compliance, ESG, non-financial reporting) Translate regulatory requirements into actionable program plans and product deliverables Align cross-functional teams (Pro</t>
+          <t>Lead the delivery of SaaS programs focused on mandated regulatory reporting, non-financial disclosures, and sustainability reporting. Ensure alignment across product, engineering, implementation, and client/partner teams while meeting evolving regulatory requirements. Drive end-to-end delivery of regulatory reporting solutions (e.g., compliance, ESG, non-financial reporting) Translate regulatory requirements into actionable program plans and product deliverables Align cross-functional teams (Product, Engineering, Implementation, Data, Partners) Manage timelines, dependencies, risks, and regulatory deadlines Ensure accurate and timely client implementations for mandated reporting Act as the bridge between domain experts, clients, and technical teams Oversee release planning aligned with regulatory changes and updates Monitor data quality, reporting accuracy, and audit readiness Provide stakeholder updates, including leadership and external partners</t>
         </is>
       </c>
       <c r="P79" s="6" t="inlineStr">
@@ -7572,7 +7597,7 @@
       </c>
       <c r="Q79" s="6" t="inlineStr">
         <is>
-          <t>[general_esg] The job description mentions ESG/sustainability reporting solutions, non-financial disclosures, and regulatory reporting, which are all relevant to environmental, social, and governance topics.</t>
+          <t>The job description mentions ESG/sustainability reporting solutions, non-financial disclosures, and regulatory reporting, which are all relevant to environmental, social, and governance topics.</t>
         </is>
       </c>
       <c r="R79" s="2" t="inlineStr"/>
@@ -7639,17 +7664,17 @@
       </c>
       <c r="O80" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nello specifico: si interfaccerà con i focal point all’interno delle società del Gruppo, costruirà modelli per la valutazione di specifici rischi aziendali, ne analizzerà i risultati definendo strategie di mitigazione e azioni correttive dei rischi identificati, e monitorandone il relativo piano di implementazione si interfaccerà con le funzioni Compliance e Internal Audit al fine di mappare, valutare e rappresentare all’Alta Direzione aziendale i rischi rilevanti del Gruppo si occuperà di risk </t>
+          <t>Nello specifico: si interfaccerà con i focal point all’interno delle società del Gruppo, costruirà modelli per la valutazione di specifici rischi aziendali, ne analizzerà i risultati definendo strategie di mitigazione e azioni correttive dei rischi identificati, e monitorandone il relativo piano di implementazione si interfaccerà con le funzioni Compliance e Internal Audit al fine di mappare, valutare e rappresentare all’Alta Direzione aziendale i rischi rilevanti del Gruppo si occuperà di risk assessment integrato (ERM- Enterprise Risk Management) con riferimento a tematiche ESG e climate change, e di progetti di assessment BIA (Business Impact Analysis)</t>
         </is>
       </c>
       <c r="P80" s="6" t="inlineStr">
         <is>
-          <t>modelli di valutazione economica-finanziaria di risk management, metodologie statistiche di analisi dati (modelli probabilistici VaR e PaR), utilizzo di software di analisi quali R Project e Python, conoscenza del software MESA_Procomp, orientamento quantitativo, capacità di sintesi e analisi dei fe</t>
+          <t>modelli di valutazione economica-finanziaria di risk management, metodologie statistiche di analisi dati (modelli probabilistici VaR e PaR), utilizzo di software di analisi quali R Project e Python, conoscenza del software MESA_Procomp, orientamento quantitativo, capacità di sintesi e analisi dei fenomeni, capacità relazionali, conoscenza della lingua inglese (livello B2)</t>
         </is>
       </c>
       <c r="Q80" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions risk assessment integrato (ERM- Enterprise Risk Management) with reference to ESG and climate change, which indicates a focus on climate risk management.</t>
+          <t>The job description mentions risk assessment integrato (ERM- Enterprise Risk Management) with reference to ESG and climate change, which indicates a focus on climate risk management.</t>
         </is>
       </c>
       <c r="R80" s="2" t="inlineStr"/>
@@ -7716,17 +7741,17 @@
       </c>
       <c r="O81" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sarai inserito nel department Risk Management &amp; Policies a riporto del responsabile del team ed avrai un ruolo primario in tutte le attività di analisi e pianificazione in ambito risk management e di progettualità strategiche come la revisione dei processi del credito di Unicredit Leasing SpA. In questo ruolo ti occuperai di svolgere le attività finalizzate a: garantire l’attività di controllo e misurazione dei rischi di credito, dei rischi C&amp;E (Climate &amp; Environmental), dei rischi di liquidità </t>
+          <t>Sarai inserito nel department Risk Management &amp; Policies a riporto del responsabile del team ed avrai un ruolo primario in tutte le attività di analisi e pianificazione in ambito risk management e di progettualità strategiche come la revisione dei processi del credito di Unicredit Leasing SpA. In questo ruolo ti occuperai di svolgere le attività finalizzate a: garantire l’attività di controllo e misurazione dei rischi di credito, dei rischi C&amp;E (Climate &amp; Environmental), dei rischi di liquidità e di mercato e di altre tipologie di rischio rilevanti per il perimetro Leasing, formulando analisi, studi, indagini e simulazioni dettagliate per i principali driver; trasformare ed efficientare i processi aziendali nell’ambito di progetti strategici e per rispondere a richieste di necessità di Business, effettuando test e formulando analisi; assicurare la reportistica e il monitoraggio a presidio del rischio, in continua evoluzione con lo sviluppi strategici di Business, nonché a supporto dei vari Organi Aziendali e alla Capogruppo anche a fronte di specifiche richieste (es. Bankit, ECB,…); effettuando test e formulando analisi provvedere all’elaborazione dei forecast mensili e FY dell’anno in corso sui principali driver di rischio (quali loan loss provisions, dinamiche dei non perfoming, asset quality), gestendo in autonomia il modello previsionale, nonché garantendo il monitoraggio del budget.</t>
         </is>
       </c>
       <c r="P81" s="6" t="inlineStr">
         <is>
-          <t>Forte attitudine analitica, approccio strutturato e orientamento alla risoluzione di problemi complesse Ottime capacità relazionali, comunicative e predisposizione al lavoro in team sia in remoto che in presenza Flessibilità, spirito di iniziativa e desiderio di apprendere in un contesto multidiscip</t>
+          <t>Forte attitudine analitica, approccio strutturato e orientamento alla risoluzione di problemi complesse Ottime capacità relazionali, comunicative e predisposizione al lavoro in team sia in remoto che in presenza Flessibilità, spirito di iniziativa e desiderio di apprendere in un contesto multidisciplinare Ottima conoscenza della lingua italiana e buona padronanza dell’inglese Background scolastico caratterizzato da studi quantitativi Buona conoscenza dei principali tool informatici e familiarità con modelli matematici/statistici applicati alla gestione del rischio</t>
         </is>
       </c>
       <c r="Q81" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions 'rischi C&amp;E (Climate &amp; Environmental)' which indicates that the role involves climate-related risk management, making it a good fit for the climate_risk profile.</t>
+          <t>The job description mentions 'rischi C&amp;E (Climate &amp; Environmental)' which indicates that the role involves climate-related risk management, making it a good fit for the climate_risk profile.</t>
         </is>
       </c>
       <c r="R81" s="2" t="inlineStr"/>
@@ -7798,12 +7823,12 @@
       </c>
       <c r="P82" s="6" t="inlineStr">
         <is>
-          <t>Conoscenza del quadro internazionale di mitigazione e adattamento ai cambiamenti climatici e metodi e strumenti di analisi finanziaria; Conoscenza dei framework di sostenibilità (es. SFDR, Taxonomy Regulation, ECB aspettative, CSR, DNF, PRI ecc.); Competenza tecnica nell'analisi dei dati e dei softw</t>
+          <t>Conoscenza del quadro internazionale di mitigazione e adattamento ai cambiamenti climatici e metodi e strumenti di analisi finanziaria; Conoscenza dei framework di sostenibilità (es. SFDR, Taxonomy Regulation, ECB aspettative, CSR, DNF, PRI ecc.); Competenza tecnica nell'analisi dei dati e dei software di mercato (R/Phyton, SAS, Qlik, SQL, PowerBi); Conoscenza di indici internazionali di sostenibilità come TCFD, GRI, CDP, SBTi e indici ESG</t>
         </is>
       </c>
       <c r="Q82" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[general_esg] The job description mentions working in the Climate &amp; Sustainability team, promoting sustainability, and having knowledge of sustainability frameworks (SFDR, Taxonomy Regulation, CSR, etc.) and international sustainability indices (TCFD, GRI, CDP, SBTi, etc.), which are all related to </t>
+          <t>The job description mentions working in the Climate &amp; Sustainability team, promoting sustainability, and having knowledge of sustainability frameworks (SFDR, Taxonomy Regulation, CSR, etc.) and international sustainability indices (TCFD, GRI, CDP, SBTi, etc.), which are all related to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
       <c r="R82" s="2" t="inlineStr"/>
@@ -7882,7 +7907,7 @@
       </c>
       <c r="O83" s="6" t="inlineStr">
         <is>
-          <t>Manage the design and delivery of inclusive sport and recreation spaces in Kingston, Help shape sustainable spaces for a growing community, Provide expert leadership and direction across the planning, design and delivery of Council’s active leisure, sport and recreation projects, Oversee a multidisciplinary team to translate Kingston’s strategic targets and community aspirations into inclusive, sustainable and financially responsible infrastructure, Guide projects from concept to completion, ens</t>
+          <t>Manage the design and delivery of inclusive sport and recreation spaces in Kingston, Help shape sustainable spaces for a growing community, Provide expert leadership and direction across the planning, design and delivery of Council’s active leisure, sport and recreation projects, Oversee a multidisciplinary team to translate Kingston’s strategic targets and community aspirations into inclusive, sustainable and financially responsible infrastructure, Guide projects from concept to completion, ensuring each one meets quality, governance, budget and time requirements, Direction and coordination of capital works projects, including sport and recreation facilities, playgrounds and foreshore infrastructure, High quality design outcomes that reflect Council and community priorities, embedding sustainability, accessibility and universal design principles, Asset planning and renewal strategies that support long term community needs and responsible investment, Strong partnerships and open communication with stakeholders, including Councillors, community groups, sporting clubs and government agencies, to deliver shared outcomes, A positive and inclusive team environment that empowers people to perform at their best and celebrate collective success</t>
         </is>
       </c>
       <c r="P83" s="6" t="inlineStr">
@@ -7892,7 +7917,7 @@
       </c>
       <c r="Q83" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions 'sustainable spaces', 'sustainability', and 'environment' in the context of sport and recreation spaces, which aligns with the clean energy adjacent profile, The role also involves managing projects related to sport and recreation facilities, play</t>
+          <t>The job description mentions 'sustainable spaces', 'sustainability', and 'environment' in the context of sport and recreation spaces, which aligns with the clean energy adjacent profile, The role also involves managing projects related to sport and recreation facilities, playgrounds, and foreshore infrastructure, which are related to environmental and conservation topics</t>
         </is>
       </c>
       <c r="R83" s="2" t="inlineStr">
@@ -7981,7 +8006,7 @@
       </c>
       <c r="Q84" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions Renewable Energy/Power-to-X, Life Sciences, and other sectors related to environmental sustainability, which aligns with the clean energy adjacent profile.</t>
+          <t>The job description mentions Renewable Energy/Power-to-X, Life Sciences, and other sectors related to environmental sustainability, which aligns with the clean energy adjacent profile.</t>
         </is>
       </c>
       <c r="R84" s="2" t="inlineStr">
@@ -8064,17 +8089,17 @@
       </c>
       <c r="O85" s="6" t="inlineStr">
         <is>
-          <t>Deliver on the Balance Sheet &amp; Income Statement projections for the Enterprise-wide Stress Testing (EWST) exercises, Carry out the movement analysis &amp; narratives for BS/PnL metrics, Carry out analysis on Capital numbers including CET1, Total capital and compare against Basel and reg requirements, Ensure compliance to EWST procedures, methodologies, and controls, Manage all governance related aspects of the execution of stress testing, Drive process improvements and best practices for more effici</t>
+          <t>Deliver on the Balance Sheet &amp; Income Statement projections for the Enterprise-wide Stress Testing (EWST) exercises, Carry out the movement analysis &amp; narratives for BS/PnL metrics, Carry out analysis on Capital numbers including CET1, Total capital and compare against Basel and reg requirements, Ensure compliance to EWST procedures, methodologies, and controls, Manage all governance related aspects of the execution of stress testing, Drive process improvements and best practices for more efficiency and productivity, Support development and maintenance of underlying models to enhance stress testing methodology, Deliver adequate documentation on stress testing methodology subject to management, model validation, audit &amp; regulatory scrutiny, Deliver on the operational risk framework for the stress test process, Risk Management: Ensure all activity adheres to the Enterprise Risk Management Framework, relevant policies, and standards, Processes: Support the establishment and documentation of all processes and effective controls for the hub team, Governance: Demonstrate an awareness and understanding of the regulatory framework in which SCB operates, and the regulatory requirements and expectations relevant to the role, Regulatory &amp; Business Conduct: Display exemplary conduct and live by the SCB’s Values and Code of Conduct</t>
         </is>
       </c>
       <c r="P85" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exceptional written / verbal communication skills, Flexible and adaptable; able to work in ambiguous situations independently, Display a methodical &amp; meticulous approach to problem solving and root cause analysis, Be a team player and able to work collaboratively with others, Knowledge of Python or </t>
+          <t>Exceptional written / verbal communication skills, Flexible and adaptable; able to work in ambiguous situations independently, Display a methodical &amp; meticulous approach to problem solving and root cause analysis, Be a team player and able to work collaboratively with others, Knowledge of Python or equivalent software packages for data analysis, Knowledge of data visualization tools like Tableau / Power BI, Knowledge of IFRS9 Regulation, Financial Analysis, External Reporting, Effective Communications, Project Management, Process Management</t>
         </is>
       </c>
       <c r="Q85" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions 'Climate Risk Stress Tests: A new area of analysis focussing on the impact of climate change on Banking industry', which indicates that the role is related to climate risk and its impact on the banking industry.</t>
+          <t>The job description mentions 'Climate Risk Stress Tests: A new area of analysis focussing on the impact of climate change on Banking industry', which indicates that the role is related to climate risk and its impact on the banking industry.</t>
         </is>
       </c>
       <c r="R85" s="2" t="inlineStr">
@@ -8163,7 +8188,7 @@
       </c>
       <c r="Q86" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions developing catastrophe models for extreme weather events, simulating the full distribution of possible events consistent with a changing climate, and improving the accuracy of representing atmospheric perils, which are all related to climate risk.</t>
+          <t>The job description mentions developing catastrophe models for extreme weather events, simulating the full distribution of possible events consistent with a changing climate, and improving the accuracy of representing atmospheric perils, which are all related to climate risk.</t>
         </is>
       </c>
       <c r="R86" s="2" t="inlineStr">
@@ -8242,17 +8267,17 @@
       </c>
       <c r="O87" s="6" t="inlineStr">
         <is>
-          <t>Perform independent validation of Advanced IRB / Foundation IRB models including: PD, LGD, EAD, and CCF modelling methodologies, Rating system design and performance, RWA attribution and capital impact assessment, Assess model methodologies and assumptions for diverse wholesale product exposures, Evaluate model conceptual soundness, data representativeness, risk differentiation, and calibration methodology, Review and challenge: Model segmentation, overrides, downturn calibration, and economic c</t>
+          <t>Perform independent validation of Advanced IRB / Foundation IRB models including: PD, LGD, EAD, and CCF modelling methodologies, Rating system design and performance, RWA attribution and capital impact assessment, Assess model methodologies and assumptions for diverse wholesale product exposures, Evaluate model conceptual soundness, data representativeness, risk differentiation, and calibration methodology, Review and challenge: Model segmentation, overrides, downturn calibration, and economic cycle considerations, Treatment of collateral, guarantees, credit mitigants, and default definitions, Regulatory compliance with Basel III/IV IRB requirements and regional supervisory rules, Conduct model performance testing, Prepare high-quality validation documentation, Support regulatory engagements, Partner with Model Development, Credit Policy, Data Governance, and Capital Management teams</t>
         </is>
       </c>
       <c r="P87" s="6" t="inlineStr">
         <is>
-          <t>Experience with Corporate lending, project finance, commercial real estate, private equity exposures, Stress testing frameworks (CCAR/ICAAP) and IRB-to-IFRS 9 model linkages, Regulatory interactions with PRA, ECB, Fed/OCC, OSFI, etc., Ability to articulate quantitative findings to non-technical seni</t>
+          <t>Experience with Corporate lending, project finance, commercial real estate, private equity exposures, Stress testing frameworks (CCAR/ICAAP) and IRB-to-IFRS 9 model linkages, Regulatory interactions with PRA, ECB, Fed/OCC, OSFI, etc., Ability to articulate quantitative findings to non-technical senior stakeholders, Strong technical skills in Python, R, SAS, SQL and knowledge of credit modelling statistics</t>
         </is>
       </c>
       <c r="Q87" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions Climate Risk Modelling experience, which is a key aspect of climate risk management, and the role involves validating IRB models that consider environmental policies, indicating a focus on climate-related risks.</t>
+          <t>The job description mentions Climate Risk Modelling experience, which is a key aspect of climate risk management, and the role involves validating IRB models that consider environmental policies, indicating a focus on climate-related risks.</t>
         </is>
       </c>
       <c r="R87" s="2" t="inlineStr"/>
@@ -8331,7 +8356,7 @@
       </c>
       <c r="O88" s="6" t="inlineStr">
         <is>
-          <t>Your role: We are seeking a Site Construction &amp; EHS Manager for a remediation project in Charleroi. This role combines environmental remediation execution with EHS (Environment, Health &amp; Safety) management on-site. You will be responsible for managing the progress of the site work activities ensuring the safe and compliant execution of remediation activities, coordinating with contractors, and maintaining high standards of environmental and safety performance. Key Responsibilities: Oversee and c</t>
+          <t>Your role: We are seeking a Site Construction &amp; EHS Manager for a remediation project in Charleroi. This role combines environmental remediation execution with EHS (Environment, Health &amp; Safety) management on-site. You will be responsible for managing the progress of the site work activities ensuring the safe and compliant execution of remediation activities, coordinating with contractors, and maintaining high standards of environmental and safety performance. Key Responsibilities: Oversee and coordinate remediation and excavation activities on-site in time and budget, Ensure full compliance with Belgian EHS legislation and internal safety protocols, Conduct EHS training sessions for personnel and contractors, Monitor and report on site progress, safety performance, and environmental impact, Implement and maintain site documentation and control tools, Liaise with project stakeholders, suppliers, and regulatory bodies, Identify risks and propose preventive and corrective actions, Promote a culture of safety and continuous improvement on-site, Support project reporting and documentation for internal and external audits</t>
         </is>
       </c>
       <c r="P88" s="6" t="inlineStr">
@@ -8341,7 +8366,7 @@
       </c>
       <c r="Q88" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions environmental remediation, excavation, waste management, and site remediation, which are related to environmental science and conservation, fitting the clean_energy_adjacent profile.</t>
+          <t>The job description mentions environmental remediation, excavation, waste management, and site remediation, which are related to environmental science and conservation, fitting the clean_energy_adjacent profile.</t>
         </is>
       </c>
       <c r="R88" s="2" t="inlineStr">
@@ -8424,17 +8449,17 @@
       </c>
       <c r="O89" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">As a Senior Specialist, Data Management, you will play a critical role in ensuring Telstra Enterprise and TB-MM have trusted, well-governed customer and identity data that enables digital-first selling, customer self-service, automation and AI at scale. You will lead the definition of data requirements, controls and governance that underpin high-quality customer and identity data across platforms. This includes assessing data readiness and risk early, translating complex data and identity needs </t>
+          <t>As a Senior Specialist, Data Management, you will play a critical role in ensuring Telstra Enterprise and TB-MM have trusted, well-governed customer and identity data that enables digital-first selling, customer self-service, automation and AI at scale. You will lead the definition of data requirements, controls and governance that underpin high-quality customer and identity data across platforms. This includes assessing data readiness and risk early, translating complex data and identity needs into clear, actionable requirements, and embedding preventative controls directly into systems and processes.</t>
         </is>
       </c>
       <c r="P89" s="6" t="inlineStr">
         <is>
-          <t>A practical, outcomes-focused approach, with experience driving exception-only remediation and automation to address root causes and reduce recurring data issues. A strong understanding of enterprise systems and application interconnectedness, including how data flows end-to-end and how changes impa</t>
+          <t>A practical, outcomes-focused approach, with experience driving exception-only remediation and automation to address root causes and reduce recurring data issues. A strong understanding of enterprise systems and application interconnectedness, including how data flows end-to-end and how changes impact customers. A customer-centric mindset, with the ability to use data analysis and insights to improve digital experiences, trust, auditability and operational efficiency.</t>
         </is>
       </c>
       <c r="Q89" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[general_esg] The job description mentions working in the Climate &amp; Sustainability team, promoting sustainability, and having knowledge of sustainability frameworks (SFDR, Taxonomy Regulation, CSR, etc.) and international sustainability indices (TCFD, GRI, CDP, SBTi, etc.), which are all related to </t>
+          <t>The job description does not mention any specific ESG/sustainability topics, such as climate risk, sustainable finance, or carbon markets. The mention of 'sustainability' is in the context of the company's general commitment to sustainability, but it is not directly related to the job role or responsibilities.</t>
         </is>
       </c>
       <c r="R89" s="2" t="inlineStr">
@@ -8517,7 +8542,7 @@
       </c>
       <c r="O90" s="6" t="inlineStr">
         <is>
-          <t>Working as part of our established Geoscience and Remediation Services (GRS) team, you will collaborate with a team of environmental engineers, scientists, hydrogeologists and geologists to provide contaminated land assessment, environmental monitoring, and remediation consulting across a wide range of projects, including those in the oil and gas, mining, Department of Defence, and public sectors. The substantive role involves working on challenging projects across various industries, with a pri</t>
+          <t>Working as part of our established Geoscience and Remediation Services (GRS) team, you will collaborate with a team of environmental engineers, scientists, hydrogeologists and geologists to provide contaminated land assessment, environmental monitoring, and remediation consulting across a wide range of projects, including those in the oil and gas, mining, Department of Defence, and public sectors. The substantive role involves working on challenging projects across various industries, with a primary focus on fieldwork supported by occasional office-based tasks. You will also have the opportunity to work on remote client sites, collaborating with internal teams, subcontractors, and clients. Primarily assist with fieldwork and environmental data collection across a variety of project sites, including short, medium and / or long-term site programs in QLD, and occasionally work interstate to support the national GRS team as opportunities arise. Support surface water and groundwater monitoring programs. Contribute to contamination investigations and remediation projects of varying size and complexity. Collect, handle, and manage environmental samples from a range of media, ensuring safety and sample quality. Support the development of technical environmental reports. Collaborate with offices across Australia and New Zealand, gaining exposure to a wide range of projects and disciplines.</t>
         </is>
       </c>
       <c r="P90" s="6" t="inlineStr">
@@ -8527,7 +8552,7 @@
       </c>
       <c r="Q90" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions environmental science, contaminated land assessment, environmental monitoring, and remediation consulting, which are related to environmental science and conservation, fitting the clean_energy_adjacent profile.</t>
+          <t>The job description mentions environmental science, contaminated land assessment, environmental monitoring, and remediation consulting, which are related to environmental science and conservation, fitting the clean_energy_adjacent profile.</t>
         </is>
       </c>
       <c r="R90" s="2" t="inlineStr">
@@ -8610,7 +8635,7 @@
       </c>
       <c r="O91" s="6" t="inlineStr">
         <is>
-          <t>Working as part of our established Geoscience and Remediation Services (GRS) team, you will collaborate with a team of environmental engineers, scientists, hydrogeologists and geologists to provide contaminated land assessment, environmental monitoring, and remediation consulting across a wide range of projects, including those in the oil and gas, mining, Department of Defence, and public sectors. The substantive role involves working on challenging projects across various industries, with a pri</t>
+          <t>Working as part of our established Geoscience and Remediation Services (GRS) team, you will collaborate with a team of environmental engineers, scientists, hydrogeologists and geologists to provide contaminated land assessment, environmental monitoring, and remediation consulting across a wide range of projects, including those in the oil and gas, mining, Department of Defence, and public sectors. The substantive role involves working on challenging projects across various industries, with a primary focus on fieldwork supported by occasional office-based tasks. You will also have the opportunity to work on remote client sites, collaborating with internal teams, subcontractors, and clients. Primarily assist with fieldwork and environmental data collection across a variety of project sites, including short, medium and / or long-term site programs in QLD, and occasionally work interstate to support the national GRS team as opportunities arise. Support surface water and groundwater monitoring programs. Contribute to contamination investigations and remediation projects of varying size and complexity. Collect, handle, and manage environmental samples from a range of media, ensuring safety and sample quality. Support the development of technical environmental reports. Collaborate with offices across Australia and New Zealand, gaining exposure to a wide range of projects and disciplines.</t>
         </is>
       </c>
       <c r="P91" s="6" t="inlineStr">
@@ -8620,7 +8645,7 @@
       </c>
       <c r="Q91" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions environmental science, contaminated land assessment, environmental monitoring, and remediation consulting, which are related to environmental science and conservation, fitting the clean_energy_adjacent profile.</t>
+          <t>The job description mentions environmental science, contaminated land assessment, environmental monitoring, and remediation consulting, which are related to environmental science and conservation, fitting the clean_energy_adjacent profile.</t>
         </is>
       </c>
       <c r="R91" s="2" t="inlineStr">
@@ -8708,12 +8733,12 @@
       </c>
       <c r="P92" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Excellent quantitative skills, including the ability to identify and interpret data, carry out data analysis, and present findings in a visually compelling way; experience of building and running three-statement financial models; excellent written and presentational skills, including the ability to </t>
+          <t>Excellent quantitative skills, including the ability to identify and interpret data, carry out data analysis, and present findings in a visually compelling way; experience of building and running three-statement financial models; excellent written and presentational skills, including the ability to produce deliverables to a high quality and to present them in a compelling fashion; social and interpersonal skills, with the ability to influence stakeholders and build consensus;</t>
         </is>
       </c>
       <c r="Q92" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions experience in sustainable finance, including climate, development, and/or nature finance, and the company's mission is to address global development challenges through strategic investments that promote sustainable and inclusive economic growth.</t>
+          <t>The job description mentions experience in sustainable finance, including climate, development, and/or nature finance, and the company's mission is to address global development challenges through strategic investments that promote sustainable and inclusive economic growth.</t>
         </is>
       </c>
       <c r="R92" s="2" t="inlineStr">
@@ -8796,7 +8821,7 @@
       </c>
       <c r="O93" s="6" t="inlineStr">
         <is>
-          <t>Assist the EIK team on operational areas, such as: Assisting with the initiation, development, and implementation of Technical Assistance (TA) projects. Supporting contracting processes with TA beneficiaries and consultants, including Know Your Customer (KYC) procedures. Assisting in managing procurements of consultants that execute TA projects and ensuring compliance with procurement procedures. Supporting portfolio and/or program management across different business lines and mandates. Contrib</t>
+          <t>Assist the EIK team on operational areas, such as: Assisting with the initiation, development, and implementation of Technical Assistance (TA) projects. Supporting contracting processes with TA beneficiaries and consultants, including Know Your Customer (KYC) procedures. Assisting in managing procurements of consultants that execute TA projects and ensuring compliance with procurement procedures. Supporting portfolio and/or program management across different business lines and mandates. Contribute to effective communication of impact through: Assisting the development and distribution of newsletters, impact reports, and other communication materials for external stakeholders. Supporting the creation of case studies and impact stories . Coordinating with relevant teams to gather content and updates for communication materials. Support the design and implementation of a data repository for storing and analyzing impact and general data, through: Assisting in data entry, validation, and analysis of impact data. Generating reports and presentations based on collected data for internal and external stakeholders. Communicate key findings and insights from data analysis to support decision-making processes.</t>
         </is>
       </c>
       <c r="P93" s="6" t="inlineStr">
@@ -8806,7 +8831,7 @@
       </c>
       <c r="Q93" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions impact investing, ESG, and sustainable development, which are key concepts in sustainable finance. The company's mission and values also align with sustainable finance principles.</t>
+          <t>The job description mentions impact investing, ESG, and sustainable development, which are key concepts in sustainable finance. The company's mission and values also align with sustainable finance principles.</t>
         </is>
       </c>
       <c r="R93" s="2" t="inlineStr">
@@ -8885,17 +8910,17 @@
       </c>
       <c r="O94" s="6" t="inlineStr">
         <is>
-          <t>As a core function, this team executes sustainable financing solutions aligned with evolving ESG standards and market trends. Execution support - intermediate structuring experience, with a growing level of autonomy. Be responsible of specific tasks for the execution of Sustainable Loan and Bond transactions, under the supervision of a senior team members but with a growing level of autonomy. Advise on transaction execution, by framing, designing and supporting the delivery of sustainable financ</t>
+          <t>As a core function, this team executes sustainable financing solutions aligned with evolving ESG standards and market trends. Execution support - intermediate structuring experience, with a growing level of autonomy. Be responsible of specific tasks for the execution of Sustainable Loan and Bond transactions, under the supervision of a senior team members but with a growing level of autonomy. Advise on transaction execution, by framing, designing and supporting the delivery of sustainable finance mandates. Perform analysis of the ESG profile and strategy of issuers/borrowers and key industry trends, and provide structuring recommendations based on findings. Prepare high-quality presentations to clients. Keep abreast with sustainable finance market developments.</t>
         </is>
       </c>
       <c r="P94" s="6" t="inlineStr">
         <is>
-          <t>Proficient in Office (Excel, PowerPoint). Proficient in Bloomberg. Knowledge in: Financial markets - Structuring; Sustainable Finance &amp; Corporate Social Responsibility - Integration of ESG challenges; Sustainable Finance &amp; Corporate Social Responsibility - Transition towards Low Carbon Economy; Data</t>
+          <t>Proficient in Office (Excel, PowerPoint). Proficient in Bloomberg. Knowledge in: Financial markets - Structuring; Sustainable Finance &amp; Corporate Social Responsibility - Integration of ESG challenges; Sustainable Finance &amp; Corporate Social Responsibility - Transition towards Low Carbon Economy; Data - Business Analytics; Sustainable Finance &amp; Corporate Social Responsibility - Sustainable Savings, investment and Financing; Investment &amp; Wholesale Banking - Debt Capital Market – Bonds; Investment &amp; Wholesale Banking - Debt Capital Market - Loans.</t>
         </is>
       </c>
       <c r="Q94" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions 'sustainable financing solutions', 'sustainable finance', 'ESG standards', 'sustainable loan and bond transactions', and 'transition to a greener economy', which are all related to sustainable finance and ESG investing.</t>
+          <t>The job description mentions 'sustainable financing solutions', 'sustainable finance', 'ESG standards', 'sustainable loan and bond transactions', and 'transition to a greener economy', which are all related to sustainable finance and ESG investing.</t>
         </is>
       </c>
       <c r="R94" s="2" t="inlineStr">
@@ -8982,7 +9007,7 @@
       </c>
       <c r="O95" s="6" t="inlineStr">
         <is>
-          <t>Execution support, advise on and oversee transaction execution, perform analysis of the ESG profile and strategy of issuers/borrowers, prepare high-quality presentations, keep abreast of key sustainable finance market developments, identify and implement innovative solutions, deepen knowledge on sustainable financing, collect and analyze data, maintain open communication with team members, support junior members, raise awareness on sustainable finance, oversee systematic follow-ups on action poi</t>
+          <t>Execution support, advise on and oversee transaction execution, perform analysis of the ESG profile and strategy of issuers/borrowers, prepare high-quality presentations, keep abreast of key sustainable finance market developments, identify and implement innovative solutions, deepen knowledge on sustainable financing, collect and analyze data, maintain open communication with team members, support junior members, raise awareness on sustainable finance, oversee systematic follow-ups on action points, assist in strengthening the Portugal platform</t>
         </is>
       </c>
       <c r="P95" s="6" t="inlineStr">
@@ -8992,7 +9017,7 @@
       </c>
       <c r="Q95" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions sustainable finance, ESG standards, green economy, and sustainable financing solutions, which are all key aspects of sustainable finance</t>
+          <t>The job description mentions sustainable finance, ESG standards, green economy, and sustainable financing solutions, which are all key aspects of sustainable finance</t>
         </is>
       </c>
       <c r="R95" s="2" t="inlineStr">
@@ -9079,7 +9104,7 @@
       </c>
       <c r="O96" s="6" t="inlineStr">
         <is>
-          <t>Manage and mentor a diverse team of credit risk analytics professionals, fostering a culture of excellence and innovation. Provide direction and oversight across specialized functions including IRB modeling, counterparty credit risk analytics and credit stress testing/provisioning. Develop team members' skills and careers, and promote an inclusive, collaborative environment. Drive the strategic development of the Firms credit risk measurement methodologies. Set the vision for next-generation cre</t>
+          <t>Manage and mentor a diverse team of credit risk analytics professionals, fostering a culture of excellence and innovation. Provide direction and oversight across specialized functions including IRB modeling, counterparty credit risk analytics and credit stress testing/provisioning. Develop team members' skills and careers, and promote an inclusive, collaborative environment. Drive the strategic development of the Firms credit risk measurement methodologies. Set the vision for next-generation credit risk models and analytics tools, ensuring they align with business objectives and emerging risks. Continuously improve model frameworks to enhance risk-adjusted return on capital and support prudent risk taking by the Firm. Lead the Credit Risk Analytics teams response to regulatory initiatives and requirements. Oversee the implementation of frameworks such as Basel III Internal Ratings-Based approaches and stress testing programs. Engage with regulators and internal Model Risk Management on model approvals, validation exercises, and regulatory examinations. Ensure all credit risk models and processes meet the highest standards of compliance and transparency. Work closely with a broad range of stakeholders to integrate credit risk insights into decision-making. Partner with Credit Risk Managers and business units to ensure models adequately capture risks and inform credit decisions and limit setting. Collaborate with Technology teams to drive the development of analytics infrastructure and data capabilities. Provide senior leadership with timely, insightful analysis of credit risk findings and trends. Oversee the end-to-end lifecycle of credit risk models, from design and development through validation, implementation, and ongoing performance monitoring. Chair internal model committees and ensure methodological rigor, robust documentation, and adherence to model risk governance standards. Proactively identify model limitations and guide enhancements or redevelopment as needed. Maintain a strong control environment around model usage and results interpretation. Coordinate with Risk Analytics colleagues and other risk stripes globally to ensure consistency and best practices in risk modeling. Contribute to firm-wide risk initiatives and working groups, sharing expertise in credit risk analytics. Leverage the global footprint of the team by seamlessly integrating efforts between Mumbai, New York, London, and Budapest offices.</t>
         </is>
       </c>
       <c r="P96" s="6" t="inlineStr">
@@ -9089,7 +9114,7 @@
       </c>
       <c r="Q96" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions 'Climate Risk Stress Tests: A new area of analysis focussing on the impact of climate change on Banking industry', which indicates that the role is related to climate risk and its impact on the banking industry.</t>
+          <t>The job description does not explicitly mention ESG, sustainability, climate risk, or other related topics. The focus is on credit risk management and analytics, which is a traditional finance role.</t>
         </is>
       </c>
       <c r="R96" s="2" t="inlineStr">
@@ -9168,17 +9193,17 @@
       </c>
       <c r="O97" s="6" t="inlineStr">
         <is>
-          <t>Lead a team of 5-6 Senior consultants, analysts for engagement execution and delivery. Showcase exceptional project management abilities and foster a collaborative environment and accountability among team members on engagements. Demonstrate deep technical expertise and industry knowledge, particularly in financial products with a focus on lending solutions. Design, assessment, and benchmarking of financial risk management policies, frameworks, methodologies covering a range of risk domains such</t>
+          <t>Lead a team of 5-6 Senior consultants, analysts for engagement execution and delivery. Showcase exceptional project management abilities and foster a collaborative environment and accountability among team members on engagements. Demonstrate deep technical expertise and industry knowledge, particularly in financial products with a focus on lending solutions. Design, assessment, and benchmarking of financial risk management policies, frameworks, methodologies covering a range of risk domains such as credit risk, market risk, operational risk, liquidity risk, climate risk, and integrated risk topics viz., capital adequacy and stress testing measurement methodologies in financial institutions (FI). Stay abreast of market trends and challenges in the financial services sector to understand client needs and industry dynamics. Understand EY and its service lines and actively assess what the firm can deliver to serve clients. Monitor project progress, manage risks, and effectively communicate status, issues, and priorities to key stakeholders to ensure successful outcomes. Review, analyze, and validate the work completed by junior team members to ensure accuracy and quality. Adapt to projects involving model audits, validation, and development, demonstrating flexibility and domain knowledge.</t>
         </is>
       </c>
       <c r="P97" s="6" t="inlineStr">
         <is>
-          <t>Advanced technical skills, with proficiency in Python, SAS, SQL, R, and Excel. Excellent Oral and written communication and presentation skills. Strong documentation skills, with the ability to quickly grasp complex concepts and present them clearly in documents or presentations. Strong multi-taskin</t>
+          <t>Advanced technical skills, with proficiency in Python, SAS, SQL, R, and Excel. Excellent Oral and written communication and presentation skills. Strong documentation skills, with the ability to quickly grasp complex concepts and present them clearly in documents or presentations. Strong multi-tasking skills with demonstrated ability to manage expectations and deliver high quality results under tight deadlines and minimal supervision. Professional certifications such as FRM, CFA, PRM, or SCR. Knowledge of regulatory modeling (BASEL, CCAR, IFRS9) is preferred. Exposure to regulatory stress testing processes around credit risk &amp; ICAAP. Experience in climatic risk space preferably in the areas of stress testing /scenario designing. Exposure to Interest Rate Risk in Banking Book (IRRBB). Experience in data/business intelligence (BI) reporting. Familiarity with machine learning models and their practical applications.</t>
         </is>
       </c>
       <c r="Q97" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions climate risk, stress testing, and regulatory risk, which are relevant to the climate risk profile. Additionally, the job requires experience in climatic risk space, preferably in the areas of stress testing/scenario designing, which further supports the cl</t>
+          <t>The job description mentions climate risk, stress testing, and regulatory risk, which are relevant to the climate risk profile. Additionally, the job requires experience in climatic risk space, preferably in the areas of stress testing/scenario designing, which further supports the classification as climate_risk.</t>
         </is>
       </c>
       <c r="R97" s="2" t="inlineStr"/>
@@ -9253,7 +9278,7 @@
       </c>
       <c r="O98" s="6" t="inlineStr">
         <is>
-          <t>Team members work on a diverse set of client engagements as part of multi-disciplinary project teams, encompassing subject matter authorities, engagement managers, and others. In this role you will develop and use data and analytical skills to create, review, and deliver analyses to clients, frequently using BlackRock proprietary technology platforms. Candidates must be interested in financial markets and be able to apply creative solutions to solve client objectives and challenges. Team members</t>
+          <t>Team members work on a diverse set of client engagements as part of multi-disciplinary project teams, encompassing subject matter authorities, engagement managers, and others. In this role you will develop and use data and analytical skills to create, review, and deliver analyses to clients, frequently using BlackRock proprietary technology platforms. Candidates must be interested in financial markets and be able to apply creative solutions to solve client objectives and challenges. Team members will gain subject matter expertise about financial institutions and relevant capital markets and sustainability objectives.</t>
         </is>
       </c>
       <c r="P98" s="6" t="inlineStr">
@@ -9263,7 +9288,7 @@
       </c>
       <c r="Q98" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions 'climate risk analytics and advisory' as one of the areas of support, indicating that the role involves working with climate-related risks, which aligns with the climate_risk profile.</t>
+          <t>The job description mentions 'climate risk analytics and advisory' as one of the areas of support, indicating that the role involves working with climate-related risks, which aligns with the climate_risk profile.</t>
         </is>
       </c>
       <c r="R98" s="2" t="inlineStr"/>
@@ -9356,7 +9381,7 @@
       </c>
       <c r="Q99" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions 'climate risks' under the 'Emerging Risks' section, indicating that the role involves identifying, measuring, and monitoring climate-related risks.</t>
+          <t>The job description mentions 'climate risks' under the 'Emerging Risks' section, indicating that the role involves identifying, measuring, and monitoring climate-related risks.</t>
         </is>
       </c>
       <c r="R99" s="2" t="inlineStr">
@@ -9443,17 +9468,17 @@
       </c>
       <c r="O100" s="6" t="inlineStr">
         <is>
-          <t>Lead a team of 5-6 Senior consultants, analysts for engagement execution and delivery. Showcase exceptional project management abilities and foster a collaborative environment and accountability among team members on engagements. Demonstrate deep technical expertise and industry knowledge, particularly in financial products with a focus on lending solutions. Design, assessment, and benchmarking of financial risk management policies, frameworks, methodologies covering a range of risk domains such</t>
+          <t>Lead a team of 5-6 Senior consultants, analysts for engagement execution and delivery. Showcase exceptional project management abilities and foster a collaborative environment and accountability among team members on engagements. Demonstrate deep technical expertise and industry knowledge, particularly in financial products with a focus on lending solutions. Design, assessment, and benchmarking of financial risk management policies, frameworks, methodologies covering a range of risk domains such as credit risk, market risk, operational risk, liquidity risk, climate risk, and integrated risk topics viz., capital adequacy and stress testing measurement methodologies in financial institutions (FI). Stay abreast of market trends and challenges in the financial services sector to understand client needs and industry dynamics. Understand EY and its service lines and actively assess what the firm can deliver to serve clients. Monitor project progress, manage risks, and effectively communicate status, issues, and priorities to key stakeholders to ensure successful outcomes. Review, analyze, and validate the work completed by junior team members to ensure accuracy and quality. Adapt to projects involving model audits, validation, and development, demonstrating flexibility and domain knowledge.</t>
         </is>
       </c>
       <c r="P100" s="6" t="inlineStr">
         <is>
-          <t>Advanced technical skills, with proficiency in Python, SAS, SQL, R, and Excel. Excellent Oral and written communication and presentation skills. Strong documentation skills, with the ability to quickly grasp complex concepts and present them clearly in documents or presentations. Strong multi-taskin</t>
+          <t>Advanced technical skills, with proficiency in Python, SAS, SQL, R, and Excel. Excellent Oral and written communication and presentation skills. Strong documentation skills, with the ability to quickly grasp complex concepts and present them clearly in documents or presentations. Strong multi-tasking skills with demonstrated ability to manage expectations and deliver high quality results under tight deadlines and minimal supervision. Familiarity with machine learning models and their practical applications.</t>
         </is>
       </c>
       <c r="Q100" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions climate risk, stress testing, and scenario designing, which are relevant to climate risk management. Additionally, the job requires experience in climatic risk space, which further supports the classification as climate_risk.</t>
+          <t>The job description mentions climate risk, stress testing, and scenario designing, which are relevant to climate risk management. Additionally, the job requires experience in climatic risk space, which further supports the classification as climate_risk.</t>
         </is>
       </c>
       <c r="R100" s="2" t="inlineStr">
@@ -9540,17 +9565,17 @@
       </c>
       <c r="O101" s="6" t="inlineStr">
         <is>
-          <t>Collaborate with the global team and clients to analyze ESG data, providing valuable insights to investors and decision-makers. Conduct comprehensive ESG Rating assessments, Gap Analyses, ESG Due Diligence, EU Taxonomy, CSRD assessments, SFDR Compliance, Sustainability-linked loan assessments, and develop Carbon Footprint strategy reports. Utilize deep expertise in ESG and sustainability to deliver high-quality advisory services on ESG reporting, sustainability strategy, and risk management. Sta</t>
+          <t>Collaborate with the global team and clients to analyze ESG data, providing valuable insights to investors and decision-makers. Conduct comprehensive ESG Rating assessments, Gap Analyses, ESG Due Diligence, EU Taxonomy, CSRD assessments, SFDR Compliance, Sustainability-linked loan assessments, and develop Carbon Footprint strategy reports. Utilize deep expertise in ESG and sustainability to deliver high-quality advisory services on ESG reporting, sustainability strategy, and risk management. Stay current with global ESG standards and frameworks, ensuring the firms services meet evolving market expectations. Contribute to the refinement of existing ESG products and the development of new ones. Lead initiatives to enhance the sustainability performance of Apex Group.</t>
         </is>
       </c>
       <c r="P101" s="6" t="inlineStr">
         <is>
-          <t>Proficiency in quantitative and qualitative data collection, analysis, and reporting. Exceptional organizational skills with keen attention to detail. Excellent interpersonal skills with the ability to communicate and influence internal and external stakeholders, including proficiency in video confe</t>
+          <t>Proficiency in quantitative and qualitative data collection, analysis, and reporting. Exceptional organizational skills with keen attention to detail. Excellent interpersonal skills with the ability to communicate and influence internal and external stakeholders, including proficiency in video conferencing, written communication, and presentation. Proficiency in MS Office; knowledge of programming languages is a plus.</t>
         </is>
       </c>
       <c r="Q101" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[general_esg] The job description mentions ESG ratings, ESG reporting, sustainability strategy, and risk management, which are all key aspects of general ESG. Additionally, the job requires expertise in ESG and sustainability, and involves working with ESG data and standards, further supporting the </t>
+          <t>The job description mentions ESG ratings, ESG reporting, sustainability strategy, and risk management, which are all key aspects of general ESG. Additionally, the job requires expertise in ESG and sustainability, and involves working with ESG data and standards, further supporting the classification as general ESG.</t>
         </is>
       </c>
       <c r="R101" s="2" t="inlineStr">
@@ -9621,7 +9646,7 @@
       </c>
       <c r="O102" s="6" t="inlineStr">
         <is>
-          <t>La risorsa Experienced sarà inserita in un team di lavoro, affiancando colleghi senior e occupandosi di: Supporto tecnico-specialistico allo svolgimento delle attività di controllo e verifica relativamente alle operazioni poste in essere in attuazione dei programmi regionali finanziati a livello europeo, aventi l’obiettivo di rafforzare la competitività, l'innovazione, la transizione ecologica e digitale, la mobilità sostenibile, l'istruzione e l'inclusione sociale, riducendo i divari territoria</t>
+          <t>La risorsa Experienced sarà inserita in un team di lavoro, affiancando colleghi senior e occupandosi di: Supporto tecnico-specialistico allo svolgimento delle attività di controllo e verifica relativamente alle operazioni poste in essere in attuazione dei programmi regionali finanziati a livello europeo, aventi l’obiettivo di rafforzare la competitività, l'innovazione, la transizione ecologica e digitale, la mobilità sostenibile, l'istruzione e l'inclusione sociale, riducendo i divari territoriali tramite investimenti in ricerca, imprese, ambiente e infrastrutture. Contribuire alla corretta esecuzione delle attività in cui è coinvolto, apportando le proprie conoscenze tecniche, nel rispetto degli indirizzi e degli obiettivi stabiliti, nonché produrre la documentazione e le analisi a supporto della corretta esecuzione delle attività. Supporto tecnico-specialistico in ambito/materia valutazione ambientale strategica (c.d. VAS) e/o nella verifica del rispetto del principio del DNSH (i.e. non arrecare un danno significativo), nell’ambito dell’attuazione dei programmi regionali</t>
         </is>
       </c>
       <c r="P102" s="6" t="inlineStr">
@@ -9631,7 +9656,7 @@
       </c>
       <c r="Q102" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions 'Sustainable Finance' team, 'strategie ESG', 'conformità normativa', 'integrazione dei fattori di sostenibilità', and 'evoluzione sostenibile del settore finanziario', which are all related to sustainable finance and ESG investing.</t>
+          <t>The job description mentions 'Sustainable Finance' team, 'strategie ESG', 'conformità normativa', 'integrazione dei fattori di sostenibilità', and 'evoluzione sostenibile del settore finanziario', which are all related to sustainable finance and ESG investing.</t>
         </is>
       </c>
       <c r="R102" s="2" t="inlineStr"/>
@@ -9698,7 +9723,7 @@
       </c>
       <c r="O103" s="6" t="inlineStr">
         <is>
-          <t>Gestirai sfidanti progetti di evoluzione e trasformazione del business dei principali player nei settori Infrastructure, Energy &amp; Utility, Industrial Manufacturing, Pharmaceutical attraverso l’efficientamento e la reingegnerizzazione dei processi interni. Attraverso l'affiancamento a risorse PwC di livello manageriale, la risorsa potrà sviluppare competenze di processo in ambito Risk Management (sia entreprise che per tematiche di business verticali), conoscere l'organizzazione di un progetto st</t>
+          <t>Gestirai sfidanti progetti di evoluzione e trasformazione del business dei principali player nei settori Infrastructure, Energy &amp; Utility, Industrial Manufacturing, Pharmaceutical attraverso l’efficientamento e la reingegnerizzazione dei processi interni. Attraverso l'affiancamento a risorse PwC di livello manageriale, la risorsa potrà sviluppare competenze di processo in ambito Risk Management (sia entreprise che per tematiche di business verticali), conoscere l'organizzazione di un progetto strutturato e collaborare alle attività di project management; conoscere la metodologia internazionale Perform di process &amp; skill improvement. All’interno del gruppo ERM, ti occuperai di: Predisposizione e/o sviluppo di framework ERM (in accordo con le normative ISO 31000, CoSo) e PRM; Identificazione e valutazione, attraverso approcci qualitativi e quantitativi, dei principali rischi ed opportunità aziendali, misurando i potenziali impatti economici-finanziari sul business; Valutazione della flessibilità della strategia di business, contribuendo alle scelte aziendali per la definizione del piano strategico al fine di aumentare la resilienza e garantire nel tempo la generazione del valore; Sviluppo di modelli per l’analisi dei rischi ESG in rispondenza alle principali normative di settore (TCFD, ESRS, EU taxonomy, etc.); Soluzioni di Business Continuity Managament.</t>
         </is>
       </c>
       <c r="P103" s="6" t="inlineStr">
@@ -9708,7 +9733,7 @@
       </c>
       <c r="Q103" s="6" t="inlineStr">
         <is>
-          <t>[general_esg] The job description mentions ESG risk analysis, TCFD, ESRS, and EU taxonomy, which are all related to environmental, social, and governance topics, indicating a relevance to general ESG strategy and corporate sustainability.</t>
+          <t>The job description mentions ESG risk analysis, TCFD, ESRS, and EU taxonomy, which are all related to environmental, social, and governance topics, indicating a relevance to general ESG strategy and corporate sustainability.</t>
         </is>
       </c>
       <c r="R103" s="2" t="inlineStr"/>
@@ -9775,7 +9800,7 @@
       </c>
       <c r="O104" s="6" t="inlineStr">
         <is>
-          <t>Beleidsontwikkeling en advisering op het gebied van duurzaam beleggen, Monitoring van ESG-dienstverleners en vermogensbeheerders, Monitoring van impactbeleggingsmandaten en vastgoedbeleggingen, Opstellen van klimaatanalyses van vastgoedbedrijven, Begeleiden en coördineren van engagementtrajecten en internationale samenwerkingen, Coördineren van verschillende werk- en stuurgroepen, Organiseren en ondersteunen bij opleidingen en events, Onderzoeken en analyseren van systemische barrières in de int</t>
+          <t>Beleidsontwikkeling en advisering op het gebied van duurzaam beleggen, Monitoring van ESG-dienstverleners en vermogensbeheerders, Monitoring van impactbeleggingsmandaten en vastgoedbeleggingen, Opstellen van klimaatanalyses van vastgoedbedrijven, Begeleiden en coördineren van engagementtrajecten en internationale samenwerkingen, Coördineren van verschillende werk- en stuurgroepen, Organiseren en ondersteunen bij opleidingen en events, Onderzoeken en analyseren van systemische barrières in de internationale vastgoedmarkt</t>
         </is>
       </c>
       <c r="P104" s="6" t="inlineStr">
@@ -9785,7 +9810,7 @@
       </c>
       <c r="Q104" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions ESG, duurzaam beleggen, impactbeleggen, and klimaatanalyses, which are all related to sustainable finance. The company also works with institutionele beleggers and pensioenfondsen to implement ESG in their beleggingsportefeuille.</t>
+          <t>The job description mentions ESG, duurzaam beleggen, impactbeleggen, and klimaatanalyses, which are all related to sustainable finance. The company also works with institutionele beleggers and pensioenfondsen to implement ESG in their beleggingsportefeuille.</t>
         </is>
       </c>
       <c r="R104" s="2" t="inlineStr"/>
@@ -9852,17 +9877,17 @@
       </c>
       <c r="O105" s="6" t="inlineStr">
         <is>
-          <t>Are you ready to lead the charge in groundbreaking clinical studies? As a Global Study Director (GSD), you will play a pivotal role in the Cell Therapy Clinical Operations organization, driving the operational planning and delivery of high-priority and complex clinical studies. Your expertise will ensure the successful execution of clinical trials, managing quality, timelines, budgets, resources, investigational sites, vendors, and key project deliverables. Leading a cross-functional study team,</t>
+          <t>Are you ready to lead the charge in groundbreaking clinical studies? As a Global Study Director (GSD), you will play a pivotal role in the Cell Therapy Clinical Operations organization, driving the operational planning and delivery of high-priority and complex clinical studies. Your expertise will ensure the successful execution of clinical trials, managing quality, timelines, budgets, resources, investigational sites, vendors, and key project deliverables. Leading a cross-functional study team, you will provide direction and guidance to achieve study milestones. Collaborate with internal and external stakeholders to resolve issues and ensure compliance with SOPs, regulatory requirements, and ICH/GCP guidelines. Your leadership will extend to mentoring GSADs and spearheading non-drug programs and improvement projects. Accountabilities Lead and coordinate a cross-functional study team to ensure clinical study progress according to timelines, budget, and quality standards. Contribute to vendor/ESP selection activities and lead operational oversight at the study level. Assist with operational planning for upcoming clinical studies, interfacing with cross-functional partners. Collaborate to establish strategies for increasing efficiency of global study teams. Facilitate communication across functions and provide guidance to study team members. Serve as the primary AZ contact for outsourced studies, ensuring delivery according to agreed standards. Hold accountability for essential study level documents development. Ensure external service providers perform to contracted goals and timelines. Develop and maintain relevant study plans, including risk management planning. Oversee study level performance against plans, milestones, and KPIs. Identify and report quality issues within the study and collaborate to overcome barriers. Ensure Trial Master File completion and compliance with governance controls. Manage study budget through lifecycle and provide progress reports. Ensure studies are inspection-ready at all times. Support professional development of team members. Provide guidance and mentoring to less experienced colleagues. Lead non-drug project work and improvement projects.</t>
         </is>
       </c>
       <c r="P105" s="6" t="inlineStr">
         <is>
-          <t>Essential Skills/Experience University degree or equivalent in medical or biological sciences or discipline associated with clinical research. Proven project management experience and training. At least 7 years of clinical trial experience. At least 3 years of experience in global study leadership a</t>
+          <t>Essential Skills/Experience University degree or equivalent in medical or biological sciences or discipline associated with clinical research. Proven project management experience and training. At least 7 years of clinical trial experience. At least 3 years of experience in global study leadership and team leadership. Demonstrated clinical trial expertise in hematology and/or oncology. Extensive knowledge of ICH-GCP guidelines and clinical research regulatory requirements. Thorough understanding of the cross-functional clinical trial process. Strong strategic and critical thinking abilities. Proven skills in complex problem solving and decision-making. Strong abilities in establishing effective working relationships with senior stakeholders. Demonstrated abilities in mentoring. Excellent communication and interpersonal skills. Ability to manage multiple competing priorities. Experience in external provider oversight and management. Desirable Skills/Experience Advanced degree, masters level education or higher. Project management certification. 5 years of experience in global study leadership and team leadership. Significant hematology/oncology expertise. Expertise in different phases of clinical delivery. Experience with project management software solutions. Cell therapy/CAR-T experience. Global phase 3 study experience.</t>
         </is>
       </c>
       <c r="Q105" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions experience in sustainable finance, including climate, development, and/or nature finance, and the company's mission is to address global development challenges through strategic investments that promote sustainable and inclusive economic growth.</t>
+          <t>Although the company mentions dedication to sustainability, it is in the context of a broader company culture and not directly related to the job responsibilities, requirements, or skills. The job itself is focused on clinical trials and cell therapy, which does not fit into any of the specified ESG/sustainability profiles.</t>
         </is>
       </c>
       <c r="R105" s="2" t="inlineStr"/>
@@ -9934,12 +9959,12 @@
       </c>
       <c r="P106" s="6" t="inlineStr">
         <is>
-          <t>Proven experience in estimating, managing, and controlling personnel cost budgets, as well as in developing financial models and conducting economic evaluations of collective labor agreements. Strong negotiation and conflict management skills. Analytical mindset and practical problem-solving orienta</t>
+          <t>Proven experience in estimating, managing, and controlling personnel cost budgets, as well as in developing financial models and conducting economic evaluations of collective labor agreements. Strong negotiation and conflict management skills. Analytical mindset and practical problem-solving orientation. Excellent communication and influencing skills at all organizational levels.</t>
         </is>
       </c>
       <c r="Q106" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions impact investing, ESG, and sustainable development, which are key concepts in sustainable finance. The company's mission and values also align with sustainable finance principles.</t>
+          <t>The job description does not mention any ESG/sustainability topics, climate change, or environmental issues. The focus is on labor relations, law, and human resources, which does not fit any of the provided profiles.</t>
         </is>
       </c>
       <c r="R106" s="2" t="inlineStr"/>
@@ -10095,17 +10120,17 @@
       </c>
       <c r="O108" s="6" t="inlineStr">
         <is>
-          <t>To support BlackRock’s extensive Australian and global business through the provision of high quality and commercially focused legal advice. To interact with the broader BlackRock global community both in Australia and abroad, reflecting the global interconnectivity of our business. To ensure that BlackRock continues to be regarded by regulators and peers as a company with high compliance standards and strong legal acumen. Provide high quality and commercial legal advice to the Australian busine</t>
+          <t>To support BlackRock’s extensive Australian and global business through the provision of high quality and commercially focused legal advice. To interact with the broader BlackRock global community both in Australia and abroad, reflecting the global interconnectivity of our business. To ensure that BlackRock continues to be regarded by regulators and peers as a company with high compliance standards and strong legal acumen. Provide high quality and commercial legal advice to the Australian business on all aspects of asset management and investments. Act as a primary stakeholder in the product development process, fund registration, exchange admission processes, disclosure, distribution, and marketing. Engage with government, regulators, industry groups, and external counsel. Draft and negotiate contracts, including investment management agreements, investment platform agreements, distribution agreements, custody and administration agreements, and services agreements. Draft papers and present advice to internal stakeholders and committees.</t>
         </is>
       </c>
       <c r="P108" s="6" t="inlineStr">
         <is>
-          <t>Strong technical skills, including statutory and contractual interpretation, research and drafting. Proven ability to deliver high quality legal advice. Excellent verbal and written communication skills, including to confidently present to an audience. Ability to work autonomously and operate in a f</t>
+          <t>Strong technical skills, including statutory and contractual interpretation, research and drafting. Proven ability to deliver high quality legal advice. Excellent verbal and written communication skills, including to confidently present to an audience. Ability to work autonomously and operate in a fast-paced global environment with flexibility to adapt to change. An analytical mindset and ability to innovate and generate new ideas to solve complex problems. High levels of attention to detail and document management skills. Relationship management skills to effectively influence stakeholders and to manage competing stakeholder relationships and priorities.</t>
         </is>
       </c>
       <c r="Q108" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions 'sustainable finance practices' as one of the current and emerging trends and regulatory priorities, indicating a connection to ESG investing and sustainable finance.</t>
+          <t>The job description mentions 'sustainable finance practices' as one of the current and emerging trends and regulatory priorities, indicating a connection to ESG investing and sustainable finance.</t>
         </is>
       </c>
       <c r="R108" s="2" t="inlineStr">
@@ -10188,17 +10213,17 @@
       </c>
       <c r="O109" s="6" t="inlineStr">
         <is>
-          <t>Prioritize internal and external feedback to build clear and cohesive development roadmaps. Translate desired features into precise specifications for developers using documentation, mock-ups, or visual tools. Follow up on newly released features to ensure they work effectively in real operational settings. Strengthen customer communication around product updates, new features, and enhancements. Support digital product operations and internal improvement initiatives. Establish and improve workfl</t>
+          <t>Prioritize internal and external feedback to build clear and cohesive development roadmaps. Translate desired features into precise specifications for developers using documentation, mock-ups, or visual tools. Follow up on newly released features to ensure they work effectively in real operational settings. Strengthen customer communication around product updates, new features, and enhancements. Support digital product operations and internal improvement initiatives. Establish and improve workflows for proactively collecting user feedback. Document processes and product knowledge to ensure shared understanding across teams. Manage and maintain data pipelines; analyze business and regulatory-related datasets. Learn and apply maritime emissions regulations to ensure our digital processes and data structures meet compliance needs. Support teams and customers in ad hoc tasks, identifying opportunities for automation and efficiency. Act as a point of contact toward the internal IT organization for specifying and coordinating digital projects.</t>
         </is>
       </c>
       <c r="P109" s="6" t="inlineStr">
         <is>
-          <t>Ability to write and run SQL queries. Ability to read and understand Python code (C# familiarity is a plus). Experience analyzing data using APIs and a programming language, preferably Python. Familiarity with Git-based version control tools (Azure DevOps, GitHub). Understanding of Agile/Scrum or si</t>
+          <t>Ability to write and run SQL queries. Ability to read and understand Python code (C# familiarity is a plus). Experience analyzing data using APIs and a programming language, preferably Python. Familiarity with Git-based version control tools (Azure DevOps, GitHub). Understanding of Agile/Scrum or similar digital project methodologies. Interest in specialized emissions software, databases, or registry platforms.</t>
         </is>
       </c>
       <c r="Q109" s="6" t="inlineStr">
         <is>
-          <t>[carbon_markets] The job description mentions experience with maritime emissions regulations, carbon markets, and environmental financial products, which are all relevant to the carbon markets profile.</t>
+          <t>The job description mentions experience with maritime emissions regulations, carbon markets, and environmental financial products, which are all relevant to the carbon markets profile.</t>
         </is>
       </c>
       <c r="R109" s="2" t="inlineStr">
@@ -10281,7 +10306,7 @@
       </c>
       <c r="O110" s="6" t="inlineStr">
         <is>
-          <t>You’ll be at the forefront of our sales function, guiding customers through their home energy transition. You’ll convert inbound inquiries, proactively follow up on leads, and design technical solutions that meet customer needs while exceeding expectations. You’ll also play a key role in maintaining high compliance standards and identifying new business opportunities. Key Responsibilities: Lead Engagement, Follow-Up &amp; Conversion, Customer Support, Solution Design, Compliance &amp; Standards, Busines</t>
+          <t>You’ll be at the forefront of our sales function, guiding customers through their home energy transition. You’ll convert inbound inquiries, proactively follow up on leads, and design technical solutions that meet customer needs while exceeding expectations. You’ll also play a key role in maintaining high compliance standards and identifying new business opportunities. Key Responsibilities: Lead Engagement, Follow-Up &amp; Conversion, Customer Support, Solution Design, Compliance &amp; Standards, Business Development, CRM &amp; Reporting, Industry Presence, Team Collaboration</t>
         </is>
       </c>
       <c r="P110" s="6" t="inlineStr">
@@ -10291,7 +10316,7 @@
       </c>
       <c r="Q110" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions renewable energy solutions, heat pumps, solar panels, and carbon-neutral home energy solutions, which are all related to clean energy and environmental sustainability.</t>
+          <t>The job description mentions renewable energy solutions, heat pumps, solar panels, and carbon-neutral home energy solutions, which are all related to clean energy and environmental sustainability.</t>
         </is>
       </c>
       <c r="R110" s="2" t="inlineStr">
@@ -10384,7 +10409,7 @@
       </c>
       <c r="Q111" s="6" t="inlineStr">
         <is>
-          <t>[general_esg] The job description mentions sustainable development, climate change, and environmental health, which are related to ESG topics. Although the role is not explicitly focused on ESG, the context suggests that it may involve working on projects that contribute to sustainable development a</t>
+          <t>The job description mentions sustainable development, climate change, and environmental health, which are related to ESG topics. Although the role is not explicitly focused on ESG, the context suggests that it may involve working on projects that contribute to sustainable development and environmental health.</t>
         </is>
       </c>
       <c r="R111" s="2" t="inlineStr">
@@ -10477,7 +10502,7 @@
       </c>
       <c r="Q112" s="6" t="inlineStr">
         <is>
-          <t>[general_esg] The job description mentions working with teams focused on sustainable development, climate change, and environmental issues, which aligns with the general ESG profile.</t>
+          <t>The job description mentions working with teams focused on sustainable development, climate change, and environmental issues, which aligns with the general ESG profile.</t>
         </is>
       </c>
       <c r="R112" s="2" t="inlineStr">
@@ -10556,17 +10581,17 @@
       </c>
       <c r="O113" s="6" t="inlineStr">
         <is>
-          <t>Identify focus countries/locations, strategic partners, outward delegation itineraries, event formats; plan B2B/B2G meetings and prepare talking points &amp; press notes. Coordinate with Invest India, Chambers, Missions; build investor lists, outreach plans, and track conversion. Draft invitation, program scripts, and proceedings; prepare participation summaries. Prepare project/sector/infrastructure profiles, brochures/flyers, web &amp; social content; support monthly newsletters. Facilitate meetings w</t>
+          <t>Identify focus countries/locations, strategic partners, outward delegation itineraries, event formats; plan B2B/B2G meetings and prepare talking points &amp; press notes. Coordinate with Invest India, Chambers, Missions; build investor lists, outreach plans, and track conversion. Draft invitation, program scripts, and proceedings; prepare participation summaries. Prepare project/sector/infrastructure profiles, brochures/flyers, web &amp; social content; support monthly newsletters. Facilitate meetings with inward delegations; ensure documentation of minutes, outcomes, and actions for all delegations.</t>
         </is>
       </c>
       <c r="P113" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mandatory skill sets: Investor targeting &amp; engagement; event/roadshow planning; strong writing for talking points, invites, briefs, and press notes; comfort with collaboration tools; data-driven outreach tracking. Preferred skill sets: Quality &amp; timeliness of event concept notes; roadshow execution </t>
+          <t>Mandatory skill sets: Investor targeting &amp; engagement; event/roadshow planning; strong writing for talking points, invites, briefs, and press notes; comfort with collaboration tools; data-driven outreach tracking. Preferred skill sets: Quality &amp; timeliness of event concept notes; roadshow execution &amp; meeting conversions; quality of collaterals; completeness of proceedings reports; responsiveness to client instructions. Required Skills: Data Analysis</t>
         </is>
       </c>
       <c r="Q113" s="6" t="inlineStr">
         <is>
-          <t>[general_esg] The job description mentions working with clients on transformation in Government with a focus on Sustainability, Climate Change, and Environment, indicating a role related to ESG strategy and corporate sustainability.</t>
+          <t>The job description mentions working with clients on transformation in Government with a focus on Sustainability, Climate Change, and Environment, indicating a role related to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
       <c r="R113" s="2" t="inlineStr"/>
@@ -10645,7 +10670,7 @@
       </c>
       <c r="O114" s="6" t="inlineStr">
         <is>
-          <t>Research Leadership: Taking forward RAND Europe’s successful research track record in technology policy research, developing and leading a varied portfolio of research projects and expanding into new areas of work. Providing thought leadership on technology policy issues. Mentoring research staff and facilitating development of others' project management and methodological skills. Taking a leading role in ensuring that RAND Europe’s research has a positive impact within policy communities. Busin</t>
+          <t>Research Leadership: Taking forward RAND Europe’s successful research track record in technology policy research, developing and leading a varied portfolio of research projects and expanding into new areas of work. Providing thought leadership on technology policy issues. Mentoring research staff and facilitating development of others' project management and methodological skills. Taking a leading role in ensuring that RAND Europe’s research has a positive impact within policy communities. Business development: Contributing to the work of SET, through contributing to or supporting the delivery of research group target revenues and sales by securing funding for research and supporting others in doing so. Co-ordinating, managing and supporting a portfolio of business development initiatives including leading and supporting bid and proposal activity, often as multi-partner proposals. Consolidating and initiating networks and contacts with funders and collaborators in the biosecurity and wider biotechnology policy sector. Group and other responsibilities: Working with other team members and the Research Group Director to develop SET’s research and strategy. As a senior member of the team, setting a collegiate tone and contributing to the development and profile of the wider organisation. Leading on innovative ways to raise RAND Europe’s profile and communicate research findings to maximise impact.</t>
         </is>
       </c>
       <c r="P114" s="6" t="inlineStr">
@@ -10655,7 +10680,7 @@
       </c>
       <c r="Q114" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions biotechnology, biosecurity, and technology policy, which are related to environmental science and sustainability. Although the job is not directly focused on renewable energy or conservation, it is adjacent to the clean energy field and involves r</t>
+          <t>The job description mentions biotechnology, biosecurity, and technology policy, which are related to environmental science and sustainability. Although the job is not directly focused on renewable energy or conservation, it is adjacent to the clean energy field and involves research and policy development related to emerging technologies.</t>
         </is>
       </c>
       <c r="R114" s="2" t="inlineStr">
@@ -10742,7 +10767,7 @@
       </c>
       <c r="O115" s="6" t="inlineStr">
         <is>
-          <t>Během auditu trávíme spoustu času u klientů, kde pečlivě procházíme čísla a informace, které o sobě zveřejňují. Ověřujeme jejich pravdivost, aby byli v očích svých obchodních partnerů, akcionářů, věřitelů i veřejnosti důvěryhodní. Ze začátku budeš pracovat spolu se zkušenými kolegy, kteří ti všechno vysvětlí a k ruce dostaneš i counselora, který tě bude provádět nejen auditem, ale pomůže ti i s kariérním růstem. Postupem času poznáš firemní procesy a ovládneš české účetnictví i mezinárodní audit</t>
+          <t>Během auditu trávíme spoustu času u klientů, kde pečlivě procházíme čísla a informace, které o sobě zveřejňují. Ověřujeme jejich pravdivost, aby byli v očích svých obchodních partnerů, akcionářů, věřitelů i veřejnosti důvěryhodní. Ze začátku budeš pracovat spolu se zkušenými kolegy, kteří ti všechno vysvětlí a k ruce dostaneš i counselora, který tě bude provádět nejen auditem, ale pomůže ti i s kariérním růstem. Postupem času poznáš firemní procesy a ovládneš české účetnictví i mezinárodní auditorské a účetní standardy. Potkáš se se zástupci firem napříč odvětvími a naučíš se s nimi komunikovat. Časem se setkáš i s řediteli a členy boardů.</t>
         </is>
       </c>
       <c r="P115" s="6" t="inlineStr">
@@ -10752,7 +10777,7 @@
       </c>
       <c r="Q115" s="6" t="inlineStr">
         <is>
-          <t>[general_esg] The job description mentions experience with ESG (Environmental, Social, and Governance) and sustainability services, specifically Climate Change and Sustainability Services (CCaSS), which indicates a connection to ESG strategy and corporate sustainability.</t>
+          <t>The job description mentions experience with ESG (Environmental, Social, and Governance) and sustainability services, specifically Climate Change and Sustainability Services (CCaSS), which indicates a connection to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
       <c r="R115" s="2" t="inlineStr">
@@ -10835,7 +10860,7 @@
       </c>
       <c r="O116" s="6" t="inlineStr">
         <is>
-          <t>Během auditu trávíme spoustu času u klientů, kde pečlivě procházíme čísla a informace, které o sobě zveřejňují. Ověřujeme jejich pravdivost, aby byli v očích svých obchodních partnerů, akcionářů, věřitelů i veřejnosti důvěryhodní. Postupem času poznáš firemní procesy a ovládneš české účetnictví i mezinárodní auditorské a účetní standardy. Potkáš se se zástupci firem napříč odvětvími a naučíš se s nimi komunikovat. Časem se setkáš i s řediteli a členy boardů. Díky auditu nahlédneš do různých obla</t>
+          <t>Během auditu trávíme spoustu času u klientů, kde pečlivě procházíme čísla a informace, které o sobě zveřejňují. Ověřujeme jejich pravdivost, aby byli v očích svých obchodních partnerů, akcionářů, věřitelů i veřejnosti důvěryhodní. Postupem času poznáš firemní procesy a ovládneš české účetnictví i mezinárodní auditorské a účetní standardy. Potkáš se se zástupci firem napříč odvětvími a naučíš se s nimi komunikovat. Časem se setkáš i s řediteli a členy boardů. Díky auditu nahlédneš do různých oblastí firmy – od financí, účetnictví, daní až po oceňování a IT procesy.</t>
         </is>
       </c>
       <c r="P116" s="6" t="inlineStr">
@@ -10845,7 +10870,7 @@
       </c>
       <c r="Q116" s="6" t="inlineStr">
         <is>
-          <t>[general_esg] The job description mentions 'zprávy o udržitelnosti' (sustainability reports) and 'ESG odborníků' (ESG experts), indicating a connection to environmental, social, and governance topics.</t>
+          <t>The job description mentions 'zprávy o udržitelnosti' (sustainability reports) and 'ESG odborníků' (ESG experts), indicating a connection to environmental, social, and governance topics.</t>
         </is>
       </c>
       <c r="R116" s="2" t="inlineStr">
@@ -10924,7 +10949,7 @@
       </c>
       <c r="O117" s="6" t="inlineStr">
         <is>
-          <t>The work duties include conducting research within the project Human Rights for a Politically and Culturally Sustainable World, with a specific focus on the digital and green transition. Through theoretical and/or empirical studies, you will examine new standard threats to human rights, aiming to develop a model for what human rights need to be able to address in a new era. The work involves some travel – to conferences as well as potential field, study or archive trips – although the majority o</t>
+          <t>The work duties include conducting research within the project Human Rights for a Politically and Culturally Sustainable World, with a specific focus on the digital and green transition. Through theoretical and/or empirical studies, you will examine new standard threats to human rights, aiming to develop a model for what human rights need to be able to address in a new era. The work involves some travel – to conferences as well as potential field, study or archive trips – although the majority of the project will be carried out at the workplace. The position also includes some pedagogical training. In addition to research, the position includes teaching, supervision, and other teaching-related tasks amounting to 20% of the working time.</t>
         </is>
       </c>
       <c r="P117" s="6" t="inlineStr">
@@ -10934,7 +10959,7 @@
       </c>
       <c r="Q117" s="6" t="inlineStr">
         <is>
-          <t>[general_esg] The job description mentions human rights, digitisation, and the green transition, which are all related to environmental, social, and governance topics. The focus on human rights as a concept and practice to address risks linked to societal transformations and an uncertain future also</t>
+          <t>The job description mentions human rights, digitisation, and the green transition, which are all related to environmental, social, and governance topics. The focus on human rights as a concept and practice to address risks linked to societal transformations and an uncertain future also indicates relevance to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
       <c r="R117" s="2" t="inlineStr"/>
@@ -11023,7 +11048,7 @@
       </c>
       <c r="Q118" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions ESG, sustainability, and translating sustainability data into financial impact, which are key aspects of sustainable finance.</t>
+          <t>The job description mentions ESG, sustainability, and translating sustainability data into financial impact, which are key aspects of sustainable finance.</t>
         </is>
       </c>
       <c r="R118" s="2" t="inlineStr">
@@ -11116,7 +11141,7 @@
       </c>
       <c r="Q119" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions 'Sustainable Finance' as one of the possible rotation areas, and also mentions 'supporting the transition to a climate-resilient future by structuring loans so they are linked to achieving environmental, social and corporate governance (ESG) outcome</t>
+          <t>The job description mentions 'Sustainable Finance' as one of the possible rotation areas, and also mentions 'supporting the transition to a climate-resilient future by structuring loans so they are linked to achieving environmental, social and corporate governance (ESG) outcomes', indicating a focus on sustainable finance and ESG.</t>
         </is>
       </c>
       <c r="R119" s="2" t="inlineStr">
@@ -11199,17 +11224,17 @@
       </c>
       <c r="O120" s="6" t="inlineStr">
         <is>
-          <t>The Lead - Finance &amp; Accounts-SM is responsible for managing the financial and accounting operations of smart metering projects within AESL, overseeing activities such as bookkeeping, accounts payable, accounts receivable, and financial reporting. The role ensures the accurate and timely execution of financial processes while serving as the Controller of Accounts and Tax for the business. It drives operational efficiency, ensures compliance with financial regulations, and provides critical finan</t>
+          <t>The Lead - Finance &amp; Accounts-SM is responsible for managing the financial and accounting operations of smart metering projects within AESL, overseeing activities such as bookkeeping, accounts payable, accounts receivable, and financial reporting. The role ensures the accurate and timely execution of financial processes while serving as the Controller of Accounts and Tax for the business. It drives operational efficiency, ensures compliance with financial regulations, and provides critical financial insights to support decision-making, cost optimization, and sustainable business growth in smart metering operations.</t>
         </is>
       </c>
       <c r="P120" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP FICO, MM, FM Module, BI/BPC Tools, Advance Excel, SAP BG Module, Accounts knowledge, Control Over SAP FICO, MM, FM Module &amp; basic Knowledge SAP BI &amp; BPC Tools, Commercial acumen, Knowledge on Different VAT act, Income Tax Act, and update on Same, Strong interpersonal skills, Coordination skill, </t>
+          <t>SAP FICO, MM, FM Module, BI/BPC Tools, Advance Excel, SAP BG Module, Accounts knowledge, Control Over SAP FICO, MM, FM Module &amp; basic Knowledge SAP BI &amp; BPC Tools, Commercial acumen, Knowledge on Different VAT act, Income Tax Act, and update on Same, Strong interpersonal skills, Coordination skill, Good Team player, Communication Skill, Leadership qualities</t>
         </is>
       </c>
       <c r="Q120" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions smart metering projects, energy infrastructure, and power transmission, which are related to renewable energy and environmental science, making it a clean energy adjacent profile.</t>
+          <t>The job description mentions smart metering projects, energy infrastructure, and power transmission, which are related to renewable energy and environmental science, making it a clean energy adjacent profile.</t>
         </is>
       </c>
       <c r="R120" s="2" t="inlineStr">
@@ -11280,17 +11305,17 @@
       </c>
       <c r="O121" s="6" t="inlineStr">
         <is>
-          <t>The primary role is to make immediate, direct contributions to enhancing our clients’ competitive position and performance in ways that are distinctive, innovative, and sustainable. The SAP EHSM professional will be responsible for tasks related to liaise with customer, understand business processes, apply analytical skills, act as a trusted advisor in the business and technology consulting of SAP S/4HANA Product Compliance and classical Product Safety solution, also experience in SAP EHSM – Inc</t>
+          <t>The primary role is to make immediate, direct contributions to enhancing our clients’ competitive position and performance in ways that are distinctive, innovative, and sustainable. The SAP EHSM professional will be responsible for tasks related to liaise with customer, understand business processes, apply analytical skills, act as a trusted advisor in the business and technology consulting of SAP S/4HANA Product Compliance and classical Product Safety solution, also experience in SAP EHSM – Incident Management, Risk Assessment, Environment Management, Audit Management, Management of Change and Master data management.</t>
         </is>
       </c>
       <c r="P121" s="6" t="inlineStr">
         <is>
-          <t>SAP S/4HANA EHSM, Good communication skill to collaborate with business process owners, project team and other stakeholders / vendors, Good proficiency in Industrial Health &amp; Safety practices and business knowledge like OSHA regulations and ability to understand global regulatory safety standards to</t>
+          <t>SAP S/4HANA EHSM, Good communication skill to collaborate with business process owners, project team and other stakeholders / vendors, Good proficiency in Industrial Health &amp; Safety practices and business knowledge like OSHA regulations and ability to understand global regulatory safety standards to interact with the customer and business process owners, Proficiency in SAP Sustainability modules like Sustainability Footprint Management, Sustainability Control Tower, SAP Green Token are an added advantage</t>
         </is>
       </c>
       <c r="Q121" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[general_esg] The job description mentions experience in SAP EHSM, Sustainability Footprint Management, Sustainability Control Tower, and SAP Green Token, which are related to environmental sustainability and ESG. The role also involves working with clients to enhance their competitive position and </t>
+          <t>The job description mentions experience in SAP EHSM, Sustainability Footprint Management, Sustainability Control Tower, and SAP Green Token, which are related to environmental sustainability and ESG. The role also involves working with clients to enhance their competitive position and performance in a sustainable way, which aligns with the general ESG profile.</t>
         </is>
       </c>
       <c r="R121" s="2" t="inlineStr"/>
@@ -11357,17 +11382,17 @@
       </c>
       <c r="O122" s="6" t="inlineStr">
         <is>
-          <t>Individuals responsible for In-business Risk Management oversee risk identification, assessment, measurement, monitoring, and reporting. They design and implement risk mitigation actions and focus on managing one or more risks in support of business activities. Key Responsibilities: Design and lead projects to execute control enhancements over processes. Document processes developed, actions taken and track matters to ensure resolution. Collaborate with ICRM Sanctions regularly to ensure correct</t>
+          <t>Individuals responsible for In-business Risk Management oversee risk identification, assessment, measurement, monitoring, and reporting. They design and implement risk mitigation actions and focus on managing one or more risks in support of business activities. Key Responsibilities: Design and lead projects to execute control enhancements over processes. Document processes developed, actions taken and track matters to ensure resolution. Collaborate with ICRM Sanctions regularly to ensure correct interpretation and application of sanctions compliance and policy requirements. Liaise with Compliance Assurance and Internal Audit to facilitate resolution of any issues (or corrective actions plans) identified. Maintain oversight through review of metrics, monitoring of activity, and tracking of corrective action plans. Prepare presentations to update senior management and various governance committees on developments, emerging risks, control issues, and enhancements. Ensure the maintenance of a robust Manager’s Control Assessment (MCA) in compliance with the Citi’s Risk Policy. Assess high-risk clients with significant sanctions exposure, including the write up/drafting of internal sanctions risk memos for senior management engagement. Design and develop process plans, notes or guidelines documents. Support any Internal Audit or ICRM Sanctions inquiries and ensure that all audit requests are timely and appropriately provided.</t>
         </is>
       </c>
       <c r="P122" s="6" t="inlineStr">
         <is>
-          <t>Essential: Strong proficiency with Microsoft Suite, excellent organizational and communication skills. Desirable: Project management capabilities, strategic and/or analytical thinking skills. Most Relevant Skills: Analytical Thinking, Business Acumen, Constructive Debate, Escalation Management, Issu</t>
+          <t>Essential: Strong proficiency with Microsoft Suite, excellent organizational and communication skills. Desirable: Project management capabilities, strategic and/or analytical thinking skills. Most Relevant Skills: Analytical Thinking, Business Acumen, Constructive Debate, Escalation Management, Issue Management, Policy and Procedure, Policy and Regulation, Risk Controls and Monitors, Risk Identification and Assessment, Stakeholder Management.</t>
         </is>
       </c>
       <c r="Q122" s="6" t="inlineStr">
         <is>
-          <t>[carbon_markets] The job description mentions experience with maritime emissions regulations, carbon markets, and environmental financial products, which are all relevant to the carbon markets profile.</t>
+          <t>The job description does not mention any specific ESG/sustainability topics, climate risk, or sustainable finance. The role is focused on risk management, compliance, and sanctions, which does not fit into any of the specified profiles.</t>
         </is>
       </c>
       <c r="R122" s="2" t="inlineStr"/>
@@ -11439,12 +11464,12 @@
       </c>
       <c r="P123" s="6" t="inlineStr">
         <is>
-          <t>Strong hands-on experience with: ETL / ELT Cloud platforms (AWS, Snowflake , Open source), Databricks, Open Source, SAP Analytics (BW, HANA, S/4) Data Warehousing and, Strong grasp of: Data modeling and semantic layers, Analytics performance and scalability, Integration patterns across heterogeneous</t>
+          <t>Strong hands-on experience with: ETL / ELT Cloud platforms (AWS, Snowflake , Open source), Databricks, Open Source, SAP Analytics (BW, HANA, S/4) Data Warehousing and, Strong grasp of: Data modeling and semantic layers, Analytics performance and scalability, Integration patterns across heterogeneous source systems, Experience with BI platforms (Power BI, Looker, Tableau, Qlik, etc.)</t>
         </is>
       </c>
       <c r="Q123" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions 'intelligent climate and energy solutions' and ' Carrier Global Corporation' which is a company that provides solutions for climate and energy, indicating a connection to renewable energy and environmental science.</t>
+          <t>The job description mentions 'intelligent climate and energy solutions' and ' Carrier Global Corporation' which is a company that provides solutions for climate and energy, indicating a connection to renewable energy and environmental science.</t>
         </is>
       </c>
       <c r="R123" s="2" t="inlineStr"/>
@@ -11511,17 +11536,17 @@
       </c>
       <c r="O124" s="6" t="inlineStr">
         <is>
-          <t>Develop and refine the test strategy and test planning for embedded systems. Collaborate with software testers and developers to expand and improve test automation and testing strategies. Execute test cases, analyze results, and clearly document findings. Design and execute advanced system tests (both manual and automated). Develop test environments and tools for hardware-near testing. Troubleshoot and analyze complex system failures. Ensure testability during the design phase through requiremen</t>
+          <t>Develop and refine the test strategy and test planning for embedded systems. Collaborate with software testers and developers to expand and improve test automation and testing strategies. Execute test cases, analyze results, and clearly document findings. Design and execute advanced system tests (both manual and automated). Develop test environments and tools for hardware-near testing. Troubleshoot and analyze complex system failures. Ensure testability during the design phase through requirements review and technical guidance. Lead and support junior testers. Collaborate with development, product management, and quality teams to ensure quality throughout the development lifecycle. Report test results, risks, and improvement suggestions to stakeholders.</t>
         </is>
       </c>
       <c r="P124" s="6" t="inlineStr">
         <is>
-          <t>RTOS, microcontrollers, embedded Linux, communication protocols (e.g., Modbus, I2C), test automation using tools such as Python, Robot Framework, or similar, hardware-near development, troubleshooting, CI/CD, version control (e.g., Git, Jenkins, Azure DevOps), SCRUM, test plan design, test case exec</t>
+          <t>RTOS, microcontrollers, embedded Linux, communication protocols (e.g., Modbus, I2C), test automation using tools such as Python, Robot Framework, or similar, hardware-near development, troubleshooting, CI/CD, version control (e.g., Git, Jenkins, Azure DevOps), SCRUM, test plan design, test case execution, strong team player, collaborative mindset, problem-solving ability, strategic and analytical skills, committed to quality and technical excellence, excellent verbal and written communication skills.</t>
         </is>
       </c>
       <c r="Q124" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions 'sustainable climate solutions' and 'energy-efficient solutions for industrial environments', which indicates a focus on environmental sustainability and renewable energy. Although it's not a direct match with renewable energy, the company's produ</t>
+          <t>The job description mentions 'sustainable climate solutions' and 'energy-efficient solutions for industrial environments', which indicates a focus on environmental sustainability and renewable energy. Although it's not a direct match with renewable energy, the company's products and mission are closely related to the clean energy sector.</t>
         </is>
       </c>
       <c r="R124" s="2" t="inlineStr"/>
@@ -11610,7 +11635,7 @@
       </c>
       <c r="Q125" s="6" t="inlineStr">
         <is>
-          <t>[general_esg] The job description mentions ESG, sustainability, and supply chain concepts, indicating a focus on environmental, social, and governance topics. The role involves working with ESG data, conducting QA reviews, and supporting the improvement of internal processes, which aligns with the g</t>
+          <t>The job description mentions ESG, sustainability, and supply chain concepts, indicating a focus on environmental, social, and governance topics. The role involves working with ESG data, conducting QA reviews, and supporting the improvement of internal processes, which aligns with the general ESG profile.</t>
         </is>
       </c>
       <c r="R125" s="2" t="inlineStr">
@@ -11703,7 +11728,7 @@
       </c>
       <c r="Q126" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions supporting the transition to a climate-resilient future, structuring loans linked to achieving environmental, social and corporate governance (ESG) outcomes, and a rotation in Sustainable Finance.</t>
+          <t>The job description mentions supporting the transition to a climate-resilient future, structuring loans linked to achieving environmental, social and corporate governance (ESG) outcomes, and a rotation in Sustainable Finance.</t>
         </is>
       </c>
       <c r="R126" s="2" t="inlineStr">
@@ -11786,7 +11811,7 @@
       </c>
       <c r="O127" s="6" t="inlineStr">
         <is>
-          <t>This is a versatile, high-impact role for someone who wants to make a real difference at an early-stage climate-tech company. As Business Development Manager, you will work across two of BBB's most important growth areas: securing funding through grants and supporting commercial sales activity to agricultural, utilities, and industrial organisations. You will identify and write applications, help shape proposals, coordinate inputs, and manage submissions, while also supporting the commercial tea</t>
+          <t>This is a versatile, high-impact role for someone who wants to make a real difference at an early-stage climate-tech company. As Business Development Manager, you will work across two of BBB's most important growth areas: securing funding through grants and supporting commercial sales activity to agricultural, utilities, and industrial organisations. You will identify and write applications, help shape proposals, coordinate inputs, and manage submissions, while also supporting the commercial team with sales outreach, customer enquiries, lead follow-up, CRM management, and event representation.</t>
         </is>
       </c>
       <c r="P127" s="6" t="inlineStr">
@@ -11796,7 +11821,7 @@
       </c>
       <c r="Q127" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[clean_energy_adjacent] The job description mentions biochar, carbon removal, regenerative agriculture, and climate-tech, which are all related to renewable energy and environmental science. The company's mission is to improve soil health and remove carbon from the atmosphere, which aligns with the </t>
+          <t>The job description mentions biochar, carbon removal, regenerative agriculture, and climate-tech, which are all related to renewable energy and environmental science. The company's mission is to improve soil health and remove carbon from the atmosphere, which aligns with the clean energy adjacent profile.</t>
         </is>
       </c>
       <c r="R127" s="2" t="inlineStr">
@@ -11885,7 +11910,7 @@
       </c>
       <c r="Q128" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions utility-scale solar projects in Southern Africa, renewable energy transactions, and impact investment funds, which are all related to clean energy and environmental sustainability.</t>
+          <t>The job description mentions utility-scale solar projects in Southern Africa, renewable energy transactions, and impact investment funds, which are all related to clean energy and environmental sustainability.</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr">
@@ -11956,7 +11981,7 @@
       </c>
       <c r="O129" s="6" t="inlineStr">
         <is>
-          <t>The Regional Service Delivery Manager - Business Services supports the Assistant Chief Officer Business Services and the Regional Leadership Team with the assessment of operational capability and capacity needs within the region, delivery of support services to members at a Regional level, including the development of a strategically aligned annual operational plan and budget for the Region that includes operational workforce and asset (facility, fleet and equipment) planning, infrastructure pla</t>
+          <t>The Regional Service Delivery Manager - Business Services supports the Assistant Chief Officer Business Services and the Regional Leadership Team with the assessment of operational capability and capacity needs within the region, delivery of support services to members at a Regional level, including the development of a strategically aligned annual operational plan and budget for the Region that includes operational workforce and asset (facility, fleet and equipment) planning, infrastructure planning and delivery, information management and records management, resource allocation support and monitoring processes. The role also supports the ACO Business Services with ensuring the region has in place both Business Continuity and Service Continuity plans and the coordination of risk and issues management with VICSES Business Partners at the regional level. The role provides leadership to business support staff, collaborates closely with internal and external stakeholders, and represents VICSES in regional forums. It drives continuous improvement, supports change initiatives, and ensures that service delivery functions enable volunteers and operational staff to focus on emergency response outcomes.</t>
         </is>
       </c>
       <c r="P129" s="2" t="inlineStr">
@@ -11964,9 +11989,9 @@
           <t>Requires experience in business operations, strategic planning, budget management, risk management, and team leadership.</t>
         </is>
       </c>
-      <c r="Q129" s="2" t="inlineStr">
-        <is>
-          <t>VICSES is a volunteer-based emergency service that focuses on building community resilience through preparedness and response to emergencies.</t>
+      <c r="Q129" s="6" t="inlineStr">
+        <is>
+          <t>The job description does not mention any ESG/sustainability topics, climate risk, sustainable finance, carbon markets, EU Taxonomy, or other related keywords. The role is focused on emergency service delivery and management, which does not fit any of the specified profiles.</t>
         </is>
       </c>
       <c r="R129" s="2" t="inlineStr"/>
@@ -12033,7 +12058,7 @@
       </c>
       <c r="O130" s="6" t="inlineStr">
         <is>
-          <t>You will own the end-to-end product and commercialisation agenda and bring it to life through action, influence and delivery. This includes: Scanning the market relentlessly to identify smart, connected and solution-based water opportunities across residential, commercial and institutional segments. Deeply understanding customers, uncovering real pain points through research, interviews and partner engagement, and validating where value truly lies. Designing compelling commercial models, includi</t>
+          <t>You will own the end-to-end product and commercialisation agenda and bring it to life through action, influence and delivery. This includes: Scanning the market relentlessly to identify smart, connected and solution-based water opportunities across residential, commercial and institutional segments. Deeply understanding customers, uncovering real pain points through research, interviews and partner engagement, and validating where value truly lies. Designing compelling commercial models, including pricing, installation, service, maintenance and subscription or recurring revenue streams. Shaping and optimising the portfolio, making clear calls on what to scale, improve, pivot or exit. Building and owning a multi-year roadmap that balances near-term revenue with long-term platform and ecosystem bets. Leading go-to-market strategy and execution, personally driving value propositions, positioning, solution narratives and sales enablement. Defining operating models that ensure solutions can be sold, installed, supported and maintained at scale. Applying a constructive lens to ways of working, bringing clarity, structure and commercial discipline to complex, ambiguous problems. Acting as a dynamic connector, building strong relationships across Innovation, Technology, Finance, Supply Chain and Sales.</t>
         </is>
       </c>
       <c r="P130" s="6" t="inlineStr">
@@ -12043,7 +12068,7 @@
       </c>
       <c r="Q130" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions 'sustainable water solutions', 'smart and connected water solutions', and 'water opportunities', indicating a focus on environmental sustainability and water management, which aligns with the clean energy adjacent profile.</t>
+          <t>The job description mentions 'sustainable water solutions', 'smart and connected water solutions', and 'water opportunities', indicating a focus on environmental sustainability and water management, which aligns with the clean energy adjacent profile.</t>
         </is>
       </c>
       <c r="R130" s="2" t="inlineStr"/>
@@ -12110,7 +12135,7 @@
       </c>
       <c r="O131" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Als Project- en Procesmanager binnen Royal Smit en Zoon ben je verantwoordelijk voor het initiëren, ontwikkelen en realiseren van investeringsprojecten en contract manufacturing-activiteiten. Je zorgt voor een veilige, efficiënte en toekomstbestendige productiecapaciteit, technische integriteit van assets en naleving van QESH- en procesveiligheidsnormen. Je ondersteunt hierbij de productielocaties in Weesp en Amersfoort en levert een belangrijke bijdrage aan de strategische ontwikkeling van het </t>
+          <t>Als Project- en Procesmanager binnen Royal Smit en Zoon ben je verantwoordelijk voor het initiëren, ontwikkelen en realiseren van investeringsprojecten en contract manufacturing-activiteiten. Je zorgt voor een veilige, efficiënte en toekomstbestendige productiecapaciteit, technische integriteit van assets en naleving van QESH- en procesveiligheidsnormen. Je ondersteunt hierbij de productielocaties in Weesp en Amersfoort en levert een belangrijke bijdrage aan de strategische ontwikkeling van het productie- en assetportfolio van Royal Smit &amp; Zoon.</t>
         </is>
       </c>
       <c r="P131" s="6" t="inlineStr">
@@ -12120,7 +12145,7 @@
       </c>
       <c r="Q131" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions 'duurzame grondstoffen' (sustainable raw materials) and 'de waardeketen van de leerindustrie verduurzamen' (sustaining the leather industry's value chain), indicating a focus on environmental sustainability, and 'procesveiligheid' (process safety)</t>
+          <t>The job description mentions 'duurzame grondstoffen' (sustainable raw materials) and 'de waardeketen van de leerindustrie verduurzamen' (sustaining the leather industry's value chain), indicating a focus on environmental sustainability, and 'procesveiligheid' (process safety) and 'technische integriteit' (technical integrity), which are relevant to the clean energy adjacent profile.</t>
         </is>
       </c>
       <c r="R131" s="2" t="inlineStr"/>
@@ -12187,7 +12212,7 @@
       </c>
       <c r="O132" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">This role is central to advancing NORCAP’s commitment to climate action, peace, democracy, and human rights through strategic leadership, policy influence, and effective programme delivery. You will lead one of NORCAP’s most forward‑looking portfolios—where strategic leadership, programme quality, and policy influence come together. You will guide a strong team, shape partnerships, and steer a portfolio that has the mandate to rethink how aid can better address climate‑related risks, strengthen </t>
+          <t>This role is central to advancing NORCAP’s commitment to climate action, peace, democracy, and human rights through strategic leadership, policy influence, and effective programme delivery. You will lead one of NORCAP’s most forward‑looking portfolios—where strategic leadership, programme quality, and policy influence come together. You will guide a strong team, shape partnerships, and steer a portfolio that has the mandate to rethink how aid can better address climate‑related risks, strengthen peaceful societies, and uphold democratic space.</t>
         </is>
       </c>
       <c r="P132" s="6" t="inlineStr">
@@ -12197,7 +12222,7 @@
       </c>
       <c r="Q132" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions 'climate action', 'climate change', and 'climate‑related risks', indicating a strong focus on climate risk management and mitigation.</t>
+          <t>The job description mentions 'climate action', 'climate change', and 'climate‑related risks', indicating a strong focus on climate risk management and mitigation.</t>
         </is>
       </c>
       <c r="R132" s="2" t="inlineStr"/>
@@ -12264,7 +12289,7 @@
       </c>
       <c r="O133" s="6" t="inlineStr">
         <is>
-          <t>Algorithm Development &amp; Signal Processing: Lead the design, implementation, and optimization of ECG signal‑processing algorithms. Develop robust algorithms suitable for embedded systems. Analyze diverse ECG datasets to ensure algorithm reliability. Conduct algorithm performance benchmarking and validation. Software Engineering &amp; Design Transfer: Implement algorithms in production-quality code and support Design Transfer. Cross-functional &amp; Technical Collaboration: Collaborate with internal and e</t>
+          <t>Algorithm Development &amp; Signal Processing: Lead the design, implementation, and optimization of ECG signal‑processing algorithms. Develop robust algorithms suitable for embedded systems. Analyze diverse ECG datasets to ensure algorithm reliability. Conduct algorithm performance benchmarking and validation. Software Engineering &amp; Design Transfer: Implement algorithms in production-quality code and support Design Transfer. Cross-functional &amp; Technical Collaboration: Collaborate with internal and external partners. Quality, Compliance &amp; Documentation: Develop and maintain detailed documentation and ensure compliance with regulatory standards. Support, Debugging &amp; Continuous Improvement: Support troubleshooting and drive continuous improvement initiatives.</t>
         </is>
       </c>
       <c r="P133" s="6" t="inlineStr">
@@ -12274,7 +12299,7 @@
       </c>
       <c r="Q133" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions ESG, sustainability, and translating sustainability data into financial impact, which are key aspects of sustainable finance.</t>
+          <t>The job description does not explicitly mention ESG, sustainability, climate risk, or other related topics. While the company mentions 'combat climate change' in its description, this is not directly related to the job responsibilities or requirements.</t>
         </is>
       </c>
       <c r="R133" s="2" t="inlineStr"/>
@@ -12353,17 +12378,17 @@
       </c>
       <c r="O134" s="6" t="inlineStr">
         <is>
-          <t>The carbon removal market is at an inflection point. Buyers are becoming more sophisticated, the supply side is maturing, and the conversations shaping this market - about quality, integrity, and scale - are happening right now. Carbonfuture sits at the center of those conversations, and we need someone who can make sure our voice is heard. This is a hands-on writing role. You'll own Carbonfuture's editorial output, from content to sharp thought leadership and press outreach. You'll help our exp</t>
+          <t>The carbon removal market is at an inflection point. Buyers are becoming more sophisticated, the supply side is maturing, and the conversations shaping this market - about quality, integrity, and scale - are happening right now. Carbonfuture sits at the center of those conversations, and we need someone who can make sure our voice is heard. This is a hands-on writing role. You'll own Carbonfuture's editorial output, from content to sharp thought leadership and press outreach. You'll help our experts show up well at events and in interviews. And you'll develop the formats that keep Carbonfuture at the center of the conversation.</t>
         </is>
       </c>
       <c r="P134" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exceptional written English — you write with the fluency and precision of a native speaker, across formats and audiences. Strong editorial judgement: you know and love to tinker with what makes a story work, and what makes it fall flat. Ability to translate complex, technical topics into compelling </t>
+          <t>Exceptional written English — you write with the fluency and precision of a native speaker, across formats and audiences. Strong editorial judgement: you know and love to tinker with what makes a story work, and what makes it fall flat. Ability to translate complex, technical topics into compelling narratives for non-expert audiences. Comfortable working cross-functionally — extracting insight from busy subject-matter experts and turning it into content without slowing anyone down. Self-directed and organized, able to manage multiple content streams in parallel</t>
         </is>
       </c>
       <c r="Q134" s="6" t="inlineStr">
         <is>
-          <t>[carbon_markets] The job description mentions carbon removal, carbon markets, and durable carbon removal, which are all related to carbon markets. The company, Carbonfuture, provides tools and services for carbon removal, which further supports this classification.</t>
+          <t>The job description mentions carbon removal, carbon markets, and durable carbon removal, which are all related to carbon markets. The company, Carbonfuture, provides tools and services for carbon removal, which further supports this classification.</t>
         </is>
       </c>
       <c r="R134" s="2" t="inlineStr">
@@ -12456,7 +12481,7 @@
       </c>
       <c r="Q135" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions 'sustainable finance' as one of the DCM products, indicating a focus on environmental, social, or governance topics.</t>
+          <t>The job description mentions 'sustainable finance' as one of the DCM products, indicating a focus on environmental, social, or governance topics.</t>
         </is>
       </c>
       <c r="R135" s="2" t="inlineStr">
@@ -12527,7 +12552,7 @@
       </c>
       <c r="O136" s="6" t="inlineStr">
         <is>
-          <t>You provide spatial and statistical support in the assembly and pre-processing of a wide variety of maternal health indicators from household survey data, such as Demographic and Health Surveys. You offer spatial and statistical support in the assembly and pre-processing of health indicators based on environment, climate, population and infrastructure data from open data portals. You conduct geospatial modelling and analyses to examine the variation of maternal health indicators across space and</t>
+          <t>You provide spatial and statistical support in the assembly and pre-processing of a wide variety of maternal health indicators from household survey data, such as Demographic and Health Surveys. You offer spatial and statistical support in the assembly and pre-processing of health indicators based on environment, climate, population and infrastructure data from open data portals. You conduct geospatial modelling and analyses to examine the variation of maternal health indicators across space and time. You interpret spatial and temporal patterns in maternal health indicators. You apply related statistical and advanced spatial analyses to determine and understand maternal health vulnerability in urban areas.</t>
         </is>
       </c>
       <c r="P136" s="6" t="inlineStr">
@@ -12537,7 +12562,7 @@
       </c>
       <c r="Q136" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job involves geospatial analysis of maternal health indicators, which is related to environmental science and public health, and the company is involved in public health research and service delivery, which is adjacent to the clean energy and environmental science field.</t>
+          <t>The job involves geospatial analysis of maternal health indicators, which is related to environmental science and public health, and the company is involved in public health research and service delivery, which is adjacent to the clean energy and environmental science field.</t>
         </is>
       </c>
       <c r="R136" s="2" t="inlineStr"/>
@@ -12616,7 +12641,7 @@
       </c>
       <c r="O137" s="6" t="inlineStr">
         <is>
-          <t>The role will be responsible for supporting the assessment, design and implementation of the Global ESG reporting control framework and will be required to collaborate cross functionally. The role will specifically support the alignment of the ESG control framework with the Global Finance control framework. This will include the integration with the Novartis 3LOD model, which will require collaboration with the Financial Controls and Compliance team. Major accountabilities include: monitoring th</t>
+          <t>The role will be responsible for supporting the assessment, design and implementation of the Global ESG reporting control framework and will be required to collaborate cross functionally. The role will specifically support the alignment of the ESG control framework with the Global Finance control framework. This will include the integration with the Novartis 3LOD model, which will require collaboration with the Financial Controls and Compliance team. Major accountabilities include: monitoring the internal control framework over ESG reporting, supporting the uplift of the ESG reporting control framework, maintaining the accuracy of the ESG reporting RACM and RACI, supporting areas of priority and focus, driving process deep-dives to identify process-control gaps, overseeing definition and implementation of solutions to enhance internal controls assurance, supporting assurance readiness, roadmap to reasonable assurance, supporting process/systems control improvement, automation, and standardization, monitoring process changes, and continuously assessing the impact of process changes on control environment, risk and defining mitigating actions to ensure reliable processes and systems with in-built controls.</t>
         </is>
       </c>
       <c r="P137" s="6" t="inlineStr">
@@ -12626,7 +12651,7 @@
       </c>
       <c r="Q137" s="6" t="inlineStr">
         <is>
-          <t>[general_esg] The job description mentions ESG (Environmental Social Governance) risk and controls, ESG reporting, and ESG control framework, which are all related to environmental, social, and governance topics, indicating a strong fit with the general ESG profile.</t>
+          <t>The job description mentions ESG (Environmental Social Governance) risk and controls, ESG reporting, and ESG control framework, which are all related to environmental, social, and governance topics, indicating a strong fit with the general ESG profile.</t>
         </is>
       </c>
       <c r="R137" s="2" t="inlineStr">
@@ -12717,9 +12742,9 @@
           <t>Analytical skills, Effective verbal and written communication skills, Experience with process improvements, Experience with cross-functional and cross-regional process initiatives, Familiarity with EY and/or global delivery models</t>
         </is>
       </c>
-      <c r="Q138" s="2" t="inlineStr">
-        <is>
-          <t>The position is within the audit service line at EY GDS Assurance, contributing to climate change, ESG, sustainability, and finance practices.</t>
+      <c r="Q138" s="6" t="inlineStr">
+        <is>
+          <t>The job description does not mention any specific ESG/sustainability topics, climate risk, sustainable finance, carbon markets, EU Taxonomy, or clean energy. The focus is on process improvements, audit delivery, and assurance services, which are not directly related to environmental, social, or governance topics.</t>
         </is>
       </c>
       <c r="R138" s="2" t="inlineStr">
@@ -12802,7 +12827,7 @@
       </c>
       <c r="O139" s="6" t="inlineStr">
         <is>
-          <t>Lead end-to-end change management activities across programs of work, supporting digital and business transformation initiatives, partnering with subject matter experts to plan, coordinate and deliver successful change outcomes. Design and deliver targeted training solutions including training needs analysis, planning, and development of engaging learning activities aligned with adult learning principles and delivered in partnership with the Learning &amp; Development team. Manage change and communi</t>
+          <t>Lead end-to-end change management activities across programs of work, supporting digital and business transformation initiatives, partnering with subject matter experts to plan, coordinate and deliver successful change outcomes. Design and deliver targeted training solutions including training needs analysis, planning, and development of engaging learning activities aligned with adult learning principles and delivered in partnership with the Learning &amp; Development team. Manage change and communications delivery by implementing structured change and communication plans for technology-enabled initiatives, while proactively identifying and addressing risks or issues that may impact outcomes. Provide expert change advice and solutions to stakeholders, ensuring digital initiatives align with the City’s strategic priorities. Empower leaders to lead change effectively by coaching them to plan key conversations and deliver engaging information sessions, presentations, and change communications. Create impactful reports, briefings and presentations to engage stakeholders and support successful change adoption. Monitor risks and track key indicators, identifying and escalating issues early to keep change initiatives on track.</t>
         </is>
       </c>
       <c r="P139" s="6" t="inlineStr">
@@ -12812,7 +12837,7 @@
       </c>
       <c r="Q139" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions 'intelligent climate and energy solutions' and ' Carrier Global Corporation' which is a company that provides solutions for climate and energy, indicating a connection to renewable energy and environmental science.</t>
+          <t>The job description does not mention any specific ESG/sustainability topics, and the mention of 'sustainability' in the company description is in the context of general business operations, not environmental or social sustainability.</t>
         </is>
       </c>
       <c r="R139" s="2" t="inlineStr">
@@ -12895,7 +12920,7 @@
       </c>
       <c r="O140" s="6" t="inlineStr">
         <is>
-          <t>Test Strategy &amp; Execution: Define and execute system validation and integration test plans for Analog Devices' SoCs running Zephyr RTOS and embedded Linux. Build test cases covering functional correctness, corner cases, performance, power mode transitions, and boot sequence validation across virtual prototyping, emulation, and post-silicon environments. Establish test coverage metrics, pass/fail criteria, and quality gates for release milestones. CI/CD &amp; Test Infrastructure: Architect and mainta</t>
+          <t>Test Strategy &amp; Execution: Define and execute system validation and integration test plans for Analog Devices' SoCs running Zephyr RTOS and embedded Linux. Build test cases covering functional correctness, corner cases, performance, power mode transitions, and boot sequence validation across virtual prototyping, emulation, and post-silicon environments. Establish test coverage metrics, pass/fail criteria, and quality gates for release milestones. CI/CD &amp; Test Infrastructure: Architect and maintain CI/CD pipelines using GitHub Actions for automated build, test, and regression workflows across Zephyr and Linux targets. Define the test framework strategy (e.g., Zephyr Twister, custom frameworks, or hybrid approaches) and integrate static analysis, code coverage, and test reporting into CI/CD workflows. Debugging &amp; Root-Cause Analysis: Lead cross-domain debugging spanning hardware, firmware, RTOS, BSP, using debug tools, trace utilities, and logs. Collaborate with firmware, driver, and bare-metal test teams to resolve issues and refine test methodologies. Team Leadership: Mentor engineers on test methodologies and debugging best practices. Document findings and present status and risks to stakeholders.</t>
         </is>
       </c>
       <c r="P140" s="6" t="inlineStr">
@@ -12905,7 +12930,7 @@
       </c>
       <c r="Q140" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions 'sustainable climate solutions' and 'energy-efficient solutions for industrial environments', which indicates a focus on environmental sustainability and renewable energy. Although it's not a direct match with renewable energy, the company's produ</t>
+          <t>The job description does not mention any specific ESG/sustainability topics, climate change mitigation, or environmental sustainability. Although the company description mentions 'combat climate change', it is not directly related to the job responsibilities, requirements, or skills.</t>
         </is>
       </c>
       <c r="R140" s="2" t="inlineStr">
@@ -12993,12 +13018,12 @@
       </c>
       <c r="P141" s="6" t="inlineStr">
         <is>
-          <t>Experience and expertise in one or more of the six categories, including Monitoring, Evaluation and Learning, Agriculture, Food/nutrition and Water Security, Climate Change and Disaster Risk Reduction, Communications and Creatives, Program and Investment Design, and Gender, Disability, Equity and So</t>
+          <t>Experience and expertise in one or more of the six categories, including Monitoring, Evaluation and Learning, Agriculture, Food/nutrition and Water Security, Climate Change and Disaster Risk Reduction, Communications and Creatives, Program and Investment Design, and Gender, Disability, Equity and Social Inclusion.</t>
         </is>
       </c>
       <c r="Q141" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions climate change, disaster risk reduction, and climate resilience, which are all relevant to the climate risk profile.</t>
+          <t>The job description mentions climate change, disaster risk reduction, and climate resilience, which are all relevant to the climate risk profile.</t>
         </is>
       </c>
       <c r="R141" s="2" t="inlineStr">
@@ -13069,7 +13094,7 @@
       </c>
       <c r="O142" s="6" t="inlineStr">
         <is>
-          <t>Lead and/or contribute to international ESIA processes for large-scale infrastructure, energy, transport, industrial, and environmental projects. Conduct or support Environmental and Social Due Diligence (ESDD)/ Environmental, Health and Safety Due Diligence (EHS DD) assignments for IFIs, lenders, and private investors. Conduct or support Environmental Due Diligence (EDD)/ Environmental, Health and Safety Due Diligence (EHS DD) assignments in relation to mergers and acquisitions (M&amp;A). Coordinat</t>
+          <t>Lead and/or contribute to international ESIA processes for large-scale infrastructure, energy, transport, industrial, and environmental projects. Conduct or support Environmental and Social Due Diligence (ESDD)/ Environmental, Health and Safety Due Diligence (EHS DD) assignments for IFIs, lenders, and private investors. Conduct or support Environmental Due Diligence (EDD)/ Environmental, Health and Safety Due Diligence (EHS DD) assignments in relation to mergers and acquisitions (M&amp;A). Coordinate environmental and social workstreams in multidisciplinary project teams. Engage with clients, IFIs, authorities, local stakeholders and subcontractors in various countries. Prepare high quality technical documentation, including ESIA reports, EDD reports, management plans, and monitoring frameworks.</t>
         </is>
       </c>
       <c r="P142" s="6" t="inlineStr">
@@ -13079,7 +13104,7 @@
       </c>
       <c r="Q142" s="6" t="inlineStr">
         <is>
-          <t>[general_esg] The job description mentions working on sustainability-driven assignments, international environmental and social impact assessments, and environmental and social due diligence, which are all related to ESG strategy and corporate sustainability.</t>
+          <t>The job description mentions working on sustainability-driven assignments, international environmental and social impact assessments, and environmental and social due diligence, which are all related to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
       <c r="R142" s="2" t="inlineStr"/>
@@ -13146,7 +13171,7 @@
       </c>
       <c r="O143" s="6" t="inlineStr">
         <is>
-          <t>What are you going to do? Als (Junior) Consultant Green Investments word je onderdeel van het INVEST-team: een hecht en enthousiast team dat dagelijks werkt aan Europese of nationale impactvolle projecten. Je staat in direct contact met onze klanten en helpt hen bij het realiseren van duurzame investeringen. Dat doe je door kansen te signaleren, mee te denken over de beste aanpak en subsidies en regelingen te vertalen naar concrete projecten. Je brengt al een basiskennis mee van hernieuwbare ene</t>
+          <t>What are you going to do? Als (Junior) Consultant Green Investments word je onderdeel van het INVEST-team: een hecht en enthousiast team dat dagelijks werkt aan Europese of nationale impactvolle projecten. Je staat in direct contact met onze klanten en helpt hen bij het realiseren van duurzame investeringen. Dat doe je door kansen te signaleren, mee te denken over de beste aanpak en subsidies en regelingen te vertalen naar concrete projecten. Je brengt al een basiskennis mee van hernieuwbare energiesystemen, waardoor je snel kunt meedenken met klanten. Binnen het INVEST-team ontwikkel je je verder en groei je stap voor stap uit tot een volwaardige adviseur voor klanten in de industrie en energiesector, met directe impact op duurzame investeringen. Je analyseert duurzame investeringsplannen van klanten en identificeert de meest kansrijke subsidiemogelijkheden; Je verdiept je in en begrijpt de projecten van de klant inhoudelijk en vertaalt technische projectinformatie naar een heldere financiële en subsidie-technische onderbouwing; Je ontwikkelt sterke investeringsbusinesscases (CAPEX/OPEX, cashflows, terugverdientijd, risico’s); Je rol is praktisch en resultaatgericht: je werkt toe naar concrete subsidieaanvragen, méér dan alleen naar analyses of beleidsadviezen. Je levert een actieve bijdrage aan de groei van het INVEST-team door betrokkenheid bij business development en de verdere professionalisering van onze dienstverlening; Je werkt samen met collega’s om klanten optimaal te bedienen met op maat gemaakte investeringsstrategieën.</t>
         </is>
       </c>
       <c r="P143" s="6" t="inlineStr">
@@ -13156,7 +13181,7 @@
       </c>
       <c r="Q143" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions 'duurzame investeringen' (sustainable investments), 'hernieuwbare energiesystemen' (renewable energy systems), and 'energietransitie' (energy transition), which are all related to renewable energy and environmental science, fitting the clean_energ</t>
+          <t>The job description mentions 'duurzame investeringen' (sustainable investments), 'hernieuwbare energiesystemen' (renewable energy systems), and 'energietransitie' (energy transition), which are all related to renewable energy and environmental science, fitting the clean_energy_adjacent profile.</t>
         </is>
       </c>
       <c r="R143" s="2" t="inlineStr"/>
@@ -13225,7 +13250,7 @@
       <c r="P144" s="2" t="inlineStr"/>
       <c r="Q144" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] Job title contains 'Climate Action', indicating a strong focus on climate-related issues.</t>
+          <t>Job title contains 'Climate Action', indicating a strong focus on climate-related issues.</t>
         </is>
       </c>
       <c r="R144" s="2" t="inlineStr"/>
@@ -13302,7 +13327,7 @@
       </c>
       <c r="Q145" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] Job title contains 'Climate Risk Analysis' indicating a strong focus on climate risk</t>
+          <t>Job title contains 'Climate Risk Analysis' indicating a strong focus on climate risk</t>
         </is>
       </c>
       <c r="R145" s="2" t="inlineStr"/>
@@ -13381,7 +13406,7 @@
       </c>
       <c r="O146" s="6" t="inlineStr">
         <is>
-          <t>We are seeking a dynamic and experienced environmental project manager to lead and support island, marine and vulnerable species management, including conservation and intervention actions, within the Great Barrier Reef World Heritage Area. This is a dynamic position with a wide range of responsibilities including project planning and reporting, risk assessment, project evaluation, procurement, communication product development, stakeholder and Traditional Owner engagement, and some marine-based</t>
+          <t>We are seeking a dynamic and experienced environmental project manager to lead and support island, marine and vulnerable species management, including conservation and intervention actions, within the Great Barrier Reef World Heritage Area. This is a dynamic position with a wide range of responsibilities including project planning and reporting, risk assessment, project evaluation, procurement, communication product development, stakeholder and Traditional Owner engagement, and some marine-based fieldwork.</t>
         </is>
       </c>
       <c r="P146" s="6" t="inlineStr">
@@ -13391,7 +13416,7 @@
       </c>
       <c r="Q146" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions reef conservation, marine and vulnerable species management, and environmental project management, which are related to renewable energy, environmental science, and conservation, making it a good fit for the clean_energy_adjacent profile.</t>
+          <t>The job description mentions reef conservation, marine and vulnerable species management, and environmental project management, which are related to renewable energy, environmental science, and conservation, making it a good fit for the clean_energy_adjacent profile.</t>
         </is>
       </c>
       <c r="R146" s="2" t="inlineStr">
@@ -13474,7 +13499,7 @@
       </c>
       <c r="O147" s="6" t="inlineStr">
         <is>
-          <t>In this role, you will use your commodities trading knowledge and analytical skills to provide expert advice on front line trading risks for the Gas, Power and Carbon desks. You will support and facilitate the continued improvement of processes, controls and operational risk awareness and culture across our businesses. As a subject matter expert you will partner with the trading desks and leverage your technical expertise to develop a comprehensive knowledge of all processes to proactively manag</t>
+          <t>In this role, you will use your commodities trading knowledge and analytical skills to provide expert advice on front line trading risks for the Gas, Power and Carbon desks. You will support and facilitate the continued improvement of processes, controls and operational risk awareness and culture across our businesses. As a subject matter expert you will partner with the trading desks and leverage your technical expertise to develop a comprehensive knowledge of all processes to proactively manage the operational risks. You will provide advice on a broad range of risk matters, assess new product and business initiatives, investigate incidents and test effectiveness of controls.</t>
         </is>
       </c>
       <c r="P147" s="6" t="inlineStr">
@@ -13484,7 +13509,7 @@
       </c>
       <c r="Q147" s="6" t="inlineStr">
         <is>
-          <t>[carbon_markets] The job description mentions experience in Carbon markets as a plus, and the role involves providing expert advice on front line trading risks for the Gas, Power and Carbon desks, indicating a strong connection to carbon markets and emissions trading.</t>
+          <t>The job description mentions experience in Carbon markets as a plus, and the role involves providing expert advice on front line trading risks for the Gas, Power and Carbon desks, indicating a strong connection to carbon markets and emissions trading.</t>
         </is>
       </c>
       <c r="R147" s="2" t="inlineStr">
@@ -13567,7 +13592,7 @@
       </c>
       <c r="O148" s="6" t="inlineStr">
         <is>
-          <t>Managing, maintaining, and expanding the client portfolio, with a focus on new business and high potential markets. Developing our trading activities for short and long-term strategies in line with the company’s objectives. Conduct market research where you will research and analyse market trends, technological advancements, potential clients, and their industry trends, to help inform business decisions. Creating analyses and presentations to update your clients and stakeholders with market tren</t>
+          <t>Managing, maintaining, and expanding the client portfolio, with a focus on new business and high potential markets. Developing our trading activities for short and long-term strategies in line with the company’s objectives. Conduct market research where you will research and analyse market trends, technological advancements, potential clients, and their industry trends, to help inform business decisions. Creating analyses and presentations to update your clients and stakeholders with market trends, new upcoming projects, and other relevant information. Ensure brand awareness and building your network through participation in business events, fairs, and other occasions. Collaborate, learn, enjoy, and work together with other teams together to achieve the best possible for AFS Energy.</t>
         </is>
       </c>
       <c r="P148" s="6" t="inlineStr">
@@ -13577,7 +13602,7 @@
       </c>
       <c r="Q148" s="6" t="inlineStr">
         <is>
-          <t>[carbon_markets] The job description mentions 'Carbon Markets including trading dynamics related to the buy and sell side of transactions, negotiation, and other macroeconomic factors' and 'Environmental commodities', indicating a strong focus on carbon markets and environmental sustainability.</t>
+          <t>The job description mentions 'Carbon Markets including trading dynamics related to the buy and sell side of transactions, negotiation, and other macroeconomic factors' and 'Environmental commodities', indicating a strong focus on carbon markets and environmental sustainability.</t>
         </is>
       </c>
       <c r="R148" s="2" t="inlineStr">
@@ -13660,12 +13685,14 @@
       </c>
       <c r="O149" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">As a Senior Associate / Legal Director, you will: 
+          <t>As a Senior Associate / Legal Director, you will: 
    * Lead the drafting and negotiation of complex project, construction and finance documentation
    * Take primary responsibility for managing transactions, including supervising junior lawyers and coordinating multi-jurisdictional teams
    * Provide strategic advice to clients on risk allocation, structuring and execution of projects
    * Play a key role in client relationship management, acting as a trusted advisor on ongoing and new matters
-</t>
+   * Drive business development initiatives, including identifying opportunities, preparing pitches and contributing to sector-focused thought leadership
+   * Mentor and develop junior team members, fostering a collaborative and high-performing team culture
+   * Work closely with partners on practice development and contribute to the broader strategic growth of the team</t>
         </is>
       </c>
       <c r="P149" s="6" t="inlineStr">
@@ -13675,7 +13702,7 @@
       </c>
       <c r="Q149" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions experience in renewable energy, low-carbon infrastructure, carbon markets, and natural capital, which are all relevant to the clean energy and environmental sectors.</t>
+          <t>The job description mentions experience in renewable energy, low-carbon infrastructure, carbon markets, and natural capital, which are all relevant to the clean energy and environmental sectors.</t>
         </is>
       </c>
       <c r="R149" s="2" t="inlineStr">
@@ -13764,7 +13791,7 @@
       </c>
       <c r="Q150" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions renewable energy development, solar, wind, and hybrid systems, which are directly related to clean energy. The company's focus on transitioning toward clean and intelligent energy systems also supports this classification.</t>
+          <t>The job description mentions renewable energy development, solar, wind, and hybrid systems, which are directly related to clean energy. The company's focus on transitioning toward clean and intelligent energy systems also supports this classification.</t>
         </is>
       </c>
       <c r="R150" s="2" t="inlineStr">
@@ -13843,7 +13870,7 @@
       </c>
       <c r="O151" s="6" t="inlineStr">
         <is>
-          <t>Manage AIDMIs social media accounts, including Instagram, Twitter, LinkedIn, Facebook, and WhatsApp Chat Bot Integration and Management. Develop and implement social media strategies that align with AIDMIs goals and Create engaging and educational social media content, including graphics, videos, and Monitor social media trends and good practices, and incorporate new techniques and tools to remain at the forefront. Collaborate, co-create and implement at least three social media campaigns that s</t>
+          <t>Manage AIDMIs social media accounts, including Instagram, Twitter, LinkedIn, Facebook, and WhatsApp Chat Bot Integration and Management. Develop and implement social media strategies that align with AIDMIs goals and Create engaging and educational social media content, including graphics, videos, and Monitor social media trends and good practices, and incorporate new techniques and tools to remain at the forefront. Collaborate, co-create and implement at least three social media campaigns that support Develop and maintain the AIDMI website, including troubleshooting and bug fixing. Develop and implement new web-based projects such as quizzes, Google Surveys, etc., Write clean and efficient code that is easy to maintain. Ensure website and web-based projects are user-friendly, accessible, and visually appealing with high impact and visible results. Test website and web-based projects to ensure they meet the quality and performance standards of organisations such as ODI. Keep up to date with web development and social media trends and technologies, and incorporate new techniques and tools as soon as they are available. Collecting, maintaining, and analysing data for record and development processes.</t>
         </is>
       </c>
       <c r="P151" s="6" t="inlineStr">
@@ -13853,7 +13880,7 @@
       </c>
       <c r="Q151" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job title mentions 'Disaster Risk and Climate Resilience', indicating a focus on climate-related risks, and the company name 'All India Disaster Mitigation Institute' also suggests a connection to disaster risk and climate resilience.</t>
+          <t>The job title mentions 'Disaster Risk and Climate Resilience', indicating a focus on climate-related risks, and the company name 'All India Disaster Mitigation Institute' also suggests a connection to disaster risk and climate resilience.</t>
         </is>
       </c>
       <c r="R151" s="2" t="inlineStr"/>
@@ -13932,7 +13959,7 @@
       </c>
       <c r="O152" s="6" t="inlineStr">
         <is>
-          <t>Proven work experience as an Operations Manager or similar role in the Solar Energy sector. Experience with inventory management, database systems, or similar software is beneficial. Relevant training and/or certifications as an Operations Associate. O&amp;M Manager is responsible for scheduling cleaning, breakdown, and preventive maintenance activities. All reports must be sent to the client with comments within 4 hours of completing the activity. O&amp;M Manager must prepare MIS reports, verify vendor</t>
+          <t>Proven work experience as an Operations Manager or similar role in the Solar Energy sector. Experience with inventory management, database systems, or similar software is beneficial. Relevant training and/or certifications as an Operations Associate. O&amp;M Manager is responsible for scheduling cleaning, breakdown, and preventive maintenance activities. All reports must be sent to the client with comments within 4 hours of completing the activity. O&amp;M Manager must prepare MIS reports, verify vendor bills, and coordinate with the accounts team for payments. O&amp;M Manager shall coordinate with the purchase department regarding warranty claims. O&amp;M Executive will report to the O&amp;M Manager. Excellent communication and listening skills. Ability to work effectively under pressure. Strong computer proficiency.</t>
         </is>
       </c>
       <c r="P152" s="6" t="inlineStr">
@@ -13942,7 +13969,7 @@
       </c>
       <c r="Q152" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions solar energy, renewable energy, and utility-scale solar energy projects, which are all related to clean energy and environmental sustainability.</t>
+          <t>The job description mentions solar energy, renewable energy, and utility-scale solar energy projects, which are all related to clean energy and environmental sustainability.</t>
         </is>
       </c>
       <c r="R152" s="2" t="inlineStr">
@@ -14039,7 +14066,7 @@
       </c>
       <c r="Q153" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description is for a Deputy Manager-Wind Engineering role, which involves working with wind energy projects, and the company ReNew is a renewable energy company, indicating a strong connection to clean energy and environmental sustainability</t>
+          <t>The job description is for a Deputy Manager-Wind Engineering role, which involves working with wind energy projects, and the company ReNew is a renewable energy company, indicating a strong connection to clean energy and environmental sustainability</t>
         </is>
       </c>
       <c r="R153" s="2" t="inlineStr">
@@ -14122,7 +14149,7 @@
       </c>
       <c r="O154" s="6" t="inlineStr">
         <is>
-          <t>Operation and maintenance of HT, LT Electrical System. Mechanical HVAC, Pump House, ETP, STP&amp; Shift team handling -Utility. Roles to Perform preventative maintenance on electrical &amp; mechanical systems and components by the team. Troubleshoot problems and make timely repairs. Plan, execute, and coordinate within the department. Tools requirement, spare management, and team management. Shift schedule, corrective actions, special activities planning. Calibration and testing of Electrical, Mechanica</t>
+          <t>Operation and maintenance of HT, LT Electrical System. Mechanical HVAC, Pump House, ETP, STP&amp; Shift team handling -Utility. Roles to Perform preventative maintenance on electrical &amp; mechanical systems and components by the team. Troubleshoot problems and make timely repairs. Plan, execute, and coordinate within the department. Tools requirement, spare management, and team management. Shift schedule, corrective actions, special activities planning. Calibration and testing of Electrical, Mechanical Equipment. Coordinate and plan with other dept. as their requirements. Maintain safety and adhere to all recommendations.</t>
         </is>
       </c>
       <c r="P154" s="6" t="inlineStr">
@@ -14132,7 +14159,7 @@
       </c>
       <c r="Q154" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions renewable energy, solar energy projects, and utility-scale wind energy projects, which are all related to clean energy. The company, ReNew, is also described as one of the largest renewable energy companies globally.</t>
+          <t>The job description mentions renewable energy, solar energy projects, and utility-scale wind energy projects, which are all related to clean energy. The company, ReNew, is also described as one of the largest renewable energy companies globally.</t>
         </is>
       </c>
       <c r="R154" s="2" t="inlineStr">
@@ -14215,7 +14242,7 @@
       </c>
       <c r="O155" s="6" t="inlineStr">
         <is>
-          <t>As Finance Lead – WEET, you will act as the key commercial and financial partner to Project Managers and operational leaders. Reporting to the CFO, this role is responsible for driving financial performance, strengthening project governance, and improving working capital outcomes across the service line. You will provide end-to-end project finance leadership across the full project lifecycle – from bid support and project set-up, through delivery and revenue recognition, to project close. Lead f</t>
+          <t>As Finance Lead – WEET, you will act as the key commercial and financial partner to Project Managers and operational leaders. Reporting to the CFO, this role is responsible for driving financial performance, strengthening project governance, and improving working capital outcomes across the service line. You will provide end-to-end project finance leadership across the full project lifecycle – from bid support and project set-up, through delivery and revenue recognition, to project close. Lead financial performance across the WEET portfolio, fostering accountability and a high-performing culture. Partner with Project Managers on project setup, forecasting, ETC, revenue recognition (PoC), invoicing and cash flow management. Deliver accurate monthly revenue recognition in collaboration with operational teams. Conduct risk reviews on projects with overruns, delays or margin erosion and recommend corrective actions. Drive working capital performance, including weekly cash flow forecasting and reporting to leadership. Own the budgeting and forecasting cycle, including resourcing analysis, backlog and pipeline projections through to P&amp;L and operational cash flow. Provide commercial input into bids and pricing models, balancing risk and return in collaboration with legal and operational stakeholders. Support ERP rollout activities including data cleansing, process mapping, UAT testing, training and adoption monitoring. Standardise financial and operational processes, aligning master data and reporting structures across the group. Act as the SME for ERP project accounting, coaching and educating Project Managers on governance and financial controls. Liaise with APAC Shared Services (tax, accounting, payables, receivables, payroll and FP&amp;A) to ensure accurate and compliant financial operations.</t>
         </is>
       </c>
       <c r="P155" s="6" t="inlineStr">
@@ -14225,7 +14252,7 @@
       </c>
       <c r="Q155" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[clean_energy_adjacent] The job title 'Finance Lead - Water, Environment &amp; Energy Transition' and the company's focus on sustainable solutions and infrastructure indicate a connection to environmental topics, specifically water, environment, and energy transition, which aligns with the clean energy </t>
+          <t>The job title 'Finance Lead - Water, Environment &amp; Energy Transition' and the company's focus on sustainable solutions and infrastructure indicate a connection to environmental topics, specifically water, environment, and energy transition, which aligns with the clean energy adjacent profile.</t>
         </is>
       </c>
       <c r="R155" s="2" t="inlineStr">
@@ -14308,17 +14335,17 @@
       </c>
       <c r="O156" s="6" t="inlineStr">
         <is>
-          <t>Assist the global strategic research team in providing quantitative analytics, and qualitative research to support our strategic research views on long term themes, and related communication material. Keep up-to-date on current investment trends and themes; help to identify and develop Mercer’s investment themes and opportunities. Drive the production side of our processes, for instance maintaining our theme summary material or quarterly thematic updates, project managing some of our material to</t>
+          <t>Assist the global strategic research team in providing quantitative analytics, and qualitative research to support our strategic research views on long term themes, and related communication material. Keep up-to-date on current investment trends and themes; help to identify and develop Mercer’s investment themes and opportunities. Drive the production side of our processes, for instance maintaining our theme summary material or quarterly thematic updates, project managing some of our material to final delivery. Build and maintain strong relationships with external parties such as specialist fund managers to explore investment ideas, develop research agendas. Work closely with other specialist teams, in particular our manager research boutiques, alternatives teams, sustainable investment team, delegated solutions and investment consulting colleagues to refine our team’s material, and to support intellectual capital development in respect of their specialist areas. Provide ad-hoc support to consultants in preparing thematic material for internal and external research meetings.</t>
         </is>
       </c>
       <c r="P156" s="6" t="inlineStr">
         <is>
-          <t>Strong researching and critical-thinking skills; ability to interpret and use qualitative and quantitative data to reach conclusions and explain them in terms that others can understand. Proven experience of research Investment knowledge: market awareness, asset class knowledge, asset allocation kno</t>
+          <t>Strong researching and critical-thinking skills; ability to interpret and use qualitative and quantitative data to reach conclusions and explain them in terms that others can understand. Proven experience of research Investment knowledge: market awareness, asset class knowledge, asset allocation knowledge, responsible investment, investment/risk tools (including MercerInsight and Datastream/Databank); eagerness to learn and keep up to date with the investment industry and market conditions. High proficiency in Excel. Creativity – a keenness to develop new processes and techniques, and an eye for design. Bloomberg and Factset trained (strongly preferred but not essential). Willingness to study IMC/CFA.</t>
         </is>
       </c>
       <c r="Q156" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions 'responsible investment' and 'sustainable investment team', indicating a focus on ESG investing and sustainable finance.</t>
+          <t>The job description mentions 'responsible investment' and 'sustainable investment team', indicating a focus on ESG investing and sustainable finance.</t>
         </is>
       </c>
       <c r="R156" s="2" t="inlineStr">
@@ -14401,17 +14428,17 @@
       </c>
       <c r="O157" s="6" t="inlineStr">
         <is>
-          <t>The position is within the Energy &amp; Infrastructure Vertical at ASSOCHAM, playing a pivotal role in advancing division’s advocacy and industry engagement agenda. The incumbent will lead high-impact policy advocacy and drive sector-focused initiatives spanning Energy, Power, Renewable Energy, Green Hydrogen, Transmission, Highways &amp; Tunnelling, and Civil Aviation. This role will act as a catalyst for transformative government initiatives, working closely with policymakers, industry leaders, and ke</t>
+          <t>The position is within the Energy &amp; Infrastructure Vertical at ASSOCHAM, playing a pivotal role in advancing division’s advocacy and industry engagement agenda. The incumbent will lead high-impact policy advocacy and drive sector-focused initiatives spanning Energy, Power, Renewable Energy, Green Hydrogen, Transmission, Highways &amp; Tunnelling, and Civil Aviation. This role will act as a catalyst for transformative government initiatives, working closely with policymakers, industry leaders, and key stakeholders to address critical sectoral challenges and unlock opportunities for sustainable and inclusive growth. In addition, the role carries a strong mandate for expanding industry membership, deepening stakeholder engagement, and driving revenue growth through innovative programs, conferences, partnerships, and strategic projects.</t>
         </is>
       </c>
       <c r="P157" s="6" t="inlineStr">
         <is>
-          <t>Policy &amp; Regulatory Understanding, Sectoral Knowledge, Research &amp; Analytical Skills, Government &amp; Institutional Liaison, Project &amp; Event Management, Membership &amp; Revenue Development, Communication &amp; Documentation, Stakeholder Management, Strategic Thinking, Communication &amp; Influence, Networking &amp; Re</t>
+          <t>Policy &amp; Regulatory Understanding, Sectoral Knowledge, Research &amp; Analytical Skills, Government &amp; Institutional Liaison, Project &amp; Event Management, Membership &amp; Revenue Development, Communication &amp; Documentation, Stakeholder Management, Strategic Thinking, Communication &amp; Influence, Networking &amp; Relationship Building, Commercial Orientation, Execution &amp; Ownership, Proficiency in MS Office Suite</t>
         </is>
       </c>
       <c r="Q157" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions renewable energy, green hydrogen, energy transition, and other related topics, which are relevant to the clean energy and environmental science fields.</t>
+          <t>The job description mentions renewable energy, green hydrogen, energy transition, and other related topics, which are relevant to the clean energy and environmental science fields.</t>
         </is>
       </c>
       <c r="R157" s="2" t="inlineStr">
@@ -14494,7 +14521,7 @@
       </c>
       <c r="O158" s="6" t="inlineStr">
         <is>
-          <t>Candidate shall be posted in general shift &amp; will have to make himself available as and when required in any critical condition to attain the site project work. He will be responsible to electrical work in project execution and completion till the commissioning. Working knowledge in Hindi, English language is essential. Computer literate with knowledge of MS Word, Excel, Power point, auto-cad. Installation, testing and commissioning of electrical equipment, cables as per standards and customer r</t>
+          <t>Candidate shall be posted in general shift &amp; will have to make himself available as and when required in any critical condition to attain the site project work. He will be responsible to electrical work in project execution and completion till the commissioning. Working knowledge in Hindi, English language is essential. Computer literate with knowledge of MS Word, Excel, Power point, auto-cad. Installation, testing and commissioning of electrical equipment, cables as per standards and customer requirements by preparing electrical systems specification, technical drawings. Establishing construction, manufacturing, or installation standards or specifications by performing a wide range of detailed calculations. Ensuring compliance with specifications, codes, or customer requirement by directing or coordinating installation, manufacturing, construction, maintenance, documentation, support, or testing activities. Writing reports and compiling data regarding existing and potential electrical engineering projects and studies. Supervising the ongoing project and providing training to O&amp;M team members. Estimating material, labor, or construction costs for budget preparation.</t>
         </is>
       </c>
       <c r="P158" s="6" t="inlineStr">
@@ -14504,7 +14531,7 @@
       </c>
       <c r="Q158" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions renewable energy, solar energy projects, and clean energy, which are all related to the clean energy adjacent profile. The company's mission to provide clean, safe, affordable, and sustainable energy also supports this classification.</t>
+          <t>The job description mentions renewable energy, solar energy projects, and clean energy, which are all related to the clean energy adjacent profile. The company's mission to provide clean, safe, affordable, and sustainable energy also supports this classification.</t>
         </is>
       </c>
       <c r="R158" s="2" t="inlineStr">
@@ -14591,7 +14618,7 @@
       </c>
       <c r="O159" s="6" t="inlineStr">
         <is>
-          <t>Lead and manage the full end-to-end lifecycle delivery of medium to highly complex regulatory change projects from initiation through implementation and closure. Define and manage the business case, project objectives, scope, resources and expected benefits for assigned initiatives. Act as the primary delivery owner ensuring alignment across stakeholders and teams across geographies. Develop and maintain high-quality project plans including risk mitigation strategies and structured work packages</t>
+          <t>Lead and manage the full end-to-end lifecycle delivery of medium to highly complex regulatory change projects from initiation through implementation and closure. Define and manage the business case, project objectives, scope, resources and expected benefits for assigned initiatives. Act as the primary delivery owner ensuring alignment across stakeholders and teams across geographies. Develop and maintain high-quality project plans including risk mitigation strategies and structured work packages. Evaluate delivery approaches, track performance and adjust plans to ensure alignment with scope, schedule, budget and project outcomes. Provide forecasts of future change and BAU resource requirements required to support project delivery.</t>
         </is>
       </c>
       <c r="P159" s="6" t="inlineStr">
@@ -14601,7 +14628,7 @@
       </c>
       <c r="Q159" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions 'sustainable investing' and 'SFDR' which are related to sustainable finance and ESG investing. The role involves leading regulatory change initiatives within the asset management domain, which also aligns with sustainable finance.</t>
+          <t>The job description mentions 'sustainable investing' and 'SFDR' which are related to sustainable finance and ESG investing. The role involves leading regulatory change initiatives within the asset management domain, which also aligns with sustainable finance.</t>
         </is>
       </c>
       <c r="R159" s="2" t="inlineStr">
@@ -14680,17 +14707,17 @@
       </c>
       <c r="O160" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lead Fundipedia implementation and enhancement projects to optimize fund data management. Define and enforce fund data governance frameworks, including pricing governance and quality controls. Own the fund master data strategy, ensuring accuracy, timeliness, and completeness across internal and external platforms. Drive automation, standardization, and scalability of data operations using Fundipedia and other tools. Act as escalation point for fund data discrepancies, reconciliation exceptions, </t>
+          <t>Lead Fundipedia implementation and enhancement projects to optimize fund data management. Define and enforce fund data governance frameworks, including pricing governance and quality controls. Own the fund master data strategy, ensuring accuracy, timeliness, and completeness across internal and external platforms. Drive automation, standardization, and scalability of data operations using Fundipedia and other tools. Act as escalation point for fund data discrepancies, reconciliation exceptions, and complex data-related queries. Collaborate with cross-functional teams including investments, compliance, distribution, client servicing, regulatory, vendor, and global teams. Represent Investment Operations in transformation programs and data governance forums. Monitor and report KPIs, delivering insights to improve fund data quality, operational efficiency, and service excellence. Mentor and guide team members on Fundipedia usage, data best practices, and continuous improvement. Implement assurance checks to ensure data meets investment, client reporting, and regulatory standards. Conduct data analysis to support business decisions and reporting needs. Oversee sustainability data integration and reporting across investment platforms. Ensure compliance with regulatory requirements and internal controls. Lead and manage the Data Services team, fostering innovation and continuous improvement.</t>
         </is>
       </c>
       <c r="P160" s="6" t="inlineStr">
         <is>
-          <t>Deep expertise in fund structures, share classes, and investment products. Hands-on experience with Fundipedia or similar EDM platforms. Strong understanding of regulatory frameworks (e.g., UCITS, MiFID II, SFDR). Proficiency in data tools (Excel, SQL, Power BI, Python, VBA). Excellent leadership, s</t>
+          <t>Deep expertise in fund structures, share classes, and investment products. Hands-on experience with Fundipedia or similar EDM platforms. Strong understanding of regulatory frameworks (e.g., UCITS, MiFID II, SFDR). Proficiency in data tools (Excel, SQL, Power BI, Python, VBA). Excellent leadership, stakeholder management, and communication skills. Analytical mindset with ability to interpret complex fund data. Proven ability to lead teams and manage cross-functional initiatives.</t>
         </is>
       </c>
       <c r="Q160" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions SFDR, which is a key regulation in sustainable finance, and also mentions overseeing sustainability data integration and reporting across investment platforms, indicating a focus on ESG considerations in investment operations.</t>
+          <t>The job description mentions SFDR, which is a key regulation in sustainable finance, and also mentions overseeing sustainability data integration and reporting across investment platforms, indicating a focus on ESG considerations in investment operations.</t>
         </is>
       </c>
       <c r="R160" s="2" t="inlineStr"/>
@@ -14765,17 +14792,17 @@
       </c>
       <c r="O161" s="6" t="inlineStr">
         <is>
-          <t>Work within a team responsible for Investment Restriction Compliance Management violation oversight, onboarding, and query resolution. Oversee daily reviews of overnight violation monitoring; escalate and track issues through to resolution. Partner with Investment Desks, Product, and Client Executives across asset classes on investment guideline matters and pre-trade violation overrides. Maintain broker and ready-to-trade coding in Aladdin and assist Trading Desks with related queries and escala</t>
+          <t>Work within a team responsible for Investment Restriction Compliance Management violation oversight, onboarding, and query resolution. Oversee daily reviews of overnight violation monitoring; escalate and track issues through to resolution. Partner with Investment Desks, Product, and Client Executives across asset classes on investment guideline matters and pre-trade violation overrides. Maintain broker and ready-to-trade coding in Aladdin and assist Trading Desks with related queries and escalations. Deliver and review mandate investment guideline onboarding and change activities, supporting control implementation on the Aladdin platform. Process and capture commitments sourced from IMAs, regulations, or internal teams. Collaborate with internal teams and vendors to ensure best practices and a consistent control environment. Respond to audit, regulator, and client queries, ensuring timely and accurate delivery of responses. Identify process gaps, troubleshoot issues, and communicate risks while proposing effective solutions. Participate in projects and working groups related to new markets, instruments, or mandates, assessing impacts on restrictions monitoring. Coach and mentor junior team members, ensuring training materials and procedures remain current.</t>
         </is>
       </c>
       <c r="P161" s="6" t="inlineStr">
         <is>
-          <t>Strong experience in Investment Restriction Monitoring and compliance processes within Asset Management. Hands-on experience with Aladdin (or equivalent portfolio management systems). Solid understanding of investment guidelines, regulatory compliance, and mandate restriction management. Proficiency</t>
+          <t>Strong experience in Investment Restriction Monitoring and compliance processes within Asset Management. Hands-on experience with Aladdin (or equivalent portfolio management systems). Solid understanding of investment guidelines, regulatory compliance, and mandate restriction management. Proficiency in Microsoft Excel; working knowledge of Word, PowerPoint, and SQL. Excellent communication and stakeholder management skills, with proven ability to collaborate across teams. Strong attention to detail and accuracy in reviewing documentation and compliance checks. Demonstrated ability to work under pressure and meet strict deadlines in a fast-paced environment. Proven leadership and mentoring skills, with the ability to support junior colleagues. Knowledge of investment restriction regulations such as UCITS, SFDR, and SDR. Prior involvement in change initiatives or process improvement projects. Experience working with regulatory audits or client visits. Exposure to risk assessment, policy setting, and control frameworks. Familiarity with broader investment products and asset classes. Understanding of data management and automation opportunities in control processes.</t>
         </is>
       </c>
       <c r="Q161" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions SFDR, which is a key regulation in sustainable finance, and also mentions investment restriction monitoring and compliance processes, which are relevant to ESG investing and sustainable finance.</t>
+          <t>The job description mentions SFDR, which is a key regulation in sustainable finance, and also mentions investment restriction monitoring and compliance processes, which are relevant to ESG investing and sustainable finance.</t>
         </is>
       </c>
       <c r="R161" s="2" t="inlineStr"/>
@@ -14850,17 +14877,17 @@
       </c>
       <c r="O162" s="6" t="inlineStr">
         <is>
-          <t>To lead the Fund Master function within Investment Data Services, ensuring high-quality, complete, and compliant fund data management using Fundipedia. This role is pivotal in driving data governance, reconciliation, and strategic data initiatives across investment operations. Lead Fundipedia implementation and enhancement projects to optimize fund data management. Define and enforce fund data governance frameworks, including pricing governance and quality controls. Own the fund master data stra</t>
+          <t>To lead the Fund Master function within Investment Data Services, ensuring high-quality, complete, and compliant fund data management using Fundipedia. This role is pivotal in driving data governance, reconciliation, and strategic data initiatives across investment operations. Lead Fundipedia implementation and enhancement projects to optimize fund data management. Define and enforce fund data governance frameworks, including pricing governance and quality controls. Own the fund master data strategy, ensuring accuracy, timeliness, and completeness across internal and external platforms. Drive automation, standardization, and scalability of data operations using Fundipedia and other tools. Act as escalation point for fund data discrepancies, reconciliation exceptions, and complex data-related queries. Collaborate with cross-functional teams including investments, compliance, distribution, client servicing, regulatory, vendor, and global teams. Represent Investment Operations in transformation programs and data governance forums. Monitor and report KPIs, delivering insights to improve fund data quality, operational efficiency, and service excellence. Mentor and guide team members on Fundipedia usage, data best practices, and continuous improvement. Implement assurance checks to ensure data meets investment, client reporting, and regulatory standards. Conduct data analysis to support business decisions and reporting needs. Oversee sustainability data integration and reporting across investment platforms. Ensure compliance with regulatory requirements and internal controls. Lead and manage the Data Services team, fostering innovation and continuous improvement.</t>
         </is>
       </c>
       <c r="P162" s="6" t="inlineStr">
         <is>
-          <t>Deep expertise in fund structures, share classes, and investment products. Hands-on experience with Fundipedia or similar EDM platforms. Strong understanding of regulatory frameworks (e.g., UCITS, MiFID II, SFDR). Proficiency in data tools (Excel, SQL, Power BI, Python, VBA). Excellent leadership, s</t>
+          <t>Deep expertise in fund structures, share classes, and investment products. Hands-on experience with Fundipedia or similar EDM platforms. Strong understanding of regulatory frameworks (e.g., UCITS, MiFID II, SFDR). Proficiency in data tools (Excel, SQL, Power BI, Python, VBA). Excellent leadership, stakeholder management, and communication skills. Analytical mindset with ability to interpret complex fund data. Proven ability to lead teams and manage cross-functional initiatives.</t>
         </is>
       </c>
       <c r="Q162" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions SFDR, which is a key regulation in sustainable finance, and also mentions overseeing sustainability data integration and reporting across investment platforms, indicating a focus on ESG considerations in investment operations.</t>
+          <t>The job description mentions SFDR, which is a key regulation in sustainable finance, and also mentions overseeing sustainability data integration and reporting across investment platforms, indicating a focus on ESG considerations in investment operations.</t>
         </is>
       </c>
       <c r="R162" s="2" t="inlineStr"/>
@@ -14927,7 +14954,7 @@
       </c>
       <c r="O163" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deliver assurance services to multinational clients across a variety of sectors. Support Project Managers in the independent verification of GHG/ESG information, sustainability‑linked financial instruments, and product‑level claims. Contribute to high‑quality assessments that uphold ERM CVS’s reputation as a trusted global verification body. Build strong capability in sustainability assurance standards, environmental data methodologies, and emerging regulatory frameworks across APAC. Strengthen </t>
+          <t>Deliver assurance services to multinational clients across a variety of sectors. Support Project Managers in the independent verification of GHG/ESG information, sustainability‑linked financial instruments, and product‑level claims. Contribute to high‑quality assessments that uphold ERM CVS’s reputation as a trusted global verification body. Build strong capability in sustainability assurance standards, environmental data methodologies, and emerging regulatory frameworks across APAC. Strengthen client relationships through clear communication, reliable delivery, and a commitment to quality. Support Project Managers in delivering independent assurance of GHG/ESG information, including sustainability reporting, sustainability‑linked financial instruments, product claims, and carbon market requirements. Execute assurance procedures under the supervision of senior colleagues, including: Media and desktop research, Analytical review of ESG and GHG data, Evidence collection and evaluation, Site visits, Disclosure assessments. Maintain complete and accurate documentation in accordance with assurance standards and internal quality systems. Assist senior colleagues during head office and operational site visits, contributing to fieldwork and client discussions. Work collaboratively across multiple projects to ensure timely, high‑quality deliverables.</t>
         </is>
       </c>
       <c r="P163" s="6" t="inlineStr">
@@ -14937,7 +14964,7 @@
       </c>
       <c r="Q163" s="6" t="inlineStr">
         <is>
-          <t>[general_esg] The job description mentions ESG, sustainability reporting, GHG disclosures, and climate action, which are all relevant to the general ESG profile. The role involves delivering assurance services to multinational clients, supporting project managers in independent verification of GHG/E</t>
+          <t>The job description mentions ESG, sustainability reporting, GHG disclosures, and climate action, which are all relevant to the general ESG profile. The role involves delivering assurance services to multinational clients, supporting project managers in independent verification of GHG/ESG information, and contributing to high-quality assessments that uphold ERM CVS’s reputation as a trusted global verification body.</t>
         </is>
       </c>
       <c r="R163" s="2" t="inlineStr"/>
@@ -15081,7 +15108,7 @@
       </c>
       <c r="O165" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lead the delivery of sustainability and decarbonisation initiatives across operations and projects, including development of Project Sustainability Scorecards, KPIs and reporting dashboards. Manage GHG emissions accounting and emissions data validation in accordance with NGER and internal governance requirements. Provide specialist sustainability support for bids, tenders and operational decision-making, imbedding sustainability rating schemes (e.g. ISC), decarbonisation KPIs and ESG principles </t>
+          <t>Lead the delivery of sustainability and decarbonisation initiatives across operations and projects, including development of Project Sustainability Scorecards, KPIs and reporting dashboards. Manage GHG emissions accounting and emissions data validation in accordance with NGER and internal governance requirements. Provide specialist sustainability support for bids, tenders and operational decision-making, imbedding sustainability rating schemes (e.g. ISC), decarbonisation KPIs and ESG principles into delivery. Drive sustainable procurement and Scope 3 emissions considerations, collaborating with procurement and supply chain teams. Support continuous improvement by monitoring emerging sustainability legislation, market trends, and client expectations.</t>
         </is>
       </c>
       <c r="P165" s="6" t="inlineStr">
@@ -15091,7 +15118,7 @@
       </c>
       <c r="Q165" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] The job description mentions climate-related initiatives, GHG emissions accounting, carbon modelling, and decarbonisation, which are all relevant to climate risk. The role also involves managing emissions data validation, sustainability reporting, and performance metrics, which are cr</t>
+          <t>The job description mentions climate-related initiatives, GHG emissions accounting, carbon modelling, and decarbonisation, which are all relevant to climate risk. The role also involves managing emissions data validation, sustainability reporting, and performance metrics, which are critical components of climate risk management.</t>
         </is>
       </c>
       <c r="R165" s="2" t="inlineStr"/>
@@ -15158,17 +15185,17 @@
       </c>
       <c r="O166" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">We are seeking dynamic, creative, and resourceful candidates for our Bengaluru, India location to work on challenging petrophysical problems in collaboration with a multidisciplinary team of formation evaluation specialists and operations geologists based in Houston, USA. You will conduct applied project work using well logs, core data, and well test data, leveraging a variety of software platforms for petrophysical data processing and interpretation. Define project objectives, work scopes, and </t>
+          <t>We are seeking dynamic, creative, and resourceful candidates for our Bengaluru, India location to work on challenging petrophysical problems in collaboration with a multidisciplinary team of formation evaluation specialists and operations geologists based in Houston, USA. You will conduct applied project work using well logs, core data, and well test data, leveraging a variety of software platforms for petrophysical data processing and interpretation. Define project objectives, work scopes, and deliverables in collaboration with ExxonMobil’s Formation Evaluation group in Houston and relevant Business Units. Contribute to all stages of petrophysical project work, including data preparation, preprocessing, filtering/augmentation, environmental corrections, calibration and interpretation. Provide real time operational support during drilling and completion activities, ensuring accurate and timely petrophysical interpretations to guide operational decisions. Conduct model based petrophysical analyses to evaluate reservoir properties and fluid distributions across the field lifecycle. Proactively develop new and innovative approaches to enhance the efficiency of multi well workflows. Collaborate with geologists, geophysicists, engineers, and other disciplines—as well as Business Units—to ensure accurate and integrated petrophysical interpretations across conventional, unconventional, and CCS reservoirs. Perform log QA/QC, rock physics modeling, fluid substitution to support seismic studies as needed. Work with computational scientists, engineers, and geoscientists to test, deliver, and support petrophysical software tools, models, algorithms, and workflows across multiple projects globally.</t>
         </is>
       </c>
       <c r="P166" s="6" t="inlineStr">
         <is>
-          <t>Excellent communication and teamwork skills, with the ability to collaborate effectively with multidisciplinary global teams and take ownership of deliverables. Hands on experience across various stages of the field lifecycle in conventional and unconventional reservoirs with operational support, ex</t>
+          <t>Excellent communication and teamwork skills, with the ability to collaborate effectively with multidisciplinary global teams and take ownership of deliverables. Hands on experience across various stages of the field lifecycle in conventional and unconventional reservoirs with operational support, experience in cased hole log interpretation, knowledge of advanced logging measurements and data acquisition is desirable. Strong analytical and problem solving skills with the ability to interpret complex datasets. Experience with one or more integrated petrophysical analysis software suites. Coding skills and knowledge of statistical methods, machine learning, or numerical modeling are an added advantage. Proficiency in English.</t>
         </is>
       </c>
       <c r="Q166" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions experience in renewable energy, low-carbon infrastructure, carbon markets, and natural capital, which are all relevant to the clean energy and environmental sectors.</t>
+          <t>The job description does not mention any ESG/sustainability topics, climate risk, sustainable finance, carbon markets, EU Taxonomy, or other related keywords. The company's vision to lead in energy innovations that advance modern living and a net-zero future is mentioned, but it is not directly related to the job responsibilities or requirements.</t>
         </is>
       </c>
       <c r="R166" s="2" t="inlineStr"/>
@@ -15490,17 +15517,17 @@
       </c>
       <c r="O170" s="6" t="inlineStr">
         <is>
-          <t>1) Product management - Continue to build XcelGreen with the technical know how of ESG SaaS, AI Agents and ESG Regulations understanding, continue the journey from 0-1. 2) ESG Consulting - Managing ESG consulting projects, developing sustainability strategies, delivering training sessions, and fostering strong client relationships. 3) Start-up Evangelist - Grow the start-up with lean resources and budget. We are looking for 2-3 people unicorn model with AI tools &amp; resources available. The ESG Co</t>
+          <t>1) Product management - Continue to build XcelGreen with the technical know how of ESG SaaS, AI Agents and ESG Regulations understanding, continue the journey from 0-1. 2) ESG Consulting - Managing ESG consulting projects, developing sustainability strategies, delivering training sessions, and fostering strong client relationships. 3) Start-up Evangelist - Grow the start-up with lean resources and budget. We are looking for 2-3 people unicorn model with AI tools &amp; resources available. The ESG Consulting Lead will also lead cross-functional teams and stay updated on industry trends and standards to provide best-in-class recommendations.</t>
         </is>
       </c>
       <c r="P170" s="6" t="inlineStr">
         <is>
-          <t>ESG SaaS, AI Agents, ESG Regulations, AI tools, Strong Analytical Skills, Excellent Communication skills, Proficiency in Training programs and workshops, Ability to lead and collaborate with cross-functional teams, Knowledge of ESG frameworks, global reporting standards, and regional compliance regu</t>
+          <t>ESG SaaS, AI Agents, ESG Regulations, AI tools, Strong Analytical Skills, Excellent Communication skills, Proficiency in Training programs and workshops, Ability to lead and collaborate with cross-functional teams, Knowledge of ESG frameworks, global reporting standards, and regional compliance regulations</t>
         </is>
       </c>
       <c r="Q170" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[general_esg] The job description mentions ESG strategy, ESG consulting, sustainability strategies, and ESG frameworks, which are all relevant to the general ESG profile. The role also involves working with ESG data, tracking carbon performance, and evaluating regulatory requirements, which further </t>
+          <t>The job description mentions ESG strategy, ESG consulting, sustainability strategies, and ESG frameworks, which are all relevant to the general ESG profile. The role also involves working with ESG data, tracking carbon performance, and evaluating regulatory requirements, which further supports this classification.</t>
         </is>
       </c>
       <c r="R170" s="2" t="inlineStr">
@@ -15587,7 +15614,7 @@
       </c>
       <c r="O171" s="6" t="inlineStr">
         <is>
-          <t>There are a variety of tasks and responsibilities you might be assigned however some common tasks that many of our graduate engineers perform include: * Assisting senior engineers with projects: You may be asked to help with research, testing, or other tasks related to ongoing projects. * Learning Wood processes and procedures: It's important to understand how Wood operates and the specific procedures and protocols you'll be expected to follow. * Collaborating with cross-functional teams: Engine</t>
+          <t>There are a variety of tasks and responsibilities you might be assigned however some common tasks that many of our graduate engineers perform include: * Assisting senior engineers with projects: You may be asked to help with research, testing, or other tasks related to ongoing projects. * Learning Wood processes and procedures: It's important to understand how Wood operates and the specific procedures and protocols you'll be expected to follow. * Collaborating with cross-functional teams: Engineering projects often involve multiple disciplines and teams, so you may need to work with colleagues from other areas of Wood. * Debugging and troubleshooting: If a product or system isn't working as intended, you may be called upon to help identify and resolve the problem. * Preparing reports and presentations: You may need to communicate your findings and progress to your team, manager, or other stakeholders. * Continuously improving your skills and knowledge: The engineering field is constantly evolving, so it's important to stay up to date with new developments and best practices.</t>
         </is>
       </c>
       <c r="P171" s="6" t="inlineStr">
@@ -15597,7 +15624,7 @@
       </c>
       <c r="Q171" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions 'renewables and emerging energy sectors' and 'decarbonisation, hydrogen, carbon capture and storage, renewables advisory', which are related to clean energy and environmental sustainability.</t>
+          <t>The job description mentions 'renewables and emerging energy sectors' and 'decarbonisation, hydrogen, carbon capture and storage, renewables advisory', which are related to clean energy and environmental sustainability.</t>
         </is>
       </c>
       <c r="R171" s="2" t="inlineStr">
@@ -15684,7 +15711,7 @@
       </c>
       <c r="O172" s="6" t="inlineStr">
         <is>
-          <t>The role is responsible for the development, innovation, and ongoing improvement of algorithms to optimize the trading of energy assets into the Australian National Electricity Market (NEM), with a particular focus on battery energy storage systems (BESS) and renewable assets. The role involves acting as a technical lead in an "agentic coding" environment, leveraging cutting-edge AI coding assistants to rapidly build, test, and deploy sophisticated mathematical forecasters, optimizers, and autom</t>
+          <t>The role is responsible for the development, innovation, and ongoing improvement of algorithms to optimize the trading of energy assets into the Australian National Electricity Market (NEM), with a particular focus on battery energy storage systems (BESS) and renewable assets. The role involves acting as a technical lead in an "agentic coding" environment, leveraging cutting-edge AI coding assistants to rapidly build, test, and deploy sophisticated mathematical forecasters, optimizers, and automated bidders. Client communication and marketing are critical aspects of this role, including acting as an evangelist for the technology and communicating algorithm and asset performance through various channels.</t>
         </is>
       </c>
       <c r="P172" s="6" t="inlineStr">
@@ -15694,7 +15721,7 @@
       </c>
       <c r="Q172" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions renewable energy, battery energy storage systems (BESS), and energy trading, which are all related to clean energy. The company also mentions climate goals and renewable energy integration, indicating a focus on environmental sustainability.</t>
+          <t>The job description mentions renewable energy, battery energy storage systems (BESS), and energy trading, which are all related to clean energy. The company also mentions climate goals and renewable energy integration, indicating a focus on environmental sustainability.</t>
         </is>
       </c>
       <c r="R172" s="2" t="inlineStr">
@@ -15878,7 +15905,7 @@
       </c>
       <c r="O174" s="6" t="inlineStr">
         <is>
-          <t>Own the technical design and evolution of Lendable’s data and analytics platform, collaborate closely with Lendable’s Senior Director of Analytics and Lendable’s CEO to define Lendable’s long-term data strategy and roadmap, drive AI adoption across Lendable, iterate and quickly prototype solutions for technology challenges, oversee Lendable’s strategy for identifying and quickly integrating new data sources, ensure that Lendable’s data is rational, well-structured, labeled, standardized, and ult</t>
+          <t>Own the technical design and evolution of Lendable’s data and analytics platform, collaborate closely with Lendable’s Senior Director of Analytics and Lendable’s CEO to define Lendable’s long-term data strategy and roadmap, drive AI adoption across Lendable, iterate and quickly prototype solutions for technology challenges, oversee Lendable’s strategy for identifying and quickly integrating new data sources, ensure that Lendable’s data is rational, well-structured, labeled, standardized, and ultimately understandable, establish the systems, controls, and accountability structures that guarantee the accuracy, speed, and trustworthiness of all data used across Lendable, manage a team and oversee the processes and systems to ensure that Lendable’s integrations with borrower systems are accurate, resilient, and continuously verified.</t>
         </is>
       </c>
       <c r="P174" s="6" t="inlineStr">
@@ -15888,7 +15915,7 @@
       </c>
       <c r="Q174" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions 'responsible investment' and 'sustainable investment team', indicating a focus on ESG investing and sustainable finance.</t>
+          <t>The job description does not explicitly mention ESG, sustainability, or environmental topics, and the focus is on data strategy, architecture, and governance in a financial services context.</t>
         </is>
       </c>
       <c r="R174" s="2" t="inlineStr">
@@ -15969,7 +15996,7 @@
       </c>
       <c r="Q175" s="6" t="inlineStr">
         <is>
-          <t>[climate_risk] Job title contains 'Climate', indicating a strong focus on climate-related work</t>
+          <t>Job title contains 'Climate', indicating a strong focus on climate-related work</t>
         </is>
       </c>
       <c r="R175" s="2" t="inlineStr"/>
@@ -16053,7 +16080,9 @@
 * Facilitating transactions in line with both client and Amsterdam Renewable Markets' standards. 
 * Striving to meet and exceed annual sales targets, ensuring sustained growth. 
 * Engaging in trading activities involving renewable power certificates, carbon offsets, among others. 
-* Daily interactions with team clients, expertly m</t>
+* Daily interactions with team clients, expertly managing existing portfolios while simultaneously expanding the client base. 
+* Continuously monitoring environmental commodities market shifts and proactively aiding Amsterdam Renewable Markets' growth. 
+* Innovating commodity deal structures that satisfy both client and company objectives.</t>
         </is>
       </c>
       <c r="P176" s="6" t="inlineStr">
@@ -16063,7 +16092,7 @@
       </c>
       <c r="Q176" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions environmental commodities, renewable energy markets, carbon offsets, and reducing carbon footprints, which are all related to clean energy and environmental sustainability.</t>
+          <t>The job description mentions environmental commodities, renewable energy markets, carbon offsets, and reducing carbon footprints, which are all related to clean energy and environmental sustainability.</t>
         </is>
       </c>
       <c r="R176" s="2" t="inlineStr">
@@ -16146,7 +16175,7 @@
       </c>
       <c r="O177" s="6" t="inlineStr">
         <is>
-          <t>You will support the New Market Certification team with general project work and tasks, including revision of PCFs, preparing presentation and reports, general research tasks, research of emission factors and development of Excel-based PCF calculations. You will support research activities for different areas related to sustainability certifications and PCFs, including topics such as, biogenic materials and renewable energy. You will support the team in preparing presentations and slides for tra</t>
+          <t>You will support the New Market Certification team with general project work and tasks, including revision of PCFs, preparing presentation and reports, general research tasks, research of emission factors and development of Excel-based PCF calculations. You will support research activities for different areas related to sustainability certifications and PCFs, including topics such as, biogenic materials and renewable energy. You will support the team in preparing presentations and slides for trainings or customer communications. You will support the team in communication with different internal and external stakeholders.</t>
         </is>
       </c>
       <c r="P177" s="6" t="inlineStr">
@@ -16156,7 +16185,7 @@
       </c>
       <c r="Q177" s="6" t="inlineStr">
         <is>
-          <t>[carbon_markets] The job description mentions carbon footprint certification, product carbon footprints, life cycle assessment, and sustainability certification, which are all related to carbon markets and emissions trading.</t>
+          <t>The job description mentions carbon footprint certification, product carbon footprints, life cycle assessment, and sustainability certification, which are all related to carbon markets and emissions trading.</t>
         </is>
       </c>
       <c r="R177" s="2" t="inlineStr">
@@ -16243,7 +16272,7 @@
       </c>
       <c r="O178" s="6" t="inlineStr">
         <is>
-          <t>Be willing to be a pioneer and have an interest in ESG &amp; Corporate Governance. Curiosity and passion for researching and highlighting recent trends in sustainability (environmental and social issues), business ethics, regulations and sustainable development goals. Use analytical tools and intellect to question, challenge and evaluate current practices in the evolving area of ESG. Highlight key sustainability / ESG issues that are material to an industry / company. Prepare sector research reports</t>
+          <t>Be willing to be a pioneer and have an interest in ESG &amp; Corporate Governance. Curiosity and passion for researching and highlighting recent trends in sustainability (environmental and social issues), business ethics, regulations and sustainable development goals. Use analytical tools and intellect to question, challenge and evaluate current practices in the evolving area of ESG. Highlight key sustainability / ESG issues that are material to an industry / company. Prepare sector research reports and rank companies based on their sustainability disclosures, performance and qualitative factors. Travel to meet with the company management to understand the company s overall sustainability strategy and progress. Able to vote for proxy voting for all the resolutions for portfolio companies. Prepare database of Proxy Voting, Stewardship Code, SFDR</t>
         </is>
       </c>
       <c r="P178" s="6" t="inlineStr">
@@ -16253,7 +16282,7 @@
       </c>
       <c r="Q178" s="6" t="inlineStr">
         <is>
-          <t>[sustainable_finance] The job description mentions ESG research, sustainability disclosures, performance, and qualitative factors, which are key aspects of sustainable finance. Additionally, the mention of SFDR (Sustainable Finance Disclosure Regulation) further supports this classification.</t>
+          <t>The job description mentions ESG research, sustainability disclosures, performance, and qualitative factors, which are key aspects of sustainable finance. Additionally, the mention of SFDR (Sustainable Finance Disclosure Regulation) further supports this classification.</t>
         </is>
       </c>
       <c r="R178" s="2" t="inlineStr">
@@ -16336,17 +16365,17 @@
       </c>
       <c r="O179" s="6" t="inlineStr">
         <is>
-          <t>Within our Energy Advisory capability, we advise clients on the challenges and opportunities regarding decarbonisation/net zero issues specifically in relation to requirements for delivering the global energy transition. This includes decentralised low carbon generation, innovation in technologies and energy sources, as well as policy and regulatory support. The successful applicant shall also have strong knowledge of the broader water industry in terms of growth and challenges to decarbonisatio</t>
+          <t>Within our Energy Advisory capability, we advise clients on the challenges and opportunities regarding decarbonisation/net zero issues specifically in relation to requirements for delivering the global energy transition. This includes decentralised low carbon generation, innovation in technologies and energy sources, as well as policy and regulatory support. The successful applicant shall also have strong knowledge of the broader water industry in terms of growth and challenges to decarbonisation, with knowledge on how to support our clients in developing decarbonisation strategies and business case assessment applying energy resources and demands, with a drive to also build-up the water network in the Energy Advisory team. Key Responsibilities Include: Lead technical delivery and being accountable for key tasks and quality data outputs through project reviewer role, Engaging with a range of stakeholders at all levels, Maintaining knowledge of energy/carbon policy developments, energy markets and wider energy/sustainability issues, Key inputs with respect to energy in the development or review of engineering design through-out project life-cycle, Energy technology options or energy efficiency appraisals and life cycle cost analysis, Energy management, energy efficiency, asset reviews and audit surveys, energy demand modelling and preparing low carbon energy solutions that are either led by reconfiguring existing operations at sites or developing new strategies, Mentoring and training colleagues in aspects of the water and energy sectors.</t>
         </is>
       </c>
       <c r="P179" s="6" t="inlineStr">
         <is>
-          <t>Strong verbal and written communication skills, excellent quantitative and problem-solving skills, ability to lead bid preparation, deliver to tight timescales, be technically accurate and to manage a number of schemes simultaneously, Strong project management skills, Knowledge of current and antici</t>
+          <t>Strong verbal and written communication skills, excellent quantitative and problem-solving skills, ability to lead bid preparation, deliver to tight timescales, be technically accurate and to manage a number of schemes simultaneously, Strong project management skills, Knowledge of current and anticipated environmental, carbon and energy policy and legislation, Ability to develop standard engineering deliverables such as heat and mass balances</t>
         </is>
       </c>
       <c r="Q179" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] The job description mentions decarbonisation, net zero, low carbon generation, energy efficiency, and energy transition, which are all relevant to the clean energy adjacent profile. Additionally, the job requires experience working on water sector energy projects and knowledg</t>
+          <t>The job description mentions decarbonisation, net zero, low carbon generation, energy efficiency, and energy transition, which are all relevant to the clean energy adjacent profile. Additionally, the job requires experience working on water sector energy projects and knowledge of the broader water industry in terms of growth and challenges to decarbonisation.</t>
         </is>
       </c>
       <c r="R179" s="2" t="inlineStr">
@@ -16427,7 +16456,7 @@
       </c>
       <c r="Q180" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] Job title contains 'Renewables', indicating a connection to renewable energy</t>
+          <t>Job title contains 'Renewables', indicating a connection to renewable energy</t>
         </is>
       </c>
       <c r="R180" s="2" t="inlineStr"/>
@@ -16504,7 +16533,7 @@
       </c>
       <c r="Q181" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] Job title contains 'Circular Bioeconomy', indicating a focus on environmental science and circular economy, which aligns with the clean energy adjacent profile.</t>
+          <t>Job title contains 'Circular Bioeconomy', indicating a focus on environmental science and circular economy, which aligns with the clean energy adjacent profile.</t>
         </is>
       </c>
       <c r="R181" s="2" t="inlineStr"/>
@@ -16581,7 +16610,7 @@
       </c>
       <c r="Q182" s="6" t="inlineStr">
         <is>
-          <t>[clean_energy_adjacent] Job title contains 'Wind', indicating a focus on renewable energy</t>
+          <t>Job title contains 'Wind', indicating a focus on renewable energy</t>
         </is>
       </c>
       <c r="R182" s="2" t="inlineStr"/>

--- a/src/jobs/jobs.xlsx
+++ b/src/jobs/jobs.xlsx
@@ -766,7 +766,7 @@
           <t>The job description mentions climate risk assessment, physical risk assessments, transition risk assessments, climate scenario analysis, and climate resilience strategy development, which are all key aspects of climate risk management.</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -855,7 +855,7 @@
           <t>The job description explicitly mentions climate change, decarbonization, emissions assessments, and climate risk assessment, which are all key aspects of the climate risk profile.</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/company/wsp-in-canada</t>
         </is>
@@ -952,7 +952,7 @@
           <t>The job description mentions climate change, climate risk, decarbonisation, GHG accounting, and climate scenario analysis, which are all relevant to the climate risk profile.</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -1049,7 +1049,7 @@
           <t>The job description mentions climate change services, GHG accounting, climate risk, decarbonisation approaches, and climate strategy, which are all relevant to the climate risk profile.</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -1146,7 +1146,7 @@
           <t>The job description mentions sustainable finance, ESG investments, green bonds, and climate-focused fundraising, which are all key aspects of sustainable finance.</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -1243,7 +1243,7 @@
           <t>The job description mentions climate change mitigation and adaptation, energy efficiency, and renewable energy solutions, which are related to environmental sustainability and clean energy. Although it does not directly fit into the other categories, it is adjacent to clean energy and has some relevance to environmental sustainability.</t>
         </is>
       </c>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="R8" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -1332,7 +1332,7 @@
           <t>The role involves ESG disclosure program, sustainability reporting, climate risk, and emissions reporting, which are all key aspects of ESG strategy and corporate sustainability.</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="R9" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/csenergyqld</t>
         </is>
@@ -1425,7 +1425,7 @@
           <t>The job description mentions climate change, climate risk, decarbonisation, and greenhouse gas emissions, which are all relevant to the climate risk profile. The role also involves working with clients to develop and implement sustainability strategies, and assisting them in navigating complex regulatory environments, which further supports the climate risk profile classification</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="R10" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -1514,7 +1514,7 @@
           <t>The job description mentions ESG oriented investing, impact investing, and sustainable finance, which are key aspects of the sustainable finance profile. The role also involves working with a renewable energy investment firm, which further supports this classification.</t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="R11" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/h9-technical-recruitment-ltd</t>
         </is>
@@ -1692,7 +1692,7 @@
           <t>The job description mentions ESG (Environmental, Social &amp; Governance) and sustainability, which are key aspects of general ESG profile. The job also involves climate risk assessment, greenhouse gas accounting, and decarbonization initiatives, which are all relevant to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="R13" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -1785,7 +1785,7 @@
           <t>The job description mentions climate-related risks, GHG emissions, and climate impact analysis, which are all relevant to the climate risk profile.</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="R14" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/iss-sustainabilitysolutions</t>
         </is>
@@ -1882,7 +1882,7 @@
           <t>The job description mentions sustainable finance, ESG risk, climate risk, and regulatory frameworks such as EU Taxonomy and CSRD, indicating a strong focus on sustainable finance and ESG topics.</t>
         </is>
       </c>
-      <c r="R15" s="2" t="inlineStr">
+      <c r="R15" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/natwest-group</t>
         </is>
@@ -1979,7 +1979,7 @@
           <t>The job description mentions specific EU regulations such as EU Taxonomy, CSRD, and SFDR, which are key components of the EU Taxonomy and SFDR profile. The role also involves ESG reporting, analysis, and due diligence, which are closely related to the EU Taxonomy and SFDR regulations.</t>
         </is>
       </c>
-      <c r="R16" s="2" t="inlineStr">
+      <c r="R16" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/pwc-india</t>
         </is>
@@ -2068,7 +2068,7 @@
           <t>This role contributes to accelerating the transition to a low-carbon economy by supporting climate markets and sustainable project development.</t>
         </is>
       </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="R17" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/cyan-ventures</t>
         </is>
@@ -2161,7 +2161,7 @@
           <t>The job description mentions ESG (Environmental, Social &amp; Governance) policies and implementing environmental and sustainability measures across office operations, which aligns with the general ESG profile.</t>
         </is>
       </c>
-      <c r="R18" s="2" t="inlineStr">
+      <c r="R18" s="3" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/munich-re</t>
         </is>
@@ -2250,7 +2250,7 @@
           <t>The job description mentions carbon credits, carbon markets, and environmental policy, indicating a strong focus on carbon markets. The role involves selling carbon credit offerings and staying on top of developments in carbon markets, standards, and regulation.</t>
         </is>
       </c>
-      <c r="R19" s="2" t="inlineStr">
+      <c r="R19" s="3" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/klim-eco</t>
         </is>
@@ -2335,7 +2335,7 @@
           <t>This role focuses on supporting companies with their environmental, social, and governance (ESG) strategies and transition to sustainable practices.</t>
         </is>
       </c>
-      <c r="R20" s="2" t="inlineStr">
+      <c r="R20" s="3" t="inlineStr">
         <is>
           <t>https://it.linkedin.com/company/joinrs-international</t>
         </is>
@@ -2428,7 +2428,7 @@
           <t>The job description mentions working on sustainability, energy transition, and environmental challenges, which aligns with the clean energy adjacent profile. The role involves developing data-driven solutions for complex challenges in safety, sustainability, and energy transition, and the company is involved in navigating the transition to a decarbonized and more sustainable energy future.</t>
         </is>
       </c>
-      <c r="R21" s="2" t="inlineStr">
+      <c r="R21" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/pollination-climate-advisory-investment</t>
         </is>
@@ -2521,7 +2521,7 @@
           <t>The job description mentions various environmental and sustainability-related roles such as Rock Engineering, Geotechnical Engineering, Hydrogeology, Contaminated Areas, Acoustics, and Environmental Management - Sustainability &amp; Climate Change, which are all related to environmental science, conservation, and sustainability, making it a good fit for the clean_energy_adjacent profile</t>
         </is>
       </c>
-      <c r="R22" s="2" t="inlineStr">
+      <c r="R22" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/pwc-india</t>
         </is>
@@ -2618,7 +2618,7 @@
           <t>The job description mentions EU Corporate Sustainability Reporting Directive (CSRD), EU Taxonomy, and other ESG-related regulations, indicating a strong focus on EU Taxonomy and SFDR compliance.</t>
         </is>
       </c>
-      <c r="R23" s="2" t="inlineStr">
+      <c r="R23" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/citi</t>
         </is>
@@ -2715,7 +2715,7 @@
           <t>The job description mentions integrating sustainability principles into mergers and acquisitions, private equity transactions, and corporate strategies, which is related to sustainable finance. It also mentions ESG ratings methodology, ESG policies, and ESG due diligences, which are key aspects of sustainable finance.</t>
         </is>
       </c>
-      <c r="R24" s="2" t="inlineStr">
+      <c r="R24" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/pwc-india</t>
         </is>
@@ -2817,7 +2817,7 @@
           <t>The job description explicitly mentions climate risk, climate-related risks, climate strategy development, and climate disclosure frameworks, which are all key aspects of climate risk assessment and management.</t>
         </is>
       </c>
-      <c r="R25" s="2" t="inlineStr">
+      <c r="R25" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/enemix</t>
         </is>
@@ -2916,7 +2916,7 @@
           <t>The job description mentions GHG accounting, decarbonization, climate risk modeling, and assessment, which are all related to climate risk. The job also mentions following IPCC Guidelines and GHG Protocol, and applying PCAF guidelines, which are all relevant to climate risk management.</t>
         </is>
       </c>
-      <c r="R26" s="2" t="inlineStr">
+      <c r="R26" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/wsp-consultants-india-ltd</t>
         </is>
@@ -3013,7 +3013,7 @@
           <t>The job description mentions climate risk, GHG emissions, and Net Zero reports, which are key indicators of a climate risk profile.</t>
         </is>
       </c>
-      <c r="R27" s="2" t="inlineStr">
+      <c r="R27" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/the-nature-conservancy</t>
         </is>
@@ -3102,7 +3102,7 @@
           <t>The role involves leading client engagements and managing senior team members in the Sustainability Reporting Advisory practice, with a focus on interpreting and applying sustainability reporting requirements, and providing technical leadership and market profile.</t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr">
+      <c r="R28" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/grant-thornton-australia</t>
         </is>
@@ -3191,7 +3191,7 @@
           <t>The job description explicitly mentions carbon markets, Article 6, and carbon crediting, which are all key concepts in the carbon markets profile.</t>
         </is>
       </c>
-      <c r="R29" s="2" t="inlineStr">
+      <c r="R29" s="3" t="inlineStr">
         <is>
           <t>https://kr.linkedin.com/company/global-green-growth-institute</t>
         </is>
@@ -3284,7 +3284,7 @@
           <t>The job description explicitly mentions climate risk, physical risk, and climate modelling, which are key aspects of the climate risk profile.</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
+      <c r="R30" s="3" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/munich-re</t>
         </is>
@@ -3377,7 +3377,7 @@
           <t>The job description explicitly mentions climate risk, decarbonisation, and retrofit, which are key aspects of climate risk management. The role requires the candidate to have experience in real estate sustainability, decarbonisation, and ESG advisory, which are all relevant to climate risk.</t>
         </is>
       </c>
-      <c r="R31" s="2" t="inlineStr">
+      <c r="R31" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/mapmortar</t>
         </is>
@@ -3547,7 +3547,7 @@
           <t>The job description mentions experience in renewable energy, decarbonisation, infrastructure or nature-based projects as highly desirable, and the company is a specialist climate change investment and advisory firm, indicating a strong focus on environmental sustainability and clean energy.</t>
         </is>
       </c>
-      <c r="R33" s="2" t="inlineStr">
+      <c r="R33" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/pollination-climate-advisory-investment</t>
         </is>
@@ -3640,7 +3640,7 @@
           <t>The job description mentions voluntary carbon markets, carbon credits, CORSIA, and compliance-linked carbon markets, which are all related to carbon markets. The role involves originating and executing transactions across voluntary carbon markets, and the ideal candidate should have experience in carbon markets, environmental commodities, energy trading, or a related field.</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr">
+      <c r="R34" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/cfpenergy</t>
         </is>
@@ -3737,7 +3737,7 @@
           <t>The job description mentions research on riverine carbon dynamics and fluxes in the Congo Basin, which is related to environmental science and the management of natural resources, fitting the clean_energy_adjacent profile.</t>
         </is>
       </c>
-      <c r="R35" s="2" t="inlineStr">
+      <c r="R35" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/strategen-environmental-consultants</t>
         </is>
@@ -3930,7 +3930,7 @@
           <t>The job description mentions social responsibility, sustainability, human rights, and responsible sourcing, which are all relevant to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
-      <c r="R37" s="2" t="inlineStr">
+      <c r="R37" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/enemix</t>
         </is>
@@ -4027,7 +4027,7 @@
           <t>The job description mentions carbon project development, Verra VCS methodologies, and carbon credits, which are all related to carbon markets.</t>
         </is>
       </c>
-      <c r="R38" s="2" t="inlineStr">
+      <c r="R38" s="3" t="inlineStr">
         <is>
           <t>https://ee.linkedin.com/company/arbonics</t>
         </is>
@@ -4120,7 +4120,7 @@
           <t>The job description mentions 'impact technology', 'driving global climate action', 'ESG experts', and 'sustainability' in the context of financial products, indicating a strong focus on sustainable finance and ESG investing.</t>
         </is>
       </c>
-      <c r="R39" s="2" t="inlineStr">
+      <c r="R39" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/the-nature-conservancy</t>
         </is>
@@ -4217,7 +4217,7 @@
           <t>The job description mentions ESG, sustainability, climate change risk assessments, and social and human rights impact assessments, which are all related to environmental, social, and governance topics.</t>
         </is>
       </c>
-      <c r="R40" s="2" t="inlineStr">
+      <c r="R40" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/strategen-environmental-consultants</t>
         </is>
@@ -4314,7 +4314,7 @@
           <t>The job description mentions sustainable finance, ESG risk, climate-related financial risk, and European sustainability regulatory frameworks, indicating a strong focus on sustainable finance and ESG topics.</t>
         </is>
       </c>
-      <c r="R41" s="2" t="inlineStr">
+      <c r="R41" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/adani-electricity</t>
         </is>
@@ -4407,7 +4407,7 @@
           <t>The job involves implementation of robust climate action/sustainability strategies, oversight of scheme design and planning processes, and knowledge of key issues and management strategies associated with climate change/sustainability, environmental, social and governance factors on large scale building projects.</t>
         </is>
       </c>
-      <c r="R42" s="2" t="inlineStr">
+      <c r="R42" s="3" t="inlineStr">
         <is>
           <t>https://ie.linkedin.com/company/fk-international</t>
         </is>
@@ -4500,7 +4500,7 @@
           <t>The role involves working on flood risk and hydrology projects, including flood mapping, flood risk assessments, and water environment EIA and consenting studies, which are related to environmental science and water management.</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr">
+      <c r="R43" s="3" t="inlineStr">
         <is>
           <t>https://nl.linkedin.com/company/arcadis</t>
         </is>
@@ -4593,7 +4593,7 @@
           <t>The job description explicitly mentions flood risk modelling and mapping, climate resilience, and the strategic use of data and evidence to inform policy and investment decisions, which are all key aspects of climate risk management.</t>
         </is>
       </c>
-      <c r="R44" s="2" t="inlineStr">
+      <c r="R44" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/environment-agency</t>
         </is>
@@ -4686,7 +4686,7 @@
           <t>The job involves working on energy transition and decarbonization projects in the Oil &amp; Gas industry, which is related to the clean energy and environmental science fields.</t>
         </is>
       </c>
-      <c r="R45" s="2" t="inlineStr">
+      <c r="R45" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/boston-consulting-group</t>
         </is>
@@ -4779,7 +4779,7 @@
           <t>The job description mentions energy transition, renewable energy, electricity market design, and other related topics, indicating a strong focus on clean energy and adjacent fields.</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr">
+      <c r="R46" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/deloitte</t>
         </is>
@@ -4868,7 +4868,7 @@
           <t>The job description mentions research on the impact, effectiveness and coordination of transition policies, climate scenario analysis, and the financial and/or macroeconomic consequences of climate change and the green transition.</t>
         </is>
       </c>
-      <c r="R47" s="2" t="inlineStr">
+      <c r="R47" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/school/london-school-of-economics/</t>
         </is>
@@ -4957,7 +4957,7 @@
           <t>The job involves quantifying catastrophe risk, working with catastrophe models, and analyzing natural disasters, which are all directly related to climate risk.</t>
         </is>
       </c>
-      <c r="R48" s="2" t="inlineStr">
+      <c r="R48" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/gallagher-re</t>
         </is>
@@ -5046,7 +5046,7 @@
           <t>The job involves working on a project related to water resilience and climate change, which is closely related to the clean energy and environmental science domain.</t>
         </is>
       </c>
-      <c r="R49" s="2" t="inlineStr">
+      <c r="R49" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/school/iihsin/</t>
         </is>
@@ -5143,7 +5143,7 @@
           <t>This role focuses on supporting resource projects in the mining and minerals processing industry, contributing to decarbonization efforts and net-zero emissions targets.</t>
         </is>
       </c>
-      <c r="R50" s="2" t="inlineStr">
+      <c r="R50" s="3" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/company/bnp-paribas</t>
         </is>
@@ -5390,7 +5390,7 @@
           <t>The job description mentions climate risk assessments, scenario analysis, and sustainability reporting, which are key aspects of climate risk management. The role also involves providing advice on sustainability and climate-related financial reporting, which is a critical component of climate risk management.</t>
         </is>
       </c>
-      <c r="R53" s="2" t="inlineStr">
+      <c r="R53" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/bdo-in-australia</t>
         </is>
@@ -5483,7 +5483,7 @@
           <t>The job description mentions ESG data expertise, EU taxonomy, climate risk, and sustainable investing, which are all relevant to the ESG profile.</t>
         </is>
       </c>
-      <c r="R54" s="2" t="inlineStr">
+      <c r="R54" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/morningstar</t>
         </is>
@@ -5580,7 +5580,7 @@
           <t>The job description mentions natural catastrophes, climate change, and geospatial risk assessment, which are all relevant to climate risk, The company is also working to make the world more resilient, which implies a focus on managing and mitigating climate-related risks</t>
         </is>
       </c>
-      <c r="R55" s="2" t="inlineStr">
+      <c r="R55" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/bendigo-advertiser</t>
         </is>
@@ -5673,7 +5673,7 @@
           <t>The job description mentions climate risk, climate resilience, and climate change, indicating a strong focus on climate-related issues. The role involves working on Nature-Based Solutions for Climate Resilience, which is a key area of focus for climate risk management.</t>
         </is>
       </c>
-      <c r="R56" s="2" t="inlineStr">
+      <c r="R56" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/neural-alpha</t>
         </is>
@@ -5766,7 +5766,7 @@
           <t>The job description is focused on renewable energy projects, utility-scale solar, wind, battery storage, and hybrid energy projects, which are all related to clean energy and environmental science.</t>
         </is>
       </c>
-      <c r="R57" s="2" t="inlineStr">
+      <c r="R57" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/enemix</t>
         </is>
@@ -5863,7 +5863,7 @@
           <t>The job description mentions experience with sustainable finance and ESG trends, and the role involves working with non-grant instruments financed by the Green Climate Fund, which is related to sustainable finance and impact investing.</t>
         </is>
       </c>
-      <c r="R58" s="2" t="inlineStr">
+      <c r="R58" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/the-nature-conservancy</t>
         </is>
@@ -5956,7 +5956,7 @@
           <t>The job description mentions working on environmental projects, including renewable energy, and conducting ecological field surveys, which aligns with the clean energy adjacent profile.</t>
         </is>
       </c>
-      <c r="R59" s="2" t="inlineStr">
+      <c r="R59" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/grayedgeconsultingllc</t>
         </is>
@@ -6053,7 +6053,7 @@
           <t>The job description mentions ESG reporting, climate risk analysis, corporate ESG disclosures, and decarbonization strategies, which are all relevant to environmental, social, and governance topics, indicating a strong fit for the general_esg profile.</t>
         </is>
       </c>
-      <c r="R60" s="2" t="inlineStr">
+      <c r="R60" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/hatch-team</t>
         </is>
@@ -6150,7 +6150,7 @@
           <t>The job description mentions ESG Advisory, Sustainability Reporting, GHG Accounting, Decarbonization Roadmap, and Sustainable Financing, which are all related to environmental, social, and governance topics, indicating a strong fit with the general ESG profile.</t>
         </is>
       </c>
-      <c r="R61" s="2" t="inlineStr">
+      <c r="R61" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/adani-electricity</t>
         </is>
@@ -6239,7 +6239,7 @@
           <t>The role involves ESG compliance initiatives, sustainability reporting, climate risk, and emissions reduction initiatives, which are all core aspects of ESG strategy and corporate sustainability.</t>
         </is>
       </c>
-      <c r="R62" s="2" t="inlineStr">
+      <c r="R62" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/moir-group</t>
         </is>
@@ -6332,7 +6332,7 @@
           <t>The job description mentions climate risk assessments, climate resilience analysis, and environmental analysis, which are all key aspects of climate risk management.</t>
         </is>
       </c>
-      <c r="R63" s="2" t="inlineStr">
+      <c r="R63" s="3" t="inlineStr">
         <is>
           <t>https://gr.linkedin.com/company/pwc-greece</t>
         </is>
@@ -6425,7 +6425,7 @@
           <t>The job involves catastrophe modelling, risk management, and analysis of natural disasters, which are directly related to climate risk.</t>
         </is>
       </c>
-      <c r="R64" s="2" t="inlineStr">
+      <c r="R64" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/gallagher-re</t>
         </is>
@@ -6518,7 +6518,7 @@
           <t>The job description mentions supporting climate risk assessments focused on physical threats (e.g., extreme weather, flooding, wildfires) to critical sites and infrastructure, and leading segment mitigation strategies that enhance long-term operational resilience.</t>
         </is>
       </c>
-      <c r="R65" s="2" t="inlineStr">
+      <c r="R65" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/gehealthcare</t>
         </is>
@@ -6607,7 +6607,7 @@
           <t>The job description mentions climate risk as one of the areas of knowledge and activities for the Factor Analytics Product Specialist team, indicating that the role involves work in this domain.</t>
         </is>
       </c>
-      <c r="R66" s="2" t="inlineStr">
+      <c r="R66" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/msci-inc</t>
         </is>
@@ -6696,7 +6696,7 @@
           <t>The job involves working on urban themes such as climate change, risk and sustainability, and the company provides services related to human settlements and urbanisation.</t>
         </is>
       </c>
-      <c r="R67" s="2" t="inlineStr">
+      <c r="R67" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/school/iihsin/</t>
         </is>
@@ -6789,7 +6789,7 @@
           <t>The job description mentions sustainability, climate change, and ESG frameworks, indicating a focus on environmental, social, and governance topics.</t>
         </is>
       </c>
-      <c r="R68" s="2" t="inlineStr">
+      <c r="R68" s="3" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/company/bnp-paribas</t>
         </is>
@@ -6882,7 +6882,7 @@
           <t>The job description mentions 'sustainable finance', 'ESG risks', and 'investment risk analysis', which are key terms related to sustainable finance and ESG investing.</t>
         </is>
       </c>
-      <c r="R69" s="2" t="inlineStr">
+      <c r="R69" s="3" t="inlineStr">
         <is>
           <t>https://ee.linkedin.com/company/luminor-group</t>
         </is>
@@ -6975,7 +6975,7 @@
           <t>The job description mentions cleantech, circularity, materials, chemistry, and industrial transition, which are all related to environmental science and sustainability, and specifically mentions the development of low-CO₂ construction materials, plastics recycling, and bio-economy, which are all relevant to the clean energy and environmental science fields</t>
         </is>
       </c>
-      <c r="R70" s="2" t="inlineStr">
+      <c r="R70" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -7068,7 +7068,7 @@
           <t>The job description mentions sustainability, social and behaviour change, and environmental footprint, which are all related to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
-      <c r="R71" s="2" t="inlineStr">
+      <c r="R71" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/icemarkets</t>
         </is>
@@ -7161,7 +7161,7 @@
           <t>The job description mentions 'sustainable finance &amp; ESG instruments' and the company is committed to fast-tracking the shift to a carbon neutral world, indicating a focus on sustainable finance and ESG concepts.</t>
         </is>
       </c>
-      <c r="R72" s="2" t="inlineStr">
+      <c r="R72" s="3" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/company/societegenerale-corporate-and-investment-banking</t>
         </is>
@@ -7258,7 +7258,7 @@
           <t>The job description mentions ESG factors, sustainable finance, green finance, and sustainable investment initiatives, which are all relevant to the sustainable finance profile.</t>
         </is>
       </c>
-      <c r="R73" s="2" t="inlineStr">
+      <c r="R73" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/asthalaxmi</t>
         </is>
@@ -7351,7 +7351,7 @@
           <t>The job description mentions natural capital investments, forestry, and sustainable forestry investments, which are related to environmental science and conservation, fitting the clean_energy_adjacent profile.</t>
         </is>
       </c>
-      <c r="R74" s="2" t="inlineStr">
+      <c r="R74" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/varaha-carbontech</t>
         </is>
@@ -7444,7 +7444,7 @@
           <t>The job description mentions integrating sustainability considerations into financial analysis, and the role is part of the Corporate &amp; Sustainability Advisory team, indicating a focus on sustainable finance.</t>
         </is>
       </c>
-      <c r="R75" s="2" t="inlineStr">
+      <c r="R75" s="3" t="inlineStr">
         <is>
           <t>https://dk.linkedin.com/company/danskebank</t>
         </is>
@@ -7541,7 +7541,7 @@
           <t>The job description mentions GHG Footprint, LCA, ESG, BRSR Reporting, and GHG reduction schemes, which are directly related to climate risk and transition risk.</t>
         </is>
       </c>
-      <c r="R76" s="2" t="inlineStr">
+      <c r="R76" s="3" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/company/bnp-paribas</t>
         </is>
@@ -7626,7 +7626,7 @@
           <t>The job description explicitly mentions carbon markets, tokenized carbon credits, and secondary trading, indicating a strong focus on carbon markets</t>
         </is>
       </c>
-      <c r="R77" s="2" t="inlineStr">
+      <c r="R77" s="3" t="inlineStr">
         <is>
           <t>https://ng.linkedin.com/company/petrodatycs</t>
         </is>
@@ -7711,7 +7711,7 @@
           <t>The job involves implementing sustainability reporting frameworks (CSRD-style), integrating ESG data into risk and reporting processes and aligning sustainability with data architecture, which indicates that the role directly involves ESG work as a significant part.</t>
         </is>
       </c>
-      <c r="R78" s="2" t="inlineStr">
+      <c r="R78" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/deloitte</t>
         </is>
@@ -7804,7 +7804,7 @@
           <t>The job description mentions working on probabilistic flood hazard models, climate change analytics, and scenario modeling, which are all directly related to climate risk.</t>
         </is>
       </c>
-      <c r="R79" s="2" t="inlineStr">
+      <c r="R79" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/verisk-analytics</t>
         </is>
@@ -7893,7 +7893,7 @@
           <t>The job involves conducting in-depth ESG research, performing climate risk and transition assessments, and producing high-quality research notes and reports integrating ESG insights.</t>
         </is>
       </c>
-      <c r="R80" s="2" t="inlineStr">
+      <c r="R80" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/crisil</t>
         </is>
@@ -7982,7 +7982,7 @@
           <t>The job involves working on water resilience, infrastructure planning, and development planning, which are related to environmental science and water management, making it a good fit for the clean_energy_adjacent profile.</t>
         </is>
       </c>
-      <c r="R81" s="2" t="inlineStr">
+      <c r="R81" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/school/iihsin/</t>
         </is>
@@ -8071,7 +8071,7 @@
           <t>The job involves working on water resilience, climate-proofing water and sanitation systems, and implementing public infrastructure projects, which are related to renewable energy, environmental science, and conservation.</t>
         </is>
       </c>
-      <c r="R82" s="2" t="inlineStr">
+      <c r="R82" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/school/iihsin/</t>
         </is>
@@ -8164,7 +8164,7 @@
           <t>[clean_energy_adjacent] The job description mentions natural capital investments, forestry, and sustainable forestry investments, which are related to environmental science and conservation, fitting the clean_energy_adjacent profile.</t>
         </is>
       </c>
-      <c r="R83" s="2" t="inlineStr">
+      <c r="R83" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/cityofkingston</t>
         </is>
@@ -8257,7 +8257,7 @@
           <t>The job description does not explicitly mention ESG, sustainability, or climate-related responsibilities, requirements, or skills, despite the company being involved in climate change innovation and green energy. The role is focused on HR project and transformation leadership, which does not fit into any of the specified ESG/sustainability profiles.</t>
         </is>
       </c>
-      <c r="R84" s="2" t="inlineStr">
+      <c r="R84" s="3" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/company/onetoone-corporate-finance</t>
         </is>
@@ -8350,7 +8350,7 @@
           <t>The job description does not explicitly mention ESG, sustainability, or environmental topics in the context of the role's responsibilities, requirements, or skills, except for a general mention of 'sustainable' in the company description which is not directly related to the job's responsibilities</t>
         </is>
       </c>
-      <c r="R85" s="2" t="inlineStr">
+      <c r="R85" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/standard-chartered-india</t>
         </is>
@@ -8439,7 +8439,7 @@
           <t>The job description does not mention any specific ESG, sustainability, or climate-related responsibilities, requirements, or skills that would fit into one of the provided profiles.</t>
         </is>
       </c>
-      <c r="R86" s="2" t="inlineStr">
+      <c r="R86" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/hackajob</t>
         </is>
@@ -8536,7 +8536,7 @@
           <t>The job description mentions environmental and social performance management, impact assessment, and due diligence, which are all relevant to ESG strategy and corporate sustainability. The role also involves providing advice on environmental and social performance to mining clients, which aligns with the general ESG profile.</t>
         </is>
       </c>
-      <c r="R87" s="2" t="inlineStr">
+      <c r="R87" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/bendigo-advertiser</t>
         </is>
@@ -8629,7 +8629,7 @@
           <t>The job description mentions experience selling into financial institutions, asset managers or large corporates, and knowledge of ESG, sustainable finance, or regulatory frameworks such as ISSB, CSRD, EU Taxonomy, SFDR and TNFD, indicating a strong connection to sustainable finance.</t>
         </is>
       </c>
-      <c r="R88" s="2" t="inlineStr">
+      <c r="R88" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/neural-alpha</t>
         </is>
@@ -8722,7 +8722,7 @@
           <t>The job description is related to the conservation of forests, reduction of deforestation, and promotion of sustainable development, which are all relevant to the clean energy and environmental conservation sector.</t>
         </is>
       </c>
-      <c r="R89" s="2" t="inlineStr">
+      <c r="R89" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/undpcareers</t>
         </is>
@@ -8815,7 +8815,7 @@
           <t>The job description does not explicitly mention ESG, sustainability, or environmental topics in the context of the role's responsibilities, requirements, or skills, other than the company's general sustainability policy which is not directly related to the job.</t>
         </is>
       </c>
-      <c r="R90" s="2" t="inlineStr">
+      <c r="R90" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/grayedgeconsultingllc</t>
         </is>
@@ -8908,7 +8908,7 @@
           <t>The job description mentions climate change, disaster risk management, and climate resilience, which are all related to climate risk. The role also involves working with the Global Facility for Disaster Reduction and Recovery (GFDRR), which is a global partnership that helps low- and middle-income countries better understand and reduce their vulnerability to natural hazards and climate change.</t>
         </is>
       </c>
-      <c r="R91" s="2" t="inlineStr">
+      <c r="R91" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/hatch-team</t>
         </is>
@@ -9001,7 +9001,7 @@
           <t>The job description mentions 'sustainable finance workgroup' and 'climate risk modelling for financial institutions', indicating a focus on sustainable finance and ESG considerations in the context of financial risk management.</t>
         </is>
       </c>
-      <c r="R92" s="2" t="inlineStr">
+      <c r="R92" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/adani-electricity</t>
         </is>
@@ -9096,7 +9096,7 @@
           <t>The job description mentions 'atmospheric perils', 'extreme weather events', 'changing climate', and 'climate modelling' which are all related to climate risk.</t>
         </is>
       </c>
-      <c r="R93" s="2" t="inlineStr">
+      <c r="R93" s="3" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/company/bnpparibascorporateandinstitutionalbanking</t>
         </is>
@@ -9189,7 +9189,7 @@
           <t>The job description mentions 'sustainable democracy', 'climate change and democracy', and 'democracy and inclusion', which are related to environmental, social, and governance topics, but the primary focus is on democratic institutions and processes, making it a better fit for the general ESG profile.</t>
         </is>
       </c>
-      <c r="R94" s="2" t="inlineStr">
+      <c r="R94" s="3" t="inlineStr">
         <is>
           <t>https://ch.linkedin.com/company/novartis</t>
         </is>
@@ -9286,7 +9286,7 @@
           <t>The job description mentions 'Sustainability Climate Change and Risk', 'Energy Transition &amp; Markets', 'Decarbonisation and Physical Risk Strategy', which are all related to climate risk and sustainability.</t>
         </is>
       </c>
-      <c r="R95" s="2" t="inlineStr">
+      <c r="R95" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/aurecon</t>
         </is>
@@ -9383,7 +9383,7 @@
           <t>The job description mentions climate change, climate resilience, disaster risk reduction, and climate‑inclusive development, which are all relevant to the climate risk profile</t>
         </is>
       </c>
-      <c r="R96" s="2" t="inlineStr">
+      <c r="R96" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/tetra-tech</t>
         </is>
@@ -9480,7 +9480,7 @@
           <t>The job description mentions 'climate risk' as one of the risk domains, and also mentions 'experience in climatic risk space preferably in the areas of stress testing /scenario designing', indicating that the role involves working with climate-related risks.</t>
         </is>
       </c>
-      <c r="R97" s="2" t="inlineStr">
+      <c r="R97" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -9577,7 +9577,7 @@
           <t>The job description mentions ESG data, ESG reporting standards, and ESG product users, which are all relevant to sustainable finance. The role also involves working with ESG content, regulatory frameworks, and capital markets, which are key aspects of sustainable finance.</t>
         </is>
       </c>
-      <c r="R98" s="2" t="inlineStr">
+      <c r="R98" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/icemarkets</t>
         </is>
@@ -9674,7 +9674,7 @@
           <t>The job description mentions 'sustainable buildings', 'climate-related innovation', 'net zero carbon emissions', and 'energy management', which are related to environmental sustainability and clean energy. Although the primary focus is on building technologies, the company's commitment to sustainability and reducing carbon emissions aligns with the clean energy adjacent profile.</t>
         </is>
       </c>
-      <c r="R99" s="2" t="inlineStr">
+      <c r="R99" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/woodplc</t>
         </is>
@@ -9771,7 +9771,7 @@
           <t>The job description mentions renewable energy, solar, wind, and BESS, which are all related to clean energy. The company's focus on transitioning to a carbon-free and sustainable economy also supports this classification.</t>
         </is>
       </c>
-      <c r="R100" s="2" t="inlineStr">
+      <c r="R100" s="3" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/company/bnp-paribas</t>
         </is>
@@ -9868,7 +9868,7 @@
           <t>The job description mentions performing Climate Risk-related assessments, including end to end measurement of physical and transition risk, scenario analysis, and supporting disclosure requirements, which directly relates to climate risk management.</t>
         </is>
       </c>
-      <c r="R101" s="2" t="inlineStr">
+      <c r="R101" s="3" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/company/societegenerale-corporate-and-investment-banking</t>
         </is>
@@ -9961,7 +9961,7 @@
           <t>The job description mentions environmental and social performance management, impact assessment, due diligence, and management systems, which are all relevant to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
-      <c r="R102" s="2" t="inlineStr">
+      <c r="R102" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/slr-consulting</t>
         </is>
@@ -10069,7 +10069,7 @@
           <t>The job description mentions ESG (Environnement, Social, Gouvernance), finance durable, SFDR, and MIFID ESG, which are all related to sustainable finance. The job also involves promoting and developing ESG offers, ensuring compliance with regulations, and contributing to the development of sustainable finance within a private bank.</t>
         </is>
       </c>
-      <c r="R103" s="2" t="inlineStr">
+      <c r="R103" s="3" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/company/bnp-paribas</t>
         </is>
@@ -10162,7 +10162,7 @@
           <t>The job description mentions sustainable investment, hedging, and financing solutions, ESG criteria, sustainable finance market studies, and ESG advisory team, which are all related to sustainable finance</t>
         </is>
       </c>
-      <c r="R104" s="2" t="inlineStr">
+      <c r="R104" s="3" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/company/societegenerale-corporate-and-investment-banking</t>
         </is>
@@ -10259,7 +10259,7 @@
           <t>The job description mentions carbon credits, carbon markets, and sustainable development, which are key aspects of the carbon markets profile. The company's focus on generating carbon credits and working on agroforestry projects also aligns with this profile.</t>
         </is>
       </c>
-      <c r="R105" s="2" t="inlineStr">
+      <c r="R105" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/asthalaxmi</t>
         </is>
@@ -10352,7 +10352,7 @@
           <t>The job description mentions carbon removal, carbon markets, climate tech, and high integrity carbon markets, indicating a strong focus on carbon markets and climate-related topics.</t>
         </is>
       </c>
-      <c r="R106" s="2" t="inlineStr">
+      <c r="R106" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/varaha-carbontech</t>
         </is>
@@ -10445,7 +10445,7 @@
           <t>The job description mentions developing catastrophe models for the insurance and reinsurance industries, simulating extreme weather events consistent with a changing climate, and advancing the development of atmospheric peril models, which are all related to climate risk</t>
         </is>
       </c>
-      <c r="R107" s="2" t="inlineStr">
+      <c r="R107" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/verisk-analytics</t>
         </is>
@@ -10542,7 +10542,7 @@
           <t>The job description mentions climate risk, carbon emissions tracking, carbon footprint assessments, GHG assessment, climate risk advisory, and decarbonization strategies, which are all relevant to climate risk. Additionally, the job requires experience in climate change, environmental issues, and sustainability, and proficiency in ESG frameworks such as TCFD, which further supports the classification as climate_risk.</t>
         </is>
       </c>
-      <c r="R108" s="2" t="inlineStr">
+      <c r="R108" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/adani-electricity</t>
         </is>
@@ -10635,7 +10635,7 @@
           <t>The job description mentions working on the energy transition, becoming climate neutral, and improving forecasting accuracy and transparency across commodity value streams, which are all related to renewable energy and environmental science</t>
         </is>
       </c>
-      <c r="R109" s="2" t="inlineStr">
+      <c r="R109" s="3" t="inlineStr">
         <is>
           <t>https://nl.linkedin.com/company/eneco</t>
         </is>
@@ -10728,7 +10728,7 @@
           <t>The role involves developing and implementing HSE standards, policies, and procedures, ensuring compliance with legislation and regulations, and driving a culture of continuous improvement. While the role does mention climate change and carbon reduction, it is primarily focused on health, safety, and environmental management, which falls under the general ESG profile.</t>
         </is>
       </c>
-      <c r="R110" s="2" t="inlineStr">
+      <c r="R110" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/pure-data-centres-group</t>
         </is>
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr"/>
-      <c r="R111" s="2" t="inlineStr">
+      <c r="R111" s="3" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/munich-re</t>
         </is>
@@ -10910,7 +10910,7 @@
           <t>The role involves advancing NORCAP’s work on peace, democracy, human rights, rule of law, and credible elections across global and national systems, which aligns with the general ESG profile.</t>
         </is>
       </c>
-      <c r="R112" s="2" t="inlineStr">
+      <c r="R112" s="3" t="inlineStr">
         <is>
           <t>https://no.linkedin.com/company/norwegian-refugee-council</t>
         </is>
@@ -10999,7 +10999,7 @@
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr"/>
-      <c r="R113" s="2" t="inlineStr">
+      <c r="R113" s="3" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/munich-re</t>
         </is>
@@ -11088,7 +11088,7 @@
           <t>The job description mentions working on real-world systems balancing risk, resilience, compliance and sustainability, and applying AI and data to global, nature-based challenges that matter, which are directly related to climate risk.</t>
         </is>
       </c>
-      <c r="R114" s="2" t="inlineStr">
+      <c r="R114" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/treefera</t>
         </is>
@@ -11181,7 +11181,7 @@
           <t>The job description mentions sustainability strategy, sustainable business models, and sustainability-related financial disclosure, which are all relevant to ESG. The role also involves advising on climate- and nature-related financial analysis and embedding sustainability into business operations.</t>
         </is>
       </c>
-      <c r="R115" s="2" t="inlineStr">
+      <c r="R115" s="3" t="inlineStr">
         <is>
           <t>https://nz.linkedin.com/company/kpmg-new-zealand</t>
         </is>
@@ -11274,7 +11274,7 @@
           <t>[general_esg] The job description mentions environmental and social performance management, impact assessment, due diligence, and management systems, which are all relevant to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
-      <c r="R116" s="2" t="inlineStr">
+      <c r="R116" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/verisk-analytics</t>
         </is>
@@ -11463,7 +11463,7 @@
           <t>The job description mentions ESG/sustainability reporting solutions, non-financial disclosures, and regulatory reporting, which are all relevant to environmental, social, and governance topics.</t>
         </is>
       </c>
-      <c r="R118" s="2" t="inlineStr">
+      <c r="R118" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/grayedgeconsultingllc</t>
         </is>
@@ -11556,7 +11556,7 @@
           <t>The job description mentions risk assessment integrato (ERM- Enterprise Risk Management) with reference to ESG and climate change, which indicates a focus on climate risk management.</t>
         </is>
       </c>
-      <c r="R119" s="2" t="inlineStr">
+      <c r="R119" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/hatch-team</t>
         </is>
@@ -11649,7 +11649,7 @@
           <t>The job description mentions 'rischi C&amp;E (Climate &amp; Environmental)' which indicates that the role involves climate-related risk management, making it a good fit for the climate_risk profile.</t>
         </is>
       </c>
-      <c r="R120" s="2" t="inlineStr">
+      <c r="R120" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/adani-electricity</t>
         </is>
@@ -11819,7 +11819,7 @@
           <t>The job description mentions 'sustainable spaces', 'sustainability', and 'environment' in the context of sport and recreation spaces, which aligns with the clean energy adjacent profile, The role also involves managing projects related to sport and recreation facilities, playgrounds, and foreshore infrastructure, which are related to environmental and conservation topics</t>
         </is>
       </c>
-      <c r="R122" s="2" t="inlineStr">
+      <c r="R122" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/cityofkingston</t>
         </is>
@@ -11912,7 +11912,7 @@
           <t>The job description mentions Renewable Energy/Power-to-X, Life Sciences, and other sectors related to environmental sustainability, which aligns with the clean energy adjacent profile.</t>
         </is>
       </c>
-      <c r="R123" s="2" t="inlineStr">
+      <c r="R123" s="3" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/company/onetoone-corporate-finance</t>
         </is>
@@ -12005,7 +12005,7 @@
           <t>The job description mentions 'Climate Risk Stress Tests: A new area of analysis focussing on the impact of climate change on Banking industry', which indicates that the role is related to climate risk and its impact on the banking industry.</t>
         </is>
       </c>
-      <c r="R124" s="2" t="inlineStr">
+      <c r="R124" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/standard-chartered-india</t>
         </is>
@@ -12098,7 +12098,7 @@
           <t>The job description mentions developing catastrophe models for extreme weather events, simulating the full distribution of possible events consistent with a changing climate, and improving the accuracy of representing atmospheric perils, which are all related to climate risk.</t>
         </is>
       </c>
-      <c r="R125" s="2" t="inlineStr">
+      <c r="R125" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/hackajob</t>
         </is>
@@ -12195,7 +12195,7 @@
           <t>The job description mentions Climate Risk Modelling experience, which is a key aspect of climate risk management, and the role involves validating IRB models that consider environmental policies, indicating a focus on climate-related risks.</t>
         </is>
       </c>
-      <c r="R126" s="2" t="inlineStr">
+      <c r="R126" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/hatch-team</t>
         </is>
@@ -12288,7 +12288,7 @@
           <t>The job description mentions environmental remediation, excavation, waste management, and site remediation, which are related to environmental science and conservation, fitting the clean_energy_adjacent profile.</t>
         </is>
       </c>
-      <c r="R127" s="2" t="inlineStr">
+      <c r="R127" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/renew</t>
         </is>
@@ -12381,7 +12381,7 @@
           <t>The job description does not mention any specific ESG/sustainability topics, such as climate risk, sustainable finance, or carbon markets. The mention of 'sustainability' is in the context of the company's general commitment to sustainability, but it is not directly related to the job role or responsibilities.</t>
         </is>
       </c>
-      <c r="R128" s="2" t="inlineStr">
+      <c r="R128" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/hsbc</t>
         </is>
@@ -12474,7 +12474,7 @@
           <t>The job description mentions environmental science, contaminated land assessment, environmental monitoring, and remediation consulting, which are related to environmental science and conservation, fitting the clean_energy_adjacent profile.</t>
         </is>
       </c>
-      <c r="R129" s="2" t="inlineStr">
+      <c r="R129" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/egis-anz</t>
         </is>
@@ -12567,7 +12567,7 @@
           <t>The job description mentions environmental science, contaminated land assessment, environmental monitoring, and remediation consulting, which are related to environmental science and conservation, fitting the clean_energy_adjacent profile.</t>
         </is>
       </c>
-      <c r="R130" s="2" t="inlineStr">
+      <c r="R130" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/mercer</t>
         </is>
@@ -12660,7 +12660,7 @@
           <t>The job description mentions experience in sustainable finance, including climate, development, and/or nature finance, and the company's mission is to address global development challenges through strategic investments that promote sustainable and inclusive economic growth.</t>
         </is>
       </c>
-      <c r="R131" s="2" t="inlineStr">
+      <c r="R131" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/british-international-investment</t>
         </is>
@@ -12753,7 +12753,7 @@
           <t>The job description mentions impact investing, ESG, and sustainable development, which are key concepts in sustainable finance. The company's mission and values also align with sustainable finance principles.</t>
         </is>
       </c>
-      <c r="R132" s="2" t="inlineStr">
+      <c r="R132" s="3" t="inlineStr">
         <is>
           <t>https://nl.linkedin.com/company/triple-jump-bv</t>
         </is>
@@ -12842,7 +12842,7 @@
           <t>The job description mentions 'sustainable financing solutions', 'sustainable finance', 'ESG standards', 'sustainable loan and bond transactions', and 'transition to a greener economy', which are all related to sustainable finance and ESG investing.</t>
         </is>
       </c>
-      <c r="R133" s="2" t="inlineStr">
+      <c r="R133" s="3" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/company/bnpparibascorporateandinstitutionalbanking</t>
         </is>
@@ -12939,7 +12939,7 @@
           <t>The job description mentions sustainable finance, ESG standards, green economy, and sustainable financing solutions, which are all key aspects of sustainable finance</t>
         </is>
       </c>
-      <c r="R134" s="2" t="inlineStr">
+      <c r="R134" s="3" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/company/bnpparibascorporateandinstitutionalbanking</t>
         </is>
@@ -13036,7 +13036,7 @@
           <t>The job description does not explicitly mention ESG, sustainability, climate risk, or other related topics. The focus is on credit risk management and analytics, which is a traditional finance role.</t>
         </is>
       </c>
-      <c r="R135" s="2" t="inlineStr">
+      <c r="R135" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/morgan-stanley</t>
         </is>
@@ -13218,7 +13218,7 @@
           <t>The job description mentions 'climate risk analytics and advisory' as one of the areas of support, indicating that the role involves working with climate-related risks, which aligns with the climate_risk profile.</t>
         </is>
       </c>
-      <c r="R137" s="2" t="inlineStr">
+      <c r="R137" s="3" t="inlineStr">
         <is>
           <t>https://ch.linkedin.com/company/novartis</t>
         </is>
@@ -13315,7 +13315,7 @@
           <t>The job description mentions 'climate risks' under the 'Emerging Risks' section, indicating that the role involves identifying, measuring, and monitoring climate-related risks.</t>
         </is>
       </c>
-      <c r="R138" s="2" t="inlineStr">
+      <c r="R138" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/woodplc</t>
         </is>
@@ -13412,7 +13412,7 @@
           <t>The job description mentions climate risk, stress testing, and scenario designing, which are relevant to climate risk management. Additionally, the job requires experience in climatic risk space, which further supports the classification as climate_risk.</t>
         </is>
       </c>
-      <c r="R139" s="2" t="inlineStr">
+      <c r="R139" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/energy-one</t>
         </is>
@@ -13509,7 +13509,7 @@
           <t>The job description mentions ESG ratings, ESG reporting, sustainability strategy, and risk management, which are all key aspects of general ESG. Additionally, the job requires expertise in ESG and sustainability, and involves working with ESG data and standards, further supporting the classification as general ESG.</t>
         </is>
       </c>
-      <c r="R140" s="2" t="inlineStr">
+      <c r="R140" s="3" t="inlineStr">
         <is>
           <t>https://lu.linkedin.com/company/morgan-philips-group</t>
         </is>
@@ -13598,7 +13598,7 @@
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr"/>
-      <c r="R141" s="2" t="inlineStr">
+      <c r="R141" s="3" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/munich-re</t>
         </is>
@@ -13691,7 +13691,7 @@
           <t>The job involves innovation management, community building, and collaboration with business units to identify and develop new innovation ideas and projects, which are related to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
-      <c r="R142" s="2" t="inlineStr">
+      <c r="R142" s="3" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/munich-re</t>
         </is>
@@ -13780,7 +13780,7 @@
           <t>The job description mentions climate-related risk, and the role involves designing and implementing practical risk frameworks, resilience strategies, and climate risk solutions that are aligned to business strategy.</t>
         </is>
       </c>
-      <c r="R143" s="2" t="inlineStr">
+      <c r="R143" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/aon</t>
         </is>
@@ -13869,7 +13869,7 @@
           <t>The role involves supporting the development of investment-ready projects, engaging with development finance institutions and impact investors, and providing advisory support to member states on improving regulatory and policy frameworks to enhance investment readiness, all of which are related to sustainable finance.</t>
         </is>
       </c>
-      <c r="R144" s="2" t="inlineStr">
+      <c r="R144" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/commonwealth-secretariat</t>
         </is>
@@ -13958,7 +13958,7 @@
           <t>The job description explicitly mentions the role of economic and fiscal authorities in supporting the climate transition and managing the associated fiscal and economic impacts, which is a key aspect of climate risk.</t>
         </is>
       </c>
-      <c r="R145" s="2" t="inlineStr">
+      <c r="R145" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/school/london-school-of-economics/</t>
         </is>
@@ -14051,7 +14051,7 @@
           <t>The job description mentions 'Sustainable Finance' team, 'strategie ESG', 'conformità normativa', 'integrazione dei fattori di sostenibilità', and 'evoluzione sostenibile del settore finanziario', which are all related to sustainable finance and ESG investing.</t>
         </is>
       </c>
-      <c r="R146" s="2" t="inlineStr">
+      <c r="R146" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/great-barrier-reef-marine-park-authority</t>
         </is>
@@ -14144,7 +14144,7 @@
           <t>The job description mentions ESG risk analysis, TCFD, ESRS, and EU taxonomy, which are all related to environmental, social, and governance topics, indicating a relevance to general ESG strategy and corporate sustainability.</t>
         </is>
       </c>
-      <c r="R147" s="2" t="inlineStr">
+      <c r="R147" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/macquariegroup</t>
         </is>
@@ -14237,7 +14237,7 @@
           <t>The job description mentions ESG, duurzaam beleggen, impactbeleggen, and klimaatanalyses, which are all related to sustainable finance. The company also works with institutionele beleggers and pensioenfondsen to implement ESG in their beleggingsportefeuille.</t>
         </is>
       </c>
-      <c r="R148" s="2" t="inlineStr">
+      <c r="R148" s="3" t="inlineStr">
         <is>
           <t>https://nl.linkedin.com/company/afs-energy</t>
         </is>
@@ -14330,7 +14330,7 @@
           <t>Although the company mentions dedication to sustainability, it is in the context of a broader company culture and not directly related to the job responsibilities, requirements, or skills. The job itself is focused on clinical trials and cell therapy, which does not fit into any of the specified ESG/sustainability profiles.</t>
         </is>
       </c>
-      <c r="R149" s="2" t="inlineStr">
+      <c r="R149" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/clydeco</t>
         </is>
@@ -14419,7 +14419,7 @@
           <t>The job description does not mention any ESG/sustainability topics, climate change, or environmental issues. The focus is on labor relations, law, and human resources, which does not fit any of the provided profiles.</t>
         </is>
       </c>
-      <c r="R150" s="2" t="inlineStr">
+      <c r="R150" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/altm-new-and-renewable-energy-pvt-ltd</t>
         </is>
@@ -14597,7 +14597,7 @@
           <t>The job description mentions 'sustainable finance practices' as one of the current and emerging trends and regulatory priorities, indicating a connection to ESG investing and sustainable finance.</t>
         </is>
       </c>
-      <c r="R152" s="2" t="inlineStr">
+      <c r="R152" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/blackrock</t>
         </is>
@@ -14694,7 +14694,7 @@
           <t>The job description mentions experience with maritime emissions regulations, carbon markets, and environmental financial products, which are all relevant to the carbon markets profile.</t>
         </is>
       </c>
-      <c r="R153" s="2" t="inlineStr">
+      <c r="R153" s="3" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/company/wilhelmsen-ship-management</t>
         </is>
@@ -14787,7 +14787,7 @@
           <t>The job description mentions renewable energy solutions, heat pumps, solar panels, and carbon-neutral home energy solutions, which are all related to clean energy and environmental sustainability.</t>
         </is>
       </c>
-      <c r="R154" s="2" t="inlineStr">
+      <c r="R154" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/hometree-uk</t>
         </is>
@@ -14880,7 +14880,7 @@
           <t>The job description mentions sustainable development, climate change, and environmental health, which are related to ESG topics. Although the role is not explicitly focused on ESG, the context suggests that it may involve working on projects that contribute to sustainable development and environmental health.</t>
         </is>
       </c>
-      <c r="R155" s="2" t="inlineStr">
+      <c r="R155" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/undpcareers</t>
         </is>
@@ -14973,7 +14973,7 @@
           <t>The job description mentions working with teams focused on sustainable development, climate change, and environmental issues, which aligns with the general ESG profile.</t>
         </is>
       </c>
-      <c r="R156" s="2" t="inlineStr">
+      <c r="R156" s="3" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/company/international-institute-for-sustainable-development</t>
         </is>
@@ -15070,7 +15070,7 @@
           <t>The job description mentions working with clients on transformation in Government with a focus on Sustainability, Climate Change, and Environment, indicating a role related to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
-      <c r="R157" s="2" t="inlineStr">
+      <c r="R157" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/assochamforindia</t>
         </is>
@@ -15163,7 +15163,7 @@
           <t>The job description mentions biotechnology, biosecurity, and technology policy, which are related to environmental science and sustainability. Although the job is not directly focused on renewable energy or conservation, it is adjacent to the clean energy field and involves research and policy development related to emerging technologies.</t>
         </is>
       </c>
-      <c r="R158" s="2" t="inlineStr">
+      <c r="R158" s="3" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/company/bnp-paribas</t>
         </is>
@@ -15260,7 +15260,7 @@
           <t>The job description mentions experience with ESG (Environmental, Social, and Governance) and sustainability services, specifically Climate Change and Sustainability Services (CCaSS), which indicates a connection to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
-      <c r="R159" s="2" t="inlineStr">
+      <c r="R159" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/varaha-carbontech</t>
         </is>
@@ -15357,7 +15357,7 @@
           <t>The job description mentions 'zprávy o udržitelnosti' (sustainability reports) and 'ESG odborníků' (ESG experts), indicating a connection to environmental, social, and governance topics.</t>
         </is>
       </c>
-      <c r="R160" s="2" t="inlineStr">
+      <c r="R160" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/verisk-analytics</t>
         </is>
@@ -15539,7 +15539,7 @@
           <t>The job description mentions ESG, sustainability, and translating sustainability data into financial impact, which are key aspects of sustainable finance.</t>
         </is>
       </c>
-      <c r="R162" s="2" t="inlineStr">
+      <c r="R162" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/grayedgeconsultingllc</t>
         </is>
@@ -15632,7 +15632,7 @@
           <t>The job description mentions 'Sustainable Finance' as one of the possible rotation areas, and also mentions 'supporting the transition to a climate-resilient future by structuring loans so they are linked to achieving environmental, social and corporate governance (ESG) outcomes', indicating a focus on sustainable finance and ESG.</t>
         </is>
       </c>
-      <c r="R163" s="2" t="inlineStr">
+      <c r="R163" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/hatch-team</t>
         </is>
@@ -15725,7 +15725,7 @@
           <t>The job description mentions smart metering projects, energy infrastructure, and power transmission, which are related to renewable energy and environmental science, making it a clean energy adjacent profile.</t>
         </is>
       </c>
-      <c r="R164" s="2" t="inlineStr">
+      <c r="R164" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/adani-electricity</t>
         </is>
@@ -16126,7 +16126,7 @@
           <t>The job description mentions ESG, sustainability, and supply chain concepts, indicating a focus on environmental, social, and governance topics. The role involves working with ESG data, conducting QA reviews, and supporting the improvement of internal processes, which aligns with the general ESG profile.</t>
         </is>
       </c>
-      <c r="R169" s="2" t="inlineStr">
+      <c r="R169" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/purpose-bureau</t>
         </is>
@@ -16219,7 +16219,7 @@
           <t>The job description mentions supporting the transition to a climate-resilient future, structuring loans linked to achieving environmental, social and corporate governance (ESG) outcomes, and a rotation in Sustainable Finance.</t>
         </is>
       </c>
-      <c r="R170" s="2" t="inlineStr">
+      <c r="R170" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/hatch-team</t>
         </is>
@@ -16316,7 +16316,7 @@
           <t>The job description mentions biochar, carbon removal, regenerative agriculture, and climate-tech, which are all related to renewable energy and environmental science. The company's mission is to improve soil health and remove carbon from the atmosphere, which aligns with the clean energy adjacent profile.</t>
         </is>
       </c>
-      <c r="R171" s="2" t="inlineStr">
+      <c r="R171" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/black-bull-biochar-ltd</t>
         </is>
@@ -16413,7 +16413,7 @@
           <t>The job description mentions utility-scale solar projects in Southern Africa, renewable energy transactions, and impact investment funds, which are all related to clean energy and environmental sustainability.</t>
         </is>
       </c>
-      <c r="R172" s="2" t="inlineStr">
+      <c r="R172" s="3" t="inlineStr">
         <is>
           <t>https://ch.linkedin.com/company/bd-consulting-investment</t>
         </is>
@@ -16498,7 +16498,7 @@
           <t>The job description mentions decarbonisation, energy transition, and climate-related topics, indicating a strong focus on climate risk.</t>
         </is>
       </c>
-      <c r="R173" s="2" t="inlineStr">
+      <c r="R173" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/showcase/ieefa-asia-pacific/</t>
         </is>
@@ -16587,7 +16587,7 @@
           <t>The role is in the Energy &amp; Utilities business unit, which provides services and solutions for water, electricity, and other essential networks and infrastructure. The job description mentions water infrastructure projects and sustainable long-term growth, indicating a connection to the clean energy and environmental sector.</t>
         </is>
       </c>
-      <c r="R174" s="2" t="inlineStr">
+      <c r="R174" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/downer</t>
         </is>
@@ -16672,7 +16672,7 @@
           <t>The role is focused on the Carbon markets, requires experience in Carbon trading, and involves working closely with traders to build a market position.</t>
         </is>
       </c>
-      <c r="R175" s="2" t="inlineStr">
+      <c r="R175" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/rjc-group-ltd</t>
         </is>
@@ -16761,7 +16761,7 @@
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr"/>
-      <c r="R176" s="2" t="inlineStr">
+      <c r="R176" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/fourtwothree</t>
         </is>
@@ -16850,7 +16850,7 @@
           <t>The role involves delivering research-based analysis on the relationships between natural capital, finance, resilience and economic development, and leading the development of a major programme of applied research to better understand how natural capital and resilience can be embedded within economic and financial decision-making.</t>
         </is>
       </c>
-      <c r="R177" s="2" t="inlineStr">
+      <c r="R177" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/school/london-school-of-economics/</t>
         </is>
@@ -16939,7 +16939,7 @@
           <t>The job description explicitly mentions renewable energy, solar, wind, storage, and hybrid renewable energy projects, which are all related to clean energy.</t>
         </is>
       </c>
-      <c r="R178" s="2" t="inlineStr">
+      <c r="R178" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/enfinity</t>
         </is>
@@ -17028,7 +17028,7 @@
           <t>The job involves climate risk quantitative assessments and working with mathematical or statistical models involving risk and uncertainty, which aligns with the climate risk profile.</t>
         </is>
       </c>
-      <c r="R179" s="2" t="inlineStr">
+      <c r="R179" s="3" t="inlineStr">
         <is>
           <t>https://nz.linkedin.com/company/pwc-new-zealand</t>
         </is>
@@ -17348,7 +17348,7 @@
           <t>The job description mentions 'climate action', 'climate change', and 'climate‑related risks', indicating a strong focus on climate risk management and mitigation.</t>
         </is>
       </c>
-      <c r="R183" s="2" t="inlineStr">
+      <c r="R183" s="3" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/company/wsp-in-canada</t>
         </is>
@@ -17437,7 +17437,7 @@
           <t>The job description does not explicitly mention ESG, sustainability, climate risk, or other related topics. While the company mentions 'combat climate change' in its description, this is not directly related to the job responsibilities or requirements.</t>
         </is>
       </c>
-      <c r="R184" s="2" t="inlineStr">
+      <c r="R184" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/csenergyqld</t>
         </is>
@@ -17530,7 +17530,7 @@
           <t>The job description mentions carbon removal, carbon markets, and durable carbon removal, which are all related to carbon markets. The company, Carbonfuture, provides tools and services for carbon removal, which further supports this classification.</t>
         </is>
       </c>
-      <c r="R185" s="2" t="inlineStr">
+      <c r="R185" s="3" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/carbonfuture</t>
         </is>
@@ -17627,7 +17627,7 @@
           <t>The job description mentions 'sustainable finance' as one of the DCM products, indicating a focus on environmental, social, or governance topics.</t>
         </is>
       </c>
-      <c r="R186" s="2" t="inlineStr">
+      <c r="R186" s="3" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/company/bnpparibascorporateandinstitutionalbanking</t>
         </is>
@@ -17716,7 +17716,7 @@
           <t>The job involves geospatial analysis of maternal health indicators, which is related to environmental science and public health, and the company is involved in public health research and service delivery, which is adjacent to the clean energy and environmental science field.</t>
         </is>
       </c>
-      <c r="R187" s="2" t="inlineStr">
+      <c r="R187" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/cyan-ventures</t>
         </is>
@@ -17809,7 +17809,7 @@
           <t>The job description mentions ESG (Environmental Social Governance) risk and controls, ESG reporting, and ESG control framework, which are all related to environmental, social, and governance topics, indicating a strong fit with the general ESG profile.</t>
         </is>
       </c>
-      <c r="R188" s="2" t="inlineStr">
+      <c r="R188" s="3" t="inlineStr">
         <is>
           <t>https://ch.linkedin.com/company/novartis</t>
         </is>
@@ -17902,7 +17902,7 @@
           <t>The job description does not mention any specific ESG/sustainability topics, climate risk, sustainable finance, carbon markets, EU Taxonomy, or clean energy. The focus is on process improvements, audit delivery, and assurance services, which are not directly related to environmental, social, or governance topics.</t>
         </is>
       </c>
-      <c r="R189" s="2" t="inlineStr">
+      <c r="R189" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -17995,7 +17995,7 @@
           <t>The job description does not mention any specific ESG/sustainability topics, and the mention of 'sustainability' in the company description is in the context of general business operations, not environmental or social sustainability.</t>
         </is>
       </c>
-      <c r="R190" s="2" t="inlineStr">
+      <c r="R190" s="3" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/company/onetoone-corporate-finance</t>
         </is>
@@ -18088,7 +18088,7 @@
           <t>The job description does not mention any specific ESG/sustainability topics, climate change mitigation, or environmental sustainability. Although the company description mentions 'combat climate change', it is not directly related to the job responsibilities, requirements, or skills.</t>
         </is>
       </c>
-      <c r="R191" s="2" t="inlineStr">
+      <c r="R191" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/standard-chartered-india</t>
         </is>
@@ -18181,7 +18181,7 @@
           <t>The job description mentions climate change, disaster risk reduction, and climate resilience, which are all relevant to the climate risk profile.</t>
         </is>
       </c>
-      <c r="R192" s="2" t="inlineStr">
+      <c r="R192" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/dt-global</t>
         </is>
@@ -18270,7 +18270,7 @@
           <t>The job involves researching corporate targets relevant to sustainability and climate initiatives, identifying contacts within sustainability and ESG departments, and supporting meeting coordination around climate events, which are all related to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
-      <c r="R193" s="2" t="inlineStr">
+      <c r="R193" s="3" t="inlineStr">
         <is>
           <t>https://nl.linkedin.com/company/jobster-com</t>
         </is>
@@ -18359,7 +18359,7 @@
           <t>The role involves leading coverage of global biofuels markets, enhancing pricing methodologies, and driving new editorial opportunities in the energy transition space.</t>
         </is>
       </c>
-      <c r="R194" s="2" t="inlineStr">
+      <c r="R194" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/walker-lovell</t>
         </is>
@@ -18448,7 +18448,7 @@
           <t>The job description mentions energy solutions, renewable energy, decarbonisation of heat, energy management, and net zero carbon programme delivery, which are all related to clean energy and sustainability.</t>
         </is>
       </c>
-      <c r="R195" s="2" t="inlineStr">
+      <c r="R195" s="3" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/company/equans</t>
         </is>
@@ -18541,7 +18541,7 @@
           <t>The job description mentions working on climate finance, tracking sustainable investment trends, and supporting the transition to a low-carbon economy, which are all related to climate risk.</t>
         </is>
       </c>
-      <c r="R196" s="2" t="inlineStr">
+      <c r="R196" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/climate-policy-initiative</t>
         </is>
@@ -18634,7 +18634,7 @@
           <t>The job description mentions working on sustainability-driven assignments, international environmental and social impact assessments, and environmental and social due diligence, which are all related to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
-      <c r="R197" s="2" t="inlineStr">
+      <c r="R197" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/environment-agency</t>
         </is>
@@ -18727,7 +18727,7 @@
           <t>The job description mentions 'duurzame investeringen' (sustainable investments), 'hernieuwbare energiesystemen' (renewable energy systems), and 'energietransitie' (energy transition), which are all related to renewable energy and environmental science, fitting the clean_energy_adjacent profile.</t>
         </is>
       </c>
-      <c r="R198" s="2" t="inlineStr">
+      <c r="R198" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/boston-consulting-group</t>
         </is>
@@ -18820,7 +18820,7 @@
           <t>Job title contains 'Climate Action', indicating a strong focus on climate-related issues.</t>
         </is>
       </c>
-      <c r="R199" s="2" t="inlineStr">
+      <c r="R199" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/deloitte</t>
         </is>
@@ -18909,7 +18909,7 @@
           <t>Job title contains 'Climate Risk Analysis' indicating a strong focus on climate risk</t>
         </is>
       </c>
-      <c r="R200" s="2" t="inlineStr">
+      <c r="R200" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/school/london-school-of-economics/</t>
         </is>
@@ -19002,7 +19002,7 @@
           <t>The job description mentions reef conservation, marine and vulnerable species management, and environmental project management, which are related to renewable energy, environmental science, and conservation, making it a good fit for the clean_energy_adjacent profile.</t>
         </is>
       </c>
-      <c r="R201" s="2" t="inlineStr">
+      <c r="R201" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/great-barrier-reef-marine-park-authority</t>
         </is>
@@ -19095,7 +19095,7 @@
           <t>The job description mentions experience in Carbon markets as a plus, and the role involves providing expert advice on front line trading risks for the Gas, Power and Carbon desks, indicating a strong connection to carbon markets and emissions trading.</t>
         </is>
       </c>
-      <c r="R202" s="2" t="inlineStr">
+      <c r="R202" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/macquariegroup</t>
         </is>
@@ -19188,7 +19188,7 @@
           <t>The job description mentions 'Carbon Markets including trading dynamics related to the buy and sell side of transactions, negotiation, and other macroeconomic factors' and 'Environmental commodities', indicating a strong focus on carbon markets and environmental sustainability.</t>
         </is>
       </c>
-      <c r="R203" s="2" t="inlineStr">
+      <c r="R203" s="3" t="inlineStr">
         <is>
           <t>https://nl.linkedin.com/company/afs-energy</t>
         </is>
@@ -19288,7 +19288,7 @@
           <t>The job description mentions experience in renewable energy, low-carbon infrastructure, carbon markets, and natural capital, which are all relevant to the clean energy and environmental sectors.</t>
         </is>
       </c>
-      <c r="R204" s="2" t="inlineStr">
+      <c r="R204" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/clydeco</t>
         </is>
@@ -19381,7 +19381,7 @@
           <t>The job description mentions renewable energy development, solar, wind, and hybrid systems, which are directly related to clean energy. The company's focus on transitioning toward clean and intelligent energy systems also supports this classification.</t>
         </is>
       </c>
-      <c r="R205" s="2" t="inlineStr">
+      <c r="R205" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/altm-new-and-renewable-energy-pvt-ltd</t>
         </is>
@@ -19478,7 +19478,7 @@
           <t>The job title mentions 'Disaster Risk and Climate Resilience', indicating a focus on climate-related risks, and the company name 'All India Disaster Mitigation Institute' also suggests a connection to disaster risk and climate resilience.</t>
         </is>
       </c>
-      <c r="R206" s="2" t="inlineStr">
+      <c r="R206" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/gehealthcare</t>
         </is>
@@ -19571,7 +19571,7 @@
           <t>The job description mentions solar energy, renewable energy, and utility-scale solar energy projects, which are all related to clean energy and environmental sustainability.</t>
         </is>
       </c>
-      <c r="R207" s="2" t="inlineStr">
+      <c r="R207" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/renew</t>
         </is>
@@ -19668,7 +19668,7 @@
           <t>The job description is for a Deputy Manager-Wind Engineering role, which involves working with wind energy projects, and the company ReNew is a renewable energy company, indicating a strong connection to clean energy and environmental sustainability</t>
         </is>
       </c>
-      <c r="R208" s="2" t="inlineStr">
+      <c r="R208" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/hsbc</t>
         </is>
@@ -19761,7 +19761,7 @@
           <t>The job description mentions renewable energy, solar energy projects, and utility-scale wind energy projects, which are all related to clean energy. The company, ReNew, is also described as one of the largest renewable energy companies globally.</t>
         </is>
       </c>
-      <c r="R209" s="2" t="inlineStr">
+      <c r="R209" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/hsbc</t>
         </is>
@@ -19854,7 +19854,7 @@
           <t>The job title 'Finance Lead - Water, Environment &amp; Energy Transition' and the company's focus on sustainable solutions and infrastructure indicate a connection to environmental topics, specifically water, environment, and energy transition, which aligns with the clean energy adjacent profile.</t>
         </is>
       </c>
-      <c r="R210" s="2" t="inlineStr">
+      <c r="R210" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/egis-anz</t>
         </is>
@@ -19947,7 +19947,7 @@
           <t>The job description mentions 'responsible investment' and 'sustainable investment team', indicating a focus on ESG investing and sustainable finance.</t>
         </is>
       </c>
-      <c r="R211" s="2" t="inlineStr">
+      <c r="R211" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/mercer</t>
         </is>
@@ -20040,7 +20040,7 @@
           <t>The job description mentions renewable energy, green hydrogen, energy transition, and other related topics, which are relevant to the clean energy and environmental science fields.</t>
         </is>
       </c>
-      <c r="R212" s="2" t="inlineStr">
+      <c r="R212" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/assochamforindia</t>
         </is>
@@ -20133,7 +20133,7 @@
           <t>The job description mentions renewable energy, solar energy projects, and clean energy, which are all related to the clean energy adjacent profile. The company's mission to provide clean, safe, affordable, and sustainable energy also supports this classification.</t>
         </is>
       </c>
-      <c r="R213" s="2" t="inlineStr">
+      <c r="R213" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/renew</t>
         </is>
@@ -20230,7 +20230,7 @@
           <t>The job description mentions 'sustainable investing' and 'SFDR' which are related to sustainable finance and ESG investing. The role involves leading regulatory change initiatives within the asset management domain, which also aligns with sustainable finance.</t>
         </is>
       </c>
-      <c r="R214" s="2" t="inlineStr">
+      <c r="R214" s="3" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/company/bnpparibascorporateandinstitutionalbanking</t>
         </is>
@@ -20327,7 +20327,7 @@
           <t>The job description mentions SFDR, which is a key regulation in sustainable finance, and also mentions overseeing sustainability data integration and reporting across investment platforms, indicating a focus on ESG considerations in investment operations.</t>
         </is>
       </c>
-      <c r="R215" s="2" t="inlineStr">
+      <c r="R215" s="3" t="inlineStr">
         <is>
           <t>https://nl.linkedin.com/company/eneco</t>
         </is>
@@ -20424,7 +20424,7 @@
           <t>The job description mentions SFDR, which is a key regulation in sustainable finance, and also mentions investment restriction monitoring and compliance processes, which are relevant to ESG investing and sustainable finance.</t>
         </is>
       </c>
-      <c r="R216" s="2" t="inlineStr">
+      <c r="R216" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/pure-data-centres-group</t>
         </is>
@@ -20521,7 +20521,7 @@
           <t>The job description mentions SFDR, which is a key regulation in sustainable finance, and also mentions overseeing sustainability data integration and reporting across investment platforms, indicating a focus on ESG considerations in investment operations.</t>
         </is>
       </c>
-      <c r="R217" s="2" t="inlineStr">
+      <c r="R217" s="3" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/munich-re</t>
         </is>
@@ -20606,7 +20606,7 @@
           <t>The company specializes in activated carbon products and services for water treatment, air purification, and food &amp; beverage processes, which are related to environmental science and sustainability.</t>
         </is>
       </c>
-      <c r="R218" s="2" t="inlineStr">
+      <c r="R218" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/carbomaxde</t>
         </is>
@@ -20699,7 +20699,7 @@
           <t>The job description mentions ESG, sustainability reporting, GHG disclosures, and climate action, which are all relevant to the general ESG profile. The role involves delivering assurance services to multinational clients, supporting project managers in independent verification of GHG/ESG information, and contributing to high-quality assessments that uphold ERM CVS’s reputation as a trusted global verification body.</t>
         </is>
       </c>
-      <c r="R219" s="2" t="inlineStr">
+      <c r="R219" s="3" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/munich-re</t>
         </is>
@@ -20788,7 +20788,7 @@
           <t>[carbon_markets] The job description mentions experience in Carbon markets as a plus, and the role involves providing expert advice on front line trading risks for the Gas, Power and Carbon desks, indicating a strong connection to carbon markets and emissions trading.</t>
         </is>
       </c>
-      <c r="R220" s="2" t="inlineStr">
+      <c r="R220" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/treefera</t>
         </is>
@@ -20881,7 +20881,7 @@
           <t>The job description mentions climate-related initiatives, GHG emissions accounting, carbon modelling, and decarbonisation, which are all relevant to climate risk. The role also involves managing emissions data validation, sustainability reporting, and performance metrics, which are critical components of climate risk management.</t>
         </is>
       </c>
-      <c r="R221" s="2" t="inlineStr">
+      <c r="R221" s="3" t="inlineStr">
         <is>
           <t>https://nz.linkedin.com/company/kpmg-new-zealand</t>
         </is>
@@ -20974,7 +20974,7 @@
           <t>The job description does not mention any ESG/sustainability topics, climate risk, sustainable finance, carbon markets, EU Taxonomy, or other related keywords. The company's vision to lead in energy innovations that advance modern living and a net-zero future is mentioned, but it is not directly related to the job responsibilities or requirements.</t>
         </is>
       </c>
-      <c r="R222" s="2" t="inlineStr">
+      <c r="R222" s="3" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/munich-re</t>
         </is>
@@ -21067,7 +21067,7 @@
           <t>This role is within the energy and chemical industry, specifically focused on the marketing and distribution of products in India's retail sector.</t>
         </is>
       </c>
-      <c r="R223" s="2" t="inlineStr">
+      <c r="R223" s="3" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/munich-re</t>
         </is>
@@ -21156,7 +21156,7 @@
           <t>[clean_energy_adjacent] The job description mentions renewable energy development, solar, wind, and hybrid systems, which are directly related to clean energy. The company's focus on transitioning toward clean and intelligent energy systems also supports this classification.</t>
         </is>
       </c>
-      <c r="R224" s="2" t="inlineStr">
+      <c r="R224" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/aon</t>
         </is>
@@ -21249,7 +21249,7 @@
           <t>[climate_risk] The job title mentions 'Disaster Risk and Climate Resilience', indicating a focus on climate-related risks, and the company name 'All India Disaster Mitigation Institute' also suggests a connection to disaster risk and climate resilience.</t>
         </is>
       </c>
-      <c r="R225" s="2" t="inlineStr">
+      <c r="R225" s="3" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/company/totalenergies</t>
         </is>
@@ -21338,7 +21338,7 @@
           <t>The job description mentions ESG strategy, ESG consulting, sustainability strategies, and ESG frameworks, which are all relevant to the general ESG profile. The role also involves working with ESG data, tracking carbon performance, and evaluating regulatory requirements, which further supports this classification.</t>
         </is>
       </c>
-      <c r="R226" s="2" t="inlineStr">
+      <c r="R226" s="3" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/company/xcelgreen</t>
         </is>
@@ -21431,7 +21431,7 @@
           <t>The job description mentions decarbonisation, net zero, low carbon generation, energy efficiency, and energy transition, which are all relevant to the clean energy adjacent profile. Additionally, the job requires experience working on water sector energy projects and knowledge of the broader water industry in terms of growth and challenges to decarbonisation.</t>
         </is>
       </c>
-      <c r="R227" s="2" t="inlineStr">
+      <c r="R227" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/jacobs</t>
         </is>
@@ -21520,7 +21520,7 @@
           <t>Job title contains 'Renewables', indicating a connection to renewable energy</t>
         </is>
       </c>
-      <c r="R228" s="2" t="inlineStr">
+      <c r="R228" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/downer</t>
         </is>
@@ -21617,7 +21617,7 @@
           <t>The job description mentions 'renewables and emerging energy sectors' and 'decarbonisation, hydrogen, carbon capture and storage, renewables advisory', which are related to clean energy and environmental sustainability.</t>
         </is>
       </c>
-      <c r="R229" s="2" t="inlineStr">
+      <c r="R229" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/woodplc</t>
         </is>
@@ -21714,7 +21714,7 @@
           <t>The job description mentions renewable energy, battery energy storage systems (BESS), and energy trading, which are all related to clean energy. The company also mentions climate goals and renewable energy integration, indicating a focus on environmental sustainability.</t>
         </is>
       </c>
-      <c r="R230" s="2" t="inlineStr">
+      <c r="R230" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/energy-one</t>
         </is>
@@ -21811,7 +21811,7 @@
           <t xml:space="preserve">[clean_energy_adjacent] The job title 'Finance Lead - Water, Environment &amp; Energy Transition' and the company's focus on sustainable solutions and infrastructure indicate a connection to environmental topics, specifically water, environment, and energy transition, which aligns with the clean energy </t>
         </is>
       </c>
-      <c r="R231" s="2" t="inlineStr">
+      <c r="R231" s="3" t="inlineStr">
         <is>
           <t>https://lu.linkedin.com/company/morgan-philips-group</t>
         </is>
@@ -21908,7 +21908,7 @@
           <t>The job description does not explicitly mention ESG, sustainability, or environmental topics, and the focus is on data strategy, architecture, and governance in a financial services context.</t>
         </is>
       </c>
-      <c r="R232" s="2" t="inlineStr">
+      <c r="R232" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/lendable-impact</t>
         </is>
@@ -21997,7 +21997,7 @@
           <t>Job title contains 'Climate', indicating a strong focus on climate-related work</t>
         </is>
       </c>
-      <c r="R233" s="2" t="inlineStr">
+      <c r="R233" s="3" t="inlineStr">
         <is>
           <t>https://nz.linkedin.com/company/pwc-new-zealand</t>
         </is>
@@ -22097,7 +22097,7 @@
           <t>The job description mentions environmental commodities, renewable energy markets, carbon offsets, and reducing carbon footprints, which are all related to clean energy and environmental sustainability.</t>
         </is>
       </c>
-      <c r="R234" s="2" t="inlineStr">
+      <c r="R234" s="3" t="inlineStr">
         <is>
           <t>https://nl.linkedin.com/company/amsterdamrenewablemarkets</t>
         </is>
@@ -22190,7 +22190,7 @@
           <t>The job description mentions carbon footprint certification, product carbon footprints, life cycle assessment, and sustainability certification, which are all related to carbon markets and emissions trading.</t>
         </is>
       </c>
-      <c r="R235" s="2" t="inlineStr">
+      <c r="R235" s="3" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/meo-consulting-team</t>
         </is>
@@ -22287,7 +22287,7 @@
           <t>The job description mentions ESG research, sustainability disclosures, performance, and qualitative factors, which are key aspects of sustainable finance. Additionally, the mention of SFDR (Sustainable Finance Disclosure Regulation) further supports this classification.</t>
         </is>
       </c>
-      <c r="R236" s="2" t="inlineStr">
+      <c r="R236" s="3" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/company/xcelgreen</t>
         </is>
@@ -22380,7 +22380,7 @@
           <t>Job title contains 'Circular Bioeconomy', indicating a focus on environmental science and circular economy, which aligns with the clean energy adjacent profile.</t>
         </is>
       </c>
-      <c r="R237" s="2" t="inlineStr">
+      <c r="R237" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/climate-policy-initiative</t>
         </is>
@@ -22469,7 +22469,7 @@
           <t>Job title contains 'Wind', indicating a focus on renewable energy</t>
         </is>
       </c>
-      <c r="R238" s="2" t="inlineStr">
+      <c r="R238" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/carbomaxde</t>
         </is>
@@ -22483,242 +22483,461 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S98" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S99" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S100" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S101" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S102" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S103" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S104" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S105" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S106" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S107" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S108" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S109" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S110" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S111" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S112" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S113" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S114" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S115" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S116" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S117" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S118" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S119" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S120" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S121" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S122" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S123" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S124" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S125" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S126" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S127" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S128" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S129" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S130" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S131" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S132" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S133" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S134" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S135" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S136" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S137" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S138" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S139" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S140" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S141" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S142" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S143" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S144" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S145" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S146" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S147" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S148" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S149" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S150" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S151" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S152" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S153" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S154" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S155" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S156" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S157" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S158" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S159" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S160" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S161" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S162" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S163" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S164" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S165" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S166" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S167" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S168" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S169" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S170" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S171" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S172" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S173" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S174" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S175" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S176" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S177" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S178" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S179" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S180" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S181" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S182" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S183" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S184" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S185" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S186" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S187" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S188" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S189" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S190" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S191" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S192" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S193" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S194" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S195" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S196" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S197" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S198" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S199" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S200" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S201" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S202" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S203" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S204" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S205" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S206" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S207" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S208" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S209" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S210" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S211" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S212" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S213" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S214" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S215" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S216" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S217" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S218" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S219" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S220" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S221" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S222" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S223" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S224" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S225" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S226" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S227" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S228" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S229" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S230" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S231" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S232" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S233" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S234" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S235" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S236" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S237" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R21" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S23" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R24" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S24" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R25" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S25" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S26" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S28" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R29" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S29" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S30" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S31" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S32" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R33" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S33" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R34" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S34" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R35" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S35" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S36" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R37" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S37" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R38" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S38" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R39" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S39" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R40" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S40" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R41" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S41" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R42" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S42" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R43" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S43" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R44" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S44" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R45" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S45" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R46" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S46" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R47" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S47" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R48" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S48" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R49" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S49" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R50" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S50" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S51" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S52" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R53" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S53" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R54" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S54" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R55" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S55" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R56" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S56" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R57" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S57" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R58" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S58" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R59" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S59" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R60" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S60" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R61" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S61" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R62" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S62" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R63" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S63" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R64" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S64" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R65" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S65" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R66" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S66" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R67" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S67" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R68" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S68" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R69" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S69" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R70" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S70" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R71" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S71" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R72" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S72" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R73" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S73" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R74" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S74" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R75" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S75" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R76" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S76" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R77" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S77" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R78" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S78" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R79" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S79" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R80" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S80" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R81" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S81" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R82" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S82" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R83" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S83" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R84" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S84" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R85" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S85" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R86" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S86" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R87" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S87" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R88" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S88" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R89" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S89" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R90" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S90" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R91" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S91" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R92" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S92" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R93" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S93" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R94" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S94" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R95" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S95" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R96" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S96" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R97" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S97" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R98" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S98" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R99" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S99" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R100" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S100" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R101" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S101" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R102" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S102" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R103" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S103" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R104" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S104" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R105" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S105" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R106" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S106" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R107" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S107" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R108" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S108" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R109" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S109" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R110" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S110" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R111" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S111" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R112" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S112" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R113" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S113" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R114" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S114" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R115" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S115" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R116" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S116" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S117" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R118" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S118" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R119" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S119" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R120" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S120" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S121" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R122" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S122" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R123" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S123" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R124" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S124" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R125" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S125" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R126" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S126" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R127" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S127" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R128" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S128" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R129" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S129" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R130" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S130" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R131" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S131" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R132" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S132" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R133" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S133" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R134" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S134" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R135" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S135" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S136" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R137" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S137" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R138" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S138" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R139" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S139" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R140" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S140" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R141" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S141" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R142" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S142" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R143" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S143" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R144" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S144" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R145" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S145" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R146" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S146" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R147" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S147" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R148" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S148" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R149" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S149" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R150" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S150" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S151" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R152" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S152" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R153" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S153" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R154" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S154" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R155" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S155" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R156" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S156" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R157" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S157" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R158" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S158" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R159" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S159" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R160" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S160" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S161" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R162" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S162" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R163" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S163" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R164" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S164" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S165" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S166" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S167" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S168" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R169" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S169" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R170" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S170" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R171" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S171" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R172" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S172" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R173" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S173" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R174" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S174" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R175" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S175" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R176" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S176" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R177" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S177" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R178" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S178" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R179" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S179" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S180" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S181" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S182" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R183" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S183" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R184" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S184" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R185" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S185" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R186" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S186" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R187" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S187" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R188" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S188" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R189" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S189" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R190" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S190" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R191" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S191" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R192" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S192" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R193" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S193" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R194" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S194" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R195" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S195" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R196" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S196" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R197" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S197" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R198" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S198" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R199" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S199" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R200" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S200" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R201" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S201" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R202" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S202" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R203" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S203" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R204" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S204" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R205" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S205" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R206" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S206" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R207" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S207" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R208" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S208" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R209" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S209" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R210" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S210" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R211" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S211" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R212" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S212" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R213" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S213" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R214" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S214" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R215" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S215" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R216" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S216" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R217" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S217" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R218" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S218" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R219" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S219" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R220" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S220" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R221" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S221" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R222" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S222" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R223" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S223" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R224" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S224" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R225" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S225" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R226" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S226" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R227" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S227" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R228" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S228" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R229" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S229" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R230" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S230" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R231" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S231" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R232" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S232" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R233" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S233" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R234" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S234" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R235" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S235" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R236" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S236" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R237" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S237" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R238" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S238" r:id="rId456"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23246,7 +23465,7 @@
           <t>This role connects to climate change, ESG, sustainability, and finance by advising companies on managing their environmental impact and achieving sustainable business practices.</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -23349,7 +23568,7 @@
           <t>This role focuses on the impact of climate change and sustainability on businesses within the Australian market.</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -23452,7 +23671,7 @@
           <t>This role is focused on supporting businesses in understanding and managing their environmental impact and navigating sustainability challenges within the Australian market.</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -23555,7 +23774,7 @@
           <t>This role focuses on helping organizations understand and manage the risks and opportunities associated with climate change and sustainability within the Australian business sector.</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -23658,7 +23877,7 @@
           <t>This role focuses on helping companies navigate the complexities of climate change and sustainability for improved business performance.</t>
         </is>
       </c>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="R8" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -23761,7 +23980,7 @@
           <t>This role focuses on the environmental, social, and governance (ESG) aspects of business operations within the consulting industry.</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="R9" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -23864,7 +24083,7 @@
           <t>This role focuses on helping companies navigate the complexities of climate change and sustainability issues within the business sector.</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="R10" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -23967,7 +24186,7 @@
           <t>The role focuses on environmental, social, and governance (ESG) issues within the business consulting industry.</t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="R11" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -24070,7 +24289,7 @@
           <t>This role focuses on helping companies navigate the complexities of climate change and sustainability issues within a global context.</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="R12" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -24173,7 +24392,7 @@
           <t>This role focuses on helping companies navigate the complex landscape of climate change and sustainability issues, contributing to a more sustainable future.</t>
         </is>
       </c>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="R13" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -24371,7 +24590,7 @@
           <t>This role connects to climate, ESG, sustainability, and finance by supporting companies with their sustainability reporting needs.</t>
         </is>
       </c>
-      <c r="R15" s="2" t="inlineStr">
+      <c r="R15" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/bdo-in-australia</t>
         </is>
@@ -24470,7 +24689,7 @@
           <t>The role involves ESG disclosure program, sustainability reporting, climate risk, and emissions reporting, which are all key aspects of ESG strategy and corporate sustainability.</t>
         </is>
       </c>
-      <c r="R16" s="2" t="inlineStr">
+      <c r="R16" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/csenergyqld</t>
         </is>
@@ -24569,7 +24788,7 @@
           <t>The role involves leading client engagements and managing senior team members in the Sustainability Reporting Advisory practice, with a focus on interpreting and applying sustainability reporting requirements, and providing technical leadership and market profile.</t>
         </is>
       </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="R17" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/grant-thornton-australia</t>
         </is>
@@ -24676,7 +24895,7 @@
           <t>This role plays a crucial part in the Indian banking industry, contributing to the stability and growth of the sector.</t>
         </is>
       </c>
-      <c r="R18" s="2" t="inlineStr">
+      <c r="R18" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/pwc-india</t>
         </is>
@@ -24783,7 +25002,7 @@
           <t>[general_esg] The job description mentions ESG ratings, sustainability strategy, risk management, and EU Taxonomy, which are all related to environmental, social, and governance topics, indicating a strong fit with the general ESG profile.</t>
         </is>
       </c>
-      <c r="R19" s="2" t="inlineStr">
+      <c r="R19" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/pwc-india</t>
         </is>
@@ -24890,7 +25109,7 @@
           <t>This role contributes to the sustainable development of businesses within the GCC and wider MENA region by supporting them with ESG initiatives.</t>
         </is>
       </c>
-      <c r="R20" s="2" t="inlineStr">
+      <c r="R20" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/pwc-india</t>
         </is>
@@ -24997,7 +25216,7 @@
           <t>ESG consulting within the financial services industry, focusing on climate change, sustainable finance, and corporate social responsibility.</t>
         </is>
       </c>
-      <c r="R21" s="2" t="inlineStr">
+      <c r="R21" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/pwc-india</t>
         </is>
@@ -25104,7 +25323,7 @@
           <t>The role connects to climate, ESG, sustainability, and finance by providing expert advice on sustainability data and regulations for clients.</t>
         </is>
       </c>
-      <c r="R22" s="2" t="inlineStr">
+      <c r="R22" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/pwc-india</t>
         </is>
@@ -25207,7 +25426,7 @@
           <t>The job description mentions sustainability strategy, sustainable business models, and sustainability-related financial disclosure, which are all relevant to ESG. The role also involves advising on climate- and nature-related financial analysis and embedding sustainability into business operations.</t>
         </is>
       </c>
-      <c r="R23" s="2" t="inlineStr">
+      <c r="R23" s="3" t="inlineStr">
         <is>
           <t>https://nz.linkedin.com/company/kpmg-new-zealand</t>
         </is>
@@ -25310,7 +25529,7 @@
           <t>[general_esg] The job description mentions ESG data analysis, ESG reporting, sustainability strategy, and risk management, which are all key aspects of general ESG consulting. The job also mentions EU Taxonomy, CSRD, and SFDR, which are specific ESG frameworks and regulations.</t>
         </is>
       </c>
-      <c r="R24" s="2" t="inlineStr">
+      <c r="R24" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/iss-sustainabilitysolutions</t>
         </is>
@@ -25417,7 +25636,7 @@
           <t>Focuses on integrating environmental, social, economic, and governance considerations into business strategies and operations within the consulting industry.</t>
         </is>
       </c>
-      <c r="R25" s="2" t="inlineStr">
+      <c r="R25" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/pwc-india</t>
         </is>
@@ -25524,7 +25743,7 @@
           <t>The role focuses on supporting India's transition to a net-zero economy through sustainable financing solutions for climate projects.</t>
         </is>
       </c>
-      <c r="R26" s="2" t="inlineStr">
+      <c r="R26" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -25631,7 +25850,7 @@
           <t>This role connects to climate, ESG, sustainability, and finance by providing data, analytics, and advisory services to support investors in understanding and managing their exposure to climate-related risks and opportunities.</t>
         </is>
       </c>
-      <c r="R27" s="2" t="inlineStr">
+      <c r="R27" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/iss-sustainabilitysolutions</t>
         </is>
@@ -25738,7 +25957,7 @@
           <t>This role contributes to the financial services industry by supporting clients in understanding and managing their risks related to credit, market, and derivative instruments.</t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr">
+      <c r="R28" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -25841,7 +26060,7 @@
           <t>This role is within the environmental, social, and governance (ESG) consulting sector, helping businesses navigate ESG challenges and opportunities.</t>
         </is>
       </c>
-      <c r="R29" s="2" t="inlineStr">
+      <c r="R29" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -25948,7 +26167,7 @@
           <t>The role focuses on the metals &amp; mining industry, supporting clients in their transition to a more sustainable and efficient operation through digital transformation.</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
+      <c r="R30" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/wsp-consultants-india-ltd</t>
         </is>
@@ -26051,7 +26270,7 @@
           <t>This role contributes to climate risk modeling, assessment, and decarbonization efforts within the infrastructure and transportation sectors.</t>
         </is>
       </c>
-      <c r="R31" s="2" t="inlineStr">
+      <c r="R31" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/wsp-consultants-india-ltd</t>
         </is>
@@ -26158,7 +26377,7 @@
           <t>This role focuses on environmental sustainability within the transportation &amp; infrastructure sector, contributing to climate change mitigation and ESG initiatives.</t>
         </is>
       </c>
-      <c r="R32" s="2" t="inlineStr">
+      <c r="R32" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/wsp-consultants-india-ltd</t>
         </is>
@@ -26265,7 +26484,7 @@
           <t>This role focuses on climate change mitigation and sustainability within the infrastructure and transportation sector.</t>
         </is>
       </c>
-      <c r="R33" s="2" t="inlineStr">
+      <c r="R33" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/wsp-consultants-india-ltd</t>
         </is>
@@ -26368,7 +26587,7 @@
           <t>This role contributes to the development of sustainable infrastructure and cities within the transportation, energy, and environmental sectors.</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr">
+      <c r="R34" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/wsp-consultants-india-ltd</t>
         </is>
@@ -26475,7 +26694,7 @@
           <t>WSP's work focuses on sustainable infrastructure development and environmental impact assessment across various industries.</t>
         </is>
       </c>
-      <c r="R35" s="2" t="inlineStr">
+      <c r="R35" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/wsp-consultants-india-ltd</t>
         </is>
@@ -26582,7 +26801,7 @@
           <t>WSP's role focuses on engineering projects that contribute to sustainable development and climate action in the transportation, infrastructure, and environment sectors.</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr">
+      <c r="R36" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/wsp-consultants-india-ltd</t>
         </is>
@@ -26681,7 +26900,7 @@
           <t>The job description explicitly mentions climate change, decarbonization, emissions assessments, and climate risk assessment, which are all key aspects of the climate risk profile.</t>
         </is>
       </c>
-      <c r="R37" s="2" t="inlineStr">
+      <c r="R37" s="3" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/company/wsp-in-canada</t>
         </is>
@@ -26788,7 +27007,7 @@
           <t>This role contributes to the growing field of corporate sustainability assurance within the global ESG market.</t>
         </is>
       </c>
-      <c r="R38" s="2" t="inlineStr">
+      <c r="R38" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -26982,7 +27201,7 @@
           <t>The job description mentions energy solutions, renewable energy, decarbonisation of heat, energy management, and net zero carbon programme delivery, which are all related to clean energy and sustainability.</t>
         </is>
       </c>
-      <c r="R40" s="2" t="inlineStr">
+      <c r="R40" s="3" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/company/equans</t>
         </is>
@@ -27089,7 +27308,7 @@
           <t>The role is within the finance industry, focusing on managing risks related to credit, operational, market, and liquidity.</t>
         </is>
       </c>
-      <c r="R41" s="2" t="inlineStr">
+      <c r="R41" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/the-nature-conservancy</t>
         </is>
@@ -27196,7 +27415,7 @@
           <t>The role focuses on financial services risk management within the Middle East and North Africa (MENA) region, contributing to climate-conscious financial practices.</t>
         </is>
       </c>
-      <c r="R42" s="2" t="inlineStr">
+      <c r="R42" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -27303,7 +27522,7 @@
           <t>This role connects to climate, ESG, sustainability, and finance within the European capital markets.</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr">
+      <c r="R43" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/the-nature-conservancy</t>
         </is>
@@ -27410,7 +27629,7 @@
           <t>The role focuses on credit risk management within the financial services sector, addressing climate risk and sustainability concerns in a global context.</t>
         </is>
       </c>
-      <c r="R44" s="2" t="inlineStr">
+      <c r="R44" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/the-nature-conservancy</t>
         </is>
@@ -27513,7 +27732,7 @@
           <t>The job description explicitly mentions climate risk, decarbonisation, and retrofit, which are key aspects of climate risk management. The role requires the candidate to have experience in real estate sustainability, decarbonisation, and ESG advisory, which are all relevant to climate risk.</t>
         </is>
       </c>
-      <c r="R45" s="2" t="inlineStr">
+      <c r="R45" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/mapmortar</t>
         </is>
@@ -27612,7 +27831,7 @@
           <t>The job involves conducting in-depth ESG research, performing climate risk and transition assessments, and producing high-quality research notes and reports integrating ESG insights.</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr">
+      <c r="R46" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/crisil</t>
         </is>
@@ -27711,7 +27930,7 @@
           <t>The job involves conducting in-depth ESG research, performing climate risk and transition assessments, and producing ESG research notes and reports, which are all core responsibilities of an ESG analyst.</t>
         </is>
       </c>
-      <c r="R47" s="2" t="inlineStr">
+      <c r="R47" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/crisil</t>
         </is>
@@ -27810,7 +28029,7 @@
           <t>The job involves conducting in-depth ESG research, performing climate risk and transition assessments, and producing high-quality research notes and reports integrating ESG insights.</t>
         </is>
       </c>
-      <c r="R48" s="2" t="inlineStr">
+      <c r="R48" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/crisil</t>
         </is>
@@ -27917,7 +28136,7 @@
           <t>This role connects to climate, ESG, sustainability, and finance within the European capital markets sector.</t>
         </is>
       </c>
-      <c r="R49" s="2" t="inlineStr">
+      <c r="R49" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/natwest-group</t>
         </is>
@@ -28115,7 +28334,7 @@
           <t>This role focuses on climate finance within the environmental sector, specifically supporting nature-based solutions to address climate change.</t>
         </is>
       </c>
-      <c r="R51" s="2" t="inlineStr">
+      <c r="R51" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/the-nature-conservancy</t>
         </is>
@@ -28214,7 +28433,7 @@
           <t>The job description mentions carbon credits, carbon markets, and environmental policy, indicating a strong focus on carbon markets. The role involves selling carbon credit offerings and staying on top of developments in carbon markets, standards, and regulation.</t>
         </is>
       </c>
-      <c r="R52" s="2" t="inlineStr">
+      <c r="R52" s="3" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/klim-eco</t>
         </is>
@@ -28317,7 +28536,7 @@
           <t>The Sales Manager will play a key role in driving sales for Neural Alpha's AI-first platform within the financial technology sector.</t>
         </is>
       </c>
-      <c r="R53" s="2" t="inlineStr">
+      <c r="R53" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/neural-alpha</t>
         </is>
@@ -28424,7 +28643,7 @@
           <t>This role focuses on the ESG and sustainability aspects of global commodities markets, contributing to decarbonization efforts within the industry.</t>
         </is>
       </c>
-      <c r="R54" s="2" t="inlineStr">
+      <c r="R54" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/american-express</t>
         </is>
@@ -28531,7 +28750,7 @@
           <t>The role is focused on the rapidly growing carbon removal market, connecting to climate change mitigation efforts and sustainable finance.</t>
         </is>
       </c>
-      <c r="R55" s="2" t="inlineStr">
+      <c r="R55" s="3" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/carbonfuture</t>
         </is>
@@ -28634,7 +28853,7 @@
           <t>The job description explicitly mentions climate risk, physical risk, and climate modelling, which are key aspects of the climate risk profile.</t>
         </is>
       </c>
-      <c r="R56" s="2" t="inlineStr">
+      <c r="R56" s="3" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/munich-re</t>
         </is>
@@ -28741,7 +28960,7 @@
           <t>This role contributes to the energy and utilities sector by helping companies meet their climate commitments and regulatory obligations.</t>
         </is>
       </c>
-      <c r="R57" s="2" t="inlineStr">
+      <c r="R57" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/tetra-tech</t>
         </is>
@@ -28836,7 +29055,7 @@
           <t>The job involves implementing sustainability reporting frameworks (CSRD-style), integrating ESG data into risk and reporting processes and aligning sustainability with data architecture, which indicates that the role directly involves ESG work as a significant part.</t>
         </is>
       </c>
-      <c r="R58" s="2" t="inlineStr">
+      <c r="R58" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/deloitte</t>
         </is>
@@ -28943,7 +29162,7 @@
           <t>This role focuses on financial risk management within the banking and finance sector, with a focus on climate-related risks and sustainability.</t>
         </is>
       </c>
-      <c r="R59" s="2" t="inlineStr">
+      <c r="R59" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/slr-consulting</t>
         </is>
@@ -29046,7 +29265,7 @@
           <t>This role contributes to the World Bank's efforts to promote sustainable development by addressing climate-related challenges in infrastructure and disaster risk management.</t>
         </is>
       </c>
-      <c r="R60" s="2" t="inlineStr">
+      <c r="R60" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/tetra-tech</t>
         </is>
@@ -29153,7 +29372,7 @@
           <t>The role focuses on Enterprise Risk Management within American Express, contributing to climate risk assessments and sustainable business practices.</t>
         </is>
       </c>
-      <c r="R61" s="2" t="inlineStr">
+      <c r="R61" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/slr-consulting</t>
         </is>
@@ -29260,7 +29479,7 @@
           <t>This role contributes to the development and implementation of sustainable business practices within the Australian workforce.</t>
         </is>
       </c>
-      <c r="R62" s="2" t="inlineStr">
+      <c r="R62" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/strategen-environmental-consultants</t>
         </is>
@@ -29367,7 +29586,7 @@
           <t>This role focuses on Enterprise Risk Management within the financial services industry, contributing to climate risk assessment and mitigation strategies for American Express.</t>
         </is>
       </c>
-      <c r="R63" s="2" t="inlineStr">
+      <c r="R63" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/american-express</t>
         </is>
@@ -29474,7 +29693,7 @@
           <t>The role focuses on climate risk assessment within the environmental sector, supporting organizations in adapting to climate change and achieving sustainability goals.</t>
         </is>
       </c>
-      <c r="R64" s="2" t="inlineStr">
+      <c r="R64" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/slr-consulting</t>
         </is>
@@ -29581,7 +29800,7 @@
           <t>The role focuses on providing technical and strategic advice to mining companies on environmental and social performance within the mining industry.</t>
         </is>
       </c>
-      <c r="R65" s="2" t="inlineStr">
+      <c r="R65" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/slr-consulting</t>
         </is>
@@ -29684,7 +29903,7 @@
           <t>The role focuses on the mining industry, providing technical expertise and consulting services to support the development and operation of mineral properties.</t>
         </is>
       </c>
-      <c r="R66" s="2" t="inlineStr">
+      <c r="R66" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/slr-consulting</t>
         </is>
@@ -29791,7 +30010,7 @@
           <t>The role focuses on the mining industry, providing expert advice on environmental and social impact assessments, resource evaluation, and project development.</t>
         </is>
       </c>
-      <c r="R67" s="2" t="inlineStr">
+      <c r="R67" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/slr-consulting</t>
         </is>
@@ -29898,7 +30117,7 @@
           <t>The role focuses on the mining industry, providing advisory services to support technical and commercial aspects of mineral property development.</t>
         </is>
       </c>
-      <c r="R68" s="2" t="inlineStr">
+      <c r="R68" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/slr-consulting</t>
         </is>
@@ -30005,7 +30224,7 @@
           <t>The role focuses on the mining industry, providing advice on environmental and social impact assessment, due diligence, and operational improvement for mining companies.</t>
         </is>
       </c>
-      <c r="R69" s="2" t="inlineStr">
+      <c r="R69" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/slr-consulting</t>
         </is>
@@ -30112,7 +30331,7 @@
           <t>The role focuses on the global mining industry, providing advisory services to companies involved in mineral property development.</t>
         </is>
       </c>
-      <c r="R70" s="2" t="inlineStr">
+      <c r="R70" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/bendigo-advertiser</t>
         </is>
@@ -30219,7 +30438,7 @@
           <t>Sustainable Finance Consultant will work within the growing field of sustainable finance to support organizations and investors in their efforts to integrate ESG factors into financial decision-making.</t>
         </is>
       </c>
-      <c r="R71" s="2" t="inlineStr">
+      <c r="R71" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/iss-sustainabilitysolutions</t>
         </is>
@@ -30326,7 +30545,7 @@
           <t>This role focuses on financial services risk management within the banking book portfolios of clients in the MENA region, contributing to climate-related initiatives and ESG compliance.</t>
         </is>
       </c>
-      <c r="R72" s="2" t="inlineStr">
+      <c r="R72" s="3" t="inlineStr">
         <is>
           <t>https://ch.linkedin.com/company/novartis</t>
         </is>
@@ -30429,7 +30648,7 @@
           <t>The role is focused on climate change mitigation, biodiversity conservation, and sustainable development within the Central African region.</t>
         </is>
       </c>
-      <c r="R73" s="2" t="inlineStr">
+      <c r="R73" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/undpcareers</t>
         </is>
@@ -30532,7 +30751,7 @@
           <t>The job description mentions climate risk assessments, climate resilience analysis, and environmental analysis, which are all key aspects of climate risk management.</t>
         </is>
       </c>
-      <c r="R74" s="2" t="inlineStr">
+      <c r="R74" s="3" t="inlineStr">
         <is>
           <t>https://gr.linkedin.com/company/pwc-greece</t>
         </is>
@@ -30639,7 +30858,7 @@
           <t>This role focuses on environmental and social impact assessments for infrastructure, energy, transport, industrial, and environmental projects within the global finance sector.</t>
         </is>
       </c>
-      <c r="R75" s="2" t="inlineStr">
+      <c r="R75" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/renew</t>
         </is>
@@ -30746,7 +30965,7 @@
           <t>The position is within the audit service line at EY GDS Assurance, contributing to climate change, ESG, sustainability, and finance practices.</t>
         </is>
       </c>
-      <c r="R76" s="2" t="inlineStr">
+      <c r="R76" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/ernstandyoung</t>
         </is>
@@ -30845,7 +31064,7 @@
           <t>The job description explicitly mentions renewable energy, solar, wind, storage, and hybrid renewable energy projects, which are all related to clean energy.</t>
         </is>
       </c>
-      <c r="R77" s="2" t="inlineStr">
+      <c r="R77" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/enfinity</t>
         </is>
@@ -30952,7 +31171,7 @@
           <t>The role contributes to the development and operation of renewable energy projects, focusing on the efficient and sustainable use of resources to reduce carbon emissions.</t>
         </is>
       </c>
-      <c r="R78" s="2" t="inlineStr">
+      <c r="R78" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/hsbc</t>
         </is>
@@ -31059,7 +31278,7 @@
           <t>This role is within the finance division of a global financial institution focused on environmental, social, and governance (ESG) reporting compliance.</t>
         </is>
       </c>
-      <c r="R79" s="2" t="inlineStr">
+      <c r="R79" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/citi</t>
         </is>
@@ -31166,7 +31385,7 @@
           <t>This role focuses on the commodities trading industry within the global financial services sector, contributing to climate change mitigation and sustainable finance initiatives.</t>
         </is>
       </c>
-      <c r="R80" s="2" t="inlineStr">
+      <c r="R80" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/macquariegroup</t>
         </is>
@@ -31273,7 +31492,7 @@
           <t>This role focuses on government transformation with a focus on sustainability, climate change, environment &amp; digital solutions.</t>
         </is>
       </c>
-      <c r="R81" s="2" t="inlineStr">
+      <c r="R81" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/morgan-stanley</t>
         </is>
@@ -31380,7 +31599,7 @@
           <t>This role connects to climate, ESG, sustainability, and finance by managing the financing of sustainable projects and investments for a carbon neutral future.</t>
         </is>
       </c>
-      <c r="R82" s="2" t="inlineStr">
+      <c r="R82" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/wsp-consultants-india-ltd</t>
         </is>
@@ -31475,7 +31694,7 @@
           <t>The job description mentions decarbonisation, energy transition, and climate-related topics, indicating a strong focus on climate risk.</t>
         </is>
       </c>
-      <c r="R83" s="2" t="inlineStr">
+      <c r="R83" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/showcase/ieefa-asia-pacific/</t>
         </is>
@@ -31574,7 +31793,7 @@
           <t>The job description explicitly mentions carbon markets, Article 6, and carbon crediting, which are all key concepts in the carbon markets profile.</t>
         </is>
       </c>
-      <c r="R84" s="2" t="inlineStr">
+      <c r="R84" s="3" t="inlineStr">
         <is>
           <t>https://kr.linkedin.com/company/global-green-growth-institute</t>
         </is>
@@ -31681,7 +31900,7 @@
           <t>The role contributes to the financial services industry by assessing creditworthiness and managing risk exposure within a global financial institution.</t>
         </is>
       </c>
-      <c r="R85" s="2" t="inlineStr">
+      <c r="R85" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/morgan-stanley</t>
         </is>
@@ -31788,7 +32007,7 @@
           <t>The role focuses on the financial industry and its potential to drive positive change through sustainable practices.</t>
         </is>
       </c>
-      <c r="R86" s="2" t="inlineStr">
+      <c r="R86" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/hometree-uk</t>
         </is>
@@ -31891,7 +32110,7 @@
           <t>The role focuses on promoting sustainable home energy solutions within the UK's residential market, contributing to climate change mitigation and decarbonization efforts.</t>
         </is>
       </c>
-      <c r="R87" s="2" t="inlineStr">
+      <c r="R87" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/hometree-uk</t>
         </is>
@@ -31994,7 +32213,7 @@
           <t>The job description mentions working on the energy transition, becoming climate neutral, and improving forecasting accuracy and transparency across commodity value streams, which are all related to renewable energy and environmental science</t>
         </is>
       </c>
-      <c r="R88" s="2" t="inlineStr">
+      <c r="R88" s="3" t="inlineStr">
         <is>
           <t>https://nl.linkedin.com/company/eneco</t>
         </is>
@@ -32101,7 +32320,7 @@
           <t>The financial sector, specifically regulatory compliance for banking and financial institutions, with a focus on ESG reporting and sustainability initiatives.</t>
         </is>
       </c>
-      <c r="R89" s="2" t="inlineStr">
+      <c r="R89" s="3" t="inlineStr">
         <is>
           <t>https://ch.linkedin.com/company/novartis</t>
         </is>
@@ -32200,7 +32419,7 @@
           <t>The job description mentions climate-related risk, and the role involves designing and implementing practical risk frameworks, resilience strategies, and climate risk solutions that are aligned to business strategy.</t>
         </is>
       </c>
-      <c r="R90" s="2" t="inlineStr">
+      <c r="R90" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/aon</t>
         </is>
@@ -32307,7 +32526,7 @@
           <t>This role connects to climate, ESG, sustainability, and finance within the pharmaceutical industry.</t>
         </is>
       </c>
-      <c r="R91" s="2" t="inlineStr">
+      <c r="R91" s="3" t="inlineStr">
         <is>
           <t>https://ch.linkedin.com/company/novartis</t>
         </is>
@@ -32414,7 +32633,7 @@
           <t>The role connects to climate, ESG, sustainability, and finance within the Nordic corporate sector.</t>
         </is>
       </c>
-      <c r="R92" s="2" t="inlineStr">
+      <c r="R92" s="3" t="inlineStr">
         <is>
           <t>https://dk.linkedin.com/company/danskebank</t>
         </is>
@@ -32517,7 +32736,7 @@
           <t>The Business Development Manager will support a company focused on developing biochar solutions for agriculture, renewable energy, and carbon removal, contributing to climate change mitigation efforts.</t>
         </is>
       </c>
-      <c r="R93" s="2" t="inlineStr">
+      <c r="R93" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/black-bull-biochar-ltd</t>
         </is>
@@ -32624,7 +32843,7 @@
           <t>This role focuses on promoting sustainable practices within businesses across various industries, leveraging AI-powered solutions to drive environmental, social, and governance goals.</t>
         </is>
       </c>
-      <c r="R94" s="2" t="inlineStr">
+      <c r="R94" s="3" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/company/xcelgreen</t>
         </is>
@@ -32731,7 +32950,7 @@
           <t>AIPL focuses on sustainable development in Northeast India through innovative financing mechanisms, technology solutions, and community involvement.</t>
         </is>
       </c>
-      <c r="R95" s="2" t="inlineStr">
+      <c r="R95" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/asthalaxmi</t>
         </is>
@@ -32834,7 +33053,7 @@
           <t>ReNew is a leader in the Indian renewable energy sector, focusing on clean energy solutions to address climate change and promote sustainable development.</t>
         </is>
       </c>
-      <c r="R96" s="2" t="inlineStr">
+      <c r="R96" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/renew</t>
         </is>
@@ -32941,7 +33160,7 @@
           <t>This role connects to climate change and sustainability by assessing the environmental impact of projects related to greenhouse gas emissions reduction.</t>
         </is>
       </c>
-      <c r="R97" s="2" t="inlineStr">
+      <c r="R97" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/pollination-climate-advisory-investment</t>
         </is>
@@ -33044,7 +33263,7 @@
           <t>This role connects to climate change investment and advisory by supporting the development of renewable energy, nature, and climate opportunities.</t>
         </is>
       </c>
-      <c r="R98" s="2" t="inlineStr">
+      <c r="R98" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/pollination-climate-advisory-investment</t>
         </is>
@@ -33151,7 +33370,7 @@
           <t>The role focuses on data management within the telecommunications industry, supporting digital transformation initiatives and enabling AI-powered solutions.</t>
         </is>
       </c>
-      <c r="R99" s="2" t="inlineStr">
+      <c r="R99" s="3" t="inlineStr">
         <is>
           <t>https://ee.linkedin.com/company/luminor-group</t>
         </is>
@@ -33258,7 +33477,7 @@
           <t>This role is within the telecommunications industry, focusing on ensuring customer and identity data quality for digital transformation initiatives.</t>
         </is>
       </c>
-      <c r="R100" s="2" t="inlineStr">
+      <c r="R100" s="3" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/company/bnpparibascorporateandinstitutionalbanking</t>
         </is>
@@ -33365,7 +33584,7 @@
           <t>This role contributes to the development and operation of renewable energy projects, specifically focusing on solar power generation, aligning with climate action and sustainable energy solutions.</t>
         </is>
       </c>
-      <c r="R101" s="2" t="inlineStr">
+      <c r="R101" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/renew</t>
         </is>
@@ -33472,7 +33691,7 @@
           <t>ReNew is a leading renewable energy company focused on decarbonization solutions for the Indian power sector, contributing to climate action.</t>
         </is>
       </c>
-      <c r="R102" s="2" t="inlineStr">
+      <c r="R102" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/renew</t>
         </is>
@@ -33575,7 +33794,7 @@
           <t>This role focuses on the energy infrastructure sector in India, specifically related to smart metering and sustainable energy solutions.</t>
         </is>
       </c>
-      <c r="R103" s="2" t="inlineStr">
+      <c r="R103" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/adani-electricity</t>
         </is>
@@ -33682,7 +33901,7 @@
           <t>The role focuses on disaster risk management within the context of climate change and its impact on vulnerable communities in low and middle-income countries.</t>
         </is>
       </c>
-      <c r="R104" s="2" t="inlineStr">
+      <c r="R104" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/hsbc</t>
         </is>
@@ -33785,7 +34004,7 @@
           <t>This role contributes to ReNew's mission of decarbonizing India through the operation and maintenance of solar power plants, aligning with climate action and renewable energy goals.</t>
         </is>
       </c>
-      <c r="R105" s="2" t="inlineStr">
+      <c r="R105" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/renew</t>
         </is>
@@ -33884,7 +34103,7 @@
           <t>The role involves ESG compliance initiatives, sustainability reporting, climate risk, and emissions reduction initiatives, which are all core aspects of ESG strategy and corporate sustainability.</t>
         </is>
       </c>
-      <c r="R106" s="2" t="inlineStr">
+      <c r="R106" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/moir-group</t>
         </is>
@@ -33991,7 +34210,7 @@
           <t>This role contributes to ReNew's mission of decarbonizing India's power sector through efficient and sustainable wind energy solutions.</t>
         </is>
       </c>
-      <c r="R107" s="2" t="inlineStr">
+      <c r="R107" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/hsbc</t>
         </is>
@@ -34094,7 +34313,7 @@
           <t>This role contributes to IISD's work on climate change mitigation, sustainable resource management, and economic policy for a stable future.</t>
         </is>
       </c>
-      <c r="R108" s="2" t="inlineStr">
+      <c r="R108" s="3" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/company/international-institute-for-sustainable-development</t>
         </is>
@@ -34197,7 +34416,7 @@
           <t>This role contributes to UNICEF's commitment to environmental responsibility and climate action within the global development sector.</t>
         </is>
       </c>
-      <c r="R109" s="2" t="inlineStr">
+      <c r="R109" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/bdo-in-australia</t>
         </is>
@@ -34300,7 +34519,7 @@
           <t>This role is focused on the growing field of sustainability finance and ESG analytics, where organizations are seeking tools to translate environmental, social, and governance data into actionable insights for strategic decision-making.</t>
         </is>
       </c>
-      <c r="R110" s="2" t="inlineStr">
+      <c r="R110" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/grayedgeconsultingllc</t>
         </is>
@@ -34403,7 +34622,7 @@
           <t>This role connects to climate, ESG, sustainability, and finance by supporting the development and management of renewable energy projects that contribute to a carbon-free and sustainable economy.</t>
         </is>
       </c>
-      <c r="R111" s="2" t="inlineStr">
+      <c r="R111" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/jacobs</t>
         </is>
@@ -34506,7 +34725,7 @@
           <t>This role is within the energy and chemical industry, specifically focused on the marketing and distribution of products in India's retail sector.</t>
         </is>
       </c>
-      <c r="R112" s="2" t="inlineStr">
+      <c r="R112" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/enfinity</t>
         </is>
@@ -34613,7 +34832,7 @@
           <t>The role is within the energy industry, specifically focused on the marketing and distribution of chemicals and lubricants products in India, contributing to ExxonMobil's efforts towards a sustainable future.</t>
         </is>
       </c>
-      <c r="R113" s="2" t="inlineStr">
+      <c r="R113" s="3" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/company/onetoone-corporate-finance</t>
         </is>
@@ -34716,7 +34935,7 @@
           <t>The role focuses on developing and managing renewable energy projects in the Indian market, contributing to the transition to a carbon-free economy.</t>
         </is>
       </c>
-      <c r="R114" s="2" t="inlineStr">
+      <c r="R114" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/enfinity</t>
         </is>
@@ -34823,7 +35042,7 @@
           <t>The role focuses on the application of technology to improve environmental, health, and safety compliance within industries.</t>
         </is>
       </c>
-      <c r="R115" s="2" t="inlineStr">
+      <c r="R115" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/aurecon</t>
         </is>
@@ -34926,7 +35145,7 @@
           <t>This role is within the sustainability consulting field, focusing on climate change mitigation and ESG frameworks.</t>
         </is>
       </c>
-      <c r="R116" s="2" t="inlineStr">
+      <c r="R116" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/aurecon</t>
         </is>
@@ -35033,7 +35252,7 @@
           <t>This role connects to climate change, ESG, sustainability, and finance by working on projects related to energy transition, decarbonization, and physical risk strategy.</t>
         </is>
       </c>
-      <c r="R117" s="2" t="inlineStr">
+      <c r="R117" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/aurecon</t>
         </is>
@@ -35140,7 +35359,7 @@
           <t>This role connects to climate change, ESG, sustainability, and finance by working with clients on decarbonization strategies and risk management solutions.</t>
         </is>
       </c>
-      <c r="R118" s="2" t="inlineStr">
+      <c r="R118" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/aurecon</t>
         </is>
@@ -35243,7 +35462,7 @@
           <t>This role focuses on sustainability, climate change, and risk management in the engineering, advisory, and design sectors.</t>
         </is>
       </c>
-      <c r="R119" s="2" t="inlineStr">
+      <c r="R119" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/aurecon</t>
         </is>
@@ -35350,7 +35569,7 @@
           <t>Financial Markets Advisory supports clients in navigating the complexities of financial markets, with a focus on sustainability and ESG considerations.</t>
         </is>
       </c>
-      <c r="R120" s="2" t="inlineStr">
+      <c r="R120" s="3" t="inlineStr">
         <is>
           <t>https://ee.linkedin.com/company/luminor-group</t>
         </is>
@@ -35453,7 +35672,7 @@
           <t>This role contributes to the development of climate resilient communities in the Indo-Pacific region by supporting initiatives that address water, food, and energy sectors.</t>
         </is>
       </c>
-      <c r="R121" s="2" t="inlineStr">
+      <c r="R121" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/dt-global</t>
         </is>
@@ -35560,7 +35779,7 @@
           <t>This role focuses on the asset management and pension fund industry, contributing to sustainable finance practices within the financial sector.</t>
         </is>
       </c>
-      <c r="R122" s="2" t="inlineStr">
+      <c r="R122" s="3" t="inlineStr">
         <is>
           <t>https://ee.linkedin.com/company/luminor-group</t>
         </is>
@@ -35663,7 +35882,7 @@
           <t>Renewable energy sector; experience in the renewable energy sector, especially solar, wind, and energy storage, will be advantageous.</t>
         </is>
       </c>
-      <c r="R123" s="2" t="inlineStr">
+      <c r="R123" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/company/altm-new-and-renewable-energy-pvt-ltd</t>
         </is>
@@ -35762,7 +35981,7 @@
           <t>This role focuses on sustainability certification in the environmental sector, specifically related to carbon footprinting and renewable energy.</t>
         </is>
       </c>
-      <c r="R124" s="2" t="inlineStr">
+      <c r="R124" s="3" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/meo-consulting-team</t>
         </is>
@@ -35865,7 +36084,7 @@
           <t>Asset Management &amp; Pensions industry, focusing on responsible investment practices and sustainable finance within the financial sector.</t>
         </is>
       </c>
-      <c r="R125" s="2" t="inlineStr">
+      <c r="R125" s="3" t="inlineStr">
         <is>
           <t>https://ee.linkedin.com/company/luminor-group</t>
         </is>
@@ -35968,7 +36187,7 @@
           <t>[clean_energy_adjacent] The job description mentions decarbonisation, net zero, low carbon generation, energy efficiency, and energy transition, which are all relevant to the clean energy adjacent profile. Additionally, the job requires experience working on water sector energy projects and knowledge of the broader water industry in terms of growth and challenges to decarbonisation.</t>
         </is>
       </c>
-      <c r="R126" s="2" t="inlineStr">
+      <c r="R126" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/jacobs</t>
         </is>
@@ -36071,7 +36290,7 @@
           <t>[clean_energy_adjacent] The job description mentions decarbonisation, net zero, energy transition, low carbon generation, and energy efficiency, which are all relevant to the clean energy adjacent profile. The job also requires experience working on water sector energy projects and knowledge of energy policy and legislation, which further supports this classification.</t>
         </is>
       </c>
-      <c r="R127" s="2" t="inlineStr">
+      <c r="R127" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/jacobs</t>
         </is>
@@ -36174,7 +36393,7 @@
           <t>[clean_energy_adjacent] The job description mentions decarbonisation, net zero, low carbon generation, energy efficiency, and energy transition, which are all related to renewable energy and environmental science. The role also involves working on water sector projects, which is related to water management and conservation.</t>
         </is>
       </c>
-      <c r="R128" s="2" t="inlineStr">
+      <c r="R128" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/jacobs</t>
         </is>
@@ -36277,7 +36496,7 @@
           <t>[clean_energy_adjacent] The job description mentions decarbonisation, net zero, energy transition, low carbon generation, and energy efficiency, which are all related to clean energy and environmental sustainability. The role also involves working with water sector projects, which is adjacent to clean energy and renewable energy.</t>
         </is>
       </c>
-      <c r="R129" s="2" t="inlineStr">
+      <c r="R129" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/jacobs</t>
         </is>
@@ -36384,7 +36603,7 @@
           <t>[clean_energy_adjacent] The job description mentions decarbonisation, net zero, energy transition, and low carbon generation, which are all relevant to the clean energy adjacent profile. Additionally, the job requires experience working on water sector energy projects and knowledge of energy policy and legislation, which further supports this classification.</t>
         </is>
       </c>
-      <c r="R130" s="2" t="inlineStr">
+      <c r="R130" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/jacobs</t>
         </is>
@@ -36487,7 +36706,7 @@
           <t>[clean_energy_adjacent] The job description mentions decarbonisation, net zero, low carbon generation, energy efficiency, and renewable energy, which are all related to clean energy and environmental sustainability. The role also involves working with clients to develop decarbonisation strategies and assessing the environmental impacts of energy projects, which aligns with the clean energy adjacent profile.</t>
         </is>
       </c>
-      <c r="R131" s="2" t="inlineStr">
+      <c r="R131" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/jacobs</t>
         </is>
@@ -36590,7 +36809,7 @@
           <t>[clean_energy_adjacent] The job description mentions decarbonisation, net zero, low carbon generation, energy efficiency, and energy management, which are all relevant to the clean energy and environmental science fields. The role also involves working with water sector projects, which is related to water management and conservation, another aspect of the clean energy adjacent profile.</t>
         </is>
       </c>
-      <c r="R132" s="2" t="inlineStr">
+      <c r="R132" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/jacobs</t>
         </is>
@@ -36693,7 +36912,7 @@
           <t>This role works within the financial industry, specifically focusing on sustainable financing solutions to support a transition towards a greener economy.</t>
         </is>
       </c>
-      <c r="R133" s="2" t="inlineStr">
+      <c r="R133" s="3" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/company/bnpparibascorporateandinstitutionalbanking</t>
         </is>
@@ -36800,7 +37019,7 @@
           <t>Financial services industry, investment operations, data governance and regulatory compliance.</t>
         </is>
       </c>
-      <c r="R134" s="2" t="inlineStr">
+      <c r="R134" s="3" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/company/onetoone-corporate-finance</t>
         </is>
@@ -36903,7 +37122,7 @@
           <t>The job involves working on energy transition and decarbonization projects in the Oil &amp; Gas industry, which is related to the clean energy and environmental science fields.</t>
         </is>
       </c>
-      <c r="R135" s="2" t="inlineStr">
+      <c r="R135" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/boston-consulting-group</t>
         </is>
@@ -37006,7 +37225,7 @@
           <t>This role focuses on supporting resource projects in the mining and minerals processing industry, contributing to decarbonization efforts and net-zero emissions targets.</t>
         </is>
       </c>
-      <c r="R136" s="2" t="inlineStr">
+      <c r="R136" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/clydeco</t>
         </is>
@@ -37109,7 +37328,7 @@
           <t>This role contributes to Hitachi's sustainability efforts by supporting the development of a more sustainable workforce and promoting environmental awareness within the company.</t>
         </is>
       </c>
-      <c r="R137" s="2" t="inlineStr">
+      <c r="R137" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/standard-chartered-india</t>
         </is>
@@ -37390,7 +37609,7 @@
           <t>The job involves working on water resilience, infrastructure planning, and development planning, which are related to environmental science and water management, making it a good fit for the clean_energy_adjacent profile.</t>
         </is>
       </c>
-      <c r="R140" s="2" t="inlineStr">
+      <c r="R140" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/school/iihsin/</t>
         </is>
@@ -37493,7 +37712,7 @@
           <t>The role focuses on sustainable structured solutions within the financial sector, contributing to climate, ESG, sustainability, and finance initiatives.</t>
         </is>
       </c>
-      <c r="R141" s="2" t="inlineStr">
+      <c r="R141" s="3" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/company/societegenerale-corporate-and-investment-banking</t>
         </is>
@@ -37588,7 +37807,7 @@
           <t>The company specializes in activated carbon products and services for water treatment, air purification, and food &amp; beverage processes, which are related to environmental science and sustainability.</t>
         </is>
       </c>
-      <c r="R142" s="2" t="inlineStr">
+      <c r="R142" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/carbomaxde</t>
         </is>
@@ -37680,7 +37899,7 @@
         </is>
       </c>
       <c r="R143" s="2" t="n"/>
-      <c r="S143" s="2" t="inlineStr">
+      <c r="S143" s="3" t="inlineStr">
         <is>
           <t>https://nl.indeed.com/viewjob?jk=71d06a292b5ab786</t>
         </is>
@@ -37778,7 +37997,7 @@
           <t>The role connects to the Danish sustainable innovation ecosystem, focusing on Energy Transition, Digital Health, and Advanced Manufacturing.</t>
         </is>
       </c>
-      <c r="R144" s="2" t="inlineStr">
+      <c r="R144" s="3" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/company/onetoone-corporate-finance</t>
         </is>
@@ -37877,7 +38096,7 @@
           <t>This role contributes to accelerating the transition to a low-carbon economy by supporting climate markets and sustainable project development.</t>
         </is>
       </c>
-      <c r="R145" s="2" t="inlineStr">
+      <c r="R145" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/cyan-ventures</t>
         </is>
@@ -37980,7 +38199,7 @@
           <t>The role focuses on the global energy transition, advising clients on complex projects related to climate change mitigation and sustainability.</t>
         </is>
       </c>
-      <c r="R146" s="2" t="inlineStr">
+      <c r="R146" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/clydeco</t>
         </is>
@@ -38087,7 +38306,7 @@
           <t>This role focuses on the financial risk management of a global banking institution, contributing to capital adequacy assessment and regulatory compliance.</t>
         </is>
       </c>
-      <c r="R147" s="2" t="inlineStr">
+      <c r="R147" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/standard-chartered-india</t>
         </is>
@@ -38186,7 +38405,7 @@
           <t>The job involves working on water resilience, climate-proofing water and sanitation systems, and implementing public infrastructure projects, which are related to renewable energy, environmental science, and conservation.</t>
         </is>
       </c>
-      <c r="R148" s="2" t="inlineStr">
+      <c r="R148" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/school/iihsin/</t>
         </is>
@@ -38285,7 +38504,7 @@
           <t>This role is within Eaton's Power Distribution Systems &amp; Services Division, supporting projects across various industries including renewable energy, mining, industrial, and utility sectors.</t>
         </is>
       </c>
-      <c r="R149" s="2" t="inlineStr">
+      <c r="R149" s="3" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/company/societegenerale-corporate-and-investment-banking</t>
         </is>
@@ -38388,7 +38607,7 @@
           <t>The job description mentions working on probabilistic flood hazard models, climate change analytics, and scenario modeling, which are all directly related to climate risk.</t>
         </is>
       </c>
-      <c r="R150" s="2" t="inlineStr">
+      <c r="R150" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/verisk-analytics</t>
         </is>
@@ -38491,7 +38710,7 @@
           <t>The job involves innovation management, community building, and collaboration with business units to identify and develop new innovation ideas and projects, which are related to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
-      <c r="R151" s="2" t="inlineStr">
+      <c r="R151" s="3" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/munich-re</t>
         </is>
@@ -38590,7 +38809,7 @@
           <t>This role is within the mining and industrial equipment sector, focusing on financial operations for Weir Minerals' EMEA division.</t>
         </is>
       </c>
-      <c r="R152" s="2" t="inlineStr">
+      <c r="R152" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/grant-thornton-australia</t>
         </is>
@@ -38693,7 +38912,7 @@
           <t>The role focuses on Earth Observation data science for sustainability and energy transition within the energy sector.</t>
         </is>
       </c>
-      <c r="R153" s="2" t="inlineStr">
+      <c r="R153" s="3" t="inlineStr">
         <is>
           <t>https://nz.linkedin.com/company/kpmg-new-zealand</t>
         </is>
@@ -38796,7 +39015,7 @@
           <t>The job description mentions energy transition, renewable energy, electricity market design, and other related topics, indicating a strong focus on clean energy and adjacent fields.</t>
         </is>
       </c>
-      <c r="R154" s="2" t="inlineStr">
+      <c r="R154" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/deloitte</t>
         </is>
@@ -38903,7 +39122,7 @@
           <t>This role contributes to the sustainable development of Royal Smit &amp; Zoon's production and asset portfolio by managing CAPEX projects and ensuring compliance with environmental regulations.</t>
         </is>
       </c>
-      <c r="R155" s="2" t="inlineStr">
+      <c r="R155" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/cfpenergy</t>
         </is>
@@ -39006,7 +39225,7 @@
           <t>This position contributes to research on soil and water management within the context of climate change, biodiversity conservation, and sustainable resource management in the Congo Basin.</t>
         </is>
       </c>
-      <c r="R156" s="2" t="inlineStr">
+      <c r="R156" s="3" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/meo-consulting-team</t>
         </is>
@@ -39109,7 +39328,7 @@
           <t>The role focuses on audit services within the financial industry, contributing to the accuracy and transparency of financial statements.</t>
         </is>
       </c>
-      <c r="R157" s="2" t="inlineStr">
+      <c r="R157" s="3" t="inlineStr">
         <is>
           <t>https://nl.linkedin.com/company/afs-energy</t>
         </is>
@@ -39208,7 +39427,7 @@
           <t>The job description mentions research on the impact, effectiveness and coordination of transition policies, climate scenario analysis, and the financial and/or macroeconomic consequences of climate change and the green transition.</t>
         </is>
       </c>
-      <c r="R158" s="2" t="inlineStr">
+      <c r="R158" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/school/london-school-of-economics/</t>
         </is>
@@ -39311,7 +39530,7 @@
           <t>The job description mentions working on climate finance, tracking sustainable investment trends, and supporting the transition to a low-carbon economy, which are all related to climate risk.</t>
         </is>
       </c>
-      <c r="R159" s="2" t="inlineStr">
+      <c r="R159" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/climate-policy-initiative</t>
         </is>
@@ -39414,7 +39633,7 @@
           <t>Works on climate resilience solutions for sustainable infrastructure, agriculture, livelihoods, disaster preparedness, and natural resource management within the Indo-Pacific region.</t>
         </is>
       </c>
-      <c r="R160" s="2" t="inlineStr">
+      <c r="R160" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/tetra-tech</t>
         </is>
@@ -39521,7 +39740,7 @@
           <t>This role focuses on climate resilience and sustainable development across the Indo-Pacific region, connecting to climate action, ESG, sustainability, and finance initiatives.</t>
         </is>
       </c>
-      <c r="R161" s="2" t="inlineStr">
+      <c r="R161" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/tetra-tech</t>
         </is>
@@ -39620,7 +39839,7 @@
           <t>This role focuses on climate change mitigation and adaptation within the European Union's regulatory framework for environmental sustainability.</t>
         </is>
       </c>
-      <c r="R162" s="2" t="inlineStr">
+      <c r="R162" s="3" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/company/societegenerale-corporate-and-investment-banking</t>
         </is>
@@ -39719,7 +39938,7 @@
           <t>The job description mentions ESG oriented investing, impact investing, and sustainable finance, which are key aspects of the sustainable finance profile. The role also involves working with a renewable energy investment firm, which further supports this classification.</t>
         </is>
       </c>
-      <c r="R163" s="2" t="inlineStr">
+      <c r="R163" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/h9-technical-recruitment-ltd</t>
         </is>
@@ -39818,7 +40037,7 @@
           <t>The role is in the Energy &amp; Utilities business unit, which provides services and solutions for water, electricity, and other essential networks and infrastructure. The job description mentions water infrastructure projects and sustainable long-term growth, indicating a connection to the clean energy and environmental sector.</t>
         </is>
       </c>
-      <c r="R164" s="2" t="inlineStr">
+      <c r="R164" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/downer</t>
         </is>
@@ -39917,7 +40136,7 @@
           <t>The job description mentions working on real-world systems balancing risk, resilience, compliance and sustainability, and applying AI and data to global, nature-based challenges that matter, which are directly related to climate risk.</t>
         </is>
       </c>
-      <c r="R165" s="2" t="inlineStr">
+      <c r="R165" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/treefera</t>
         </is>
@@ -40020,7 +40239,7 @@
           <t>The job description mentions ESG (Environmental, Social &amp; Governance) policies and implementing environmental and sustainability measures across office operations, which aligns with the general ESG profile.</t>
         </is>
       </c>
-      <c r="R166" s="2" t="inlineStr">
+      <c r="R166" s="3" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/munich-re</t>
         </is>
@@ -40123,7 +40342,7 @@
           <t>The role contributes to environmental impact management for industries like oil and gas, mining, and public services, focusing on water resources and regulatory compliance.</t>
         </is>
       </c>
-      <c r="R167" s="2" t="inlineStr">
+      <c r="R167" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/jacobs</t>
         </is>
@@ -40226,7 +40445,7 @@
           <t>This role connects to climate action by supporting the development and trading of carbon credits, contributing to the transition to a lower-carbon economy.</t>
         </is>
       </c>
-      <c r="R168" s="2" t="inlineStr">
+      <c r="R168" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/cfpenergy</t>
         </is>
@@ -40329,7 +40548,7 @@
           <t>This role connects to climate, ESG, sustainability, and finance by working with clients in the refrigeration industry to help them transition towards more sustainable practices.</t>
         </is>
       </c>
-      <c r="R169" s="2" t="inlineStr">
+      <c r="R169" s="3" t="inlineStr">
         <is>
           <t>https://nl.linkedin.com/company/afs-energy</t>
         </is>
@@ -40428,7 +40647,7 @@
           <t>The job involves working on a project related to water resilience and climate change, which is closely related to the clean energy and environmental science domain.</t>
         </is>
       </c>
-      <c r="R170" s="2" t="inlineStr">
+      <c r="R170" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/school/iihsin/</t>
         </is>
@@ -40531,7 +40750,7 @@
           <t>This role focuses on Enterprise Risk Management within the corporate and large corporate sectors of industries such as infrastructure, energy, utilities, industrial manufacturing, and pharmaceuticals.</t>
         </is>
       </c>
-      <c r="R171" s="2" t="inlineStr">
+      <c r="R171" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/jacobs</t>
         </is>
@@ -40634,7 +40853,7 @@
           <t>This role focuses on the development and maintenance of ESG data for investment solutions within the financial industry.</t>
         </is>
       </c>
-      <c r="R172" s="2" t="inlineStr">
+      <c r="R172" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/morningstar</t>
         </is>
@@ -40733,7 +40952,7 @@
           <t>The job involves working on water resilience, infrastructure planning, and development planning, which are related to environmental science and water management, making it a good fit for the clean_energy_adjacent profile.</t>
         </is>
       </c>
-      <c r="R173" s="2" t="inlineStr">
+      <c r="R173" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/school/iihsin/</t>
         </is>
@@ -40828,7 +41047,7 @@
           <t>The company specializes in activated carbon products and services for water treatment, air purification, and food &amp; beverage processes, which are related to environmental science and sustainability.</t>
         </is>
       </c>
-      <c r="R174" s="2" t="inlineStr">
+      <c r="R174" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/carbomaxde</t>
         </is>
@@ -40927,7 +41146,7 @@
           <t>This role contributes to accelerating the transition to a low-carbon economy by supporting climate markets and sustainable project development.</t>
         </is>
       </c>
-      <c r="R175" s="2" t="inlineStr">
+      <c r="R175" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/cyan-ventures</t>
         </is>
@@ -41026,7 +41245,7 @@
           <t>The job involves working on water resilience, climate-proofing water and sanitation systems, and implementing public infrastructure projects, which are related to renewable energy, environmental science, and conservation.</t>
         </is>
       </c>
-      <c r="R176" s="2" t="inlineStr">
+      <c r="R176" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/school/iihsin/</t>
         </is>
@@ -41129,7 +41348,7 @@
           <t>The job description mentions working on probabilistic flood hazard models, climate change analytics, and scenario modeling, which are all directly related to climate risk.</t>
         </is>
       </c>
-      <c r="R177" s="2" t="inlineStr">
+      <c r="R177" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/verisk-analytics</t>
         </is>
@@ -41232,7 +41451,7 @@
           <t>The job involves innovation management, community building, and collaboration with business units to identify and develop new innovation ideas and projects, which are related to ESG strategy and corporate sustainability.</t>
         </is>
       </c>
-      <c r="R178" s="2" t="inlineStr">
+      <c r="R178" s="3" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/munich-re</t>
         </is>
@@ -41335,7 +41554,7 @@
           <t>The job description mentions energy transition, renewable energy, electricity market design, and other related topics, indicating a strong focus on clean energy and adjacent fields.</t>
         </is>
       </c>
-      <c r="R179" s="2" t="inlineStr">
+      <c r="R179" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/deloitte</t>
         </is>
@@ -41434,7 +41653,7 @@
           <t>The job description mentions research on the impact, effectiveness and coordination of transition policies, climate scenario analysis, and the financial and/or macroeconomic consequences of climate change and the green transition.</t>
         </is>
       </c>
-      <c r="R180" s="2" t="inlineStr">
+      <c r="R180" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/school/london-school-of-economics/</t>
         </is>
@@ -41537,7 +41756,7 @@
           <t>The job description mentions working on climate finance, tracking sustainable investment trends, and supporting the transition to a low-carbon economy, which are all related to climate risk.</t>
         </is>
       </c>
-      <c r="R181" s="2" t="inlineStr">
+      <c r="R181" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/climate-policy-initiative</t>
         </is>
@@ -41636,7 +41855,7 @@
           <t>The job description mentions ESG oriented investing, impact investing, and sustainable finance, which are key aspects of the sustainable finance profile. The role also involves working with a renewable energy investment firm, which further supports this classification.</t>
         </is>
       </c>
-      <c r="R182" s="2" t="inlineStr">
+      <c r="R182" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/h9-technical-recruitment-ltd</t>
         </is>
@@ -41735,7 +41954,7 @@
           <t>The role is in the Energy &amp; Utilities business unit, which provides services and solutions for water, electricity, and other essential networks and infrastructure. The job description mentions water infrastructure projects and sustainable long-term growth, indicating a connection to the clean energy and environmental sector.</t>
         </is>
       </c>
-      <c r="R183" s="2" t="inlineStr">
+      <c r="R183" s="3" t="inlineStr">
         <is>
           <t>https://au.linkedin.com/company/downer</t>
         </is>
@@ -41834,7 +42053,7 @@
           <t>The job description mentions working on real-world systems balancing risk, resilience, compliance and sustainability, and applying AI and data to global, nature-based challenges that matter, which are directly related to climate risk.</t>
         </is>
       </c>
-      <c r="R184" s="2" t="inlineStr">
+      <c r="R184" s="3" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/treefera</t>
         </is>
@@ -41937,7 +42156,7 @@
           <t>The job description mentions ESG (Environmental, Social &amp; Governance) policies and implementing environmental and sustainability measures across office operations, which aligns with the general ESG profile.</t>
         </is>
       </c>
-      <c r="R185" s="2" t="inlineStr">
+      <c r="R185" s="3" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/munich-re</t>
         </is>
@@ -42036,7 +42255,7 @@
           <t>The job involves working on a project related to water resilience and climate change, which is closely related to the clean energy and environmental science domain.</t>
         </is>
       </c>
-      <c r="R186" s="2" t="inlineStr">
+      <c r="R186" s="3" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/school/iihsin/</t>
         </is>
@@ -42061,188 +42280,366 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S98" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S99" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S100" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S101" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S102" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S103" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S104" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S105" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S106" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S107" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S108" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S109" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S110" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S111" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S112" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S113" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S114" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S115" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S116" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S117" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S118" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S119" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S120" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S121" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S122" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S123" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S124" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S125" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S126" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S127" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S128" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S129" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S130" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S131" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S132" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S133" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S134" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S135" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S136" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S137" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S138" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S139" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S140" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S141" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S142" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S144" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S145" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S146" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S147" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S148" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S149" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S150" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S151" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S152" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S153" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S154" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S155" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S156" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S157" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S158" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S159" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S160" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S161" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S162" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S163" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S164" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S165" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S166" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S167" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S168" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S169" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S170" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S171" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S172" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S173" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S174" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S175" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S176" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S177" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S178" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S179" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S180" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S181" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S182" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S183" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S184" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S185" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S186" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R21" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S23" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R24" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S24" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R25" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S25" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S26" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S28" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R29" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S29" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S30" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S31" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R32" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S32" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R33" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S33" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R34" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S34" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R35" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S35" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R36" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S36" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R37" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S37" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R38" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S38" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S39" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R40" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S40" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R41" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S41" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R42" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S42" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R43" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S43" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R44" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S44" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R45" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S45" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R46" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S46" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R47" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S47" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R48" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S48" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R49" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S49" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S50" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R51" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S51" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R52" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S52" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R53" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S53" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R54" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S54" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R55" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S55" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R56" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S56" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R57" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S57" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R58" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S58" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R59" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S59" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R60" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S60" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R61" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S61" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R62" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S62" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R63" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S63" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R64" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S64" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R65" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S65" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R66" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S66" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R67" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S67" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R68" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S68" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R69" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S69" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R70" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S70" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R71" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S71" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R72" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S72" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R73" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S73" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R74" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S74" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R75" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S75" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R76" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S76" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R77" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S77" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R78" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S78" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R79" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S79" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R80" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S80" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R81" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S81" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R82" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S82" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R83" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S83" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R84" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S84" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R85" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S85" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R86" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S86" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R87" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S87" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R88" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S88" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R89" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S89" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R90" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S90" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R91" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S91" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R92" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S92" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R93" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S93" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R94" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S94" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R95" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S95" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R96" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S96" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R97" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S97" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R98" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S98" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R99" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S99" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R100" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S100" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R101" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S101" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R102" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S102" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R103" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S103" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R104" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S104" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R105" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S105" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R106" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S106" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R107" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S107" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R108" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S108" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R109" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S109" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R110" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S110" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R111" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S111" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R112" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S112" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R113" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S113" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R114" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S114" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R115" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S115" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R116" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S116" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R117" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S117" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R118" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S118" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R119" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S119" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R120" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S120" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R121" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S121" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R122" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S122" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R123" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S123" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R124" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S124" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R125" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S125" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R126" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S126" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R127" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S127" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R128" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S128" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R129" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S129" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R130" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S130" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R131" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S131" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R132" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S132" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R133" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S133" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R134" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S134" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R135" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S135" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R136" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S136" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R137" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S137" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S138" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S139" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R140" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S140" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R141" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S141" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R142" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S142" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S143" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R144" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S144" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R145" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S145" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R146" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S146" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R147" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S147" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R148" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S148" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R149" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S149" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R150" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S150" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R151" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S151" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R152" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S152" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R153" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S153" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R154" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S154" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R155" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S155" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R156" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S156" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R157" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S157" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R158" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S158" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R159" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S159" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R160" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S160" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R161" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S161" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R162" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S162" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R163" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S163" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R164" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S164" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R165" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S165" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R166" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S166" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R167" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S167" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R168" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S168" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R169" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S169" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R170" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S170" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R171" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S171" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R172" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S172" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R173" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S173" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R174" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S174" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R175" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S175" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R176" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S176" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R177" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S177" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R178" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S178" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R179" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S179" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R180" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S180" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R181" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S181" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R182" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S182" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R183" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S183" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R184" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S184" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R185" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S185" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R186" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S186" r:id="rId362"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/jobs/jobs.xlsx
+++ b/src/jobs/jobs.xlsx
@@ -71,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -89,6 +89,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -456,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S238"/>
+  <dimension ref="A1:S239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22477,6 +22480,95 @@
       <c r="S238" s="3" t="inlineStr">
         <is>
           <t>https://es.indeed.com/viewjob?jk=6d861e6f34eb946f</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B239" s="6" t="inlineStr"/>
+      <c r="C239" s="6" t="inlineStr">
+        <is>
+          <t>climate_risk</t>
+        </is>
+      </c>
+      <c r="D239" s="6" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="E239" s="6" t="inlineStr">
+        <is>
+          <t>Climate Change Manager, Impact Group</t>
+        </is>
+      </c>
+      <c r="F239" s="6" t="inlineStr">
+        <is>
+          <t>British International Investment</t>
+        </is>
+      </c>
+      <c r="G239" s="6" t="inlineStr">
+        <is>
+          <t>DFI | Development Finance</t>
+        </is>
+      </c>
+      <c r="H239" s="6" t="inlineStr">
+        <is>
+          <t>Mumbai, Maharashtra, India</t>
+        </is>
+      </c>
+      <c r="I239" s="6" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
+      <c r="J239" s="6" t="inlineStr">
+        <is>
+          <t>mid-senior level</t>
+        </is>
+      </c>
+      <c r="K239" s="6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L239" s="6" t="inlineStr"/>
+      <c r="M239" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N239" s="6" t="inlineStr">
+        <is>
+          <t>Manual add</t>
+        </is>
+      </c>
+      <c r="O239" s="6" t="inlineStr">
+        <is>
+          <t>Support impact and investment teams developing strategies for transactions aligned with BII's framework. Provide climate expertise for early-stage investment opportunity development. Evaluate pipeline investments regarding emissions mitigation and resilience contributions. Serve as in-house climate advisor to portfolio companies and fund managers. Originate and implement climate technical assistance initiatives. Act as regional climate expertise leader. Develop strategic climate projects and thought leadership.</t>
+        </is>
+      </c>
+      <c r="P239" s="6" t="inlineStr">
+        <is>
+          <t>Climate change science and IPCC findings. Quantitative and qualitative climate finance assessment frameworks. TCFD, IFRS 2, Science-Based Targets Initiative, Partnership for Carbon Accounting Financials. Stakeholder relationship management. Capital deployment for development impact. Climate integration into investment decision-making. Adaptation and resilience expertise.</t>
+        </is>
+      </c>
+      <c r="Q239" s="6" t="inlineStr">
+        <is>
+          <t>Senior climate finance role at UK's development finance institution, leading climate initiatives across Asia, focusing on high-impact climate finance transactions and mobilizing private investors.</t>
+        </is>
+      </c>
+      <c r="R239" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/british-international-investment</t>
+        </is>
+      </c>
+      <c r="S239" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4384072005</t>
         </is>
       </c>
     </row>
@@ -22938,6 +23030,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S237" r:id="rId454"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R238" r:id="rId455"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S238" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R239" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S239" r:id="rId458"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23060,7 +23154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U186"/>
+  <dimension ref="A1:U187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -42273,6 +42367,105 @@
       <c r="U186" s="2" t="inlineStr">
         <is>
           <t>Skills:2.7 Frameworks:0.0 Seniority:10 Domain:3.8 Semantic:12.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B187" s="6" t="inlineStr"/>
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>climate_risk</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="E187" s="6" t="inlineStr">
+        <is>
+          <t>Climate Change Manager, Impact Group</t>
+        </is>
+      </c>
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>British International Investment</t>
+        </is>
+      </c>
+      <c r="G187" s="6" t="inlineStr">
+        <is>
+          <t>DFI | Development Finance</t>
+        </is>
+      </c>
+      <c r="H187" s="6" t="inlineStr">
+        <is>
+          <t>Mumbai, Maharashtra, India</t>
+        </is>
+      </c>
+      <c r="I187" s="6" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
+      <c r="J187" s="6" t="inlineStr">
+        <is>
+          <t>mid-senior level</t>
+        </is>
+      </c>
+      <c r="K187" s="6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L187" s="6" t="inlineStr"/>
+      <c r="M187" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N187" s="6" t="inlineStr">
+        <is>
+          <t>Manual add</t>
+        </is>
+      </c>
+      <c r="O187" s="6" t="inlineStr">
+        <is>
+          <t>Support impact and investment teams developing strategies for transactions aligned with BII's framework. Provide climate expertise for early-stage investment opportunity development. Evaluate pipeline investments regarding emissions mitigation and resilience contributions. Serve as in-house climate advisor to portfolio companies and fund managers. Originate and implement climate technical assistance initiatives. Act as regional climate expertise leader. Develop strategic climate projects and thought leadership.</t>
+        </is>
+      </c>
+      <c r="P187" s="6" t="inlineStr">
+        <is>
+          <t>Climate change science and IPCC findings. Quantitative and qualitative climate finance assessment frameworks. TCFD, IFRS 2, Science-Based Targets Initiative, Partnership for Carbon Accounting Financials. Stakeholder relationship management. Capital deployment for development impact. Climate integration into investment decision-making. Adaptation and resilience expertise.</t>
+        </is>
+      </c>
+      <c r="Q187" s="6" t="inlineStr">
+        <is>
+          <t>Senior climate finance role at UK's development finance institution, leading climate initiatives across Asia, focusing on high-impact climate finance transactions and mobilizing private investors.</t>
+        </is>
+      </c>
+      <c r="R187" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/british-international-investment</t>
+        </is>
+      </c>
+      <c r="S187" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4384072005</t>
+        </is>
+      </c>
+      <c r="T187" s="6" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="U187" s="6" t="inlineStr">
+        <is>
+          <t>Skills:5.5 Frameworks:10.0 Seniority:15 Domain:1.9 Semantic:22.9</t>
         </is>
       </c>
     </row>
@@ -42640,6 +42833,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S185" r:id="rId360"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R186" r:id="rId361"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S186" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R187" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S187" r:id="rId364"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
